--- a/str-deal-search/STR_DSCR_Analysis.xlsx
+++ b/str-deal-search/STR_DSCR_Analysis.xlsx
@@ -133,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="705">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="707">
   <si>
     <t xml:space="preserve">STR DSCR Search: Summary of Top Picks</t>
   </si>
@@ -315,10 +315,10 @@
     <t xml:space="preserve">Many STR DSCR lenders count ~80% of gross or T12 net of mgmt. Use DSCR (haircut) column to qualify.</t>
   </si>
   <si>
-    <t xml:space="preserve">Base insurance ($/yr): HO + wind + $1M STR liability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mainland CBS home ~$500k. Get quotes; barrier islands higher.</t>
+    <t xml:space="preserve">Default base insurance ($/yr): HO + wind + $1M STR liability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mainland CBS home ~$500k. Per-county overrides in the county table below (e.g., Monroe/Keys).</t>
   </si>
   <si>
     <t xml:space="preserve">FLOOD INSURANCE BY FEMA ZONE ($/yr)</t>
@@ -351,142 +351,148 @@
     <t xml:space="preserve">Placeholder until FEMA zone verified.</t>
   </si>
   <si>
-    <t xml:space="preserve">PROPERTY TAX BY COUNTY (% of price, non-homestead)</t>
+    <t xml:space="preserve">BY COUNTY: PROPERTY TAX (% of price, non-homestead) + BASE INSURANCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tax rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base ins. $/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manatee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unincorporated ~13.3 mills (2025) + city + non-ad valorem; reset to purchase price.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sarasota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.47 mills countywide (2025); City of Sarasota ~14.9 mills.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beach towns ~15.8-16.6 mills (2025) + non-ad valorem; ~1.4-1.7% of price est.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Placeholder: Cape Coral/Fort Myers ~16-19 mills; North Cape utility assessments extra (~$3.4k/yr).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charlotte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Placeholder.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Placeholder: lowest millage on the coast; ~1.4-1.5% incl. non-ad valorem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPERATING PROFILE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mgmt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cleaning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maint/Supplies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CapEx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-mgmt total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nightly/weekly. Full-service PM 18-30% locally; Airbnb host-only fee 15.5% (blended 10%); cleaning ~10% of gross (offset if guest-paid fees are inside the seller's gross).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seasonal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30-day+ furnished (snowbird Jan-Apr, travel nurses, insurance displacement). Fewer turns.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIXED OPERATING COSTS ($/yr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utilities (power, water, internet, streaming)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner-paid in furnished rentals.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pool + lawn + pest (with pool)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lawn + pest (no pool)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manatee + Sarasota County: STR / Seasonal Candidates with Documented Income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active as of 2026-10-18. Screened ~600 listings across Zillow (14 keyword sweeps), Redfin, brokerages and STR marketplaces. Yellow rows = recommended.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edit blue cells (Offer Price, Seller Credit %, Down Pmt %, Income, Flood Zone) to rerun. Qualify on DSCR (lender haircut) &gt;= 1.00; &gt;= 1.15 preferred. Income is seller-stated until verified with platform payout reports.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">County</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bd/Ba/SqFt/Yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">List Price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seller Credit %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Down Pmt %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stated Gross Income ($/yr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Income Basis (seller-stated)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flood Zone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOA ($/mo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loan Amount</t>
   </si>
   <si>
     <t xml:space="preserve">Rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manatee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unincorporated ~13.3 mills (2025) + city + non-ad valorem; reset to purchase price.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sarasota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.47 mills countywide (2025); City of Sarasota ~14.9 mills.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beach towns ~15.8-16.6 mills (2025) + non-ad valorem; ~1.4-1.7% of price est.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Placeholder: Cape Coral/Fort Myers ~16-19 mills; North Cape utility assessments extra (~$3.4k/yr).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charlotte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Placeholder.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Placeholder: lowest millage on the coast; ~1.4-1.5% incl. non-ad valorem.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OPERATING PROFILE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mgmt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cleaning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maint/Supplies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CapEx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-mgmt total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nightly/weekly. Full-service PM 18-30% locally; Airbnb host-only fee 15.5% (blended 10%); cleaning ~10% of gross (offset if guest-paid fees are inside the seller's gross).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seasonal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30-day+ furnished (snowbird Jan-Apr, travel nurses, insurance displacement). Fewer turns.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIXED OPERATING COSTS ($/yr)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utilities (power, water, internet, streaming)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner-paid in furnished rentals.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pool + lawn + pest (with pool)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lawn + pest (no pool)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manatee + Sarasota County: STR / Seasonal Candidates with Documented Income</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active as of 2026-10-18. Screened ~600 listings across Zillow (14 keyword sweeps), Redfin, brokerages and STR marketplaces. Yellow rows = recommended.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edit blue cells (Offer Price, Seller Credit %, Down Pmt %, Income, Flood Zone) to rerun. Qualify on DSCR (lender haircut) &gt;= 1.00; &gt;= 1.15 preferred. Income is seller-stated until verified with platform payout reports.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bd/Ba/SqFt/Yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">List Price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seller Credit %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Down Pmt %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stated Gross Income ($/yr)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Income Basis (seller-stated)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flood Zone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pool</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOA ($/mo)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loan Amount</t>
   </si>
   <si>
     <t xml:space="preserve">P&amp;I ($/mo)</t>
@@ -2518,6 +2524,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2539,10 +2549,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="170" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3414,232 +3420,232 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="47" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="47" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="47" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B10" s="47" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="47" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B12" s="47" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="47" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B14" s="47" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="47" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B16" s="47" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="47" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="B18" s="47" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="47" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B20" s="47" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C20" s="32" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C21" s="32" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="47" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="B22" s="47" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C22" s="32" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C23" s="32" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -3852,7 +3858,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="4" t="s">
         <v>60</v>
       </c>
@@ -3925,30 +3931,41 @@
       <c r="C27" s="12" t="s">
         <v>73</v>
       </c>
+      <c r="D27" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="I27" s="12" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C28" s="20" t="n">
         <v>0.015</v>
       </c>
+      <c r="D28" s="21" t="n">
+        <f aca="false">$C$19</f>
+        <v>7000</v>
+      </c>
       <c r="I28" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C29" s="20" t="n">
         <v>0.0135</v>
       </c>
+      <c r="D29" s="21" t="n">
+        <f aca="false">$C$19</f>
+        <v>7000</v>
+      </c>
       <c r="I29" s="14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3958,64 +3975,80 @@
       <c r="C30" s="20" t="n">
         <v>0.016</v>
       </c>
+      <c r="D30" s="21" t="n">
+        <f aca="false">$C$19</f>
+        <v>7000</v>
+      </c>
       <c r="I30" s="14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C31" s="20" t="n">
         <v>0.017</v>
       </c>
+      <c r="D31" s="21" t="n">
+        <f aca="false">$C$19</f>
+        <v>7000</v>
+      </c>
       <c r="I31" s="14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C32" s="20" t="n">
         <v>0.0165</v>
       </c>
+      <c r="D32" s="21" t="n">
+        <f aca="false">$C$19</f>
+        <v>7000</v>
+      </c>
       <c r="I32" s="14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C33" s="20" t="n">
         <v>0.014</v>
       </c>
+      <c r="D33" s="21" t="n">
+        <f aca="false">$C$19</f>
+        <v>7000</v>
+      </c>
       <c r="I33" s="14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I35" s="12" t="s">
         <v>35</v>
@@ -4023,7 +4056,7 @@
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C36" s="18" t="n">
         <v>0.2</v>
@@ -4040,17 +4073,17 @@
       <c r="G36" s="18" t="n">
         <v>0.05</v>
       </c>
-      <c r="H36" s="21" t="n">
+      <c r="H36" s="22" t="n">
         <f aca="false">SUM(D36:G36)</f>
         <v>0.33</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C37" s="18" t="n">
         <v>0.12</v>
@@ -4067,17 +4100,17 @@
       <c r="G37" s="18" t="n">
         <v>0.05</v>
       </c>
-      <c r="H37" s="21" t="n">
+      <c r="H37" s="22" t="n">
         <f aca="false">SUM(D37:G37)</f>
         <v>0.16</v>
       </c>
       <c r="I37" s="14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C39" s="12" t="s">
         <v>63</v>
@@ -4088,18 +4121,18 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C40" s="19" t="n">
         <v>6000</v>
       </c>
       <c r="I40" s="14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C41" s="19" t="n">
         <v>3000</v>
@@ -4108,7 +4141,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C42" s="19" t="n">
         <v>1200</v>
@@ -4169,22 +4202,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>3</v>
@@ -4193,123 +4226,123 @@
         <v>4</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q5" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="R5" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="S5" s="22" t="s">
+      <c r="Q5" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="T5" s="22" t="s">
+      <c r="R5" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="U5" s="22" t="s">
+      <c r="S5" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="V5" s="22" t="s">
+      <c r="T5" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="U5" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="V5" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="W5" s="22" t="s">
+      <c r="W5" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="X5" s="22" t="s">
+      <c r="X5" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="Y5" s="22" t="s">
+      <c r="Y5" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="Z5" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA5" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="AB5" s="22" t="s">
+      <c r="Z5" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="AC5" s="22" t="s">
+      <c r="AA5" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="AB5" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC5" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="AD5" s="22" t="s">
+      <c r="AD5" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="AE5" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="AF5" s="22" t="s">
-        <v>125</v>
+      <c r="AE5" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="AF5" s="23" t="s">
+        <v>127</v>
       </c>
       <c r="AG5" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AH5" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AI5" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AJ5" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>131</v>
-      </c>
-      <c r="D6" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="E6" s="24" t="s">
+      <c r="B6" s="24" t="s">
         <v>132</v>
       </c>
-      <c r="F6" s="24" t="s">
+      <c r="C6" s="25" t="s">
         <v>133</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>135</v>
       </c>
       <c r="G6" s="19" t="n">
         <v>584900</v>
@@ -4320,29 +4353,29 @@
       <c r="I6" s="18" t="n">
         <v>0.03</v>
       </c>
-      <c r="J6" s="26" t="n">
+      <c r="J6" s="27" t="n">
         <f aca="false">Assumptions!$C$15</f>
         <v>0.25</v>
       </c>
       <c r="K6" s="19" t="n">
         <v>85000</v>
       </c>
-      <c r="L6" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="M6" s="25" t="s">
+      <c r="L6" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="M6" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="N6" s="25" t="s">
-        <v>135</v>
+      <c r="N6" s="26" t="s">
+        <v>137</v>
       </c>
       <c r="O6" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="P6" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q6" s="27" t="n">
+      <c r="P6" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q6" s="21" t="n">
         <f aca="false">H6*(1-J6)</f>
         <v>420000</v>
       </c>
@@ -4350,19 +4383,19 @@
         <f aca="false">IF((1-J6)&gt;0.75,Assumptions!$C$11,IF((1-J6)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S6" s="27" t="n">
+      <c r="S6" s="21" t="n">
         <f aca="false">PMT(R6/12,Assumptions!$C$14,-Q6)</f>
         <v>2865.14037623601</v>
       </c>
-      <c r="T6" s="27" t="n">
+      <c r="T6" s="21" t="n">
         <f aca="false">H6*INDEX(Assumptions!$C$28:$C$33,MATCH(D6,Assumptions!$B$28:$B$33,0))/12</f>
         <v>700</v>
       </c>
-      <c r="U6" s="27" t="n">
-        <f aca="false">(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH(M6,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="U6" s="21" t="n">
+        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D6,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M6,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>750</v>
       </c>
-      <c r="V6" s="27" t="n">
+      <c r="V6" s="21" t="n">
         <f aca="false">S6+T6+U6+O6</f>
         <v>4315.14037623601</v>
       </c>
@@ -4378,65 +4411,65 @@
         <f aca="false">H6*J6+H6*(Assumptions!$C$16-I6)</f>
         <v>145600</v>
       </c>
-      <c r="Z6" s="27" t="n">
+      <c r="Z6" s="21" t="n">
         <f aca="false">V6*Assumptions!$C$17</f>
         <v>25890.842257416</v>
       </c>
-      <c r="AA6" s="27" t="n">
+      <c r="AA6" s="21" t="n">
         <f aca="false">K6*INDEX(Assumptions!$H$36:$H$37,MATCH(P6,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N6="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>37050</v>
       </c>
-      <c r="AB6" s="27" t="n">
+      <c r="AB6" s="21" t="n">
         <f aca="false">K6*INDEX(Assumptions!$C$36:$C$37,MATCH(P6,Assumptions!$B$36:$B$37,0))</f>
         <v>17000</v>
       </c>
-      <c r="AC6" s="27" t="n">
+      <c r="AC6" s="21" t="n">
         <f aca="false">K6-AA6-V6*12</f>
         <v>-3831.68451483207</v>
       </c>
-      <c r="AD6" s="27" t="n">
+      <c r="AD6" s="21" t="n">
         <f aca="false">AC6-AB6</f>
         <v>-20831.6845148321</v>
       </c>
-      <c r="AE6" s="21" t="n">
+      <c r="AE6" s="22" t="n">
         <f aca="false">IFERROR(K6/H6,0)</f>
         <v>0.151785714285714</v>
       </c>
-      <c r="AF6" s="21" t="n">
+      <c r="AF6" s="22" t="n">
         <f aca="false">IFERROR((K6-AA6-AB6)/H6,0)</f>
         <v>0.0552678571428571</v>
       </c>
-      <c r="AG6" s="24" t="s">
-        <v>136</v>
+      <c r="AG6" s="25" t="s">
+        <v>138</v>
       </c>
       <c r="AH6" s="13" t="n">
         <v>21</v>
       </c>
-      <c r="AI6" s="24" t="s">
-        <v>137</v>
+      <c r="AI6" s="25" t="s">
+        <v>139</v>
       </c>
       <c r="AJ6" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="23" t="s">
-        <v>139</v>
+      <c r="B7" s="24" t="s">
+        <v>141</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D7" s="35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F7" s="34" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G7" s="36" t="n">
         <v>475000</v>
@@ -4455,19 +4488,19 @@
         <v>73000</v>
       </c>
       <c r="L7" s="34" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="M7" s="35" t="s">
         <v>70</v>
       </c>
       <c r="N7" s="35" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="O7" s="36" t="n">
         <v>0</v>
       </c>
       <c r="P7" s="35" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q7" s="39" t="n">
         <f aca="false">H7*(1-J7)</f>
@@ -4486,7 +4519,7 @@
         <v>575</v>
       </c>
       <c r="U7" s="39" t="n">
-        <f aca="false">(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH(M7,Assumptions!$B$22:$B$25,0)))/12</f>
+        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D7,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M7,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>750</v>
       </c>
       <c r="V7" s="39" t="n">
@@ -4534,36 +4567,36 @@
         <v>0.0589347826086957</v>
       </c>
       <c r="AG7" s="34" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AH7" s="33" t="n">
         <v>14</v>
       </c>
       <c r="AI7" s="34" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AJ7" s="43" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="E8" s="24" t="s">
-        <v>132</v>
-      </c>
-      <c r="F8" s="24" t="s">
+      <c r="B8" s="24" t="s">
         <v>149</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>151</v>
       </c>
       <c r="G8" s="19" t="n">
         <v>645000</v>
@@ -4574,29 +4607,29 @@
       <c r="I8" s="18" t="n">
         <v>0.03</v>
       </c>
-      <c r="J8" s="26" t="n">
+      <c r="J8" s="27" t="n">
         <f aca="false">Assumptions!$C$15</f>
         <v>0.25</v>
       </c>
       <c r="K8" s="19" t="n">
         <v>89000</v>
       </c>
-      <c r="L8" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="M8" s="25" t="s">
+      <c r="L8" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="M8" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="N8" s="25" t="s">
-        <v>135</v>
+      <c r="N8" s="26" t="s">
+        <v>137</v>
       </c>
       <c r="O8" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="P8" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q8" s="27" t="n">
+      <c r="P8" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q8" s="21" t="n">
         <f aca="false">H8*(1-J8)</f>
         <v>450000</v>
       </c>
@@ -4604,19 +4637,19 @@
         <f aca="false">IF((1-J8)&gt;0.75,Assumptions!$C$11,IF((1-J8)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S8" s="27" t="n">
+      <c r="S8" s="21" t="n">
         <f aca="false">PMT(R8/12,Assumptions!$C$14,-Q8)</f>
         <v>3069.79326025286</v>
       </c>
-      <c r="T8" s="27" t="n">
+      <c r="T8" s="21" t="n">
         <f aca="false">H8*INDEX(Assumptions!$C$28:$C$33,MATCH(D8,Assumptions!$B$28:$B$33,0))/12</f>
         <v>750</v>
       </c>
-      <c r="U8" s="27" t="n">
-        <f aca="false">(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH(M8,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="U8" s="21" t="n">
+        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D8,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M8,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>750</v>
       </c>
-      <c r="V8" s="27" t="n">
+      <c r="V8" s="21" t="n">
         <f aca="false">S8+T8+U8+O8</f>
         <v>4569.79326025286</v>
       </c>
@@ -4632,45 +4665,45 @@
         <f aca="false">H8*J8+H8*(Assumptions!$C$16-I8)</f>
         <v>156000</v>
       </c>
-      <c r="Z8" s="27" t="n">
+      <c r="Z8" s="21" t="n">
         <f aca="false">V8*Assumptions!$C$17</f>
         <v>27418.7595615172</v>
       </c>
-      <c r="AA8" s="27" t="n">
+      <c r="AA8" s="21" t="n">
         <f aca="false">K8*INDEX(Assumptions!$H$36:$H$37,MATCH(P8,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N8="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>38370</v>
       </c>
-      <c r="AB8" s="27" t="n">
+      <c r="AB8" s="21" t="n">
         <f aca="false">K8*INDEX(Assumptions!$C$36:$C$37,MATCH(P8,Assumptions!$B$36:$B$37,0))</f>
         <v>17800</v>
       </c>
-      <c r="AC8" s="27" t="n">
+      <c r="AC8" s="21" t="n">
         <f aca="false">K8-AA8-V8*12</f>
         <v>-4207.51912303436</v>
       </c>
-      <c r="AD8" s="27" t="n">
+      <c r="AD8" s="21" t="n">
         <f aca="false">AC8-AB8</f>
         <v>-22007.5191230344</v>
       </c>
-      <c r="AE8" s="21" t="n">
+      <c r="AE8" s="22" t="n">
         <f aca="false">IFERROR(K8/H8,0)</f>
         <v>0.148333333333333</v>
       </c>
-      <c r="AF8" s="21" t="n">
+      <c r="AF8" s="22" t="n">
         <f aca="false">IFERROR((K8-AA8-AB8)/H8,0)</f>
         <v>0.0547166666666667</v>
       </c>
-      <c r="AG8" s="24" t="s">
-        <v>151</v>
+      <c r="AG8" s="25" t="s">
+        <v>153</v>
       </c>
       <c r="AH8" s="13" t="n">
         <v>23</v>
       </c>
-      <c r="AI8" s="24" t="s">
-        <v>152</v>
+      <c r="AI8" s="25" t="s">
+        <v>154</v>
       </c>
       <c r="AJ8" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4678,19 +4711,19 @@
         <v>4</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G9" s="36" t="n">
         <v>475000</v>
@@ -4709,19 +4742,19 @@
         <v>60000</v>
       </c>
       <c r="L9" s="34" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M9" s="35" t="s">
         <v>64</v>
       </c>
       <c r="N9" s="35" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="O9" s="36" t="n">
         <v>0</v>
       </c>
       <c r="P9" s="35" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q9" s="39" t="n">
         <f aca="false">H9*(1-J9)</f>
@@ -4740,7 +4773,7 @@
         <v>511.875</v>
       </c>
       <c r="U9" s="39" t="n">
-        <f aca="false">(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH(M9,Assumptions!$B$22:$B$25,0)))/12</f>
+        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D9,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M9,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>666.666666666667</v>
       </c>
       <c r="V9" s="39" t="n">
@@ -4788,36 +4821,36 @@
         <v>0.0461538461538462</v>
       </c>
       <c r="AG9" s="34" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AH9" s="33" t="n">
         <v>78</v>
       </c>
       <c r="AI9" s="34" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AJ9" s="43" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="D10" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>132</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>160</v>
+      <c r="B10" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>162</v>
       </c>
       <c r="G10" s="19" t="n">
         <v>474999</v>
@@ -4828,29 +4861,29 @@
       <c r="I10" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="26" t="n">
+      <c r="J10" s="27" t="n">
         <f aca="false">Assumptions!$C$15</f>
         <v>0.25</v>
       </c>
       <c r="K10" s="19" t="n">
         <v>54000</v>
       </c>
-      <c r="L10" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="M10" s="25" t="s">
+      <c r="L10" s="25" t="s">
+        <v>163</v>
+      </c>
+      <c r="M10" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="N10" s="25" t="s">
-        <v>135</v>
+      <c r="N10" s="26" t="s">
+        <v>137</v>
       </c>
       <c r="O10" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="P10" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q10" s="27" t="n">
+      <c r="P10" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q10" s="21" t="n">
         <f aca="false">H10*(1-J10)</f>
         <v>356249.25</v>
       </c>
@@ -4858,19 +4891,19 @@
         <f aca="false">IF((1-J10)&gt;0.75,Assumptions!$C$11,IF((1-J10)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S10" s="27" t="n">
+      <c r="S10" s="21" t="n">
         <f aca="false">PMT(R10/12,Assumptions!$C$14,-Q10)</f>
         <v>2430.24788137808</v>
       </c>
-      <c r="T10" s="27" t="n">
+      <c r="T10" s="21" t="n">
         <f aca="false">H10*INDEX(Assumptions!$C$28:$C$33,MATCH(D10,Assumptions!$B$28:$B$33,0))/12</f>
         <v>593.74875</v>
       </c>
-      <c r="U10" s="27" t="n">
-        <f aca="false">(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH(M10,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="U10" s="21" t="n">
+        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D10,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M10,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>666.666666666667</v>
       </c>
-      <c r="V10" s="27" t="n">
+      <c r="V10" s="21" t="n">
         <f aca="false">S10+T10+U10+O10</f>
         <v>3690.66329804475</v>
       </c>
@@ -4882,49 +4915,49 @@
         <f aca="false">IFERROR(K10*Assumptions!$C$18/12/V10,0)</f>
         <v>0.975434416330316</v>
       </c>
-      <c r="Y10" s="27" t="n">
+      <c r="Y10" s="21" t="n">
         <f aca="false">H10*J10+H10*(Assumptions!$C$16-I10)</f>
         <v>137749.71</v>
       </c>
-      <c r="Z10" s="27" t="n">
+      <c r="Z10" s="21" t="n">
         <f aca="false">V10*Assumptions!$C$17</f>
         <v>22143.9797882685</v>
       </c>
-      <c r="AA10" s="27" t="n">
+      <c r="AA10" s="21" t="n">
         <f aca="false">K10*INDEX(Assumptions!$H$36:$H$37,MATCH(P10,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N10="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>26820</v>
       </c>
-      <c r="AB10" s="27" t="n">
+      <c r="AB10" s="21" t="n">
         <f aca="false">K10*INDEX(Assumptions!$C$36:$C$37,MATCH(P10,Assumptions!$B$36:$B$37,0))</f>
         <v>10800</v>
       </c>
-      <c r="AC10" s="27" t="n">
+      <c r="AC10" s="21" t="n">
         <f aca="false">K10-AA10-V10*12</f>
         <v>-17107.959576537</v>
       </c>
-      <c r="AD10" s="27" t="n">
+      <c r="AD10" s="21" t="n">
         <f aca="false">AC10-AB10</f>
         <v>-27907.959576537</v>
       </c>
-      <c r="AE10" s="21" t="n">
+      <c r="AE10" s="22" t="n">
         <f aca="false">IFERROR(K10/H10,0)</f>
         <v>0.113684449862</v>
       </c>
-      <c r="AF10" s="21" t="n">
+      <c r="AF10" s="22" t="n">
         <f aca="false">IFERROR((K10-AA10-AB10)/H10,0)</f>
         <v>0.0344842831248066</v>
       </c>
-      <c r="AG10" s="24" t="s">
-        <v>162</v>
+      <c r="AG10" s="25" t="s">
+        <v>164</v>
       </c>
       <c r="AH10" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="AI10" s="24" t="s">
-        <v>163</v>
+      <c r="AI10" s="25" t="s">
+        <v>165</v>
       </c>
       <c r="AJ10" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4932,19 +4965,19 @@
         <v>6</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D11" s="35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G11" s="36" t="n">
         <v>529000</v>
@@ -4963,19 +4996,19 @@
         <v>60000</v>
       </c>
       <c r="L11" s="34" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M11" s="35" t="s">
         <v>70</v>
       </c>
       <c r="N11" s="35" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O11" s="36" t="n">
         <v>0</v>
       </c>
       <c r="P11" s="35" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q11" s="39" t="n">
         <f aca="false">H11*(1-J11)</f>
@@ -4994,7 +5027,7 @@
         <v>643.75</v>
       </c>
       <c r="U11" s="39" t="n">
-        <f aca="false">(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH(M11,Assumptions!$B$22:$B$25,0)))/12</f>
+        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D11,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M11,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>750</v>
       </c>
       <c r="V11" s="39" t="n">
@@ -5042,36 +5075,36 @@
         <v>0.0372815533980583</v>
       </c>
       <c r="AG11" s="34" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AH11" s="33" t="n">
         <v>58</v>
       </c>
       <c r="AI11" s="34" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AJ11" s="43" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>154</v>
-      </c>
-      <c r="D12" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E12" s="24" t="s">
-        <v>132</v>
-      </c>
-      <c r="F12" s="24" t="s">
-        <v>170</v>
+      <c r="B12" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>172</v>
       </c>
       <c r="G12" s="19" t="n">
         <v>524900</v>
@@ -5082,29 +5115,29 @@
       <c r="I12" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="26" t="n">
+      <c r="J12" s="27" t="n">
         <f aca="false">Assumptions!$C$15</f>
         <v>0.25</v>
       </c>
       <c r="K12" s="19" t="n">
         <v>50157</v>
       </c>
-      <c r="L12" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="M12" s="25" t="s">
+      <c r="L12" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="M12" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="N12" s="25" t="s">
-        <v>144</v>
+      <c r="N12" s="26" t="s">
+        <v>146</v>
       </c>
       <c r="O12" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="P12" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q12" s="27" t="n">
+      <c r="P12" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q12" s="21" t="n">
         <f aca="false">H12*(1-J12)</f>
         <v>378750</v>
       </c>
@@ -5112,19 +5145,19 @@
         <f aca="false">IF((1-J12)&gt;0.75,Assumptions!$C$11,IF((1-J12)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S12" s="27" t="n">
+      <c r="S12" s="21" t="n">
         <f aca="false">PMT(R12/12,Assumptions!$C$14,-Q12)</f>
         <v>2583.74266071283</v>
       </c>
-      <c r="T12" s="27" t="n">
+      <c r="T12" s="21" t="n">
         <f aca="false">H12*INDEX(Assumptions!$C$28:$C$33,MATCH(D12,Assumptions!$B$28:$B$33,0))/12</f>
         <v>568.125</v>
       </c>
-      <c r="U12" s="27" t="n">
-        <f aca="false">(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH(M12,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="U12" s="21" t="n">
+        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D12,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M12,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>666.666666666667</v>
       </c>
-      <c r="V12" s="27" t="n">
+      <c r="V12" s="21" t="n">
         <f aca="false">S12+T12+U12+O12</f>
         <v>3818.53432737949</v>
       </c>
@@ -5136,49 +5169,49 @@
         <f aca="false">IFERROR(K12*Assumptions!$C$18/12/V12,0)</f>
         <v>0.875676297061003</v>
       </c>
-      <c r="Y12" s="27" t="n">
+      <c r="Y12" s="21" t="n">
         <f aca="false">H12*J12+H12*(Assumptions!$C$16-I12)</f>
         <v>146450</v>
       </c>
-      <c r="Z12" s="27" t="n">
+      <c r="Z12" s="21" t="n">
         <f aca="false">V12*Assumptions!$C$17</f>
         <v>22911.205964277</v>
       </c>
-      <c r="AA12" s="27" t="n">
+      <c r="AA12" s="21" t="n">
         <f aca="false">K12*INDEX(Assumptions!$H$36:$H$37,MATCH(P12,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N12="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>23751.81</v>
       </c>
-      <c r="AB12" s="27" t="n">
+      <c r="AB12" s="21" t="n">
         <f aca="false">K12*INDEX(Assumptions!$C$36:$C$37,MATCH(P12,Assumptions!$B$36:$B$37,0))</f>
         <v>10031.4</v>
       </c>
-      <c r="AC12" s="27" t="n">
+      <c r="AC12" s="21" t="n">
         <f aca="false">K12-AA12-V12*12</f>
         <v>-19417.2219285539</v>
       </c>
-      <c r="AD12" s="27" t="n">
+      <c r="AD12" s="21" t="n">
         <f aca="false">AC12-AB12</f>
         <v>-29448.6219285539</v>
       </c>
-      <c r="AE12" s="21" t="n">
+      <c r="AE12" s="22" t="n">
         <f aca="false">IFERROR(K12/H12,0)</f>
         <v>0.0993207920792079</v>
       </c>
-      <c r="AF12" s="21" t="n">
+      <c r="AF12" s="22" t="n">
         <f aca="false">IFERROR((K12-AA12-AB12)/H12,0)</f>
         <v>0.0324233465346535</v>
       </c>
-      <c r="AG12" s="24" t="s">
-        <v>172</v>
+      <c r="AG12" s="25" t="s">
+        <v>174</v>
       </c>
       <c r="AH12" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="AI12" s="24" t="s">
-        <v>173</v>
+      <c r="AI12" s="25" t="s">
+        <v>175</v>
       </c>
       <c r="AJ12" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5186,19 +5219,19 @@
         <v>8</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D13" s="35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F13" s="34" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G13" s="36" t="n">
         <v>550000</v>
@@ -5217,19 +5250,19 @@
         <v>48000</v>
       </c>
       <c r="L13" s="34" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M13" s="35" t="s">
         <v>70</v>
       </c>
       <c r="N13" s="35" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O13" s="36" t="n">
         <v>8</v>
       </c>
       <c r="P13" s="35" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q13" s="39" t="n">
         <f aca="false">H13*(1-J13)</f>
@@ -5248,7 +5281,7 @@
         <v>662.5</v>
       </c>
       <c r="U13" s="39" t="n">
-        <f aca="false">(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH(M13,Assumptions!$B$22:$B$25,0)))/12</f>
+        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D13,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M13,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>750</v>
       </c>
       <c r="V13" s="39" t="n">
@@ -5296,36 +5329,36 @@
         <v>0.0255849056603774</v>
       </c>
       <c r="AG13" s="34" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AH13" s="33" t="n">
         <v>12</v>
       </c>
       <c r="AI13" s="34" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AJ13" s="43" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="24" t="s">
-        <v>179</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="D14" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="E14" s="24" t="s">
-        <v>132</v>
-      </c>
-      <c r="F14" s="24" t="s">
-        <v>180</v>
+      <c r="B14" s="25" t="s">
+        <v>181</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="F14" s="25" t="s">
+        <v>182</v>
       </c>
       <c r="G14" s="19" t="n">
         <v>385000</v>
@@ -5336,29 +5369,29 @@
       <c r="I14" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="26" t="n">
+      <c r="J14" s="27" t="n">
         <f aca="false">Assumptions!$C$15</f>
         <v>0.25</v>
       </c>
       <c r="K14" s="19" t="n">
         <v>40000</v>
       </c>
-      <c r="L14" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="M14" s="25" t="s">
+      <c r="L14" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="M14" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="N14" s="25" t="s">
-        <v>144</v>
+      <c r="N14" s="26" t="s">
+        <v>146</v>
       </c>
       <c r="O14" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="P14" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q14" s="27" t="n">
+      <c r="P14" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q14" s="21" t="n">
         <f aca="false">H14*(1-J14)</f>
         <v>270000</v>
       </c>
@@ -5366,19 +5399,19 @@
         <f aca="false">IF((1-J14)&gt;0.75,Assumptions!$C$11,IF((1-J14)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S14" s="27" t="n">
+      <c r="S14" s="21" t="n">
         <f aca="false">PMT(R14/12,Assumptions!$C$14,-Q14)</f>
         <v>1841.87595615172</v>
       </c>
-      <c r="T14" s="27" t="n">
+      <c r="T14" s="21" t="n">
         <f aca="false">H14*INDEX(Assumptions!$C$28:$C$33,MATCH(D14,Assumptions!$B$28:$B$33,0))/12</f>
         <v>450</v>
       </c>
-      <c r="U14" s="27" t="n">
-        <f aca="false">(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH(M14,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="U14" s="21" t="n">
+        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D14,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M14,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>666.666666666667</v>
       </c>
-      <c r="V14" s="27" t="n">
+      <c r="V14" s="21" t="n">
         <f aca="false">S14+T14+U14+O14</f>
         <v>2958.54262281838</v>
       </c>
@@ -5390,49 +5423,49 @@
         <f aca="false">IFERROR(K14*Assumptions!$C$18/12/V14,0)</f>
         <v>0.901344684406247</v>
       </c>
-      <c r="Y14" s="27" t="n">
+      <c r="Y14" s="21" t="n">
         <f aca="false">H14*J14+H14*(Assumptions!$C$16-I14)</f>
         <v>104400</v>
       </c>
-      <c r="Z14" s="27" t="n">
+      <c r="Z14" s="21" t="n">
         <f aca="false">V14*Assumptions!$C$17</f>
         <v>17751.2557369103</v>
       </c>
-      <c r="AA14" s="27" t="n">
+      <c r="AA14" s="21" t="n">
         <f aca="false">K14*INDEX(Assumptions!$H$36:$H$37,MATCH(P14,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N14="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>20400</v>
       </c>
-      <c r="AB14" s="27" t="n">
+      <c r="AB14" s="21" t="n">
         <f aca="false">K14*INDEX(Assumptions!$C$36:$C$37,MATCH(P14,Assumptions!$B$36:$B$37,0))</f>
         <v>8000</v>
       </c>
-      <c r="AC14" s="27" t="n">
+      <c r="AC14" s="21" t="n">
         <f aca="false">K14-AA14-V14*12</f>
         <v>-15902.5114738206</v>
       </c>
-      <c r="AD14" s="27" t="n">
+      <c r="AD14" s="21" t="n">
         <f aca="false">AC14-AB14</f>
         <v>-23902.5114738206</v>
       </c>
-      <c r="AE14" s="21" t="n">
+      <c r="AE14" s="22" t="n">
         <f aca="false">IFERROR(K14/H14,0)</f>
         <v>0.111111111111111</v>
       </c>
-      <c r="AF14" s="21" t="n">
+      <c r="AF14" s="22" t="n">
         <f aca="false">IFERROR((K14-AA14-AB14)/H14,0)</f>
         <v>0.0322222222222222</v>
       </c>
-      <c r="AG14" s="24" t="s">
-        <v>182</v>
+      <c r="AG14" s="25" t="s">
+        <v>184</v>
       </c>
       <c r="AH14" s="13" t="n">
         <v>214</v>
       </c>
-      <c r="AI14" s="24" t="s">
-        <v>183</v>
+      <c r="AI14" s="25" t="s">
+        <v>185</v>
       </c>
       <c r="AJ14" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5440,19 +5473,19 @@
         <v>10</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D15" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F15" s="34" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="G15" s="36" t="n">
         <v>655000</v>
@@ -5471,19 +5504,19 @@
         <v>102000</v>
       </c>
       <c r="L15" s="34" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="M15" s="35" t="s">
         <v>70</v>
       </c>
       <c r="N15" s="35" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="O15" s="36" t="n">
         <v>0</v>
       </c>
       <c r="P15" s="35" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q15" s="39" t="n">
         <f aca="false">H15*(1-J15)</f>
@@ -5502,7 +5535,7 @@
         <v>736.875</v>
       </c>
       <c r="U15" s="39" t="n">
-        <f aca="false">(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH(M15,Assumptions!$B$22:$B$25,0)))/12</f>
+        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D15,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M15,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>750</v>
       </c>
       <c r="V15" s="39" t="n">
@@ -5550,36 +5583,36 @@
         <v>0.101129770992366</v>
       </c>
       <c r="AG15" s="34" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AH15" s="33" t="n">
         <v>5</v>
       </c>
       <c r="AI15" s="34" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AJ15" s="43" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>192</v>
-      </c>
-      <c r="D16" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="E16" s="24" t="s">
+      <c r="B16" s="25" t="s">
         <v>193</v>
       </c>
-      <c r="F16" s="24" t="s">
+      <c r="C16" s="25" t="s">
         <v>194</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="F16" s="25" t="s">
+        <v>196</v>
       </c>
       <c r="G16" s="19" t="n">
         <v>279000</v>
@@ -5590,29 +5623,29 @@
       <c r="I16" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="26" t="n">
+      <c r="J16" s="27" t="n">
         <f aca="false">Assumptions!$C$15</f>
         <v>0.25</v>
       </c>
       <c r="K16" s="19" t="n">
         <v>44000</v>
       </c>
-      <c r="L16" s="24" t="s">
-        <v>195</v>
-      </c>
-      <c r="M16" s="25" t="s">
+      <c r="L16" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="M16" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="N16" s="25" t="s">
-        <v>144</v>
+      <c r="N16" s="26" t="s">
+        <v>146</v>
       </c>
       <c r="O16" s="19" t="n">
         <v>477</v>
       </c>
-      <c r="P16" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q16" s="27" t="n">
+      <c r="P16" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q16" s="21" t="n">
         <f aca="false">H16*(1-J16)</f>
         <v>209250</v>
       </c>
@@ -5620,19 +5653,19 @@
         <f aca="false">IF((1-J16)&gt;0.75,Assumptions!$C$11,IF((1-J16)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S16" s="27" t="n">
+      <c r="S16" s="21" t="n">
         <f aca="false">PMT(R16/12,Assumptions!$C$14,-Q16)</f>
         <v>1427.45386601758</v>
       </c>
-      <c r="T16" s="27" t="n">
+      <c r="T16" s="21" t="n">
         <f aca="false">H16*INDEX(Assumptions!$C$28:$C$33,MATCH(D16,Assumptions!$B$28:$B$33,0))/12</f>
         <v>348.75</v>
       </c>
-      <c r="U16" s="27" t="n">
-        <f aca="false">(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH(M16,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="U16" s="21" t="n">
+        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D16,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M16,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>750</v>
       </c>
-      <c r="V16" s="27" t="n">
+      <c r="V16" s="21" t="n">
         <f aca="false">S16+T16+U16+O16</f>
         <v>3003.20386601758</v>
       </c>
@@ -5644,47 +5677,47 @@
         <f aca="false">IFERROR(K16*Assumptions!$C$18/12/V16,0)</f>
         <v>0.976734668773286</v>
       </c>
-      <c r="Y16" s="27" t="n">
+      <c r="Y16" s="21" t="n">
         <f aca="false">H16*J16+H16*(Assumptions!$C$16-I16)</f>
         <v>80910</v>
       </c>
-      <c r="Z16" s="27" t="n">
+      <c r="Z16" s="21" t="n">
         <f aca="false">V16*Assumptions!$C$17</f>
         <v>18019.2231961055</v>
       </c>
-      <c r="AA16" s="27" t="n">
+      <c r="AA16" s="21" t="n">
         <f aca="false">K16*INDEX(Assumptions!$H$36:$H$37,MATCH(P16,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N16="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>21720</v>
       </c>
-      <c r="AB16" s="27" t="n">
+      <c r="AB16" s="21" t="n">
         <f aca="false">K16*INDEX(Assumptions!$C$36:$C$37,MATCH(P16,Assumptions!$B$36:$B$37,0))</f>
         <v>8800</v>
       </c>
-      <c r="AC16" s="27" t="n">
+      <c r="AC16" s="21" t="n">
         <f aca="false">K16-AA16-V16*12</f>
         <v>-13758.446392211</v>
       </c>
-      <c r="AD16" s="27" t="n">
+      <c r="AD16" s="21" t="n">
         <f aca="false">AC16-AB16</f>
         <v>-22558.446392211</v>
       </c>
-      <c r="AE16" s="21" t="n">
+      <c r="AE16" s="22" t="n">
         <f aca="false">IFERROR(K16/H16,0)</f>
         <v>0.157706093189964</v>
       </c>
-      <c r="AF16" s="21" t="n">
+      <c r="AF16" s="22" t="n">
         <f aca="false">IFERROR((K16-AA16-AB16)/H16,0)</f>
         <v>0.0483154121863799</v>
       </c>
-      <c r="AG16" s="24"/>
+      <c r="AG16" s="25"/>
       <c r="AH16" s="13" t="n">
         <v>55</v>
       </c>
-      <c r="AI16" s="24" t="s">
-        <v>196</v>
+      <c r="AI16" s="25" t="s">
+        <v>198</v>
       </c>
       <c r="AJ16" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5692,19 +5725,19 @@
         <v>12</v>
       </c>
       <c r="B17" s="34" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D17" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E17" s="34" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F17" s="34" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G17" s="36" t="n">
         <v>639000</v>
@@ -5723,19 +5756,19 @@
         <v>50000</v>
       </c>
       <c r="L17" s="34" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M17" s="35" t="s">
         <v>66</v>
       </c>
       <c r="N17" s="35" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="O17" s="36" t="n">
         <v>945</v>
       </c>
       <c r="P17" s="35" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q17" s="39" t="n">
         <f aca="false">H17*(1-J17)</f>
@@ -5754,7 +5787,7 @@
         <v>718.875</v>
       </c>
       <c r="U17" s="39" t="n">
-        <f aca="false">(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH(M17,Assumptions!$B$22:$B$25,0)))/12</f>
+        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D17,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M17,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>958.333333333333</v>
       </c>
       <c r="V17" s="39" t="n">
@@ -5806,15 +5839,15 @@
         <v>27</v>
       </c>
       <c r="AI17" s="34" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AJ17" s="43" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5825,156 +5858,156 @@
         <v>4</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AI21" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AJ21" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>131</v>
+      <c r="B22" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>133</v>
       </c>
       <c r="G22" s="19" t="n">
         <v>619000</v>
       </c>
-      <c r="L22" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="AI22" s="24" t="s">
-        <v>210</v>
+      <c r="L22" s="25" t="s">
+        <v>211</v>
+      </c>
+      <c r="AI22" s="25" t="s">
+        <v>212</v>
       </c>
       <c r="AJ22" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="24" t="s">
-        <v>211</v>
-      </c>
-      <c r="C23" s="24" t="s">
-        <v>212</v>
+      <c r="B23" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>214</v>
       </c>
       <c r="G23" s="19" t="n">
         <v>524900</v>
       </c>
-      <c r="L23" s="24" t="s">
-        <v>213</v>
-      </c>
-      <c r="AI23" s="24" t="s">
-        <v>210</v>
+      <c r="L23" s="25" t="s">
+        <v>215</v>
+      </c>
+      <c r="AI23" s="25" t="s">
+        <v>212</v>
       </c>
       <c r="AJ23" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="24" t="s">
-        <v>214</v>
-      </c>
-      <c r="C24" s="24" t="s">
-        <v>148</v>
+      <c r="B24" s="25" t="s">
+        <v>216</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>150</v>
       </c>
       <c r="G24" s="19" t="n">
         <v>499000</v>
       </c>
-      <c r="L24" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AI24" s="24" t="s">
-        <v>210</v>
+      <c r="L24" s="25" t="s">
+        <v>217</v>
+      </c>
+      <c r="AI24" s="25" t="s">
+        <v>212</v>
       </c>
       <c r="AJ24" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="24" t="s">
-        <v>216</v>
-      </c>
-      <c r="C25" s="24" t="s">
-        <v>131</v>
+      <c r="B25" s="25" t="s">
+        <v>218</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>133</v>
       </c>
       <c r="G25" s="19" t="n">
         <v>450000</v>
       </c>
-      <c r="L25" s="24" t="s">
-        <v>217</v>
-      </c>
-      <c r="AI25" s="24" t="s">
-        <v>210</v>
+      <c r="L25" s="25" t="s">
+        <v>219</v>
+      </c>
+      <c r="AI25" s="25" t="s">
+        <v>212</v>
       </c>
       <c r="AJ25" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="C26" s="24" t="s">
-        <v>148</v>
+      <c r="B26" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>150</v>
       </c>
       <c r="G26" s="19" t="n">
         <v>625000</v>
       </c>
-      <c r="L26" s="24" t="s">
-        <v>219</v>
-      </c>
-      <c r="AI26" s="24" t="s">
-        <v>210</v>
+      <c r="L26" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="AI26" s="25" t="s">
+        <v>212</v>
       </c>
       <c r="AJ26" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="24" t="s">
-        <v>220</v>
-      </c>
-      <c r="C27" s="24" t="s">
-        <v>221</v>
+      <c r="B27" s="25" t="s">
+        <v>222</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>223</v>
       </c>
       <c r="G27" s="19" t="n">
         <v>419999</v>
       </c>
-      <c r="L27" s="24" t="s">
-        <v>222</v>
-      </c>
-      <c r="AI27" s="24" t="s">
-        <v>210</v>
+      <c r="L27" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="AI27" s="25" t="s">
+        <v>212</v>
       </c>
       <c r="AJ27" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="C28" s="24" t="s">
-        <v>224</v>
+      <c r="B28" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>226</v>
       </c>
       <c r="G28" s="19" t="n">
         <v>374900</v>
       </c>
-      <c r="L28" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="AI28" s="24" t="s">
-        <v>210</v>
+      <c r="L28" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="AI28" s="25" t="s">
+        <v>212</v>
       </c>
       <c r="AJ28" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -6067,22 +6100,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>3</v>
@@ -6091,123 +6124,123 @@
         <v>4</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q5" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="R5" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="S5" s="22" t="s">
+      <c r="Q5" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="T5" s="22" t="s">
+      <c r="R5" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="U5" s="22" t="s">
+      <c r="S5" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="V5" s="22" t="s">
+      <c r="T5" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="U5" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="V5" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="W5" s="22" t="s">
+      <c r="W5" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="X5" s="22" t="s">
+      <c r="X5" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="Y5" s="22" t="s">
+      <c r="Y5" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="Z5" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA5" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="AB5" s="22" t="s">
+      <c r="Z5" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="AC5" s="22" t="s">
+      <c r="AA5" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="AB5" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC5" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="AD5" s="22" t="s">
+      <c r="AD5" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="AE5" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="AF5" s="22" t="s">
-        <v>125</v>
+      <c r="AE5" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="AF5" s="23" t="s">
+        <v>127</v>
       </c>
       <c r="AG5" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AH5" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AI5" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AJ5" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="s">
-        <v>228</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>229</v>
-      </c>
-      <c r="D6" s="25" t="s">
+      <c r="B6" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>231</v>
+      </c>
+      <c r="D6" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="24" t="s">
-        <v>132</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>230</v>
+      <c r="E6" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>232</v>
       </c>
       <c r="G6" s="19" t="n">
         <v>499000</v>
@@ -6218,29 +6251,29 @@
       <c r="I6" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="26" t="n">
+      <c r="J6" s="27" t="n">
         <f aca="false">Assumptions!$C$15</f>
         <v>0.25</v>
       </c>
       <c r="K6" s="19" t="n">
         <v>71000</v>
       </c>
-      <c r="L6" s="24" t="s">
-        <v>231</v>
-      </c>
-      <c r="M6" s="25" t="s">
+      <c r="L6" s="25" t="s">
+        <v>233</v>
+      </c>
+      <c r="M6" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="N6" s="25" t="s">
-        <v>135</v>
+      <c r="N6" s="26" t="s">
+        <v>137</v>
       </c>
       <c r="O6" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="P6" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q6" s="27" t="n">
+      <c r="P6" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q6" s="21" t="n">
         <f aca="false">H6*(1-J6)</f>
         <v>363750</v>
       </c>
@@ -6248,19 +6281,19 @@
         <f aca="false">IF((1-J6)&gt;0.75,Assumptions!$C$11,IF((1-J6)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S6" s="27" t="n">
+      <c r="S6" s="21" t="n">
         <f aca="false">PMT(R6/12,Assumptions!$C$14,-Q6)</f>
         <v>2481.4162187044</v>
       </c>
-      <c r="T6" s="27" t="n">
+      <c r="T6" s="21" t="n">
         <f aca="false">H6*INDEX(Assumptions!$C$28:$C$33,MATCH(D6,Assumptions!$B$28:$B$33,0))/12</f>
         <v>646.666666666667</v>
       </c>
-      <c r="U6" s="27" t="n">
-        <f aca="false">(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH(M6,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="U6" s="21" t="n">
+        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D6,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M6,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>750</v>
       </c>
-      <c r="V6" s="27" t="n">
+      <c r="V6" s="21" t="n">
         <f aca="false">S6+T6+U6+O6</f>
         <v>3878.08288537106</v>
       </c>
@@ -6276,43 +6309,43 @@
         <f aca="false">H6*J6+H6*(Assumptions!$C$16-I6)</f>
         <v>140650</v>
       </c>
-      <c r="Z6" s="27" t="n">
+      <c r="Z6" s="21" t="n">
         <f aca="false">V6*Assumptions!$C$17</f>
         <v>23268.4973122264</v>
       </c>
-      <c r="AA6" s="27" t="n">
+      <c r="AA6" s="21" t="n">
         <f aca="false">K6*INDEX(Assumptions!$H$36:$H$37,MATCH(P6,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N6="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>32430</v>
       </c>
-      <c r="AB6" s="27" t="n">
+      <c r="AB6" s="21" t="n">
         <f aca="false">K6*INDEX(Assumptions!$C$36:$C$37,MATCH(P6,Assumptions!$B$36:$B$37,0))</f>
         <v>14200</v>
       </c>
-      <c r="AC6" s="27" t="n">
+      <c r="AC6" s="21" t="n">
         <f aca="false">K6-AA6-V6*12</f>
         <v>-7966.99462445278</v>
       </c>
-      <c r="AD6" s="27" t="n">
+      <c r="AD6" s="21" t="n">
         <f aca="false">AC6-AB6</f>
         <v>-22166.9946244528</v>
       </c>
-      <c r="AE6" s="21" t="n">
+      <c r="AE6" s="22" t="n">
         <f aca="false">IFERROR(K6/H6,0)</f>
         <v>0.14639175257732</v>
       </c>
-      <c r="AF6" s="21" t="n">
+      <c r="AF6" s="22" t="n">
         <f aca="false">IFERROR((K6-AA6-AB6)/H6,0)</f>
         <v>0.0502474226804124</v>
       </c>
-      <c r="AG6" s="24"/>
+      <c r="AG6" s="25"/>
       <c r="AH6" s="13" t="n">
         <v>29</v>
       </c>
-      <c r="AI6" s="24" t="s">
-        <v>232</v>
+      <c r="AI6" s="25" t="s">
+        <v>234</v>
       </c>
       <c r="AJ6" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6320,19 +6353,19 @@
         <v>2</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D7" s="35" t="s">
         <v>18</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F7" s="34" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G7" s="36" t="n">
         <v>500000</v>
@@ -6351,19 +6384,19 @@
         <v>85000</v>
       </c>
       <c r="L7" s="34" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M7" s="35" t="s">
         <v>70</v>
       </c>
       <c r="N7" s="35" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O7" s="36" t="n">
         <v>0</v>
       </c>
       <c r="P7" s="35" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q7" s="39" t="n">
         <f aca="false">H7*(1-J7)</f>
@@ -6382,7 +6415,7 @@
         <v>646.666666666667</v>
       </c>
       <c r="U7" s="39" t="n">
-        <f aca="false">(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH(M7,Assumptions!$B$22:$B$25,0)))/12</f>
+        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D7,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M7,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>750</v>
       </c>
       <c r="V7" s="39" t="n">
@@ -6434,30 +6467,30 @@
         <v>18</v>
       </c>
       <c r="AI7" s="34" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AJ7" s="43" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="24" t="s">
-        <v>238</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>239</v>
-      </c>
-      <c r="D8" s="25" t="s">
+      <c r="B8" s="25" t="s">
+        <v>240</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>241</v>
+      </c>
+      <c r="D8" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="24" t="s">
-        <v>132</v>
-      </c>
-      <c r="F8" s="24" t="s">
-        <v>240</v>
+      <c r="E8" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>242</v>
       </c>
       <c r="G8" s="19" t="n">
         <v>359000</v>
@@ -6468,29 +6501,29 @@
       <c r="I8" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="26" t="n">
+      <c r="J8" s="27" t="n">
         <f aca="false">Assumptions!$C$15</f>
         <v>0.25</v>
       </c>
       <c r="K8" s="19" t="n">
         <v>51000</v>
       </c>
-      <c r="L8" s="24" t="s">
-        <v>241</v>
-      </c>
-      <c r="M8" s="25" t="s">
+      <c r="L8" s="25" t="s">
+        <v>243</v>
+      </c>
+      <c r="M8" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="N8" s="25" t="s">
-        <v>144</v>
+      <c r="N8" s="26" t="s">
+        <v>146</v>
       </c>
       <c r="O8" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="P8" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q8" s="27" t="n">
+      <c r="P8" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q8" s="21" t="n">
         <f aca="false">H8*(1-J8)</f>
         <v>255000</v>
       </c>
@@ -6498,19 +6531,19 @@
         <f aca="false">IF((1-J8)&gt;0.75,Assumptions!$C$11,IF((1-J8)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S8" s="27" t="n">
+      <c r="S8" s="21" t="n">
         <f aca="false">PMT(R8/12,Assumptions!$C$14,-Q8)</f>
         <v>1739.54951414329</v>
       </c>
-      <c r="T8" s="27" t="n">
+      <c r="T8" s="21" t="n">
         <f aca="false">H8*INDEX(Assumptions!$C$28:$C$33,MATCH(D8,Assumptions!$B$28:$B$33,0))/12</f>
         <v>453.333333333333</v>
       </c>
-      <c r="U8" s="27" t="n">
-        <f aca="false">(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH(M8,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="U8" s="21" t="n">
+        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D8,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M8,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>750</v>
       </c>
-      <c r="V8" s="27" t="n">
+      <c r="V8" s="21" t="n">
         <f aca="false">S8+T8+U8+O8</f>
         <v>2942.88284747662</v>
       </c>
@@ -6522,47 +6555,47 @@
         <f aca="false">IFERROR(K8*Assumptions!$C$18/12/V8,0)</f>
         <v>1.15532971450608</v>
       </c>
-      <c r="Y8" s="27" t="n">
+      <c r="Y8" s="21" t="n">
         <f aca="false">H8*J8+H8*(Assumptions!$C$16-I8)</f>
         <v>98600</v>
       </c>
-      <c r="Z8" s="27" t="n">
+      <c r="Z8" s="21" t="n">
         <f aca="false">V8*Assumptions!$C$17</f>
         <v>17657.2970848597</v>
       </c>
-      <c r="AA8" s="27" t="n">
+      <c r="AA8" s="21" t="n">
         <f aca="false">K8*INDEX(Assumptions!$H$36:$H$37,MATCH(P8,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N8="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>24030</v>
       </c>
-      <c r="AB8" s="27" t="n">
+      <c r="AB8" s="21" t="n">
         <f aca="false">K8*INDEX(Assumptions!$C$36:$C$37,MATCH(P8,Assumptions!$B$36:$B$37,0))</f>
         <v>10200</v>
       </c>
-      <c r="AC8" s="27" t="n">
+      <c r="AC8" s="21" t="n">
         <f aca="false">K8-AA8-V8*12</f>
         <v>-8344.59416971947</v>
       </c>
-      <c r="AD8" s="27" t="n">
+      <c r="AD8" s="21" t="n">
         <f aca="false">AC8-AB8</f>
         <v>-18544.5941697195</v>
       </c>
-      <c r="AE8" s="21" t="n">
+      <c r="AE8" s="22" t="n">
         <f aca="false">IFERROR(K8/H8,0)</f>
         <v>0.15</v>
       </c>
-      <c r="AF8" s="21" t="n">
+      <c r="AF8" s="22" t="n">
         <f aca="false">IFERROR((K8-AA8-AB8)/H8,0)</f>
         <v>0.0493235294117647</v>
       </c>
-      <c r="AG8" s="24"/>
+      <c r="AG8" s="25"/>
       <c r="AH8" s="13" t="n">
         <v>257</v>
       </c>
-      <c r="AI8" s="24" t="s">
-        <v>242</v>
+      <c r="AI8" s="25" t="s">
+        <v>244</v>
       </c>
       <c r="AJ8" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6570,19 +6603,19 @@
         <v>4</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D9" s="35" t="s">
         <v>18</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="G9" s="36" t="n">
         <v>659900</v>
@@ -6601,19 +6634,19 @@
         <v>75000</v>
       </c>
       <c r="L9" s="34" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M9" s="35" t="s">
         <v>66</v>
       </c>
       <c r="N9" s="35" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="O9" s="36" t="n">
         <v>961</v>
       </c>
       <c r="P9" s="35" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q9" s="39" t="n">
         <f aca="false">H9*(1-J9)</f>
@@ -6632,7 +6665,7 @@
         <v>853.333333333333</v>
       </c>
       <c r="U9" s="39" t="n">
-        <f aca="false">(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH(M9,Assumptions!$B$22:$B$25,0)))/12</f>
+        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D9,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M9,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>958.333333333333</v>
       </c>
       <c r="V9" s="39" t="n">
@@ -6684,30 +6717,30 @@
         <v>36</v>
       </c>
       <c r="AI9" s="34" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AJ9" s="43" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>244</v>
-      </c>
-      <c r="D10" s="25" t="s">
+      <c r="B10" s="25" t="s">
+        <v>250</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>246</v>
+      </c>
+      <c r="D10" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>249</v>
+      <c r="E10" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>251</v>
       </c>
       <c r="G10" s="19" t="n">
         <v>575000</v>
@@ -6718,29 +6751,29 @@
       <c r="I10" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="26" t="n">
+      <c r="J10" s="27" t="n">
         <f aca="false">Assumptions!$C$15</f>
         <v>0.25</v>
       </c>
       <c r="K10" s="19" t="n">
         <v>59000</v>
       </c>
-      <c r="L10" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="M10" s="25" t="s">
+      <c r="L10" s="25" t="s">
+        <v>252</v>
+      </c>
+      <c r="M10" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="N10" s="25" t="s">
-        <v>144</v>
+      <c r="N10" s="26" t="s">
+        <v>146</v>
       </c>
       <c r="O10" s="19" t="n">
         <v>630</v>
       </c>
-      <c r="P10" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q10" s="27" t="n">
+      <c r="P10" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q10" s="21" t="n">
         <f aca="false">H10*(1-J10)</f>
         <v>420000</v>
       </c>
@@ -6748,19 +6781,19 @@
         <f aca="false">IF((1-J10)&gt;0.75,Assumptions!$C$11,IF((1-J10)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S10" s="27" t="n">
+      <c r="S10" s="21" t="n">
         <f aca="false">PMT(R10/12,Assumptions!$C$14,-Q10)</f>
         <v>2865.14037623601</v>
       </c>
-      <c r="T10" s="27" t="n">
+      <c r="T10" s="21" t="n">
         <f aca="false">H10*INDEX(Assumptions!$C$28:$C$33,MATCH(D10,Assumptions!$B$28:$B$33,0))/12</f>
         <v>746.666666666667</v>
       </c>
-      <c r="U10" s="27" t="n">
-        <f aca="false">(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH(M10,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="U10" s="21" t="n">
+        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D10,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M10,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>958.333333333333</v>
       </c>
-      <c r="V10" s="27" t="n">
+      <c r="V10" s="21" t="n">
         <f aca="false">S10+T10+U10+O10</f>
         <v>5200.14037623601</v>
       </c>
@@ -6772,47 +6805,47 @@
         <f aca="false">IFERROR(K10*Assumptions!$C$18/12/V10,0)</f>
         <v>0.756389837341349</v>
       </c>
-      <c r="Y10" s="27" t="n">
+      <c r="Y10" s="21" t="n">
         <f aca="false">H10*J10+H10*(Assumptions!$C$16-I10)</f>
         <v>162400</v>
       </c>
-      <c r="Z10" s="27" t="n">
+      <c r="Z10" s="21" t="n">
         <f aca="false">V10*Assumptions!$C$17</f>
         <v>31200.842257416</v>
       </c>
-      <c r="AA10" s="27" t="n">
+      <c r="AA10" s="21" t="n">
         <f aca="false">K10*INDEX(Assumptions!$H$36:$H$37,MATCH(P10,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N10="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>26670</v>
       </c>
-      <c r="AB10" s="27" t="n">
+      <c r="AB10" s="21" t="n">
         <f aca="false">K10*INDEX(Assumptions!$C$36:$C$37,MATCH(P10,Assumptions!$B$36:$B$37,0))</f>
         <v>11800</v>
       </c>
-      <c r="AC10" s="27" t="n">
+      <c r="AC10" s="21" t="n">
         <f aca="false">K10-AA10-V10*12</f>
         <v>-30071.6845148321</v>
       </c>
-      <c r="AD10" s="27" t="n">
+      <c r="AD10" s="21" t="n">
         <f aca="false">AC10-AB10</f>
         <v>-41871.6845148321</v>
       </c>
-      <c r="AE10" s="21" t="n">
+      <c r="AE10" s="22" t="n">
         <f aca="false">IFERROR(K10/H10,0)</f>
         <v>0.105357142857143</v>
       </c>
-      <c r="AF10" s="21" t="n">
+      <c r="AF10" s="22" t="n">
         <f aca="false">IFERROR((K10-AA10-AB10)/H10,0)</f>
         <v>0.0366607142857143</v>
       </c>
-      <c r="AG10" s="24"/>
+      <c r="AG10" s="25"/>
       <c r="AH10" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="AI10" s="24" t="s">
-        <v>251</v>
+      <c r="AI10" s="25" t="s">
+        <v>253</v>
       </c>
       <c r="AJ10" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6820,19 +6853,19 @@
         <v>6</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D11" s="35" t="s">
         <v>18</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G11" s="36" t="n">
         <v>614999</v>
@@ -6851,19 +6884,19 @@
         <v>47890</v>
       </c>
       <c r="L11" s="34" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M11" s="35" t="s">
         <v>68</v>
       </c>
       <c r="N11" s="35" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="O11" s="36" t="n">
         <v>835</v>
       </c>
       <c r="P11" s="35" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q11" s="39" t="n">
         <f aca="false">H11*(1-J11)</f>
@@ -6882,7 +6915,7 @@
         <v>786.666666666667</v>
       </c>
       <c r="U11" s="39" t="n">
-        <f aca="false">(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH(M11,Assumptions!$B$22:$B$25,0)))/12</f>
+        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D11,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M11,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>1333.33333333333</v>
       </c>
       <c r="V11" s="39" t="n">
@@ -6934,30 +6967,30 @@
         <v>152</v>
       </c>
       <c r="AI11" s="34" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AJ11" s="43" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>258</v>
-      </c>
-      <c r="D12" s="25" t="s">
+      <c r="B12" s="25" t="s">
+        <v>259</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>260</v>
+      </c>
+      <c r="D12" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="F12" s="24" t="s">
-        <v>259</v>
+      <c r="E12" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>261</v>
       </c>
       <c r="G12" s="19" t="n">
         <v>699000</v>
@@ -6968,29 +7001,29 @@
       <c r="I12" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="26" t="n">
+      <c r="J12" s="27" t="n">
         <f aca="false">Assumptions!$C$15</f>
         <v>0.25</v>
       </c>
       <c r="K12" s="19" t="n">
         <v>50000</v>
       </c>
-      <c r="L12" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="M12" s="25" t="s">
+      <c r="L12" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="M12" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="N12" s="25" t="s">
-        <v>144</v>
+      <c r="N12" s="26" t="s">
+        <v>146</v>
       </c>
       <c r="O12" s="19" t="n">
         <v>1325</v>
       </c>
-      <c r="P12" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q12" s="27" t="n">
+      <c r="P12" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q12" s="21" t="n">
         <f aca="false">H12*(1-J12)</f>
         <v>524250</v>
       </c>
@@ -6998,19 +7031,19 @@
         <f aca="false">IF((1-J12)&gt;0.75,Assumptions!$C$11,IF((1-J12)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S12" s="27" t="n">
+      <c r="S12" s="21" t="n">
         <f aca="false">PMT(R12/12,Assumptions!$C$14,-Q12)</f>
         <v>3576.30914819459</v>
       </c>
-      <c r="T12" s="27" t="n">
+      <c r="T12" s="21" t="n">
         <f aca="false">H12*INDEX(Assumptions!$C$28:$C$33,MATCH(D12,Assumptions!$B$28:$B$33,0))/12</f>
         <v>932</v>
       </c>
-      <c r="U12" s="27" t="n">
-        <f aca="false">(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH(M12,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="U12" s="21" t="n">
+        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D12,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M12,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>958.333333333333</v>
       </c>
-      <c r="V12" s="27" t="n">
+      <c r="V12" s="21" t="n">
         <f aca="false">S12+T12+U12+O12</f>
         <v>6791.64248152792</v>
       </c>
@@ -7022,52 +7055,52 @@
         <f aca="false">IFERROR(K12*Assumptions!$C$18/12/V12,0)</f>
         <v>0.490799293749548</v>
       </c>
-      <c r="Y12" s="27" t="n">
+      <c r="Y12" s="21" t="n">
         <f aca="false">H12*J12+H12*(Assumptions!$C$16-I12)</f>
         <v>202710</v>
       </c>
-      <c r="Z12" s="27" t="n">
+      <c r="Z12" s="21" t="n">
         <f aca="false">V12*Assumptions!$C$17</f>
         <v>40749.8548891675</v>
       </c>
-      <c r="AA12" s="27" t="n">
+      <c r="AA12" s="21" t="n">
         <f aca="false">K12*INDEX(Assumptions!$H$36:$H$37,MATCH(P12,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N12="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>23700</v>
       </c>
-      <c r="AB12" s="27" t="n">
+      <c r="AB12" s="21" t="n">
         <f aca="false">K12*INDEX(Assumptions!$C$36:$C$37,MATCH(P12,Assumptions!$B$36:$B$37,0))</f>
         <v>10000</v>
       </c>
-      <c r="AC12" s="27" t="n">
+      <c r="AC12" s="21" t="n">
         <f aca="false">K12-AA12-V12*12</f>
         <v>-55199.709778335</v>
       </c>
-      <c r="AD12" s="27" t="n">
+      <c r="AD12" s="21" t="n">
         <f aca="false">AC12-AB12</f>
         <v>-65199.709778335</v>
       </c>
-      <c r="AE12" s="21" t="n">
+      <c r="AE12" s="22" t="n">
         <f aca="false">IFERROR(K12/H12,0)</f>
         <v>0.0715307582260372</v>
       </c>
-      <c r="AF12" s="21" t="n">
+      <c r="AF12" s="22" t="n">
         <f aca="false">IFERROR((K12-AA12-AB12)/H12,0)</f>
         <v>0.0233190271816881</v>
       </c>
-      <c r="AG12" s="24"/>
+      <c r="AG12" s="25"/>
       <c r="AH12" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="AI12" s="24" t="s">
-        <v>261</v>
+      <c r="AI12" s="25" t="s">
+        <v>263</v>
       </c>
       <c r="AJ12" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7078,296 +7111,296 @@
         <v>4</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AI16" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AJ16" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="24" t="s">
-        <v>263</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>264</v>
+      <c r="B17" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>266</v>
       </c>
       <c r="G17" s="19" t="n">
         <v>699000</v>
       </c>
-      <c r="L17" s="24" t="s">
-        <v>265</v>
-      </c>
-      <c r="AI17" s="24" t="s">
-        <v>210</v>
+      <c r="L17" s="25" t="s">
+        <v>267</v>
+      </c>
+      <c r="AI17" s="25" t="s">
+        <v>212</v>
       </c>
       <c r="AJ17" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="24" t="s">
-        <v>266</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>267</v>
+      <c r="B18" s="25" t="s">
+        <v>268</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>269</v>
       </c>
       <c r="G18" s="19" t="n">
         <v>629000</v>
       </c>
-      <c r="L18" s="24" t="s">
-        <v>268</v>
-      </c>
-      <c r="AI18" s="24" t="s">
-        <v>210</v>
+      <c r="L18" s="25" t="s">
+        <v>270</v>
+      </c>
+      <c r="AI18" s="25" t="s">
+        <v>212</v>
       </c>
       <c r="AJ18" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="24" t="s">
-        <v>269</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>270</v>
+      <c r="B19" s="25" t="s">
+        <v>271</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>272</v>
       </c>
       <c r="G19" s="19" t="n">
         <v>575000</v>
       </c>
-      <c r="L19" s="24" t="s">
-        <v>271</v>
-      </c>
-      <c r="AI19" s="24" t="s">
-        <v>210</v>
+      <c r="L19" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="AI19" s="25" t="s">
+        <v>212</v>
       </c>
       <c r="AJ19" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="24" t="s">
-        <v>272</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>264</v>
+      <c r="B20" s="25" t="s">
+        <v>274</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>266</v>
       </c>
       <c r="G20" s="19" t="n">
         <v>599000</v>
       </c>
-      <c r="L20" s="24" t="s">
-        <v>273</v>
-      </c>
-      <c r="AI20" s="24" t="s">
-        <v>210</v>
+      <c r="L20" s="25" t="s">
+        <v>275</v>
+      </c>
+      <c r="AI20" s="25" t="s">
+        <v>212</v>
       </c>
       <c r="AJ20" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="24" t="s">
-        <v>274</v>
-      </c>
-      <c r="C21" s="24" t="s">
-        <v>275</v>
+      <c r="B21" s="25" t="s">
+        <v>276</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>277</v>
       </c>
       <c r="G21" s="19" t="n">
         <v>550000</v>
       </c>
-      <c r="L21" s="24" t="s">
-        <v>276</v>
-      </c>
-      <c r="AI21" s="24" t="s">
-        <v>210</v>
+      <c r="L21" s="25" t="s">
+        <v>278</v>
+      </c>
+      <c r="AI21" s="25" t="s">
+        <v>212</v>
       </c>
       <c r="AJ21" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="24" t="s">
-        <v>277</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>278</v>
+      <c r="B22" s="25" t="s">
+        <v>279</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>280</v>
       </c>
       <c r="G22" s="19" t="n">
         <v>425000</v>
       </c>
-      <c r="L22" s="24" t="s">
-        <v>279</v>
-      </c>
-      <c r="AI22" s="24" t="s">
-        <v>210</v>
+      <c r="L22" s="25" t="s">
+        <v>281</v>
+      </c>
+      <c r="AI22" s="25" t="s">
+        <v>212</v>
       </c>
       <c r="AJ22" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="24" t="s">
-        <v>280</v>
-      </c>
-      <c r="C23" s="24" t="s">
-        <v>281</v>
+      <c r="B23" s="25" t="s">
+        <v>282</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>283</v>
       </c>
       <c r="G23" s="19" t="n">
         <v>550000</v>
       </c>
-      <c r="L23" s="24" t="s">
-        <v>282</v>
-      </c>
-      <c r="AI23" s="24" t="s">
-        <v>210</v>
+      <c r="L23" s="25" t="s">
+        <v>284</v>
+      </c>
+      <c r="AI23" s="25" t="s">
+        <v>212</v>
       </c>
       <c r="AJ23" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="24" t="s">
-        <v>283</v>
-      </c>
-      <c r="C24" s="24" t="s">
-        <v>284</v>
+      <c r="B24" s="25" t="s">
+        <v>285</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>286</v>
       </c>
       <c r="G24" s="19" t="n">
         <v>524900</v>
       </c>
-      <c r="L24" s="24" t="s">
-        <v>285</v>
-      </c>
-      <c r="AI24" s="24" t="s">
-        <v>210</v>
+      <c r="L24" s="25" t="s">
+        <v>287</v>
+      </c>
+      <c r="AI24" s="25" t="s">
+        <v>212</v>
       </c>
       <c r="AJ24" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="24" t="s">
-        <v>286</v>
-      </c>
-      <c r="C25" s="24" t="s">
-        <v>287</v>
+      <c r="B25" s="25" t="s">
+        <v>288</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>289</v>
       </c>
       <c r="G25" s="19" t="n">
         <v>490000</v>
       </c>
-      <c r="L25" s="24" t="s">
-        <v>288</v>
-      </c>
-      <c r="AI25" s="24" t="s">
-        <v>210</v>
+      <c r="L25" s="25" t="s">
+        <v>290</v>
+      </c>
+      <c r="AI25" s="25" t="s">
+        <v>212</v>
       </c>
       <c r="AJ25" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="24" t="s">
+      <c r="B26" s="25" t="s">
+        <v>291</v>
+      </c>
+      <c r="C26" s="25" t="s">
         <v>289</v>
-      </c>
-      <c r="C26" s="24" t="s">
-        <v>287</v>
       </c>
       <c r="G26" s="19" t="n">
         <v>585000</v>
       </c>
-      <c r="L26" s="24" t="s">
-        <v>290</v>
-      </c>
-      <c r="AI26" s="24" t="s">
-        <v>210</v>
+      <c r="L26" s="25" t="s">
+        <v>292</v>
+      </c>
+      <c r="AI26" s="25" t="s">
+        <v>212</v>
       </c>
       <c r="AJ26" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="24" t="s">
-        <v>291</v>
-      </c>
-      <c r="C27" s="24" t="s">
-        <v>278</v>
+      <c r="B27" s="25" t="s">
+        <v>293</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>280</v>
       </c>
       <c r="G27" s="19" t="n">
         <v>520000</v>
       </c>
-      <c r="L27" s="24" t="s">
-        <v>292</v>
-      </c>
-      <c r="AI27" s="24" t="s">
-        <v>210</v>
+      <c r="L27" s="25" t="s">
+        <v>294</v>
+      </c>
+      <c r="AI27" s="25" t="s">
+        <v>212</v>
       </c>
       <c r="AJ27" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="24" t="s">
-        <v>293</v>
-      </c>
-      <c r="C28" s="24" t="s">
-        <v>294</v>
+      <c r="B28" s="25" t="s">
+        <v>295</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>296</v>
       </c>
       <c r="G28" s="19" t="n">
         <v>499900</v>
       </c>
-      <c r="L28" s="24" t="s">
-        <v>295</v>
-      </c>
-      <c r="AI28" s="24" t="s">
-        <v>210</v>
+      <c r="L28" s="25" t="s">
+        <v>297</v>
+      </c>
+      <c r="AI28" s="25" t="s">
+        <v>212</v>
       </c>
       <c r="AJ28" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="24" t="s">
-        <v>296</v>
-      </c>
-      <c r="C29" s="24" t="s">
-        <v>297</v>
+      <c r="B29" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>299</v>
       </c>
       <c r="G29" s="19" t="n">
         <v>594900</v>
       </c>
-      <c r="L29" s="24" t="s">
-        <v>298</v>
-      </c>
-      <c r="AI29" s="24" t="s">
-        <v>210</v>
+      <c r="L29" s="25" t="s">
+        <v>300</v>
+      </c>
+      <c r="AI29" s="25" t="s">
+        <v>212</v>
       </c>
       <c r="AJ29" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="24" t="s">
-        <v>299</v>
-      </c>
-      <c r="C30" s="24" t="s">
-        <v>300</v>
+      <c r="B30" s="25" t="s">
+        <v>301</v>
+      </c>
+      <c r="C30" s="25" t="s">
+        <v>302</v>
       </c>
       <c r="G30" s="19" t="n">
         <v>349900</v>
       </c>
-      <c r="L30" s="24" t="s">
-        <v>301</v>
-      </c>
-      <c r="AI30" s="24" t="s">
-        <v>210</v>
+      <c r="L30" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="AI30" s="25" t="s">
+        <v>212</v>
       </c>
       <c r="AJ30" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -7462,22 +7495,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>3</v>
@@ -7486,123 +7519,123 @@
         <v>4</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q5" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="R5" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="S5" s="22" t="s">
+      <c r="Q5" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="T5" s="22" t="s">
+      <c r="R5" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="U5" s="22" t="s">
+      <c r="S5" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="V5" s="22" t="s">
+      <c r="T5" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="U5" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="V5" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="W5" s="22" t="s">
+      <c r="W5" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="X5" s="22" t="s">
+      <c r="X5" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="Y5" s="22" t="s">
+      <c r="Y5" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="Z5" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA5" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="AB5" s="22" t="s">
+      <c r="Z5" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="AC5" s="22" t="s">
+      <c r="AA5" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="AB5" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC5" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="AD5" s="22" t="s">
+      <c r="AD5" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="AE5" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="AF5" s="22" t="s">
-        <v>125</v>
+      <c r="AE5" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="AF5" s="23" t="s">
+        <v>127</v>
       </c>
       <c r="AG5" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AH5" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AI5" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AJ5" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="24" t="s">
-        <v>304</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>305</v>
-      </c>
-      <c r="D6" s="25" t="s">
-        <v>79</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>132</v>
-      </c>
-      <c r="F6" s="24" t="s">
+      <c r="B6" s="25" t="s">
         <v>306</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>307</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>308</v>
       </c>
       <c r="G6" s="19" t="n">
         <v>475000</v>
@@ -7613,29 +7646,29 @@
       <c r="I6" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="26" t="n">
+      <c r="J6" s="27" t="n">
         <f aca="false">Assumptions!$C$15</f>
         <v>0.25</v>
       </c>
       <c r="K6" s="19" t="n">
         <v>60000</v>
       </c>
-      <c r="L6" s="24" t="s">
-        <v>307</v>
-      </c>
-      <c r="M6" s="25" t="s">
+      <c r="L6" s="25" t="s">
+        <v>309</v>
+      </c>
+      <c r="M6" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="N6" s="25" t="s">
-        <v>135</v>
+      <c r="N6" s="26" t="s">
+        <v>137</v>
       </c>
       <c r="O6" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="P6" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q6" s="27" t="n">
+      <c r="P6" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q6" s="21" t="n">
         <f aca="false">H6*(1-J6)</f>
         <v>345000</v>
       </c>
@@ -7643,19 +7676,19 @@
         <f aca="false">IF((1-J6)&gt;0.75,Assumptions!$C$11,IF((1-J6)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S6" s="27" t="n">
+      <c r="S6" s="21" t="n">
         <f aca="false">PMT(R6/12,Assumptions!$C$14,-Q6)</f>
         <v>2353.50816619386</v>
       </c>
-      <c r="T6" s="27" t="n">
+      <c r="T6" s="21" t="n">
         <f aca="false">H6*INDEX(Assumptions!$C$28:$C$33,MATCH(D6,Assumptions!$B$28:$B$33,0))/12</f>
         <v>651.666666666667</v>
       </c>
-      <c r="U6" s="27" t="n">
-        <f aca="false">(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH(M6,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="U6" s="21" t="n">
+        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D6,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M6,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>750</v>
       </c>
-      <c r="V6" s="27" t="n">
+      <c r="V6" s="21" t="n">
         <f aca="false">S6+T6+U6+O6</f>
         <v>3755.17483286053</v>
       </c>
@@ -7667,47 +7700,47 @@
         <f aca="false">IFERROR(K6*Assumptions!$C$18/12/V6,0)</f>
         <v>1.0651967426382</v>
       </c>
-      <c r="Y6" s="27" t="n">
+      <c r="Y6" s="21" t="n">
         <f aca="false">H6*J6+H6*(Assumptions!$C$16-I6)</f>
         <v>133400</v>
       </c>
-      <c r="Z6" s="27" t="n">
+      <c r="Z6" s="21" t="n">
         <f aca="false">V6*Assumptions!$C$17</f>
         <v>22531.0489971632</v>
       </c>
-      <c r="AA6" s="27" t="n">
+      <c r="AA6" s="21" t="n">
         <f aca="false">K6*INDEX(Assumptions!$H$36:$H$37,MATCH(P6,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N6="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>28800</v>
       </c>
-      <c r="AB6" s="27" t="n">
+      <c r="AB6" s="21" t="n">
         <f aca="false">K6*INDEX(Assumptions!$C$36:$C$37,MATCH(P6,Assumptions!$B$36:$B$37,0))</f>
         <v>12000</v>
       </c>
-      <c r="AC6" s="27" t="n">
+      <c r="AC6" s="21" t="n">
         <f aca="false">K6-AA6-V6*12</f>
         <v>-13862.0979943264</v>
       </c>
-      <c r="AD6" s="27" t="n">
+      <c r="AD6" s="21" t="n">
         <f aca="false">AC6-AB6</f>
         <v>-25862.0979943264</v>
       </c>
-      <c r="AE6" s="21" t="n">
+      <c r="AE6" s="22" t="n">
         <f aca="false">IFERROR(K6/H6,0)</f>
         <v>0.130434782608696</v>
       </c>
-      <c r="AF6" s="21" t="n">
+      <c r="AF6" s="22" t="n">
         <f aca="false">IFERROR((K6-AA6-AB6)/H6,0)</f>
         <v>0.0417391304347826</v>
       </c>
-      <c r="AG6" s="24"/>
+      <c r="AG6" s="25"/>
       <c r="AH6" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="AI6" s="24" t="s">
-        <v>308</v>
+      <c r="AI6" s="25" t="s">
+        <v>310</v>
       </c>
       <c r="AJ6" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7715,19 +7748,19 @@
         <v>2</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D7" s="35" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F7" s="34" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="G7" s="36" t="n">
         <v>589900</v>
@@ -7746,19 +7779,19 @@
         <v>60000</v>
       </c>
       <c r="L7" s="34" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M7" s="35" t="s">
         <v>66</v>
       </c>
       <c r="N7" s="35" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="O7" s="36" t="n">
         <v>583</v>
       </c>
       <c r="P7" s="35" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q7" s="39" t="n">
         <f aca="false">H7*(1-J7)</f>
@@ -7777,7 +7810,7 @@
         <v>835.691666666667</v>
       </c>
       <c r="U7" s="39" t="n">
-        <f aca="false">(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH(M7,Assumptions!$B$22:$B$25,0)))/12</f>
+        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D7,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M7,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>958.333333333333</v>
       </c>
       <c r="V7" s="39" t="n">
@@ -7829,30 +7862,30 @@
         <v>23</v>
       </c>
       <c r="AI7" s="34" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AJ7" s="43" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="24" t="s">
-        <v>314</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>315</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="E8" s="24" t="s">
-        <v>199</v>
-      </c>
-      <c r="F8" s="24" t="s">
+      <c r="B8" s="25" t="s">
         <v>316</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>317</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>201</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>318</v>
       </c>
       <c r="G8" s="19" t="n">
         <v>530000</v>
@@ -7863,29 +7896,29 @@
       <c r="I8" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="26" t="n">
+      <c r="J8" s="27" t="n">
         <f aca="false">Assumptions!$C$15</f>
         <v>0.25</v>
       </c>
       <c r="K8" s="19" t="n">
         <v>29250</v>
       </c>
-      <c r="L8" s="24" t="s">
-        <v>317</v>
-      </c>
-      <c r="M8" s="25" t="s">
+      <c r="L8" s="25" t="s">
+        <v>319</v>
+      </c>
+      <c r="M8" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="N8" s="25" t="s">
-        <v>144</v>
+      <c r="N8" s="26" t="s">
+        <v>146</v>
       </c>
       <c r="O8" s="19" t="n">
         <v>520</v>
       </c>
-      <c r="P8" s="25" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q8" s="27" t="n">
+      <c r="P8" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q8" s="21" t="n">
         <f aca="false">H8*(1-J8)</f>
         <v>397500</v>
       </c>
@@ -7893,19 +7926,19 @@
         <f aca="false">IF((1-J8)&gt;0.75,Assumptions!$C$11,IF((1-J8)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S8" s="27" t="n">
+      <c r="S8" s="21" t="n">
         <f aca="false">PMT(R8/12,Assumptions!$C$14,-Q8)</f>
         <v>2711.65071322336</v>
       </c>
-      <c r="T8" s="27" t="n">
+      <c r="T8" s="21" t="n">
         <f aca="false">H8*INDEX(Assumptions!$C$28:$C$33,MATCH(D8,Assumptions!$B$28:$B$33,0))/12</f>
         <v>728.75</v>
       </c>
-      <c r="U8" s="27" t="n">
-        <f aca="false">(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH(M8,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="U8" s="21" t="n">
+        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D8,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M8,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>750</v>
       </c>
-      <c r="V8" s="27" t="n">
+      <c r="V8" s="21" t="n">
         <f aca="false">S8+T8+U8+O8</f>
         <v>4710.40071322336</v>
       </c>
@@ -7917,52 +7950,52 @@
         <f aca="false">IFERROR(K8*Assumptions!$C$18/12/V8,0)</f>
         <v>0.413977518839496</v>
       </c>
-      <c r="Y8" s="27" t="n">
+      <c r="Y8" s="21" t="n">
         <f aca="false">H8*J8+H8*(Assumptions!$C$16-I8)</f>
         <v>153700</v>
       </c>
-      <c r="Z8" s="27" t="n">
+      <c r="Z8" s="21" t="n">
         <f aca="false">V8*Assumptions!$C$17</f>
         <v>28262.4042793402</v>
       </c>
-      <c r="AA8" s="27" t="n">
+      <c r="AA8" s="21" t="n">
         <f aca="false">K8*INDEX(Assumptions!$H$36:$H$37,MATCH(P8,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N8="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>11880</v>
       </c>
-      <c r="AB8" s="27" t="n">
+      <c r="AB8" s="21" t="n">
         <f aca="false">K8*INDEX(Assumptions!$C$36:$C$37,MATCH(P8,Assumptions!$B$36:$B$37,0))</f>
         <v>3510</v>
       </c>
-      <c r="AC8" s="27" t="n">
+      <c r="AC8" s="21" t="n">
         <f aca="false">K8-AA8-V8*12</f>
         <v>-39154.8085586803</v>
       </c>
-      <c r="AD8" s="27" t="n">
+      <c r="AD8" s="21" t="n">
         <f aca="false">AC8-AB8</f>
         <v>-42664.8085586803</v>
       </c>
-      <c r="AE8" s="21" t="n">
+      <c r="AE8" s="22" t="n">
         <f aca="false">IFERROR(K8/H8,0)</f>
         <v>0.055188679245283</v>
       </c>
-      <c r="AF8" s="21" t="n">
+      <c r="AF8" s="22" t="n">
         <f aca="false">IFERROR((K8-AA8-AB8)/H8,0)</f>
         <v>0.0261509433962264</v>
       </c>
-      <c r="AG8" s="24"/>
+      <c r="AG8" s="25"/>
       <c r="AH8" s="13" t="n">
         <v>126</v>
       </c>
-      <c r="AI8" s="24" t="s">
-        <v>318</v>
+      <c r="AI8" s="25" t="s">
+        <v>320</v>
       </c>
       <c r="AJ8" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7973,196 +8006,196 @@
         <v>4</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AI12" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AJ12" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="24" t="s">
-        <v>320</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>321</v>
+      <c r="B13" s="25" t="s">
+        <v>322</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>323</v>
       </c>
       <c r="G13" s="19" t="n">
         <v>599000</v>
       </c>
-      <c r="L13" s="24" t="s">
-        <v>322</v>
-      </c>
-      <c r="AI13" s="24" t="s">
-        <v>210</v>
+      <c r="L13" s="25" t="s">
+        <v>324</v>
+      </c>
+      <c r="AI13" s="25" t="s">
+        <v>212</v>
       </c>
       <c r="AJ13" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="24" t="s">
-        <v>323</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>324</v>
+      <c r="B14" s="25" t="s">
+        <v>325</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>326</v>
       </c>
       <c r="G14" s="19" t="n">
         <v>542500</v>
       </c>
-      <c r="L14" s="24" t="s">
-        <v>325</v>
-      </c>
-      <c r="AI14" s="24" t="s">
-        <v>210</v>
+      <c r="L14" s="25" t="s">
+        <v>327</v>
+      </c>
+      <c r="AI14" s="25" t="s">
+        <v>212</v>
       </c>
       <c r="AJ14" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="24" t="s">
-        <v>326</v>
-      </c>
-      <c r="C15" s="24" t="s">
-        <v>321</v>
+      <c r="B15" s="25" t="s">
+        <v>328</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>323</v>
       </c>
       <c r="G15" s="19" t="n">
         <v>599900</v>
       </c>
-      <c r="L15" s="24" t="s">
-        <v>327</v>
-      </c>
-      <c r="AI15" s="24" t="s">
-        <v>210</v>
+      <c r="L15" s="25" t="s">
+        <v>329</v>
+      </c>
+      <c r="AI15" s="25" t="s">
+        <v>212</v>
       </c>
       <c r="AJ15" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="24" t="s">
-        <v>328</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>321</v>
+      <c r="B16" s="25" t="s">
+        <v>330</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>323</v>
       </c>
       <c r="G16" s="19" t="n">
         <v>659900</v>
       </c>
-      <c r="L16" s="24" t="s">
-        <v>329</v>
-      </c>
-      <c r="AI16" s="24" t="s">
-        <v>210</v>
+      <c r="L16" s="25" t="s">
+        <v>331</v>
+      </c>
+      <c r="AI16" s="25" t="s">
+        <v>212</v>
       </c>
       <c r="AJ16" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="24" t="s">
-        <v>330</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>324</v>
+      <c r="B17" s="25" t="s">
+        <v>332</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>326</v>
       </c>
       <c r="G17" s="19" t="n">
         <v>390000</v>
       </c>
-      <c r="L17" s="24" t="s">
-        <v>331</v>
-      </c>
-      <c r="AI17" s="24" t="s">
-        <v>210</v>
+      <c r="L17" s="25" t="s">
+        <v>333</v>
+      </c>
+      <c r="AI17" s="25" t="s">
+        <v>212</v>
       </c>
       <c r="AJ17" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="24" t="s">
-        <v>332</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>333</v>
+      <c r="B18" s="25" t="s">
+        <v>334</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>335</v>
       </c>
       <c r="G18" s="19" t="n">
         <v>599000</v>
       </c>
-      <c r="L18" s="24" t="s">
-        <v>334</v>
-      </c>
-      <c r="AI18" s="24" t="s">
-        <v>210</v>
+      <c r="L18" s="25" t="s">
+        <v>336</v>
+      </c>
+      <c r="AI18" s="25" t="s">
+        <v>212</v>
       </c>
       <c r="AJ18" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="24" t="s">
-        <v>335</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>336</v>
+      <c r="B19" s="25" t="s">
+        <v>337</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>338</v>
       </c>
       <c r="G19" s="19" t="n">
         <v>659000</v>
       </c>
-      <c r="L19" s="24" t="s">
-        <v>337</v>
-      </c>
-      <c r="AI19" s="24" t="s">
-        <v>210</v>
+      <c r="L19" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="AI19" s="25" t="s">
+        <v>212</v>
       </c>
       <c r="AJ19" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="24" t="s">
-        <v>338</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>339</v>
+      <c r="B20" s="25" t="s">
+        <v>340</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>341</v>
       </c>
       <c r="G20" s="19" t="n">
         <v>449900</v>
       </c>
-      <c r="L20" s="24" t="s">
-        <v>340</v>
-      </c>
-      <c r="AI20" s="24" t="s">
-        <v>210</v>
+      <c r="L20" s="25" t="s">
+        <v>342</v>
+      </c>
+      <c r="AI20" s="25" t="s">
+        <v>212</v>
       </c>
       <c r="AJ20" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="24" t="s">
-        <v>341</v>
-      </c>
-      <c r="C21" s="24" t="s">
-        <v>342</v>
+      <c r="B21" s="25" t="s">
+        <v>343</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>344</v>
       </c>
       <c r="G21" s="19" t="n">
         <v>665000</v>
       </c>
-      <c r="L21" s="24" t="s">
-        <v>343</v>
-      </c>
-      <c r="AI21" s="24" t="s">
-        <v>210</v>
+      <c r="L21" s="25" t="s">
+        <v>345</v>
+      </c>
+      <c r="AI21" s="25" t="s">
+        <v>212</v>
       </c>
       <c r="AJ21" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -8229,38 +8262,38 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>7</v>
@@ -8269,10 +8302,10 @@
         <v>8</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>11</v>
@@ -8281,10 +8314,10 @@
         <v>12</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8299,7 +8332,7 @@
         <f aca="false">'Manatee-Sarasota'!$H$6</f>
         <v>560000</v>
       </c>
-      <c r="D5" s="26" t="n">
+      <c r="D5" s="27" t="n">
         <f aca="false">'Manatee-Sarasota'!$I$6</f>
         <v>0.03</v>
       </c>
@@ -8307,7 +8340,7 @@
         <f aca="false">'Manatee-Sarasota'!$K$6</f>
         <v>85000</v>
       </c>
-      <c r="F5" s="27" t="n">
+      <c r="F5" s="21" t="n">
         <f aca="false">C5*(1-B5)</f>
         <v>448000</v>
       </c>
@@ -8315,12 +8348,12 @@
         <f aca="false">IF((1-B5)&gt;0.75,Assumptions!$C$11,IF((1-B5)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.075</v>
       </c>
-      <c r="H5" s="27" t="n">
+      <c r="H5" s="21" t="n">
         <f aca="false">PMT(G5/12,Assumptions!$C$14,-F5)</f>
         <v>3132.48099831645</v>
       </c>
-      <c r="I5" s="27" t="n">
-        <f aca="false">H5+C5*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$6,Assumptions!$B$28:$B$33,0))/12+(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$6,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$6</f>
+      <c r="I5" s="21" t="n">
+        <f aca="false">H5+C5*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$6,Assumptions!$B$28:$B$33,0))/12+(INDEX(Assumptions!$D$28:$D$33,MATCH('Manatee-Sarasota'!$D$6,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$6,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$6</f>
         <v>4582.48099831645</v>
       </c>
       <c r="J5" s="29" t="n">
@@ -8331,24 +8364,24 @@
         <f aca="false">IFERROR(E5*Assumptions!$C$18/12/I5,0)</f>
         <v>1.2365935982601</v>
       </c>
-      <c r="L5" s="27" t="n">
+      <c r="L5" s="21" t="n">
         <f aca="false">C5*B5+C5*(Assumptions!$C$16-D5)</f>
         <v>117600</v>
       </c>
-      <c r="M5" s="27" t="n">
+      <c r="M5" s="21" t="n">
         <f aca="false">E5-(E5*INDEX(Assumptions!$H$36:$H$37,MATCH('Manatee-Sarasota'!$P$6,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF('Manatee-Sarasota'!$N$6="Y",Assumptions!$C$41,Assumptions!$C$42))-I5*12</f>
         <v>-7039.77197979741</v>
       </c>
-      <c r="N5" s="27" t="n">
+      <c r="N5" s="21" t="n">
         <f aca="false">M5-E5*INDEX(Assumptions!$C$36:$C$37,MATCH('Manatee-Sarasota'!$P$6,Assumptions!$B$36:$B$37,0))</f>
         <v>-24039.7719797974</v>
       </c>
-      <c r="O5" s="21" t="n">
+      <c r="O5" s="22" t="n">
         <f aca="false">IFERROR(M5/L5,0)</f>
         <v>-0.0598620066309303</v>
       </c>
       <c r="P5" s="46" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8363,7 +8396,7 @@
         <f aca="false">'Manatee-Sarasota'!$H$6</f>
         <v>560000</v>
       </c>
-      <c r="D6" s="26" t="n">
+      <c r="D6" s="27" t="n">
         <f aca="false">'Manatee-Sarasota'!$I$6</f>
         <v>0.03</v>
       </c>
@@ -8371,7 +8404,7 @@
         <f aca="false">'Manatee-Sarasota'!$K$6</f>
         <v>85000</v>
       </c>
-      <c r="F6" s="27" t="n">
+      <c r="F6" s="21" t="n">
         <f aca="false">C6*(1-B6)</f>
         <v>420000</v>
       </c>
@@ -8379,12 +8412,12 @@
         <f aca="false">IF((1-B6)&gt;0.75,Assumptions!$C$11,IF((1-B6)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="H6" s="27" t="n">
+      <c r="H6" s="21" t="n">
         <f aca="false">PMT(G6/12,Assumptions!$C$14,-F6)</f>
         <v>2865.14037623601</v>
       </c>
-      <c r="I6" s="27" t="n">
-        <f aca="false">H6+C6*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$6,Assumptions!$B$28:$B$33,0))/12+(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$6,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$6</f>
+      <c r="I6" s="21" t="n">
+        <f aca="false">H6+C6*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$6,Assumptions!$B$28:$B$33,0))/12+(INDEX(Assumptions!$D$28:$D$33,MATCH('Manatee-Sarasota'!$D$6,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$6,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$6</f>
         <v>4315.14037623601</v>
       </c>
       <c r="J6" s="29" t="n">
@@ -8395,23 +8428,23 @@
         <f aca="false">IFERROR(E6*Assumptions!$C$18/12/I6,0)</f>
         <v>1.31320563703412</v>
       </c>
-      <c r="L6" s="27" t="n">
+      <c r="L6" s="21" t="n">
         <f aca="false">C6*B6+C6*(Assumptions!$C$16-D6)</f>
         <v>145600</v>
       </c>
-      <c r="M6" s="27" t="n">
+      <c r="M6" s="21" t="n">
         <f aca="false">E6-(E6*INDEX(Assumptions!$H$36:$H$37,MATCH('Manatee-Sarasota'!$P$6,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF('Manatee-Sarasota'!$N$6="Y",Assumptions!$C$41,Assumptions!$C$42))-I6*12</f>
         <v>-3831.68451483207</v>
       </c>
-      <c r="N6" s="27" t="n">
+      <c r="N6" s="21" t="n">
         <f aca="false">M6-E6*INDEX(Assumptions!$C$36:$C$37,MATCH('Manatee-Sarasota'!$P$6,Assumptions!$B$36:$B$37,0))</f>
         <v>-20831.6845148321</v>
       </c>
-      <c r="O6" s="21" t="n">
+      <c r="O6" s="22" t="n">
         <f aca="false">IFERROR(M6/L6,0)</f>
         <v>-0.0263165145249455</v>
       </c>
-      <c r="P6" s="21" t="n">
+      <c r="P6" s="22" t="n">
         <f aca="false">IFERROR((M6-M5)/(L6-L5),0)</f>
         <v>0.114574552320191</v>
       </c>
@@ -8428,7 +8461,7 @@
         <f aca="false">'Manatee-Sarasota'!$H$6</f>
         <v>560000</v>
       </c>
-      <c r="D7" s="26" t="n">
+      <c r="D7" s="27" t="n">
         <f aca="false">'Manatee-Sarasota'!$I$6</f>
         <v>0.03</v>
       </c>
@@ -8436,7 +8469,7 @@
         <f aca="false">'Manatee-Sarasota'!$K$6</f>
         <v>85000</v>
       </c>
-      <c r="F7" s="27" t="n">
+      <c r="F7" s="21" t="n">
         <f aca="false">C7*(1-B7)</f>
         <v>392000</v>
       </c>
@@ -8444,12 +8477,12 @@
         <f aca="false">IF((1-B7)&gt;0.75,Assumptions!$C$11,IF((1-B7)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.07125</v>
       </c>
-      <c r="H7" s="27" t="n">
+      <c r="H7" s="21" t="n">
         <f aca="false">PMT(G7/12,Assumptions!$C$14,-F7)</f>
         <v>2640.97661134044</v>
       </c>
-      <c r="I7" s="27" t="n">
-        <f aca="false">H7+C7*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$6,Assumptions!$B$28:$B$33,0))/12+(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$6,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$6</f>
+      <c r="I7" s="21" t="n">
+        <f aca="false">H7+C7*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$6,Assumptions!$B$28:$B$33,0))/12+(INDEX(Assumptions!$D$28:$D$33,MATCH('Manatee-Sarasota'!$D$6,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$6,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$6</f>
         <v>4090.97661134044</v>
       </c>
       <c r="J7" s="29" t="n">
@@ -8460,23 +8493,23 @@
         <f aca="false">IFERROR(E7*Assumptions!$C$18/12/I7,0)</f>
         <v>1.3851623230889</v>
       </c>
-      <c r="L7" s="27" t="n">
+      <c r="L7" s="21" t="n">
         <f aca="false">C7*B7+C7*(Assumptions!$C$16-D7)</f>
         <v>173600</v>
       </c>
-      <c r="M7" s="27" t="n">
+      <c r="M7" s="21" t="n">
         <f aca="false">E7-(E7*INDEX(Assumptions!$H$36:$H$37,MATCH('Manatee-Sarasota'!$P$6,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF('Manatee-Sarasota'!$N$6="Y",Assumptions!$C$41,Assumptions!$C$42))-I7*12</f>
         <v>-1141.71933608533</v>
       </c>
-      <c r="N7" s="27" t="n">
+      <c r="N7" s="21" t="n">
         <f aca="false">M7-E7*INDEX(Assumptions!$C$36:$C$37,MATCH('Manatee-Sarasota'!$P$6,Assumptions!$B$36:$B$37,0))</f>
         <v>-18141.7193360853</v>
       </c>
-      <c r="O7" s="21" t="n">
+      <c r="O7" s="22" t="n">
         <f aca="false">IFERROR(M7/L7,0)</f>
         <v>-0.00657672428620584</v>
       </c>
-      <c r="P7" s="21" t="n">
+      <c r="P7" s="22" t="n">
         <f aca="false">IFERROR((M7-M6)/(L7-L6),0)</f>
         <v>0.0960701849552406</v>
       </c>
@@ -8493,7 +8526,7 @@
         <f aca="false">'Manatee-Sarasota'!$H$7</f>
         <v>460000</v>
       </c>
-      <c r="D9" s="26" t="n">
+      <c r="D9" s="27" t="n">
         <f aca="false">'Manatee-Sarasota'!$I$7</f>
         <v>0</v>
       </c>
@@ -8501,7 +8534,7 @@
         <f aca="false">'Manatee-Sarasota'!$K$7</f>
         <v>73000</v>
       </c>
-      <c r="F9" s="27" t="n">
+      <c r="F9" s="21" t="n">
         <f aca="false">C9*(1-B9)</f>
         <v>368000</v>
       </c>
@@ -8509,12 +8542,12 @@
         <f aca="false">IF((1-B9)&gt;0.75,Assumptions!$C$11,IF((1-B9)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.075</v>
       </c>
-      <c r="H9" s="27" t="n">
+      <c r="H9" s="21" t="n">
         <f aca="false">PMT(G9/12,Assumptions!$C$14,-F9)</f>
         <v>2573.10939147423</v>
       </c>
-      <c r="I9" s="27" t="n">
-        <f aca="false">H9+C9*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$7,Assumptions!$B$28:$B$33,0))/12+(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$7,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$7</f>
+      <c r="I9" s="21" t="n">
+        <f aca="false">H9+C9*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$7,Assumptions!$B$28:$B$33,0))/12+(INDEX(Assumptions!$D$28:$D$33,MATCH('Manatee-Sarasota'!$D$7,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$7,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$7</f>
         <v>3898.10939147423</v>
       </c>
       <c r="J9" s="29" t="n">
@@ -8525,24 +8558,24 @@
         <f aca="false">IFERROR(E9*Assumptions!$C$18/12/I9,0)</f>
         <v>1.24846846969221</v>
       </c>
-      <c r="L9" s="27" t="n">
+      <c r="L9" s="21" t="n">
         <f aca="false">C9*B9+C9*(Assumptions!$C$16-D9)</f>
         <v>110400</v>
       </c>
-      <c r="M9" s="27" t="n">
+      <c r="M9" s="21" t="n">
         <f aca="false">E9-(E9*INDEX(Assumptions!$H$36:$H$37,MATCH('Manatee-Sarasota'!$P$7,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF('Manatee-Sarasota'!$N$7="Y",Assumptions!$C$41,Assumptions!$C$42))-I9*12</f>
         <v>-5067.31269769074</v>
       </c>
-      <c r="N9" s="27" t="n">
+      <c r="N9" s="21" t="n">
         <f aca="false">M9-E9*INDEX(Assumptions!$C$36:$C$37,MATCH('Manatee-Sarasota'!$P$7,Assumptions!$B$36:$B$37,0))</f>
         <v>-19667.3126976907</v>
       </c>
-      <c r="O9" s="21" t="n">
+      <c r="O9" s="22" t="n">
         <f aca="false">IFERROR(M9/L9,0)</f>
         <v>-0.0458995715370538</v>
       </c>
       <c r="P9" s="46" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8557,7 +8590,7 @@
         <f aca="false">'Manatee-Sarasota'!$H$7</f>
         <v>460000</v>
       </c>
-      <c r="D10" s="26" t="n">
+      <c r="D10" s="27" t="n">
         <f aca="false">'Manatee-Sarasota'!$I$7</f>
         <v>0</v>
       </c>
@@ -8565,7 +8598,7 @@
         <f aca="false">'Manatee-Sarasota'!$K$7</f>
         <v>73000</v>
       </c>
-      <c r="F10" s="27" t="n">
+      <c r="F10" s="21" t="n">
         <f aca="false">C10*(1-B10)</f>
         <v>345000</v>
       </c>
@@ -8573,12 +8606,12 @@
         <f aca="false">IF((1-B10)&gt;0.75,Assumptions!$C$11,IF((1-B10)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="H10" s="27" t="n">
+      <c r="H10" s="21" t="n">
         <f aca="false">PMT(G10/12,Assumptions!$C$14,-F10)</f>
         <v>2353.50816619386</v>
       </c>
-      <c r="I10" s="27" t="n">
-        <f aca="false">H10+C10*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$7,Assumptions!$B$28:$B$33,0))/12+(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$7,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$7</f>
+      <c r="I10" s="21" t="n">
+        <f aca="false">H10+C10*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$7,Assumptions!$B$28:$B$33,0))/12+(INDEX(Assumptions!$D$28:$D$33,MATCH('Manatee-Sarasota'!$D$7,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$7,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$7</f>
         <v>3678.50816619386</v>
       </c>
       <c r="J10" s="29" t="n">
@@ -8589,23 +8622,23 @@
         <f aca="false">IFERROR(E10*Assumptions!$C$18/12/I10,0)</f>
         <v>1.32300009862482</v>
       </c>
-      <c r="L10" s="27" t="n">
+      <c r="L10" s="21" t="n">
         <f aca="false">C10*B10+C10*(Assumptions!$C$16-D10)</f>
         <v>133400</v>
       </c>
-      <c r="M10" s="27" t="n">
+      <c r="M10" s="21" t="n">
         <f aca="false">E10-(E10*INDEX(Assumptions!$H$36:$H$37,MATCH('Manatee-Sarasota'!$P$7,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF('Manatee-Sarasota'!$N$7="Y",Assumptions!$C$41,Assumptions!$C$42))-I10*12</f>
         <v>-2432.09799432634</v>
       </c>
-      <c r="N10" s="27" t="n">
+      <c r="N10" s="21" t="n">
         <f aca="false">M10-E10*INDEX(Assumptions!$C$36:$C$37,MATCH('Manatee-Sarasota'!$P$7,Assumptions!$B$36:$B$37,0))</f>
         <v>-17032.0979943263</v>
       </c>
-      <c r="O10" s="21" t="n">
+      <c r="O10" s="22" t="n">
         <f aca="false">IFERROR(M10/L10,0)</f>
         <v>-0.0182316191478737</v>
       </c>
-      <c r="P10" s="21" t="n">
+      <c r="P10" s="22" t="n">
         <f aca="false">IFERROR((M10-M9)/(L10-L9),0)</f>
         <v>0.114574552320191</v>
       </c>
@@ -8622,7 +8655,7 @@
         <f aca="false">'Manatee-Sarasota'!$H$7</f>
         <v>460000</v>
       </c>
-      <c r="D11" s="26" t="n">
+      <c r="D11" s="27" t="n">
         <f aca="false">'Manatee-Sarasota'!$I$7</f>
         <v>0</v>
       </c>
@@ -8630,7 +8663,7 @@
         <f aca="false">'Manatee-Sarasota'!$K$7</f>
         <v>73000</v>
       </c>
-      <c r="F11" s="27" t="n">
+      <c r="F11" s="21" t="n">
         <f aca="false">C11*(1-B11)</f>
         <v>322000</v>
       </c>
@@ -8638,12 +8671,12 @@
         <f aca="false">IF((1-B11)&gt;0.75,Assumptions!$C$11,IF((1-B11)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.07125</v>
       </c>
-      <c r="H11" s="27" t="n">
+      <c r="H11" s="21" t="n">
         <f aca="false">PMT(G11/12,Assumptions!$C$14,-F11)</f>
         <v>2169.37364502965</v>
       </c>
-      <c r="I11" s="27" t="n">
-        <f aca="false">H11+C11*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$7,Assumptions!$B$28:$B$33,0))/12+(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$7,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$7</f>
+      <c r="I11" s="21" t="n">
+        <f aca="false">H11+C11*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$7,Assumptions!$B$28:$B$33,0))/12+(INDEX(Assumptions!$D$28:$D$33,MATCH('Manatee-Sarasota'!$D$7,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$7,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$7</f>
         <v>3494.37364502965</v>
       </c>
       <c r="J11" s="29" t="n">
@@ -8654,23 +8687,23 @@
         <f aca="false">IFERROR(E11*Assumptions!$C$18/12/I11,0)</f>
         <v>1.39271502164313</v>
       </c>
-      <c r="L11" s="27" t="n">
+      <c r="L11" s="21" t="n">
         <f aca="false">C11*B11+C11*(Assumptions!$C$16-D11)</f>
         <v>156400</v>
       </c>
-      <c r="M11" s="27" t="n">
+      <c r="M11" s="21" t="n">
         <f aca="false">E11-(E11*INDEX(Assumptions!$H$36:$H$37,MATCH('Manatee-Sarasota'!$P$7,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF('Manatee-Sarasota'!$N$7="Y",Assumptions!$C$41,Assumptions!$C$42))-I11*12</f>
         <v>-222.483740355812</v>
       </c>
-      <c r="N11" s="27" t="n">
+      <c r="N11" s="21" t="n">
         <f aca="false">M11-E11*INDEX(Assumptions!$C$36:$C$37,MATCH('Manatee-Sarasota'!$P$7,Assumptions!$B$36:$B$37,0))</f>
         <v>-14822.4837403558</v>
       </c>
-      <c r="O11" s="21" t="n">
+      <c r="O11" s="22" t="n">
         <f aca="false">IFERROR(M11/L11,0)</f>
         <v>-0.00142253030918038</v>
       </c>
-      <c r="P11" s="21" t="n">
+      <c r="P11" s="22" t="n">
         <f aca="false">IFERROR((M11-M10)/(L11-L10),0)</f>
         <v>0.0960701849552405</v>
       </c>
@@ -8687,7 +8720,7 @@
         <f aca="false">'Manatee-Sarasota'!$H$8</f>
         <v>600000</v>
       </c>
-      <c r="D13" s="26" t="n">
+      <c r="D13" s="27" t="n">
         <f aca="false">'Manatee-Sarasota'!$I$8</f>
         <v>0.03</v>
       </c>
@@ -8695,7 +8728,7 @@
         <f aca="false">'Manatee-Sarasota'!$K$8</f>
         <v>89000</v>
       </c>
-      <c r="F13" s="27" t="n">
+      <c r="F13" s="21" t="n">
         <f aca="false">C13*(1-B13)</f>
         <v>480000</v>
       </c>
@@ -8703,12 +8736,12 @@
         <f aca="false">IF((1-B13)&gt;0.75,Assumptions!$C$11,IF((1-B13)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.075</v>
       </c>
-      <c r="H13" s="27" t="n">
+      <c r="H13" s="21" t="n">
         <f aca="false">PMT(G13/12,Assumptions!$C$14,-F13)</f>
         <v>3356.22964105334</v>
       </c>
-      <c r="I13" s="27" t="n">
-        <f aca="false">H13+C13*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$8,Assumptions!$B$28:$B$33,0))/12+(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$8,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$8</f>
+      <c r="I13" s="21" t="n">
+        <f aca="false">H13+C13*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$8,Assumptions!$B$28:$B$33,0))/12+(INDEX(Assumptions!$D$28:$D$33,MATCH('Manatee-Sarasota'!$D$8,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$8,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$8</f>
         <v>4856.22964105334</v>
       </c>
       <c r="J13" s="29" t="n">
@@ -8719,24 +8752,24 @@
         <f aca="false">IFERROR(E13*Assumptions!$C$18/12/I13,0)</f>
         <v>1.22179834396101</v>
       </c>
-      <c r="L13" s="27" t="n">
+      <c r="L13" s="21" t="n">
         <f aca="false">C13*B13+C13*(Assumptions!$C$16-D13)</f>
         <v>126000</v>
       </c>
-      <c r="M13" s="27" t="n">
+      <c r="M13" s="21" t="n">
         <f aca="false">E13-(E13*INDEX(Assumptions!$H$36:$H$37,MATCH('Manatee-Sarasota'!$P$8,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF('Manatee-Sarasota'!$N$8="Y",Assumptions!$C$41,Assumptions!$C$42))-I13*12</f>
         <v>-7644.75569264008</v>
       </c>
-      <c r="N13" s="27" t="n">
+      <c r="N13" s="21" t="n">
         <f aca="false">M13-E13*INDEX(Assumptions!$C$36:$C$37,MATCH('Manatee-Sarasota'!$P$8,Assumptions!$B$36:$B$37,0))</f>
         <v>-25444.7556926401</v>
       </c>
-      <c r="O13" s="21" t="n">
+      <c r="O13" s="22" t="n">
         <f aca="false">IFERROR(M13/L13,0)</f>
         <v>-0.0606726642273022</v>
       </c>
       <c r="P13" s="46" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8751,7 +8784,7 @@
         <f aca="false">'Manatee-Sarasota'!$H$8</f>
         <v>600000</v>
       </c>
-      <c r="D14" s="26" t="n">
+      <c r="D14" s="27" t="n">
         <f aca="false">'Manatee-Sarasota'!$I$8</f>
         <v>0.03</v>
       </c>
@@ -8759,7 +8792,7 @@
         <f aca="false">'Manatee-Sarasota'!$K$8</f>
         <v>89000</v>
       </c>
-      <c r="F14" s="27" t="n">
+      <c r="F14" s="21" t="n">
         <f aca="false">C14*(1-B14)</f>
         <v>450000</v>
       </c>
@@ -8767,12 +8800,12 @@
         <f aca="false">IF((1-B14)&gt;0.75,Assumptions!$C$11,IF((1-B14)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="H14" s="27" t="n">
+      <c r="H14" s="21" t="n">
         <f aca="false">PMT(G14/12,Assumptions!$C$14,-F14)</f>
         <v>3069.79326025286</v>
       </c>
-      <c r="I14" s="27" t="n">
-        <f aca="false">H14+C14*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$8,Assumptions!$B$28:$B$33,0))/12+(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$8,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$8</f>
+      <c r="I14" s="21" t="n">
+        <f aca="false">H14+C14*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$8,Assumptions!$B$28:$B$33,0))/12+(INDEX(Assumptions!$D$28:$D$33,MATCH('Manatee-Sarasota'!$D$8,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$8,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$8</f>
         <v>4569.79326025286</v>
       </c>
       <c r="J14" s="29" t="n">
@@ -8783,23 +8816,23 @@
         <f aca="false">IFERROR(E14*Assumptions!$C$18/12/I14,0)</f>
         <v>1.29838112917279</v>
       </c>
-      <c r="L14" s="27" t="n">
+      <c r="L14" s="21" t="n">
         <f aca="false">C14*B14+C14*(Assumptions!$C$16-D14)</f>
         <v>156000</v>
       </c>
-      <c r="M14" s="27" t="n">
+      <c r="M14" s="21" t="n">
         <f aca="false">E14-(E14*INDEX(Assumptions!$H$36:$H$37,MATCH('Manatee-Sarasota'!$P$8,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF('Manatee-Sarasota'!$N$8="Y",Assumptions!$C$41,Assumptions!$C$42))-I14*12</f>
         <v>-4207.51912303436</v>
       </c>
-      <c r="N14" s="27" t="n">
+      <c r="N14" s="21" t="n">
         <f aca="false">M14-E14*INDEX(Assumptions!$C$36:$C$37,MATCH('Manatee-Sarasota'!$P$8,Assumptions!$B$36:$B$37,0))</f>
         <v>-22007.5191230344</v>
       </c>
-      <c r="O14" s="21" t="n">
+      <c r="O14" s="22" t="n">
         <f aca="false">IFERROR(M14/L14,0)</f>
         <v>-0.0269712764297075</v>
       </c>
-      <c r="P14" s="21" t="n">
+      <c r="P14" s="22" t="n">
         <f aca="false">IFERROR((M14-M13)/(L14-L13),0)</f>
         <v>0.114574552320191</v>
       </c>
@@ -8816,7 +8849,7 @@
         <f aca="false">'Manatee-Sarasota'!$H$8</f>
         <v>600000</v>
       </c>
-      <c r="D15" s="26" t="n">
+      <c r="D15" s="27" t="n">
         <f aca="false">'Manatee-Sarasota'!$I$8</f>
         <v>0.03</v>
       </c>
@@ -8824,7 +8857,7 @@
         <f aca="false">'Manatee-Sarasota'!$K$8</f>
         <v>89000</v>
       </c>
-      <c r="F15" s="27" t="n">
+      <c r="F15" s="21" t="n">
         <f aca="false">C15*(1-B15)</f>
         <v>420000</v>
       </c>
@@ -8832,12 +8865,12 @@
         <f aca="false">IF((1-B15)&gt;0.75,Assumptions!$C$11,IF((1-B15)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.07125</v>
       </c>
-      <c r="H15" s="27" t="n">
+      <c r="H15" s="21" t="n">
         <f aca="false">PMT(G15/12,Assumptions!$C$14,-F15)</f>
         <v>2829.61779786476</v>
       </c>
-      <c r="I15" s="27" t="n">
-        <f aca="false">H15+C15*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$8,Assumptions!$B$28:$B$33,0))/12+(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$8,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$8</f>
+      <c r="I15" s="21" t="n">
+        <f aca="false">H15+C15*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$8,Assumptions!$B$28:$B$33,0))/12+(INDEX(Assumptions!$D$28:$D$33,MATCH('Manatee-Sarasota'!$D$8,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$8,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$8</f>
         <v>4329.61779786476</v>
       </c>
       <c r="J15" s="29" t="n">
@@ -8848,23 +8881,23 @@
         <f aca="false">IFERROR(E15*Assumptions!$C$18/12/I15,0)</f>
         <v>1.37040579800357</v>
       </c>
-      <c r="L15" s="27" t="n">
+      <c r="L15" s="21" t="n">
         <f aca="false">C15*B15+C15*(Assumptions!$C$16-D15)</f>
         <v>186000</v>
       </c>
-      <c r="M15" s="27" t="n">
+      <c r="M15" s="21" t="n">
         <f aca="false">E15-(E15*INDEX(Assumptions!$H$36:$H$37,MATCH('Manatee-Sarasota'!$P$8,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF('Manatee-Sarasota'!$N$8="Y",Assumptions!$C$41,Assumptions!$C$42))-I15*12</f>
         <v>-1325.41357437715</v>
       </c>
-      <c r="N15" s="27" t="n">
+      <c r="N15" s="21" t="n">
         <f aca="false">M15-E15*INDEX(Assumptions!$C$36:$C$37,MATCH('Manatee-Sarasota'!$P$8,Assumptions!$B$36:$B$37,0))</f>
         <v>-19125.4135743771</v>
       </c>
-      <c r="O15" s="21" t="n">
+      <c r="O15" s="22" t="n">
         <f aca="false">IFERROR(M15/L15,0)</f>
         <v>-0.0071258794321352</v>
       </c>
-      <c r="P15" s="21" t="n">
+      <c r="P15" s="22" t="n">
         <f aca="false">IFERROR((M15-M14)/(L15-L14),0)</f>
         <v>0.0960701849552405</v>
       </c>
@@ -8881,7 +8914,7 @@
         <f aca="false">Pinellas!$H$6</f>
         <v>485000</v>
       </c>
-      <c r="D17" s="26" t="n">
+      <c r="D17" s="27" t="n">
         <f aca="false">Pinellas!$I$6</f>
         <v>0</v>
       </c>
@@ -8889,7 +8922,7 @@
         <f aca="false">Pinellas!$K$6</f>
         <v>71000</v>
       </c>
-      <c r="F17" s="27" t="n">
+      <c r="F17" s="21" t="n">
         <f aca="false">C17*(1-B17)</f>
         <v>388000</v>
       </c>
@@ -8897,12 +8930,12 @@
         <f aca="false">IF((1-B17)&gt;0.75,Assumptions!$C$11,IF((1-B17)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.075</v>
       </c>
-      <c r="H17" s="27" t="n">
+      <c r="H17" s="21" t="n">
         <f aca="false">PMT(G17/12,Assumptions!$C$14,-F17)</f>
         <v>2712.95229318478</v>
       </c>
-      <c r="I17" s="27" t="n">
-        <f aca="false">H17+C17*INDEX(Assumptions!$C$28:$C$33,MATCH(Pinellas!$D$6,Assumptions!$B$28:$B$33,0))/12+(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH(Pinellas!$M$6,Assumptions!$B$22:$B$25,0)))/12+Pinellas!$O$6</f>
+      <c r="I17" s="21" t="n">
+        <f aca="false">H17+C17*INDEX(Assumptions!$C$28:$C$33,MATCH(Pinellas!$D$6,Assumptions!$B$28:$B$33,0))/12+(INDEX(Assumptions!$D$28:$D$33,MATCH(Pinellas!$D$6,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(Pinellas!$M$6,Assumptions!$B$22:$B$25,0)))/12+Pinellas!$O$6</f>
         <v>4109.61895985145</v>
       </c>
       <c r="J17" s="29" t="n">
@@ -8913,24 +8946,24 @@
         <f aca="false">IFERROR(E17*Assumptions!$C$18/12/I17,0)</f>
         <v>1.15176939263109</v>
       </c>
-      <c r="L17" s="27" t="n">
+      <c r="L17" s="21" t="n">
         <f aca="false">C17*B17+C17*(Assumptions!$C$16-D17)</f>
         <v>116400</v>
       </c>
-      <c r="M17" s="27" t="n">
+      <c r="M17" s="21" t="n">
         <f aca="false">E17-(E17*INDEX(Assumptions!$H$36:$H$37,MATCH(Pinellas!$P$6,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(Pinellas!$N$6="Y",Assumptions!$C$41,Assumptions!$C$42))-I17*12</f>
         <v>-10745.4275182174</v>
       </c>
-      <c r="N17" s="27" t="n">
+      <c r="N17" s="21" t="n">
         <f aca="false">M17-E17*INDEX(Assumptions!$C$36:$C$37,MATCH(Pinellas!$P$6,Assumptions!$B$36:$B$37,0))</f>
         <v>-24945.4275182174</v>
       </c>
-      <c r="O17" s="21" t="n">
+      <c r="O17" s="22" t="n">
         <f aca="false">IFERROR(M17/L17,0)</f>
         <v>-0.0923146694004932</v>
       </c>
       <c r="P17" s="46" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8945,7 +8978,7 @@
         <f aca="false">Pinellas!$H$6</f>
         <v>485000</v>
       </c>
-      <c r="D18" s="26" t="n">
+      <c r="D18" s="27" t="n">
         <f aca="false">Pinellas!$I$6</f>
         <v>0</v>
       </c>
@@ -8953,7 +8986,7 @@
         <f aca="false">Pinellas!$K$6</f>
         <v>71000</v>
       </c>
-      <c r="F18" s="27" t="n">
+      <c r="F18" s="21" t="n">
         <f aca="false">C18*(1-B18)</f>
         <v>363750</v>
       </c>
@@ -8961,12 +8994,12 @@
         <f aca="false">IF((1-B18)&gt;0.75,Assumptions!$C$11,IF((1-B18)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="H18" s="27" t="n">
+      <c r="H18" s="21" t="n">
         <f aca="false">PMT(G18/12,Assumptions!$C$14,-F18)</f>
         <v>2481.4162187044</v>
       </c>
-      <c r="I18" s="27" t="n">
-        <f aca="false">H18+C18*INDEX(Assumptions!$C$28:$C$33,MATCH(Pinellas!$D$6,Assumptions!$B$28:$B$33,0))/12+(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH(Pinellas!$M$6,Assumptions!$B$22:$B$25,0)))/12+Pinellas!$O$6</f>
+      <c r="I18" s="21" t="n">
+        <f aca="false">H18+C18*INDEX(Assumptions!$C$28:$C$33,MATCH(Pinellas!$D$6,Assumptions!$B$28:$B$33,0))/12+(INDEX(Assumptions!$D$28:$D$33,MATCH(Pinellas!$D$6,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(Pinellas!$M$6,Assumptions!$B$22:$B$25,0)))/12+Pinellas!$O$6</f>
         <v>3878.08288537106</v>
       </c>
       <c r="J18" s="29" t="n">
@@ -8977,23 +9010,23 @@
         <f aca="false">IFERROR(E18*Assumptions!$C$18/12/I18,0)</f>
         <v>1.22053433958012</v>
       </c>
-      <c r="L18" s="27" t="n">
+      <c r="L18" s="21" t="n">
         <f aca="false">C18*B18+C18*(Assumptions!$C$16-D18)</f>
         <v>140650</v>
       </c>
-      <c r="M18" s="27" t="n">
+      <c r="M18" s="21" t="n">
         <f aca="false">E18-(E18*INDEX(Assumptions!$H$36:$H$37,MATCH(Pinellas!$P$6,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(Pinellas!$N$6="Y",Assumptions!$C$41,Assumptions!$C$42))-I18*12</f>
         <v>-7966.99462445278</v>
       </c>
-      <c r="N18" s="27" t="n">
+      <c r="N18" s="21" t="n">
         <f aca="false">M18-E18*INDEX(Assumptions!$C$36:$C$37,MATCH(Pinellas!$P$6,Assumptions!$B$36:$B$37,0))</f>
         <v>-22166.9946244528</v>
       </c>
-      <c r="O18" s="21" t="n">
+      <c r="O18" s="22" t="n">
         <f aca="false">IFERROR(M18/L18,0)</f>
         <v>-0.0566441139314097</v>
       </c>
-      <c r="P18" s="21" t="n">
+      <c r="P18" s="22" t="n">
         <f aca="false">IFERROR((M18-M17)/(L18-L17),0)</f>
         <v>0.114574552320191</v>
       </c>
@@ -9010,7 +9043,7 @@
         <f aca="false">Pinellas!$H$6</f>
         <v>485000</v>
       </c>
-      <c r="D19" s="26" t="n">
+      <c r="D19" s="27" t="n">
         <f aca="false">Pinellas!$I$6</f>
         <v>0</v>
       </c>
@@ -9018,7 +9051,7 @@
         <f aca="false">Pinellas!$K$6</f>
         <v>71000</v>
       </c>
-      <c r="F19" s="27" t="n">
+      <c r="F19" s="21" t="n">
         <f aca="false">C19*(1-B19)</f>
         <v>339500</v>
       </c>
@@ -9026,12 +9059,12 @@
         <f aca="false">IF((1-B19)&gt;0.75,Assumptions!$C$11,IF((1-B19)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.07125</v>
       </c>
-      <c r="H19" s="27" t="n">
+      <c r="H19" s="21" t="n">
         <f aca="false">PMT(G19/12,Assumptions!$C$14,-F19)</f>
         <v>2287.27438660735</v>
       </c>
-      <c r="I19" s="27" t="n">
-        <f aca="false">H19+C19*INDEX(Assumptions!$C$28:$C$33,MATCH(Pinellas!$D$6,Assumptions!$B$28:$B$33,0))/12+(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH(Pinellas!$M$6,Assumptions!$B$22:$B$25,0)))/12+Pinellas!$O$6</f>
+      <c r="I19" s="21" t="n">
+        <f aca="false">H19+C19*INDEX(Assumptions!$C$28:$C$33,MATCH(Pinellas!$D$6,Assumptions!$B$28:$B$33,0))/12+(INDEX(Assumptions!$D$28:$D$33,MATCH(Pinellas!$D$6,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(Pinellas!$M$6,Assumptions!$B$22:$B$25,0)))/12+Pinellas!$O$6</f>
         <v>3683.94105327402</v>
       </c>
       <c r="J19" s="29" t="n">
@@ -9042,23 +9075,23 @@
         <f aca="false">IFERROR(E19*Assumptions!$C$18/12/I19,0)</f>
         <v>1.28485588256812</v>
       </c>
-      <c r="L19" s="27" t="n">
+      <c r="L19" s="21" t="n">
         <f aca="false">C19*B19+C19*(Assumptions!$C$16-D19)</f>
         <v>164900</v>
       </c>
-      <c r="M19" s="27" t="n">
+      <c r="M19" s="21" t="n">
         <f aca="false">E19-(E19*INDEX(Assumptions!$H$36:$H$37,MATCH(Pinellas!$P$6,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(Pinellas!$N$6="Y",Assumptions!$C$41,Assumptions!$C$42))-I19*12</f>
         <v>-5637.29263928819</v>
       </c>
-      <c r="N19" s="27" t="n">
+      <c r="N19" s="21" t="n">
         <f aca="false">M19-E19*INDEX(Assumptions!$C$36:$C$37,MATCH(Pinellas!$P$6,Assumptions!$B$36:$B$37,0))</f>
         <v>-19837.2926392882</v>
       </c>
-      <c r="O19" s="21" t="n">
+      <c r="O19" s="22" t="n">
         <f aca="false">IFERROR(M19/L19,0)</f>
         <v>-0.03418612880102</v>
       </c>
-      <c r="P19" s="21" t="n">
+      <c r="P19" s="22" t="n">
         <f aca="false">IFERROR((M19-M18)/(L19-L18),0)</f>
         <v>0.0960701849552405</v>
       </c>
@@ -9075,7 +9108,7 @@
         <f aca="false">Pinellas!$H$7</f>
         <v>485000</v>
       </c>
-      <c r="D21" s="26" t="n">
+      <c r="D21" s="27" t="n">
         <f aca="false">Pinellas!$I$7</f>
         <v>0</v>
       </c>
@@ -9083,7 +9116,7 @@
         <f aca="false">Pinellas!$K$7</f>
         <v>85000</v>
       </c>
-      <c r="F21" s="27" t="n">
+      <c r="F21" s="21" t="n">
         <f aca="false">C21*(1-B21)</f>
         <v>388000</v>
       </c>
@@ -9091,12 +9124,12 @@
         <f aca="false">IF((1-B21)&gt;0.75,Assumptions!$C$11,IF((1-B21)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.075</v>
       </c>
-      <c r="H21" s="27" t="n">
+      <c r="H21" s="21" t="n">
         <f aca="false">PMT(G21/12,Assumptions!$C$14,-F21)</f>
         <v>2712.95229318478</v>
       </c>
-      <c r="I21" s="27" t="n">
-        <f aca="false">H21+C21*INDEX(Assumptions!$C$28:$C$33,MATCH(Pinellas!$D$7,Assumptions!$B$28:$B$33,0))/12+(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH(Pinellas!$M$7,Assumptions!$B$22:$B$25,0)))/12+Pinellas!$O$7</f>
+      <c r="I21" s="21" t="n">
+        <f aca="false">H21+C21*INDEX(Assumptions!$C$28:$C$33,MATCH(Pinellas!$D$7,Assumptions!$B$28:$B$33,0))/12+(INDEX(Assumptions!$D$28:$D$33,MATCH(Pinellas!$D$7,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(Pinellas!$M$7,Assumptions!$B$22:$B$25,0)))/12+Pinellas!$O$7</f>
         <v>4109.61895985145</v>
       </c>
       <c r="J21" s="29" t="n">
@@ -9107,24 +9140,24 @@
         <f aca="false">IFERROR(E21*Assumptions!$C$18/12/I21,0)</f>
         <v>1.378878850333</v>
       </c>
-      <c r="L21" s="27" t="n">
+      <c r="L21" s="21" t="n">
         <f aca="false">C21*B21+C21*(Assumptions!$C$16-D21)</f>
         <v>116400</v>
       </c>
-      <c r="M21" s="27" t="n">
+      <c r="M21" s="21" t="n">
         <f aca="false">E21-(E21*INDEX(Assumptions!$H$36:$H$37,MATCH(Pinellas!$P$7,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(Pinellas!$N$7="Y",Assumptions!$C$41,Assumptions!$C$42))-I21*12</f>
         <v>-1365.4275182174</v>
       </c>
-      <c r="N21" s="27" t="n">
+      <c r="N21" s="21" t="n">
         <f aca="false">M21-E21*INDEX(Assumptions!$C$36:$C$37,MATCH(Pinellas!$P$7,Assumptions!$B$36:$B$37,0))</f>
         <v>-18365.4275182174</v>
       </c>
-      <c r="O21" s="21" t="n">
+      <c r="O21" s="22" t="n">
         <f aca="false">IFERROR(M21/L21,0)</f>
         <v>-0.0117304769606306</v>
       </c>
       <c r="P21" s="46" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9139,7 +9172,7 @@
         <f aca="false">Pinellas!$H$7</f>
         <v>485000</v>
       </c>
-      <c r="D22" s="26" t="n">
+      <c r="D22" s="27" t="n">
         <f aca="false">Pinellas!$I$7</f>
         <v>0</v>
       </c>
@@ -9147,7 +9180,7 @@
         <f aca="false">Pinellas!$K$7</f>
         <v>85000</v>
       </c>
-      <c r="F22" s="27" t="n">
+      <c r="F22" s="21" t="n">
         <f aca="false">C22*(1-B22)</f>
         <v>363750</v>
       </c>
@@ -9155,12 +9188,12 @@
         <f aca="false">IF((1-B22)&gt;0.75,Assumptions!$C$11,IF((1-B22)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="H22" s="27" t="n">
+      <c r="H22" s="21" t="n">
         <f aca="false">PMT(G22/12,Assumptions!$C$14,-F22)</f>
         <v>2481.4162187044</v>
       </c>
-      <c r="I22" s="27" t="n">
-        <f aca="false">H22+C22*INDEX(Assumptions!$C$28:$C$33,MATCH(Pinellas!$D$7,Assumptions!$B$28:$B$33,0))/12+(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH(Pinellas!$M$7,Assumptions!$B$22:$B$25,0)))/12+Pinellas!$O$7</f>
+      <c r="I22" s="21" t="n">
+        <f aca="false">H22+C22*INDEX(Assumptions!$C$28:$C$33,MATCH(Pinellas!$D$7,Assumptions!$B$28:$B$33,0))/12+(INDEX(Assumptions!$D$28:$D$33,MATCH(Pinellas!$D$7,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(Pinellas!$M$7,Assumptions!$B$22:$B$25,0)))/12+Pinellas!$O$7</f>
         <v>3878.08288537106</v>
       </c>
       <c r="J22" s="29" t="n">
@@ -9171,23 +9204,23 @@
         <f aca="false">IFERROR(E22*Assumptions!$C$18/12/I22,0)</f>
         <v>1.46120308259592</v>
       </c>
-      <c r="L22" s="27" t="n">
+      <c r="L22" s="21" t="n">
         <f aca="false">C22*B22+C22*(Assumptions!$C$16-D22)</f>
         <v>140650</v>
       </c>
-      <c r="M22" s="27" t="n">
+      <c r="M22" s="21" t="n">
         <f aca="false">E22-(E22*INDEX(Assumptions!$H$36:$H$37,MATCH(Pinellas!$P$7,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(Pinellas!$N$7="Y",Assumptions!$C$41,Assumptions!$C$42))-I22*12</f>
         <v>1413.00537554723</v>
       </c>
-      <c r="N22" s="27" t="n">
+      <c r="N22" s="21" t="n">
         <f aca="false">M22-E22*INDEX(Assumptions!$C$36:$C$37,MATCH(Pinellas!$P$7,Assumptions!$B$36:$B$37,0))</f>
         <v>-15586.9946244528</v>
       </c>
-      <c r="O22" s="21" t="n">
+      <c r="O22" s="22" t="n">
         <f aca="false">IFERROR(M22/L22,0)</f>
         <v>0.0100462522257179</v>
       </c>
-      <c r="P22" s="21" t="n">
+      <c r="P22" s="22" t="n">
         <f aca="false">IFERROR((M22-M21)/(L22-L21),0)</f>
         <v>0.114574552320191</v>
       </c>
@@ -9204,7 +9237,7 @@
         <f aca="false">Pinellas!$H$7</f>
         <v>485000</v>
       </c>
-      <c r="D23" s="26" t="n">
+      <c r="D23" s="27" t="n">
         <f aca="false">Pinellas!$I$7</f>
         <v>0</v>
       </c>
@@ -9212,7 +9245,7 @@
         <f aca="false">Pinellas!$K$7</f>
         <v>85000</v>
       </c>
-      <c r="F23" s="27" t="n">
+      <c r="F23" s="21" t="n">
         <f aca="false">C23*(1-B23)</f>
         <v>339500</v>
       </c>
@@ -9220,12 +9253,12 @@
         <f aca="false">IF((1-B23)&gt;0.75,Assumptions!$C$11,IF((1-B23)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.07125</v>
       </c>
-      <c r="H23" s="27" t="n">
+      <c r="H23" s="21" t="n">
         <f aca="false">PMT(G23/12,Assumptions!$C$14,-F23)</f>
         <v>2287.27438660735</v>
       </c>
-      <c r="I23" s="27" t="n">
-        <f aca="false">H23+C23*INDEX(Assumptions!$C$28:$C$33,MATCH(Pinellas!$D$7,Assumptions!$B$28:$B$33,0))/12+(Assumptions!$C$19+INDEX(Assumptions!$C$22:$C$25,MATCH(Pinellas!$M$7,Assumptions!$B$22:$B$25,0)))/12+Pinellas!$O$7</f>
+      <c r="I23" s="21" t="n">
+        <f aca="false">H23+C23*INDEX(Assumptions!$C$28:$C$33,MATCH(Pinellas!$D$7,Assumptions!$B$28:$B$33,0))/12+(INDEX(Assumptions!$D$28:$D$33,MATCH(Pinellas!$D$7,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(Pinellas!$M$7,Assumptions!$B$22:$B$25,0)))/12+Pinellas!$O$7</f>
         <v>3683.94105327402</v>
       </c>
       <c r="J23" s="29" t="n">
@@ -9236,23 +9269,23 @@
         <f aca="false">IFERROR(E23*Assumptions!$C$18/12/I23,0)</f>
         <v>1.53820774673649</v>
       </c>
-      <c r="L23" s="27" t="n">
+      <c r="L23" s="21" t="n">
         <f aca="false">C23*B23+C23*(Assumptions!$C$16-D23)</f>
         <v>164900</v>
       </c>
-      <c r="M23" s="27" t="n">
+      <c r="M23" s="21" t="n">
         <f aca="false">E23-(E23*INDEX(Assumptions!$H$36:$H$37,MATCH(Pinellas!$P$7,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(Pinellas!$N$7="Y",Assumptions!$C$41,Assumptions!$C$42))-I23*12</f>
         <v>3742.70736071181</v>
       </c>
-      <c r="N23" s="27" t="n">
+      <c r="N23" s="21" t="n">
         <f aca="false">M23-E23*INDEX(Assumptions!$C$36:$C$37,MATCH(Pinellas!$P$7,Assumptions!$B$36:$B$37,0))</f>
         <v>-13257.2926392882</v>
       </c>
-      <c r="O23" s="21" t="n">
+      <c r="O23" s="22" t="n">
         <f aca="false">IFERROR(M23/L23,0)</f>
         <v>0.0226968305682948</v>
       </c>
-      <c r="P23" s="21" t="n">
+      <c r="P23" s="22" t="n">
         <f aca="false">IFERROR((M23-M22)/(L23-L22),0)</f>
         <v>0.0960701849552405</v>
       </c>
@@ -9290,76 +9323,76 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="n">
+      <c r="A5" s="25" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9367,191 +9400,191 @@
         <v>2</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D6" s="47" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E6" s="47" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F6" s="47" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="G6" s="47" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H6" s="47" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I6" s="47" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="J6" s="47" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="47" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D8" s="47" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E8" s="47" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F8" s="47" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G8" s="47" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="H8" s="47" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="I8" s="47" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="J8" s="47" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="n">
+      <c r="A9" s="25" t="n">
         <v>3</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="47" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B10" s="47" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D10" s="47" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="E10" s="47" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F10" s="47" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="G10" s="47" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H10" s="47" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="I10" s="47" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="J10" s="47" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="24" t="n">
+      <c r="A11" s="25" t="n">
         <v>4</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9559,63 +9592,63 @@
         <v>5</v>
       </c>
       <c r="B12" s="47" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D12" s="47" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E12" s="47" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F12" s="47" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="G12" s="47" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="H12" s="47" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="I12" s="47" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="J12" s="47" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="24" t="n">
+      <c r="A13" s="25" t="n">
         <v>6</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9623,63 +9656,63 @@
         <v>7</v>
       </c>
       <c r="B14" s="47" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D14" s="47" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E14" s="47" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F14" s="47" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="G14" s="47" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="H14" s="47" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="I14" s="47" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="J14" s="47" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="24" t="n">
+      <c r="A15" s="25" t="n">
         <v>8</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C15" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="J15" s="9" t="s">
         <v>451</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>452</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>453</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>455</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>456</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>457</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9687,63 +9720,63 @@
         <v>9</v>
       </c>
       <c r="B16" s="47" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D16" s="47" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E16" s="47" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F16" s="47" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="G16" s="47" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="H16" s="47" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="I16" s="47" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="J16" s="47" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="24" t="n">
+      <c r="A17" s="25" t="n">
         <v>10</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C17" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="J17" s="9" t="s">
         <v>467</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>436</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>468</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>469</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>470</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>471</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9751,63 +9784,63 @@
         <v>11</v>
       </c>
       <c r="B18" s="47" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C18" s="47" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D18" s="47" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E18" s="47" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="F18" s="47" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="G18" s="47" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="H18" s="47" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="I18" s="47" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="J18" s="47" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="24" t="n">
+      <c r="A19" s="25" t="n">
         <v>12</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9815,63 +9848,63 @@
         <v>13</v>
       </c>
       <c r="B20" s="47" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C20" s="47" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="D20" s="47" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E20" s="47" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F20" s="47" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="G20" s="47" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="H20" s="47" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="I20" s="47" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="J20" s="47" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
   </sheetData>
@@ -9904,288 +9937,288 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="47" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D6" s="47" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E6" s="47" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="F6" s="47" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="G6" s="47" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="47" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D8" s="47" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E8" s="47" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="F8" s="47" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="G8" s="47" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="47" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B10" s="47" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D10" s="47" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E10" s="47" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="F10" s="47" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="G10" s="47" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="47" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B12" s="47" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D12" s="47" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E12" s="47" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F12" s="47" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="G12" s="47" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="47" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B14" s="47" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D14" s="47" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="E14" s="47" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F14" s="47" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="G14" s="47" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10193,22 +10226,22 @@
         <v>18</v>
       </c>
       <c r="B16" s="47" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D16" s="47" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E16" s="47" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="F16" s="47" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="G16" s="47" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10216,22 +10249,22 @@
         <v>18</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10239,22 +10272,22 @@
         <v>18</v>
       </c>
       <c r="B18" s="47" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C18" s="47" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D18" s="47" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E18" s="47" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="F18" s="47" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="G18" s="47" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10262,22 +10295,22 @@
         <v>18</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10285,22 +10318,22 @@
         <v>18</v>
       </c>
       <c r="B20" s="47" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C20" s="47" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="D20" s="47" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E20" s="47" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F20" s="47" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="G20" s="47" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10308,22 +10341,22 @@
         <v>18</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10331,22 +10364,22 @@
         <v>18</v>
       </c>
       <c r="B22" s="47" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C22" s="47" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="D22" s="47" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E22" s="47" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F22" s="47" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="G22" s="47" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10354,22 +10387,22 @@
         <v>18</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10377,22 +10410,22 @@
         <v>18</v>
       </c>
       <c r="B24" s="47" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C24" s="47" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D24" s="47" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="E24" s="47" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="F24" s="47" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="G24" s="47" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10400,22 +10433,22 @@
         <v>18</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10423,206 +10456,206 @@
         <v>18</v>
       </c>
       <c r="B26" s="47" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C26" s="47" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="D26" s="47" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E26" s="47" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="F26" s="47" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="G26" s="47" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="47" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B28" s="47" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C28" s="47" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D28" s="47" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="E28" s="47" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F28" s="47" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="G28" s="47" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="47" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B30" s="47" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C30" s="47" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="D30" s="47" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E30" s="47" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F30" s="47" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="G30" s="47" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="47" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B32" s="47" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C32" s="47" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D32" s="47" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="E32" s="47" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="F32" s="47" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="G32" s="47" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="47" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B34" s="47" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C34" s="47" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="D34" s="47" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E34" s="47" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F34" s="47" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="G34" s="47" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
   </sheetData>
@@ -10651,34 +10684,34 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="n">
+      <c r="A5" s="25" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10686,21 +10719,21 @@
         <v>2</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24" t="n">
+      <c r="A7" s="25" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10708,21 +10741,21 @@
         <v>4</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="n">
+      <c r="A9" s="25" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10730,21 +10763,21 @@
         <v>6</v>
       </c>
       <c r="B10" s="47" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="24" t="n">
+      <c r="A11" s="25" t="n">
         <v>7</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10752,21 +10785,21 @@
         <v>8</v>
       </c>
       <c r="B12" s="47" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="24" t="n">
+      <c r="A13" s="25" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10774,10 +10807,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="47" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
   </sheetData>

--- a/str-deal-search/STR_DSCR_Analysis.xlsx
+++ b/str-deal-search/STR_DSCR_Analysis.xlsx
@@ -133,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="708">
   <si>
     <t xml:space="preserve">STR DSCR Search: Summary of Top Picks</t>
   </si>
@@ -447,7 +447,7 @@
     <t xml:space="preserve">Active as of 2026-10-18. Screened ~600 listings across Zillow (14 keyword sweeps), Redfin, brokerages and STR marketplaces. Yellow rows = recommended.</t>
   </si>
   <si>
-    <t xml:space="preserve">Edit blue cells (Offer Price, Seller Credit %, Down Pmt %, Income, Flood Zone) to rerun. Qualify on DSCR (lender haircut) &gt;= 1.00; &gt;= 1.15 preferred. Income is seller-stated until verified with platform payout reports.</t>
+    <t xml:space="preserve">Edit blue cells (Offer Price, Seller Credit %, Down Pmt %, Income, Flood Zone, Ins Override) to rerun. Ins Override (blank = county base + flood) is for condos with master wind/flood policies. Qualify on DSCR (lender haircut) &gt;= 1.00; &gt;= 1.15 preferred. Income is seller-stated until verified with platform payout reports.</t>
   </si>
   <si>
     <t xml:space="preserve">Rank</t>
@@ -484,6 +484,9 @@
   </si>
   <si>
     <t xml:space="preserve">HOA ($/mo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ins Override ($/yr)</t>
   </si>
   <si>
     <t xml:space="preserve">Profile</t>
@@ -2970,27 +2973,27 @@
         <v>85000</v>
       </c>
       <c r="F5" s="6" t="n">
-        <f aca="false">'Manatee-Sarasota'!$V$6</f>
+        <f aca="false">'Manatee-Sarasota'!$W$6</f>
         <v>4315.14037623601</v>
       </c>
       <c r="G5" s="7" t="n">
-        <f aca="false">'Manatee-Sarasota'!$W$6</f>
+        <f aca="false">'Manatee-Sarasota'!$X$6</f>
         <v>1.64150704629265</v>
       </c>
       <c r="H5" s="7" t="n">
-        <f aca="false">'Manatee-Sarasota'!$X$6</f>
+        <f aca="false">'Manatee-Sarasota'!$Y$6</f>
         <v>1.31320563703412</v>
       </c>
       <c r="I5" s="6" t="n">
-        <f aca="false">'Manatee-Sarasota'!$Y$6</f>
+        <f aca="false">'Manatee-Sarasota'!$Z$6</f>
         <v>145600</v>
       </c>
       <c r="J5" s="6" t="n">
-        <f aca="false">'Manatee-Sarasota'!$AC$6</f>
+        <f aca="false">'Manatee-Sarasota'!$AD$6</f>
         <v>-3831.68451483207</v>
       </c>
       <c r="K5" s="6" t="n">
-        <f aca="false">'Manatee-Sarasota'!$AD$6</f>
+        <f aca="false">'Manatee-Sarasota'!$AE$6</f>
         <v>-20831.6845148321</v>
       </c>
       <c r="L5" s="8" t="s">
@@ -3018,27 +3021,27 @@
         <v>73000</v>
       </c>
       <c r="F6" s="6" t="n">
-        <f aca="false">'Manatee-Sarasota'!$V$7</f>
+        <f aca="false">'Manatee-Sarasota'!$W$7</f>
         <v>3678.50816619386</v>
       </c>
       <c r="G6" s="7" t="n">
-        <f aca="false">'Manatee-Sarasota'!$W$7</f>
+        <f aca="false">'Manatee-Sarasota'!$X$7</f>
         <v>1.65375012328102</v>
       </c>
       <c r="H6" s="7" t="n">
-        <f aca="false">'Manatee-Sarasota'!$X$7</f>
+        <f aca="false">'Manatee-Sarasota'!$Y$7</f>
         <v>1.32300009862482</v>
       </c>
       <c r="I6" s="6" t="n">
-        <f aca="false">'Manatee-Sarasota'!$Y$7</f>
+        <f aca="false">'Manatee-Sarasota'!$Z$7</f>
         <v>133400</v>
       </c>
       <c r="J6" s="6" t="n">
-        <f aca="false">'Manatee-Sarasota'!$AC$7</f>
+        <f aca="false">'Manatee-Sarasota'!$AD$7</f>
         <v>-2432.09799432634</v>
       </c>
       <c r="K6" s="6" t="n">
-        <f aca="false">'Manatee-Sarasota'!$AD$7</f>
+        <f aca="false">'Manatee-Sarasota'!$AE$7</f>
         <v>-17032.0979943263</v>
       </c>
       <c r="L6" s="9" t="s">
@@ -3066,27 +3069,27 @@
         <v>89000</v>
       </c>
       <c r="F7" s="6" t="n">
-        <f aca="false">'Manatee-Sarasota'!$V$8</f>
+        <f aca="false">'Manatee-Sarasota'!$W$8</f>
         <v>4569.79326025286</v>
       </c>
       <c r="G7" s="7" t="n">
-        <f aca="false">'Manatee-Sarasota'!$W$8</f>
+        <f aca="false">'Manatee-Sarasota'!$X$8</f>
         <v>1.62297641146599</v>
       </c>
       <c r="H7" s="7" t="n">
-        <f aca="false">'Manatee-Sarasota'!$X$8</f>
+        <f aca="false">'Manatee-Sarasota'!$Y$8</f>
         <v>1.29838112917279</v>
       </c>
       <c r="I7" s="6" t="n">
-        <f aca="false">'Manatee-Sarasota'!$Y$8</f>
+        <f aca="false">'Manatee-Sarasota'!$Z$8</f>
         <v>156000</v>
       </c>
       <c r="J7" s="6" t="n">
-        <f aca="false">'Manatee-Sarasota'!$AC$8</f>
+        <f aca="false">'Manatee-Sarasota'!$AD$8</f>
         <v>-4207.51912303436</v>
       </c>
       <c r="K7" s="6" t="n">
-        <f aca="false">'Manatee-Sarasota'!$AD$8</f>
+        <f aca="false">'Manatee-Sarasota'!$AE$8</f>
         <v>-22007.5191230344</v>
       </c>
       <c r="L7" s="9" t="s">
@@ -3114,27 +3117,27 @@
         <v>71000</v>
       </c>
       <c r="F8" s="6" t="n">
-        <f aca="false">Pinellas!$V$6</f>
+        <f aca="false">Pinellas!$W$6</f>
         <v>3878.08288537106</v>
       </c>
       <c r="G8" s="7" t="n">
-        <f aca="false">Pinellas!$W$6</f>
+        <f aca="false">Pinellas!$X$6</f>
         <v>1.52566792447515</v>
       </c>
       <c r="H8" s="7" t="n">
-        <f aca="false">Pinellas!$X$6</f>
+        <f aca="false">Pinellas!$Y$6</f>
         <v>1.22053433958012</v>
       </c>
       <c r="I8" s="6" t="n">
-        <f aca="false">Pinellas!$Y$6</f>
+        <f aca="false">Pinellas!$Z$6</f>
         <v>140650</v>
       </c>
       <c r="J8" s="6" t="n">
-        <f aca="false">Pinellas!$AC$6</f>
+        <f aca="false">Pinellas!$AD$6</f>
         <v>-7966.99462445278</v>
       </c>
       <c r="K8" s="6" t="n">
-        <f aca="false">Pinellas!$AD$6</f>
+        <f aca="false">Pinellas!$AE$6</f>
         <v>-22166.9946244528</v>
       </c>
       <c r="L8" s="9" t="s">
@@ -3162,27 +3165,27 @@
         <v>85000</v>
       </c>
       <c r="F9" s="6" t="n">
-        <f aca="false">Pinellas!$V$7</f>
+        <f aca="false">Pinellas!$W$7</f>
         <v>3878.08288537106</v>
       </c>
       <c r="G9" s="7" t="n">
-        <f aca="false">Pinellas!$W$7</f>
+        <f aca="false">Pinellas!$X$7</f>
         <v>1.8265038532449</v>
       </c>
       <c r="H9" s="7" t="n">
-        <f aca="false">Pinellas!$X$7</f>
+        <f aca="false">Pinellas!$Y$7</f>
         <v>1.46120308259592</v>
       </c>
       <c r="I9" s="6" t="n">
-        <f aca="false">Pinellas!$Y$7</f>
+        <f aca="false">Pinellas!$Z$7</f>
         <v>140650</v>
       </c>
       <c r="J9" s="6" t="n">
-        <f aca="false">Pinellas!$AC$7</f>
+        <f aca="false">Pinellas!$AD$7</f>
         <v>1413.00537554723</v>
       </c>
       <c r="K9" s="6" t="n">
-        <f aca="false">Pinellas!$AD$7</f>
+        <f aca="false">Pinellas!$AE$7</f>
         <v>-15586.9946244528</v>
       </c>
       <c r="L9" s="9" t="s">
@@ -3210,27 +3213,27 @@
         <v>51000</v>
       </c>
       <c r="F10" s="6" t="n">
-        <f aca="false">Pinellas!$V$8</f>
+        <f aca="false">Pinellas!$W$8</f>
         <v>2942.88284747662</v>
       </c>
       <c r="G10" s="7" t="n">
-        <f aca="false">Pinellas!$W$8</f>
+        <f aca="false">Pinellas!$X$8</f>
         <v>1.4441621431326</v>
       </c>
       <c r="H10" s="7" t="n">
-        <f aca="false">Pinellas!$X$8</f>
+        <f aca="false">Pinellas!$Y$8</f>
         <v>1.15532971450608</v>
       </c>
       <c r="I10" s="6" t="n">
-        <f aca="false">Pinellas!$Y$8</f>
+        <f aca="false">Pinellas!$Z$8</f>
         <v>98600</v>
       </c>
       <c r="J10" s="6" t="n">
-        <f aca="false">Pinellas!$AC$8</f>
+        <f aca="false">Pinellas!$AD$8</f>
         <v>-8344.59416971947</v>
       </c>
       <c r="K10" s="6" t="n">
-        <f aca="false">Pinellas!$AD$8</f>
+        <f aca="false">Pinellas!$AE$8</f>
         <v>-18544.5941697195</v>
       </c>
       <c r="L10" s="9" t="s">
@@ -3258,27 +3261,27 @@
         <v>60000</v>
       </c>
       <c r="F11" s="6" t="n">
-        <f aca="false">'Other SWFL Listings'!$V$6</f>
+        <f aca="false">'Other SWFL Listings'!$W$6</f>
         <v>3755.17483286053</v>
       </c>
       <c r="G11" s="7" t="n">
-        <f aca="false">'Other SWFL Listings'!$W$6</f>
+        <f aca="false">'Other SWFL Listings'!$X$6</f>
         <v>1.33149592829776</v>
       </c>
       <c r="H11" s="7" t="n">
-        <f aca="false">'Other SWFL Listings'!$X$6</f>
+        <f aca="false">'Other SWFL Listings'!$Y$6</f>
         <v>1.0651967426382</v>
       </c>
       <c r="I11" s="6" t="n">
-        <f aca="false">'Other SWFL Listings'!$Y$6</f>
+        <f aca="false">'Other SWFL Listings'!$Z$6</f>
         <v>133400</v>
       </c>
       <c r="J11" s="6" t="n">
-        <f aca="false">'Other SWFL Listings'!$AC$6</f>
+        <f aca="false">'Other SWFL Listings'!$AD$6</f>
         <v>-13862.0979943264</v>
       </c>
       <c r="K11" s="6" t="n">
-        <f aca="false">'Other SWFL Listings'!$AD$6</f>
+        <f aca="false">'Other SWFL Listings'!$AE$6</f>
         <v>-25862.0979943264</v>
       </c>
       <c r="L11" s="9" t="s">
@@ -3420,232 +3423,232 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="47" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="47" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="47" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B10" s="47" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="47" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B12" s="47" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="47" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B14" s="47" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="47" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B16" s="47" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="47" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B18" s="47" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="47" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B20" s="47" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C20" s="32" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C21" s="32" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="47" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B22" s="47" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C22" s="32" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C23" s="32" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -4164,7 +4167,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AJ28"/>
+  <dimension ref="A1:AK28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -4180,24 +4183,26 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="19" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="31" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="20" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="32" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4264,7 +4269,7 @@
       <c r="P5" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="Q5" s="23" t="s">
+      <c r="Q5" s="3" t="s">
         <v>118</v>
       </c>
       <c r="R5" s="23" t="s">
@@ -4280,19 +4285,19 @@
         <v>122</v>
       </c>
       <c r="V5" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="W5" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="W5" s="23" t="s">
+      <c r="X5" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="X5" s="23" t="s">
+      <c r="Y5" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="Y5" s="23" t="s">
+      <c r="Z5" s="23" t="s">
         <v>10</v>
-      </c>
-      <c r="Z5" s="23" t="s">
-        <v>123</v>
       </c>
       <c r="AA5" s="23" t="s">
         <v>124</v>
@@ -4301,18 +4306,18 @@
         <v>125</v>
       </c>
       <c r="AC5" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="AD5" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="AD5" s="23" t="s">
+      <c r="AE5" s="23" t="s">
         <v>12</v>
-      </c>
-      <c r="AE5" s="23" t="s">
-        <v>126</v>
       </c>
       <c r="AF5" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="AG5" s="3" t="s">
+      <c r="AG5" s="23" t="s">
         <v>128</v>
       </c>
       <c r="AH5" s="3" t="s">
@@ -4323,6 +4328,9 @@
       </c>
       <c r="AJ5" s="3" t="s">
         <v>131</v>
+      </c>
+      <c r="AK5" s="3" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4330,19 +4338,19 @@
         <v>1</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D6" s="26" t="s">
         <v>75</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G6" s="19" t="n">
         <v>584900</v>
@@ -4361,95 +4369,96 @@
         <v>85000</v>
       </c>
       <c r="L6" s="25" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M6" s="26" t="s">
         <v>70</v>
       </c>
       <c r="N6" s="26" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O6" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="P6" s="26" t="s">
+      <c r="P6" s="19"/>
+      <c r="Q6" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="Q6" s="21" t="n">
+      <c r="R6" s="21" t="n">
         <f aca="false">H6*(1-J6)</f>
         <v>420000</v>
       </c>
-      <c r="R6" s="28" t="n">
+      <c r="S6" s="28" t="n">
         <f aca="false">IF((1-J6)&gt;0.75,Assumptions!$C$11,IF((1-J6)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S6" s="21" t="n">
-        <f aca="false">PMT(R6/12,Assumptions!$C$14,-Q6)</f>
+      <c r="T6" s="21" t="n">
+        <f aca="false">PMT(S6/12,Assumptions!$C$14,-R6)</f>
         <v>2865.14037623601</v>
       </c>
-      <c r="T6" s="21" t="n">
+      <c r="U6" s="21" t="n">
         <f aca="false">H6*INDEX(Assumptions!$C$28:$C$33,MATCH(D6,Assumptions!$B$28:$B$33,0))/12</f>
         <v>700</v>
       </c>
-      <c r="U6" s="21" t="n">
-        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D6,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M6,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="V6" s="21" t="n">
+        <f aca="false">IF(ISNUMBER(P6),P6,INDEX(Assumptions!$D$28:$D$33,MATCH(D6,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M6,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>750</v>
       </c>
-      <c r="V6" s="21" t="n">
-        <f aca="false">S6+T6+U6+O6</f>
+      <c r="W6" s="21" t="n">
+        <f aca="false">T6+U6+V6+O6</f>
         <v>4315.14037623601</v>
       </c>
-      <c r="W6" s="29" t="n">
-        <f aca="false">IFERROR(K6/12/V6,0)</f>
+      <c r="X6" s="29" t="n">
+        <f aca="false">IFERROR(K6/12/W6,0)</f>
         <v>1.64150704629265</v>
       </c>
-      <c r="X6" s="30" t="n">
-        <f aca="false">IFERROR(K6*Assumptions!$C$18/12/V6,0)</f>
+      <c r="Y6" s="30" t="n">
+        <f aca="false">IFERROR(K6*Assumptions!$C$18/12/W6,0)</f>
         <v>1.31320563703412</v>
       </c>
-      <c r="Y6" s="31" t="n">
+      <c r="Z6" s="31" t="n">
         <f aca="false">H6*J6+H6*(Assumptions!$C$16-I6)</f>
         <v>145600</v>
       </c>
-      <c r="Z6" s="21" t="n">
-        <f aca="false">V6*Assumptions!$C$17</f>
+      <c r="AA6" s="21" t="n">
+        <f aca="false">W6*Assumptions!$C$17</f>
         <v>25890.842257416</v>
       </c>
-      <c r="AA6" s="21" t="n">
-        <f aca="false">K6*INDEX(Assumptions!$H$36:$H$37,MATCH(P6,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N6="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
+      <c r="AB6" s="21" t="n">
+        <f aca="false">K6*INDEX(Assumptions!$H$36:$H$37,MATCH(Q6,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N6="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>37050</v>
       </c>
-      <c r="AB6" s="21" t="n">
-        <f aca="false">K6*INDEX(Assumptions!$C$36:$C$37,MATCH(P6,Assumptions!$B$36:$B$37,0))</f>
+      <c r="AC6" s="21" t="n">
+        <f aca="false">K6*INDEX(Assumptions!$C$36:$C$37,MATCH(Q6,Assumptions!$B$36:$B$37,0))</f>
         <v>17000</v>
       </c>
-      <c r="AC6" s="21" t="n">
-        <f aca="false">K6-AA6-V6*12</f>
+      <c r="AD6" s="21" t="n">
+        <f aca="false">K6-AB6-W6*12</f>
         <v>-3831.68451483207</v>
       </c>
-      <c r="AD6" s="21" t="n">
-        <f aca="false">AC6-AB6</f>
+      <c r="AE6" s="21" t="n">
+        <f aca="false">AD6-AC6</f>
         <v>-20831.6845148321</v>
       </c>
-      <c r="AE6" s="22" t="n">
+      <c r="AF6" s="22" t="n">
         <f aca="false">IFERROR(K6/H6,0)</f>
         <v>0.151785714285714</v>
       </c>
-      <c r="AF6" s="22" t="n">
-        <f aca="false">IFERROR((K6-AA6-AB6)/H6,0)</f>
+      <c r="AG6" s="22" t="n">
+        <f aca="false">IFERROR((K6-AB6-AC6)/H6,0)</f>
         <v>0.0552678571428571</v>
       </c>
-      <c r="AG6" s="25" t="s">
-        <v>138</v>
-      </c>
-      <c r="AH6" s="13" t="n">
+      <c r="AH6" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="AI6" s="13" t="n">
         <v>21</v>
       </c>
-      <c r="AI6" s="25" t="s">
-        <v>139</v>
-      </c>
-      <c r="AJ6" s="32" t="s">
+      <c r="AJ6" s="25" t="s">
         <v>140</v>
+      </c>
+      <c r="AK6" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4457,19 +4466,19 @@
         <v>2</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D7" s="35" t="s">
         <v>75</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F7" s="34" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G7" s="36" t="n">
         <v>475000</v>
@@ -4488,95 +4497,96 @@
         <v>73000</v>
       </c>
       <c r="L7" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M7" s="35" t="s">
         <v>70</v>
       </c>
       <c r="N7" s="35" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O7" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="P7" s="35" t="s">
+      <c r="P7" s="36"/>
+      <c r="Q7" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="Q7" s="39" t="n">
+      <c r="R7" s="39" t="n">
         <f aca="false">H7*(1-J7)</f>
         <v>345000</v>
       </c>
-      <c r="R7" s="40" t="n">
+      <c r="S7" s="40" t="n">
         <f aca="false">IF((1-J7)&gt;0.75,Assumptions!$C$11,IF((1-J7)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S7" s="39" t="n">
-        <f aca="false">PMT(R7/12,Assumptions!$C$14,-Q7)</f>
+      <c r="T7" s="39" t="n">
+        <f aca="false">PMT(S7/12,Assumptions!$C$14,-R7)</f>
         <v>2353.50816619386</v>
       </c>
-      <c r="T7" s="39" t="n">
+      <c r="U7" s="39" t="n">
         <f aca="false">H7*INDEX(Assumptions!$C$28:$C$33,MATCH(D7,Assumptions!$B$28:$B$33,0))/12</f>
         <v>575</v>
       </c>
-      <c r="U7" s="39" t="n">
-        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D7,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M7,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="V7" s="39" t="n">
+        <f aca="false">IF(ISNUMBER(P7),P7,INDEX(Assumptions!$D$28:$D$33,MATCH(D7,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M7,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>750</v>
       </c>
-      <c r="V7" s="39" t="n">
-        <f aca="false">S7+T7+U7+O7</f>
+      <c r="W7" s="39" t="n">
+        <f aca="false">T7+U7+V7+O7</f>
         <v>3678.50816619386</v>
       </c>
-      <c r="W7" s="41" t="n">
-        <f aca="false">IFERROR(K7/12/V7,0)</f>
+      <c r="X7" s="41" t="n">
+        <f aca="false">IFERROR(K7/12/W7,0)</f>
         <v>1.65375012328102</v>
       </c>
-      <c r="X7" s="30" t="n">
-        <f aca="false">IFERROR(K7*Assumptions!$C$18/12/V7,0)</f>
+      <c r="Y7" s="30" t="n">
+        <f aca="false">IFERROR(K7*Assumptions!$C$18/12/W7,0)</f>
         <v>1.32300009862482</v>
       </c>
-      <c r="Y7" s="31" t="n">
+      <c r="Z7" s="31" t="n">
         <f aca="false">H7*J7+H7*(Assumptions!$C$16-I7)</f>
         <v>133400</v>
       </c>
-      <c r="Z7" s="39" t="n">
-        <f aca="false">V7*Assumptions!$C$17</f>
+      <c r="AA7" s="39" t="n">
+        <f aca="false">W7*Assumptions!$C$17</f>
         <v>22071.0489971632</v>
       </c>
-      <c r="AA7" s="39" t="n">
-        <f aca="false">K7*INDEX(Assumptions!$H$36:$H$37,MATCH(P7,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N7="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
+      <c r="AB7" s="39" t="n">
+        <f aca="false">K7*INDEX(Assumptions!$H$36:$H$37,MATCH(Q7,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N7="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>31290</v>
       </c>
-      <c r="AB7" s="39" t="n">
-        <f aca="false">K7*INDEX(Assumptions!$C$36:$C$37,MATCH(P7,Assumptions!$B$36:$B$37,0))</f>
+      <c r="AC7" s="39" t="n">
+        <f aca="false">K7*INDEX(Assumptions!$C$36:$C$37,MATCH(Q7,Assumptions!$B$36:$B$37,0))</f>
         <v>14600</v>
       </c>
-      <c r="AC7" s="39" t="n">
-        <f aca="false">K7-AA7-V7*12</f>
+      <c r="AD7" s="39" t="n">
+        <f aca="false">K7-AB7-W7*12</f>
         <v>-2432.09799432634</v>
       </c>
-      <c r="AD7" s="39" t="n">
-        <f aca="false">AC7-AB7</f>
+      <c r="AE7" s="39" t="n">
+        <f aca="false">AD7-AC7</f>
         <v>-17032.0979943263</v>
       </c>
-      <c r="AE7" s="42" t="n">
+      <c r="AF7" s="42" t="n">
         <f aca="false">IFERROR(K7/H7,0)</f>
         <v>0.158695652173913</v>
       </c>
-      <c r="AF7" s="42" t="n">
-        <f aca="false">IFERROR((K7-AA7-AB7)/H7,0)</f>
+      <c r="AG7" s="42" t="n">
+        <f aca="false">IFERROR((K7-AB7-AC7)/H7,0)</f>
         <v>0.0589347826086957</v>
       </c>
-      <c r="AG7" s="34" t="s">
-        <v>147</v>
-      </c>
-      <c r="AH7" s="33" t="n">
+      <c r="AH7" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="AI7" s="33" t="n">
         <v>14</v>
       </c>
-      <c r="AI7" s="34" t="s">
-        <v>148</v>
-      </c>
-      <c r="AJ7" s="43" t="s">
-        <v>140</v>
+      <c r="AJ7" s="34" t="s">
+        <v>149</v>
+      </c>
+      <c r="AK7" s="43" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4584,19 +4594,19 @@
         <v>3</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D8" s="26" t="s">
         <v>75</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G8" s="19" t="n">
         <v>645000</v>
@@ -4615,95 +4625,96 @@
         <v>89000</v>
       </c>
       <c r="L8" s="25" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M8" s="26" t="s">
         <v>70</v>
       </c>
       <c r="N8" s="26" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O8" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="P8" s="26" t="s">
+      <c r="P8" s="19"/>
+      <c r="Q8" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="Q8" s="21" t="n">
+      <c r="R8" s="21" t="n">
         <f aca="false">H8*(1-J8)</f>
         <v>450000</v>
       </c>
-      <c r="R8" s="28" t="n">
+      <c r="S8" s="28" t="n">
         <f aca="false">IF((1-J8)&gt;0.75,Assumptions!$C$11,IF((1-J8)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S8" s="21" t="n">
-        <f aca="false">PMT(R8/12,Assumptions!$C$14,-Q8)</f>
+      <c r="T8" s="21" t="n">
+        <f aca="false">PMT(S8/12,Assumptions!$C$14,-R8)</f>
         <v>3069.79326025286</v>
       </c>
-      <c r="T8" s="21" t="n">
+      <c r="U8" s="21" t="n">
         <f aca="false">H8*INDEX(Assumptions!$C$28:$C$33,MATCH(D8,Assumptions!$B$28:$B$33,0))/12</f>
         <v>750</v>
       </c>
-      <c r="U8" s="21" t="n">
-        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D8,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M8,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="V8" s="21" t="n">
+        <f aca="false">IF(ISNUMBER(P8),P8,INDEX(Assumptions!$D$28:$D$33,MATCH(D8,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M8,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>750</v>
       </c>
-      <c r="V8" s="21" t="n">
-        <f aca="false">S8+T8+U8+O8</f>
+      <c r="W8" s="21" t="n">
+        <f aca="false">T8+U8+V8+O8</f>
         <v>4569.79326025286</v>
       </c>
-      <c r="W8" s="29" t="n">
-        <f aca="false">IFERROR(K8/12/V8,0)</f>
+      <c r="X8" s="29" t="n">
+        <f aca="false">IFERROR(K8/12/W8,0)</f>
         <v>1.62297641146599</v>
       </c>
-      <c r="X8" s="30" t="n">
-        <f aca="false">IFERROR(K8*Assumptions!$C$18/12/V8,0)</f>
+      <c r="Y8" s="30" t="n">
+        <f aca="false">IFERROR(K8*Assumptions!$C$18/12/W8,0)</f>
         <v>1.29838112917279</v>
       </c>
-      <c r="Y8" s="31" t="n">
+      <c r="Z8" s="31" t="n">
         <f aca="false">H8*J8+H8*(Assumptions!$C$16-I8)</f>
         <v>156000</v>
       </c>
-      <c r="Z8" s="21" t="n">
-        <f aca="false">V8*Assumptions!$C$17</f>
+      <c r="AA8" s="21" t="n">
+        <f aca="false">W8*Assumptions!$C$17</f>
         <v>27418.7595615172</v>
       </c>
-      <c r="AA8" s="21" t="n">
-        <f aca="false">K8*INDEX(Assumptions!$H$36:$H$37,MATCH(P8,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N8="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
+      <c r="AB8" s="21" t="n">
+        <f aca="false">K8*INDEX(Assumptions!$H$36:$H$37,MATCH(Q8,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N8="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>38370</v>
       </c>
-      <c r="AB8" s="21" t="n">
-        <f aca="false">K8*INDEX(Assumptions!$C$36:$C$37,MATCH(P8,Assumptions!$B$36:$B$37,0))</f>
+      <c r="AC8" s="21" t="n">
+        <f aca="false">K8*INDEX(Assumptions!$C$36:$C$37,MATCH(Q8,Assumptions!$B$36:$B$37,0))</f>
         <v>17800</v>
       </c>
-      <c r="AC8" s="21" t="n">
-        <f aca="false">K8-AA8-V8*12</f>
+      <c r="AD8" s="21" t="n">
+        <f aca="false">K8-AB8-W8*12</f>
         <v>-4207.51912303436</v>
       </c>
-      <c r="AD8" s="21" t="n">
-        <f aca="false">AC8-AB8</f>
+      <c r="AE8" s="21" t="n">
+        <f aca="false">AD8-AC8</f>
         <v>-22007.5191230344</v>
       </c>
-      <c r="AE8" s="22" t="n">
+      <c r="AF8" s="22" t="n">
         <f aca="false">IFERROR(K8/H8,0)</f>
         <v>0.148333333333333</v>
       </c>
-      <c r="AF8" s="22" t="n">
-        <f aca="false">IFERROR((K8-AA8-AB8)/H8,0)</f>
+      <c r="AG8" s="22" t="n">
+        <f aca="false">IFERROR((K8-AB8-AC8)/H8,0)</f>
         <v>0.0547166666666667</v>
       </c>
-      <c r="AG8" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="AH8" s="13" t="n">
+      <c r="AH8" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="AI8" s="13" t="n">
         <v>23</v>
       </c>
-      <c r="AI8" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="AJ8" s="32" t="s">
-        <v>140</v>
+      <c r="AJ8" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="AK8" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4711,19 +4722,19 @@
         <v>4</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D9" s="35" t="s">
         <v>77</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G9" s="36" t="n">
         <v>475000</v>
@@ -4742,95 +4753,96 @@
         <v>60000</v>
       </c>
       <c r="L9" s="34" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M9" s="35" t="s">
         <v>64</v>
       </c>
       <c r="N9" s="35" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O9" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="P9" s="35" t="s">
+      <c r="P9" s="36"/>
+      <c r="Q9" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="Q9" s="39" t="n">
+      <c r="R9" s="39" t="n">
         <f aca="false">H9*(1-J9)</f>
         <v>341250</v>
       </c>
-      <c r="R9" s="40" t="n">
+      <c r="S9" s="40" t="n">
         <f aca="false">IF((1-J9)&gt;0.75,Assumptions!$C$11,IF((1-J9)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S9" s="39" t="n">
-        <f aca="false">PMT(R9/12,Assumptions!$C$14,-Q9)</f>
+      <c r="T9" s="39" t="n">
+        <f aca="false">PMT(S9/12,Assumptions!$C$14,-R9)</f>
         <v>2327.92655569175</v>
       </c>
-      <c r="T9" s="39" t="n">
+      <c r="U9" s="39" t="n">
         <f aca="false">H9*INDEX(Assumptions!$C$28:$C$33,MATCH(D9,Assumptions!$B$28:$B$33,0))/12</f>
         <v>511.875</v>
       </c>
-      <c r="U9" s="39" t="n">
-        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D9,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M9,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="V9" s="39" t="n">
+        <f aca="false">IF(ISNUMBER(P9),P9,INDEX(Assumptions!$D$28:$D$33,MATCH(D9,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M9,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>666.666666666667</v>
       </c>
-      <c r="V9" s="39" t="n">
-        <f aca="false">S9+T9+U9+O9</f>
+      <c r="W9" s="39" t="n">
+        <f aca="false">T9+U9+V9+O9</f>
         <v>3506.46822235842</v>
       </c>
-      <c r="W9" s="41" t="n">
-        <f aca="false">IFERROR(K9/12/V9,0)</f>
+      <c r="X9" s="41" t="n">
+        <f aca="false">IFERROR(K9/12/W9,0)</f>
         <v>1.42593620786817</v>
       </c>
-      <c r="X9" s="41" t="n">
-        <f aca="false">IFERROR(K9*Assumptions!$C$18/12/V9,0)</f>
+      <c r="Y9" s="41" t="n">
+        <f aca="false">IFERROR(K9*Assumptions!$C$18/12/W9,0)</f>
         <v>1.14074896629453</v>
       </c>
-      <c r="Y9" s="39" t="n">
+      <c r="Z9" s="39" t="n">
         <f aca="false">H9*J9+H9*(Assumptions!$C$16-I9)</f>
         <v>131950</v>
       </c>
-      <c r="Z9" s="39" t="n">
-        <f aca="false">V9*Assumptions!$C$17</f>
+      <c r="AA9" s="39" t="n">
+        <f aca="false">W9*Assumptions!$C$17</f>
         <v>21038.8093341505</v>
       </c>
-      <c r="AA9" s="39" t="n">
-        <f aca="false">K9*INDEX(Assumptions!$H$36:$H$37,MATCH(P9,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N9="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
+      <c r="AB9" s="39" t="n">
+        <f aca="false">K9*INDEX(Assumptions!$H$36:$H$37,MATCH(Q9,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N9="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>27000</v>
       </c>
-      <c r="AB9" s="39" t="n">
-        <f aca="false">K9*INDEX(Assumptions!$C$36:$C$37,MATCH(P9,Assumptions!$B$36:$B$37,0))</f>
+      <c r="AC9" s="39" t="n">
+        <f aca="false">K9*INDEX(Assumptions!$C$36:$C$37,MATCH(Q9,Assumptions!$B$36:$B$37,0))</f>
         <v>12000</v>
       </c>
-      <c r="AC9" s="39" t="n">
-        <f aca="false">K9-AA9-V9*12</f>
+      <c r="AD9" s="39" t="n">
+        <f aca="false">K9-AB9-W9*12</f>
         <v>-9077.61866830105</v>
       </c>
-      <c r="AD9" s="39" t="n">
-        <f aca="false">AC9-AB9</f>
+      <c r="AE9" s="39" t="n">
+        <f aca="false">AD9-AC9</f>
         <v>-21077.6186683011</v>
       </c>
-      <c r="AE9" s="42" t="n">
+      <c r="AF9" s="42" t="n">
         <f aca="false">IFERROR(K9/H9,0)</f>
         <v>0.131868131868132</v>
       </c>
-      <c r="AF9" s="42" t="n">
-        <f aca="false">IFERROR((K9-AA9-AB9)/H9,0)</f>
+      <c r="AG9" s="42" t="n">
+        <f aca="false">IFERROR((K9-AB9-AC9)/H9,0)</f>
         <v>0.0461538461538462</v>
       </c>
-      <c r="AG9" s="34" t="s">
-        <v>159</v>
-      </c>
-      <c r="AH9" s="33" t="n">
+      <c r="AH9" s="34" t="s">
+        <v>160</v>
+      </c>
+      <c r="AI9" s="33" t="n">
         <v>78</v>
       </c>
-      <c r="AI9" s="34" t="s">
-        <v>160</v>
-      </c>
-      <c r="AJ9" s="43" t="s">
-        <v>140</v>
+      <c r="AJ9" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="AK9" s="43" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4838,19 +4850,19 @@
         <v>5</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D10" s="26" t="s">
         <v>75</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G10" s="19" t="n">
         <v>474999</v>
@@ -4869,95 +4881,96 @@
         <v>54000</v>
       </c>
       <c r="L10" s="25" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M10" s="26" t="s">
         <v>64</v>
       </c>
       <c r="N10" s="26" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O10" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="P10" s="26" t="s">
+      <c r="P10" s="19"/>
+      <c r="Q10" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="Q10" s="21" t="n">
+      <c r="R10" s="21" t="n">
         <f aca="false">H10*(1-J10)</f>
         <v>356249.25</v>
       </c>
-      <c r="R10" s="28" t="n">
+      <c r="S10" s="28" t="n">
         <f aca="false">IF((1-J10)&gt;0.75,Assumptions!$C$11,IF((1-J10)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S10" s="21" t="n">
-        <f aca="false">PMT(R10/12,Assumptions!$C$14,-Q10)</f>
+      <c r="T10" s="21" t="n">
+        <f aca="false">PMT(S10/12,Assumptions!$C$14,-R10)</f>
         <v>2430.24788137808</v>
       </c>
-      <c r="T10" s="21" t="n">
+      <c r="U10" s="21" t="n">
         <f aca="false">H10*INDEX(Assumptions!$C$28:$C$33,MATCH(D10,Assumptions!$B$28:$B$33,0))/12</f>
         <v>593.74875</v>
       </c>
-      <c r="U10" s="21" t="n">
-        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D10,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M10,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="V10" s="21" t="n">
+        <f aca="false">IF(ISNUMBER(P10),P10,INDEX(Assumptions!$D$28:$D$33,MATCH(D10,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M10,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>666.666666666667</v>
       </c>
-      <c r="V10" s="21" t="n">
-        <f aca="false">S10+T10+U10+O10</f>
+      <c r="W10" s="21" t="n">
+        <f aca="false">T10+U10+V10+O10</f>
         <v>3690.66329804475</v>
       </c>
-      <c r="W10" s="29" t="n">
-        <f aca="false">IFERROR(K10/12/V10,0)</f>
+      <c r="X10" s="29" t="n">
+        <f aca="false">IFERROR(K10/12/W10,0)</f>
         <v>1.2192930204129</v>
       </c>
-      <c r="X10" s="29" t="n">
-        <f aca="false">IFERROR(K10*Assumptions!$C$18/12/V10,0)</f>
+      <c r="Y10" s="29" t="n">
+        <f aca="false">IFERROR(K10*Assumptions!$C$18/12/W10,0)</f>
         <v>0.975434416330316</v>
       </c>
-      <c r="Y10" s="21" t="n">
+      <c r="Z10" s="21" t="n">
         <f aca="false">H10*J10+H10*(Assumptions!$C$16-I10)</f>
         <v>137749.71</v>
       </c>
-      <c r="Z10" s="21" t="n">
-        <f aca="false">V10*Assumptions!$C$17</f>
+      <c r="AA10" s="21" t="n">
+        <f aca="false">W10*Assumptions!$C$17</f>
         <v>22143.9797882685</v>
       </c>
-      <c r="AA10" s="21" t="n">
-        <f aca="false">K10*INDEX(Assumptions!$H$36:$H$37,MATCH(P10,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N10="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
+      <c r="AB10" s="21" t="n">
+        <f aca="false">K10*INDEX(Assumptions!$H$36:$H$37,MATCH(Q10,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N10="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>26820</v>
       </c>
-      <c r="AB10" s="21" t="n">
-        <f aca="false">K10*INDEX(Assumptions!$C$36:$C$37,MATCH(P10,Assumptions!$B$36:$B$37,0))</f>
+      <c r="AC10" s="21" t="n">
+        <f aca="false">K10*INDEX(Assumptions!$C$36:$C$37,MATCH(Q10,Assumptions!$B$36:$B$37,0))</f>
         <v>10800</v>
       </c>
-      <c r="AC10" s="21" t="n">
-        <f aca="false">K10-AA10-V10*12</f>
+      <c r="AD10" s="21" t="n">
+        <f aca="false">K10-AB10-W10*12</f>
         <v>-17107.959576537</v>
       </c>
-      <c r="AD10" s="21" t="n">
-        <f aca="false">AC10-AB10</f>
+      <c r="AE10" s="21" t="n">
+        <f aca="false">AD10-AC10</f>
         <v>-27907.959576537</v>
       </c>
-      <c r="AE10" s="22" t="n">
+      <c r="AF10" s="22" t="n">
         <f aca="false">IFERROR(K10/H10,0)</f>
         <v>0.113684449862</v>
       </c>
-      <c r="AF10" s="22" t="n">
-        <f aca="false">IFERROR((K10-AA10-AB10)/H10,0)</f>
+      <c r="AG10" s="22" t="n">
+        <f aca="false">IFERROR((K10-AB10-AC10)/H10,0)</f>
         <v>0.0344842831248066</v>
       </c>
-      <c r="AG10" s="25" t="s">
-        <v>164</v>
-      </c>
-      <c r="AH10" s="13" t="n">
+      <c r="AH10" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="AI10" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="AI10" s="25" t="s">
-        <v>165</v>
-      </c>
-      <c r="AJ10" s="32" t="s">
-        <v>140</v>
+      <c r="AJ10" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="AK10" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4965,19 +4978,19 @@
         <v>6</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D11" s="35" t="s">
         <v>75</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G11" s="36" t="n">
         <v>529000</v>
@@ -4996,95 +5009,96 @@
         <v>60000</v>
       </c>
       <c r="L11" s="34" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M11" s="35" t="s">
         <v>70</v>
       </c>
       <c r="N11" s="35" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O11" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="P11" s="35" t="s">
+      <c r="P11" s="36"/>
+      <c r="Q11" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="Q11" s="39" t="n">
+      <c r="R11" s="39" t="n">
         <f aca="false">H11*(1-J11)</f>
         <v>386250</v>
       </c>
-      <c r="R11" s="40" t="n">
+      <c r="S11" s="40" t="n">
         <f aca="false">IF((1-J11)&gt;0.75,Assumptions!$C$11,IF((1-J11)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S11" s="39" t="n">
-        <f aca="false">PMT(R11/12,Assumptions!$C$14,-Q11)</f>
+      <c r="T11" s="39" t="n">
+        <f aca="false">PMT(S11/12,Assumptions!$C$14,-R11)</f>
         <v>2634.90588171704</v>
       </c>
-      <c r="T11" s="39" t="n">
+      <c r="U11" s="39" t="n">
         <f aca="false">H11*INDEX(Assumptions!$C$28:$C$33,MATCH(D11,Assumptions!$B$28:$B$33,0))/12</f>
         <v>643.75</v>
       </c>
-      <c r="U11" s="39" t="n">
-        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D11,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M11,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="V11" s="39" t="n">
+        <f aca="false">IF(ISNUMBER(P11),P11,INDEX(Assumptions!$D$28:$D$33,MATCH(D11,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M11,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>750</v>
       </c>
-      <c r="V11" s="39" t="n">
-        <f aca="false">S11+T11+U11+O11</f>
+      <c r="W11" s="39" t="n">
+        <f aca="false">T11+U11+V11+O11</f>
         <v>4028.65588171704</v>
       </c>
-      <c r="W11" s="41" t="n">
-        <f aca="false">IFERROR(K11/12/V11,0)</f>
+      <c r="X11" s="41" t="n">
+        <f aca="false">IFERROR(K11/12/W11,0)</f>
         <v>1.24110873373205</v>
       </c>
-      <c r="X11" s="41" t="n">
-        <f aca="false">IFERROR(K11*Assumptions!$C$18/12/V11,0)</f>
+      <c r="Y11" s="41" t="n">
+        <f aca="false">IFERROR(K11*Assumptions!$C$18/12/W11,0)</f>
         <v>0.992886986985638</v>
       </c>
-      <c r="Y11" s="39" t="n">
+      <c r="Z11" s="39" t="n">
         <f aca="false">H11*J11+H11*(Assumptions!$C$16-I11)</f>
         <v>149350</v>
       </c>
-      <c r="Z11" s="39" t="n">
-        <f aca="false">V11*Assumptions!$C$17</f>
+      <c r="AA11" s="39" t="n">
+        <f aca="false">W11*Assumptions!$C$17</f>
         <v>24171.9352903022</v>
       </c>
-      <c r="AA11" s="39" t="n">
-        <f aca="false">K11*INDEX(Assumptions!$H$36:$H$37,MATCH(P11,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N11="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
+      <c r="AB11" s="39" t="n">
+        <f aca="false">K11*INDEX(Assumptions!$H$36:$H$37,MATCH(Q11,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N11="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>28800</v>
       </c>
-      <c r="AB11" s="39" t="n">
-        <f aca="false">K11*INDEX(Assumptions!$C$36:$C$37,MATCH(P11,Assumptions!$B$36:$B$37,0))</f>
+      <c r="AC11" s="39" t="n">
+        <f aca="false">K11*INDEX(Assumptions!$C$36:$C$37,MATCH(Q11,Assumptions!$B$36:$B$37,0))</f>
         <v>12000</v>
       </c>
-      <c r="AC11" s="39" t="n">
-        <f aca="false">K11-AA11-V11*12</f>
+      <c r="AD11" s="39" t="n">
+        <f aca="false">K11-AB11-W11*12</f>
         <v>-17143.8705806045</v>
       </c>
-      <c r="AD11" s="39" t="n">
-        <f aca="false">AC11-AB11</f>
+      <c r="AE11" s="39" t="n">
+        <f aca="false">AD11-AC11</f>
         <v>-29143.8705806045</v>
       </c>
-      <c r="AE11" s="42" t="n">
+      <c r="AF11" s="42" t="n">
         <f aca="false">IFERROR(K11/H11,0)</f>
         <v>0.116504854368932</v>
       </c>
-      <c r="AF11" s="42" t="n">
-        <f aca="false">IFERROR((K11-AA11-AB11)/H11,0)</f>
+      <c r="AG11" s="42" t="n">
+        <f aca="false">IFERROR((K11-AB11-AC11)/H11,0)</f>
         <v>0.0372815533980583</v>
       </c>
-      <c r="AG11" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="AH11" s="33" t="n">
+      <c r="AH11" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="AI11" s="33" t="n">
         <v>58</v>
       </c>
-      <c r="AI11" s="34" t="s">
-        <v>170</v>
-      </c>
-      <c r="AJ11" s="43" t="s">
-        <v>140</v>
+      <c r="AJ11" s="34" t="s">
+        <v>171</v>
+      </c>
+      <c r="AK11" s="43" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5092,19 +5106,19 @@
         <v>7</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D12" s="26" t="s">
         <v>77</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G12" s="19" t="n">
         <v>524900</v>
@@ -5123,95 +5137,96 @@
         <v>50157</v>
       </c>
       <c r="L12" s="25" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M12" s="26" t="s">
         <v>64</v>
       </c>
       <c r="N12" s="26" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O12" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="P12" s="26" t="s">
+      <c r="P12" s="19"/>
+      <c r="Q12" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="Q12" s="21" t="n">
+      <c r="R12" s="21" t="n">
         <f aca="false">H12*(1-J12)</f>
         <v>378750</v>
       </c>
-      <c r="R12" s="28" t="n">
+      <c r="S12" s="28" t="n">
         <f aca="false">IF((1-J12)&gt;0.75,Assumptions!$C$11,IF((1-J12)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S12" s="21" t="n">
-        <f aca="false">PMT(R12/12,Assumptions!$C$14,-Q12)</f>
+      <c r="T12" s="21" t="n">
+        <f aca="false">PMT(S12/12,Assumptions!$C$14,-R12)</f>
         <v>2583.74266071283</v>
       </c>
-      <c r="T12" s="21" t="n">
+      <c r="U12" s="21" t="n">
         <f aca="false">H12*INDEX(Assumptions!$C$28:$C$33,MATCH(D12,Assumptions!$B$28:$B$33,0))/12</f>
         <v>568.125</v>
       </c>
-      <c r="U12" s="21" t="n">
-        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D12,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M12,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="V12" s="21" t="n">
+        <f aca="false">IF(ISNUMBER(P12),P12,INDEX(Assumptions!$D$28:$D$33,MATCH(D12,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M12,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>666.666666666667</v>
       </c>
-      <c r="V12" s="21" t="n">
-        <f aca="false">S12+T12+U12+O12</f>
+      <c r="W12" s="21" t="n">
+        <f aca="false">T12+U12+V12+O12</f>
         <v>3818.53432737949</v>
       </c>
-      <c r="W12" s="29" t="n">
-        <f aca="false">IFERROR(K12/12/V12,0)</f>
+      <c r="X12" s="29" t="n">
+        <f aca="false">IFERROR(K12/12/W12,0)</f>
         <v>1.09459537132625</v>
       </c>
-      <c r="X12" s="29" t="n">
-        <f aca="false">IFERROR(K12*Assumptions!$C$18/12/V12,0)</f>
+      <c r="Y12" s="29" t="n">
+        <f aca="false">IFERROR(K12*Assumptions!$C$18/12/W12,0)</f>
         <v>0.875676297061003</v>
       </c>
-      <c r="Y12" s="21" t="n">
+      <c r="Z12" s="21" t="n">
         <f aca="false">H12*J12+H12*(Assumptions!$C$16-I12)</f>
         <v>146450</v>
       </c>
-      <c r="Z12" s="21" t="n">
-        <f aca="false">V12*Assumptions!$C$17</f>
+      <c r="AA12" s="21" t="n">
+        <f aca="false">W12*Assumptions!$C$17</f>
         <v>22911.205964277</v>
       </c>
-      <c r="AA12" s="21" t="n">
-        <f aca="false">K12*INDEX(Assumptions!$H$36:$H$37,MATCH(P12,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N12="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
+      <c r="AB12" s="21" t="n">
+        <f aca="false">K12*INDEX(Assumptions!$H$36:$H$37,MATCH(Q12,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N12="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>23751.81</v>
       </c>
-      <c r="AB12" s="21" t="n">
-        <f aca="false">K12*INDEX(Assumptions!$C$36:$C$37,MATCH(P12,Assumptions!$B$36:$B$37,0))</f>
+      <c r="AC12" s="21" t="n">
+        <f aca="false">K12*INDEX(Assumptions!$C$36:$C$37,MATCH(Q12,Assumptions!$B$36:$B$37,0))</f>
         <v>10031.4</v>
       </c>
-      <c r="AC12" s="21" t="n">
-        <f aca="false">K12-AA12-V12*12</f>
+      <c r="AD12" s="21" t="n">
+        <f aca="false">K12-AB12-W12*12</f>
         <v>-19417.2219285539</v>
       </c>
-      <c r="AD12" s="21" t="n">
-        <f aca="false">AC12-AB12</f>
+      <c r="AE12" s="21" t="n">
+        <f aca="false">AD12-AC12</f>
         <v>-29448.6219285539</v>
       </c>
-      <c r="AE12" s="22" t="n">
+      <c r="AF12" s="22" t="n">
         <f aca="false">IFERROR(K12/H12,0)</f>
         <v>0.0993207920792079</v>
       </c>
-      <c r="AF12" s="22" t="n">
-        <f aca="false">IFERROR((K12-AA12-AB12)/H12,0)</f>
+      <c r="AG12" s="22" t="n">
+        <f aca="false">IFERROR((K12-AB12-AC12)/H12,0)</f>
         <v>0.0324233465346535</v>
       </c>
-      <c r="AG12" s="25" t="s">
-        <v>174</v>
-      </c>
-      <c r="AH12" s="13" t="n">
+      <c r="AH12" s="25" t="s">
+        <v>175</v>
+      </c>
+      <c r="AI12" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="AI12" s="25" t="s">
-        <v>175</v>
-      </c>
-      <c r="AJ12" s="32" t="s">
-        <v>140</v>
+      <c r="AJ12" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="AK12" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5219,19 +5234,19 @@
         <v>8</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D13" s="35" t="s">
         <v>75</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F13" s="34" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G13" s="36" t="n">
         <v>550000</v>
@@ -5250,95 +5265,96 @@
         <v>48000</v>
       </c>
       <c r="L13" s="34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M13" s="35" t="s">
         <v>70</v>
       </c>
       <c r="N13" s="35" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O13" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="P13" s="35" t="s">
+      <c r="P13" s="36"/>
+      <c r="Q13" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="Q13" s="39" t="n">
+      <c r="R13" s="39" t="n">
         <f aca="false">H13*(1-J13)</f>
         <v>397500</v>
       </c>
-      <c r="R13" s="40" t="n">
+      <c r="S13" s="40" t="n">
         <f aca="false">IF((1-J13)&gt;0.75,Assumptions!$C$11,IF((1-J13)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S13" s="39" t="n">
-        <f aca="false">PMT(R13/12,Assumptions!$C$14,-Q13)</f>
+      <c r="T13" s="39" t="n">
+        <f aca="false">PMT(S13/12,Assumptions!$C$14,-R13)</f>
         <v>2711.65071322336</v>
       </c>
-      <c r="T13" s="39" t="n">
+      <c r="U13" s="39" t="n">
         <f aca="false">H13*INDEX(Assumptions!$C$28:$C$33,MATCH(D13,Assumptions!$B$28:$B$33,0))/12</f>
         <v>662.5</v>
       </c>
-      <c r="U13" s="39" t="n">
-        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D13,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M13,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="V13" s="39" t="n">
+        <f aca="false">IF(ISNUMBER(P13),P13,INDEX(Assumptions!$D$28:$D$33,MATCH(D13,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M13,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>750</v>
       </c>
-      <c r="V13" s="39" t="n">
-        <f aca="false">S13+T13+U13+O13</f>
+      <c r="W13" s="39" t="n">
+        <f aca="false">T13+U13+V13+O13</f>
         <v>4132.15071322336</v>
       </c>
-      <c r="W13" s="41" t="n">
-        <f aca="false">IFERROR(K13/12/V13,0)</f>
+      <c r="X13" s="41" t="n">
+        <f aca="false">IFERROR(K13/12/W13,0)</f>
         <v>0.968018902892272</v>
       </c>
-      <c r="X13" s="41" t="n">
-        <f aca="false">IFERROR(K13*Assumptions!$C$18/12/V13,0)</f>
+      <c r="Y13" s="41" t="n">
+        <f aca="false">IFERROR(K13*Assumptions!$C$18/12/W13,0)</f>
         <v>0.774415122313818</v>
       </c>
-      <c r="Y13" s="39" t="n">
+      <c r="Z13" s="39" t="n">
         <f aca="false">H13*J13+H13*(Assumptions!$C$16-I13)</f>
         <v>153700</v>
       </c>
-      <c r="Z13" s="39" t="n">
-        <f aca="false">V13*Assumptions!$C$17</f>
+      <c r="AA13" s="39" t="n">
+        <f aca="false">W13*Assumptions!$C$17</f>
         <v>24792.9042793402</v>
       </c>
-      <c r="AA13" s="39" t="n">
-        <f aca="false">K13*INDEX(Assumptions!$H$36:$H$37,MATCH(P13,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N13="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
+      <c r="AB13" s="39" t="n">
+        <f aca="false">K13*INDEX(Assumptions!$H$36:$H$37,MATCH(Q13,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N13="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>24840</v>
       </c>
-      <c r="AB13" s="39" t="n">
-        <f aca="false">K13*INDEX(Assumptions!$C$36:$C$37,MATCH(P13,Assumptions!$B$36:$B$37,0))</f>
+      <c r="AC13" s="39" t="n">
+        <f aca="false">K13*INDEX(Assumptions!$C$36:$C$37,MATCH(Q13,Assumptions!$B$36:$B$37,0))</f>
         <v>9600</v>
       </c>
-      <c r="AC13" s="39" t="n">
-        <f aca="false">K13-AA13-V13*12</f>
+      <c r="AD13" s="39" t="n">
+        <f aca="false">K13-AB13-W13*12</f>
         <v>-26425.8085586803</v>
       </c>
-      <c r="AD13" s="39" t="n">
-        <f aca="false">AC13-AB13</f>
+      <c r="AE13" s="39" t="n">
+        <f aca="false">AD13-AC13</f>
         <v>-36025.8085586803</v>
       </c>
-      <c r="AE13" s="42" t="n">
+      <c r="AF13" s="42" t="n">
         <f aca="false">IFERROR(K13/H13,0)</f>
         <v>0.0905660377358491</v>
       </c>
-      <c r="AF13" s="42" t="n">
-        <f aca="false">IFERROR((K13-AA13-AB13)/H13,0)</f>
+      <c r="AG13" s="42" t="n">
+        <f aca="false">IFERROR((K13-AB13-AC13)/H13,0)</f>
         <v>0.0255849056603774</v>
       </c>
-      <c r="AG13" s="34" t="s">
-        <v>179</v>
-      </c>
-      <c r="AH13" s="33" t="n">
+      <c r="AH13" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="AI13" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="AI13" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="AJ13" s="43" t="s">
-        <v>140</v>
+      <c r="AJ13" s="34" t="s">
+        <v>181</v>
+      </c>
+      <c r="AK13" s="43" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5346,19 +5362,19 @@
         <v>9</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D14" s="26" t="s">
         <v>75</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G14" s="19" t="n">
         <v>385000</v>
@@ -5377,95 +5393,96 @@
         <v>40000</v>
       </c>
       <c r="L14" s="25" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M14" s="26" t="s">
         <v>64</v>
       </c>
       <c r="N14" s="26" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O14" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="P14" s="26" t="s">
+      <c r="P14" s="19"/>
+      <c r="Q14" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="Q14" s="21" t="n">
+      <c r="R14" s="21" t="n">
         <f aca="false">H14*(1-J14)</f>
         <v>270000</v>
       </c>
-      <c r="R14" s="28" t="n">
+      <c r="S14" s="28" t="n">
         <f aca="false">IF((1-J14)&gt;0.75,Assumptions!$C$11,IF((1-J14)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S14" s="21" t="n">
-        <f aca="false">PMT(R14/12,Assumptions!$C$14,-Q14)</f>
+      <c r="T14" s="21" t="n">
+        <f aca="false">PMT(S14/12,Assumptions!$C$14,-R14)</f>
         <v>1841.87595615172</v>
       </c>
-      <c r="T14" s="21" t="n">
+      <c r="U14" s="21" t="n">
         <f aca="false">H14*INDEX(Assumptions!$C$28:$C$33,MATCH(D14,Assumptions!$B$28:$B$33,0))/12</f>
         <v>450</v>
       </c>
-      <c r="U14" s="21" t="n">
-        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D14,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M14,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="V14" s="21" t="n">
+        <f aca="false">IF(ISNUMBER(P14),P14,INDEX(Assumptions!$D$28:$D$33,MATCH(D14,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M14,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>666.666666666667</v>
       </c>
-      <c r="V14" s="21" t="n">
-        <f aca="false">S14+T14+U14+O14</f>
+      <c r="W14" s="21" t="n">
+        <f aca="false">T14+U14+V14+O14</f>
         <v>2958.54262281838</v>
       </c>
-      <c r="W14" s="29" t="n">
-        <f aca="false">IFERROR(K14/12/V14,0)</f>
+      <c r="X14" s="29" t="n">
+        <f aca="false">IFERROR(K14/12/W14,0)</f>
         <v>1.12668085550781</v>
       </c>
-      <c r="X14" s="29" t="n">
-        <f aca="false">IFERROR(K14*Assumptions!$C$18/12/V14,0)</f>
+      <c r="Y14" s="29" t="n">
+        <f aca="false">IFERROR(K14*Assumptions!$C$18/12/W14,0)</f>
         <v>0.901344684406247</v>
       </c>
-      <c r="Y14" s="21" t="n">
+      <c r="Z14" s="21" t="n">
         <f aca="false">H14*J14+H14*(Assumptions!$C$16-I14)</f>
         <v>104400</v>
       </c>
-      <c r="Z14" s="21" t="n">
-        <f aca="false">V14*Assumptions!$C$17</f>
+      <c r="AA14" s="21" t="n">
+        <f aca="false">W14*Assumptions!$C$17</f>
         <v>17751.2557369103</v>
       </c>
-      <c r="AA14" s="21" t="n">
-        <f aca="false">K14*INDEX(Assumptions!$H$36:$H$37,MATCH(P14,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N14="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
+      <c r="AB14" s="21" t="n">
+        <f aca="false">K14*INDEX(Assumptions!$H$36:$H$37,MATCH(Q14,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N14="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>20400</v>
       </c>
-      <c r="AB14" s="21" t="n">
-        <f aca="false">K14*INDEX(Assumptions!$C$36:$C$37,MATCH(P14,Assumptions!$B$36:$B$37,0))</f>
+      <c r="AC14" s="21" t="n">
+        <f aca="false">K14*INDEX(Assumptions!$C$36:$C$37,MATCH(Q14,Assumptions!$B$36:$B$37,0))</f>
         <v>8000</v>
       </c>
-      <c r="AC14" s="21" t="n">
-        <f aca="false">K14-AA14-V14*12</f>
+      <c r="AD14" s="21" t="n">
+        <f aca="false">K14-AB14-W14*12</f>
         <v>-15902.5114738206</v>
       </c>
-      <c r="AD14" s="21" t="n">
-        <f aca="false">AC14-AB14</f>
+      <c r="AE14" s="21" t="n">
+        <f aca="false">AD14-AC14</f>
         <v>-23902.5114738206</v>
       </c>
-      <c r="AE14" s="22" t="n">
+      <c r="AF14" s="22" t="n">
         <f aca="false">IFERROR(K14/H14,0)</f>
         <v>0.111111111111111</v>
       </c>
-      <c r="AF14" s="22" t="n">
-        <f aca="false">IFERROR((K14-AA14-AB14)/H14,0)</f>
+      <c r="AG14" s="22" t="n">
+        <f aca="false">IFERROR((K14-AB14-AC14)/H14,0)</f>
         <v>0.0322222222222222</v>
       </c>
-      <c r="AG14" s="25" t="s">
-        <v>184</v>
-      </c>
-      <c r="AH14" s="13" t="n">
+      <c r="AH14" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="AI14" s="13" t="n">
         <v>214</v>
       </c>
-      <c r="AI14" s="25" t="s">
-        <v>185</v>
-      </c>
-      <c r="AJ14" s="32" t="s">
-        <v>140</v>
+      <c r="AJ14" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="AK14" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5473,19 +5490,19 @@
         <v>10</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D15" s="35" t="s">
         <v>77</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F15" s="34" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G15" s="36" t="n">
         <v>655000</v>
@@ -5504,95 +5521,96 @@
         <v>102000</v>
       </c>
       <c r="L15" s="34" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M15" s="35" t="s">
         <v>70</v>
       </c>
       <c r="N15" s="35" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O15" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="P15" s="35" t="s">
+      <c r="P15" s="36"/>
+      <c r="Q15" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="Q15" s="39" t="n">
+      <c r="R15" s="39" t="n">
         <f aca="false">H15*(1-J15)</f>
         <v>491250</v>
       </c>
-      <c r="R15" s="40" t="n">
+      <c r="S15" s="40" t="n">
         <f aca="false">IF((1-J15)&gt;0.75,Assumptions!$C$11,IF((1-J15)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S15" s="39" t="n">
-        <f aca="false">PMT(R15/12,Assumptions!$C$14,-Q15)</f>
+      <c r="T15" s="39" t="n">
+        <f aca="false">PMT(S15/12,Assumptions!$C$14,-R15)</f>
         <v>3351.19097577604</v>
       </c>
-      <c r="T15" s="39" t="n">
+      <c r="U15" s="39" t="n">
         <f aca="false">H15*INDEX(Assumptions!$C$28:$C$33,MATCH(D15,Assumptions!$B$28:$B$33,0))/12</f>
         <v>736.875</v>
       </c>
-      <c r="U15" s="39" t="n">
-        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D15,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M15,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="V15" s="39" t="n">
+        <f aca="false">IF(ISNUMBER(P15),P15,INDEX(Assumptions!$D$28:$D$33,MATCH(D15,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M15,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>750</v>
       </c>
-      <c r="V15" s="39" t="n">
-        <f aca="false">S15+T15+U15+O15</f>
+      <c r="W15" s="39" t="n">
+        <f aca="false">T15+U15+V15+O15</f>
         <v>4838.06597577604</v>
       </c>
-      <c r="W15" s="41" t="n">
-        <f aca="false">IFERROR(K15/12/V15,0)</f>
+      <c r="X15" s="41" t="n">
+        <f aca="false">IFERROR(K15/12/W15,0)</f>
         <v>1.75690039006477</v>
       </c>
-      <c r="X15" s="41" t="n">
-        <f aca="false">IFERROR(K15*Assumptions!$C$18/12/V15,0)</f>
+      <c r="Y15" s="41" t="n">
+        <f aca="false">IFERROR(K15*Assumptions!$C$18/12/W15,0)</f>
         <v>1.40552031205181</v>
       </c>
-      <c r="Y15" s="39" t="n">
+      <c r="Z15" s="39" t="n">
         <f aca="false">H15*J15+H15*(Assumptions!$C$16-I15)</f>
         <v>189950</v>
       </c>
-      <c r="Z15" s="39" t="n">
-        <f aca="false">V15*Assumptions!$C$17</f>
+      <c r="AA15" s="39" t="n">
+        <f aca="false">W15*Assumptions!$C$17</f>
         <v>29028.3958546563</v>
       </c>
-      <c r="AA15" s="39" t="n">
-        <f aca="false">K15*INDEX(Assumptions!$H$36:$H$37,MATCH(P15,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N15="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
+      <c r="AB15" s="39" t="n">
+        <f aca="false">K15*INDEX(Assumptions!$H$36:$H$37,MATCH(Q15,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N15="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>23520</v>
       </c>
-      <c r="AB15" s="39" t="n">
-        <f aca="false">K15*INDEX(Assumptions!$C$36:$C$37,MATCH(P15,Assumptions!$B$36:$B$37,0))</f>
+      <c r="AC15" s="39" t="n">
+        <f aca="false">K15*INDEX(Assumptions!$C$36:$C$37,MATCH(Q15,Assumptions!$B$36:$B$37,0))</f>
         <v>12240</v>
       </c>
-      <c r="AC15" s="39" t="n">
-        <f aca="false">K15-AA15-V15*12</f>
+      <c r="AD15" s="39" t="n">
+        <f aca="false">K15-AB15-W15*12</f>
         <v>20423.2082906875</v>
       </c>
-      <c r="AD15" s="39" t="n">
-        <f aca="false">AC15-AB15</f>
+      <c r="AE15" s="39" t="n">
+        <f aca="false">AD15-AC15</f>
         <v>8183.20829068749</v>
       </c>
-      <c r="AE15" s="42" t="n">
+      <c r="AF15" s="42" t="n">
         <f aca="false">IFERROR(K15/H15,0)</f>
         <v>0.155725190839695</v>
       </c>
-      <c r="AF15" s="42" t="n">
-        <f aca="false">IFERROR((K15-AA15-AB15)/H15,0)</f>
+      <c r="AG15" s="42" t="n">
+        <f aca="false">IFERROR((K15-AB15-AC15)/H15,0)</f>
         <v>0.101129770992366</v>
       </c>
-      <c r="AG15" s="34" t="s">
-        <v>191</v>
-      </c>
-      <c r="AH15" s="33" t="n">
+      <c r="AH15" s="34" t="s">
+        <v>192</v>
+      </c>
+      <c r="AI15" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="AI15" s="34" t="s">
-        <v>192</v>
-      </c>
-      <c r="AJ15" s="43" t="s">
-        <v>140</v>
+      <c r="AJ15" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="AK15" s="43" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5600,19 +5618,19 @@
         <v>11</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D16" s="26" t="s">
         <v>75</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G16" s="19" t="n">
         <v>279000</v>
@@ -5631,93 +5649,94 @@
         <v>44000</v>
       </c>
       <c r="L16" s="25" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M16" s="26" t="s">
         <v>70</v>
       </c>
       <c r="N16" s="26" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O16" s="19" t="n">
         <v>477</v>
       </c>
-      <c r="P16" s="26" t="s">
+      <c r="P16" s="19"/>
+      <c r="Q16" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="Q16" s="21" t="n">
+      <c r="R16" s="21" t="n">
         <f aca="false">H16*(1-J16)</f>
         <v>209250</v>
       </c>
-      <c r="R16" s="28" t="n">
+      <c r="S16" s="28" t="n">
         <f aca="false">IF((1-J16)&gt;0.75,Assumptions!$C$11,IF((1-J16)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S16" s="21" t="n">
-        <f aca="false">PMT(R16/12,Assumptions!$C$14,-Q16)</f>
+      <c r="T16" s="21" t="n">
+        <f aca="false">PMT(S16/12,Assumptions!$C$14,-R16)</f>
         <v>1427.45386601758</v>
       </c>
-      <c r="T16" s="21" t="n">
+      <c r="U16" s="21" t="n">
         <f aca="false">H16*INDEX(Assumptions!$C$28:$C$33,MATCH(D16,Assumptions!$B$28:$B$33,0))/12</f>
         <v>348.75</v>
       </c>
-      <c r="U16" s="21" t="n">
-        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D16,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M16,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="V16" s="21" t="n">
+        <f aca="false">IF(ISNUMBER(P16),P16,INDEX(Assumptions!$D$28:$D$33,MATCH(D16,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M16,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>750</v>
       </c>
-      <c r="V16" s="21" t="n">
-        <f aca="false">S16+T16+U16+O16</f>
+      <c r="W16" s="21" t="n">
+        <f aca="false">T16+U16+V16+O16</f>
         <v>3003.20386601758</v>
       </c>
-      <c r="W16" s="29" t="n">
-        <f aca="false">IFERROR(K16/12/V16,0)</f>
+      <c r="X16" s="29" t="n">
+        <f aca="false">IFERROR(K16/12/W16,0)</f>
         <v>1.22091833596661</v>
       </c>
-      <c r="X16" s="29" t="n">
-        <f aca="false">IFERROR(K16*Assumptions!$C$18/12/V16,0)</f>
+      <c r="Y16" s="29" t="n">
+        <f aca="false">IFERROR(K16*Assumptions!$C$18/12/W16,0)</f>
         <v>0.976734668773286</v>
       </c>
-      <c r="Y16" s="21" t="n">
+      <c r="Z16" s="21" t="n">
         <f aca="false">H16*J16+H16*(Assumptions!$C$16-I16)</f>
         <v>80910</v>
       </c>
-      <c r="Z16" s="21" t="n">
-        <f aca="false">V16*Assumptions!$C$17</f>
+      <c r="AA16" s="21" t="n">
+        <f aca="false">W16*Assumptions!$C$17</f>
         <v>18019.2231961055</v>
       </c>
-      <c r="AA16" s="21" t="n">
-        <f aca="false">K16*INDEX(Assumptions!$H$36:$H$37,MATCH(P16,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N16="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
+      <c r="AB16" s="21" t="n">
+        <f aca="false">K16*INDEX(Assumptions!$H$36:$H$37,MATCH(Q16,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N16="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>21720</v>
       </c>
-      <c r="AB16" s="21" t="n">
-        <f aca="false">K16*INDEX(Assumptions!$C$36:$C$37,MATCH(P16,Assumptions!$B$36:$B$37,0))</f>
+      <c r="AC16" s="21" t="n">
+        <f aca="false">K16*INDEX(Assumptions!$C$36:$C$37,MATCH(Q16,Assumptions!$B$36:$B$37,0))</f>
         <v>8800</v>
       </c>
-      <c r="AC16" s="21" t="n">
-        <f aca="false">K16-AA16-V16*12</f>
+      <c r="AD16" s="21" t="n">
+        <f aca="false">K16-AB16-W16*12</f>
         <v>-13758.446392211</v>
       </c>
-      <c r="AD16" s="21" t="n">
-        <f aca="false">AC16-AB16</f>
+      <c r="AE16" s="21" t="n">
+        <f aca="false">AD16-AC16</f>
         <v>-22558.446392211</v>
       </c>
-      <c r="AE16" s="22" t="n">
+      <c r="AF16" s="22" t="n">
         <f aca="false">IFERROR(K16/H16,0)</f>
         <v>0.157706093189964</v>
       </c>
-      <c r="AF16" s="22" t="n">
-        <f aca="false">IFERROR((K16-AA16-AB16)/H16,0)</f>
+      <c r="AG16" s="22" t="n">
+        <f aca="false">IFERROR((K16-AB16-AC16)/H16,0)</f>
         <v>0.0483154121863799</v>
       </c>
-      <c r="AG16" s="25"/>
-      <c r="AH16" s="13" t="n">
+      <c r="AH16" s="25"/>
+      <c r="AI16" s="13" t="n">
         <v>55</v>
       </c>
-      <c r="AI16" s="25" t="s">
-        <v>198</v>
-      </c>
-      <c r="AJ16" s="32" t="s">
-        <v>140</v>
+      <c r="AJ16" s="25" t="s">
+        <v>199</v>
+      </c>
+      <c r="AK16" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5725,19 +5744,19 @@
         <v>12</v>
       </c>
       <c r="B17" s="34" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D17" s="35" t="s">
         <v>77</v>
       </c>
       <c r="E17" s="34" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F17" s="34" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G17" s="36" t="n">
         <v>639000</v>
@@ -5756,98 +5775,99 @@
         <v>50000</v>
       </c>
       <c r="L17" s="34" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M17" s="35" t="s">
         <v>66</v>
       </c>
       <c r="N17" s="35" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O17" s="36" t="n">
         <v>945</v>
       </c>
-      <c r="P17" s="35" t="s">
+      <c r="P17" s="36"/>
+      <c r="Q17" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="Q17" s="39" t="n">
+      <c r="R17" s="39" t="n">
         <f aca="false">H17*(1-J17)</f>
         <v>479250</v>
       </c>
-      <c r="R17" s="40" t="n">
+      <c r="S17" s="40" t="n">
         <f aca="false">IF((1-J17)&gt;0.75,Assumptions!$C$11,IF((1-J17)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S17" s="39" t="n">
-        <f aca="false">PMT(R17/12,Assumptions!$C$14,-Q17)</f>
+      <c r="T17" s="39" t="n">
+        <f aca="false">PMT(S17/12,Assumptions!$C$14,-R17)</f>
         <v>3269.3298221693</v>
       </c>
-      <c r="T17" s="39" t="n">
+      <c r="U17" s="39" t="n">
         <f aca="false">H17*INDEX(Assumptions!$C$28:$C$33,MATCH(D17,Assumptions!$B$28:$B$33,0))/12</f>
         <v>718.875</v>
       </c>
-      <c r="U17" s="39" t="n">
-        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D17,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M17,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="V17" s="39" t="n">
+        <f aca="false">IF(ISNUMBER(P17),P17,INDEX(Assumptions!$D$28:$D$33,MATCH(D17,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M17,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>958.333333333333</v>
       </c>
-      <c r="V17" s="39" t="n">
-        <f aca="false">S17+T17+U17+O17</f>
+      <c r="W17" s="39" t="n">
+        <f aca="false">T17+U17+V17+O17</f>
         <v>5891.53815550263</v>
       </c>
-      <c r="W17" s="41" t="n">
-        <f aca="false">IFERROR(K17/12/V17,0)</f>
+      <c r="X17" s="41" t="n">
+        <f aca="false">IFERROR(K17/12/W17,0)</f>
         <v>0.707229004835528</v>
       </c>
-      <c r="X17" s="41" t="n">
-        <f aca="false">IFERROR(K17*Assumptions!$C$18/12/V17,0)</f>
+      <c r="Y17" s="41" t="n">
+        <f aca="false">IFERROR(K17*Assumptions!$C$18/12/W17,0)</f>
         <v>0.565783203868422</v>
       </c>
-      <c r="Y17" s="39" t="n">
+      <c r="Z17" s="39" t="n">
         <f aca="false">H17*J17+H17*(Assumptions!$C$16-I17)</f>
         <v>185310</v>
       </c>
-      <c r="Z17" s="39" t="n">
-        <f aca="false">V17*Assumptions!$C$17</f>
+      <c r="AA17" s="39" t="n">
+        <f aca="false">W17*Assumptions!$C$17</f>
         <v>35349.2289330158</v>
       </c>
-      <c r="AA17" s="39" t="n">
-        <f aca="false">K17*INDEX(Assumptions!$H$36:$H$37,MATCH(P17,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N17="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
+      <c r="AB17" s="39" t="n">
+        <f aca="false">K17*INDEX(Assumptions!$H$36:$H$37,MATCH(Q17,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N17="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>23700</v>
       </c>
-      <c r="AB17" s="39" t="n">
-        <f aca="false">K17*INDEX(Assumptions!$C$36:$C$37,MATCH(P17,Assumptions!$B$36:$B$37,0))</f>
+      <c r="AC17" s="39" t="n">
+        <f aca="false">K17*INDEX(Assumptions!$C$36:$C$37,MATCH(Q17,Assumptions!$B$36:$B$37,0))</f>
         <v>10000</v>
       </c>
-      <c r="AC17" s="39" t="n">
-        <f aca="false">K17-AA17-V17*12</f>
+      <c r="AD17" s="39" t="n">
+        <f aca="false">K17-AB17-W17*12</f>
         <v>-44398.4578660316</v>
       </c>
-      <c r="AD17" s="39" t="n">
-        <f aca="false">AC17-AB17</f>
+      <c r="AE17" s="39" t="n">
+        <f aca="false">AD17-AC17</f>
         <v>-54398.4578660316</v>
       </c>
-      <c r="AE17" s="42" t="n">
+      <c r="AF17" s="42" t="n">
         <f aca="false">IFERROR(K17/H17,0)</f>
         <v>0.0782472613458529</v>
       </c>
-      <c r="AF17" s="42" t="n">
-        <f aca="false">IFERROR((K17-AA17-AB17)/H17,0)</f>
+      <c r="AG17" s="42" t="n">
+        <f aca="false">IFERROR((K17-AB17-AC17)/H17,0)</f>
         <v>0.025508607198748</v>
       </c>
-      <c r="AG17" s="34"/>
-      <c r="AH17" s="33" t="n">
+      <c r="AH17" s="34"/>
+      <c r="AI17" s="33" t="n">
         <v>27</v>
       </c>
-      <c r="AI17" s="34" t="s">
-        <v>204</v>
-      </c>
-      <c r="AJ17" s="43" t="s">
-        <v>140</v>
+      <c r="AJ17" s="34" t="s">
+        <v>205</v>
+      </c>
+      <c r="AK17" s="43" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5858,156 +5878,156 @@
         <v>4</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="AI21" s="3" t="s">
         <v>208</v>
       </c>
       <c r="AJ21" s="3" t="s">
         <v>209</v>
       </c>
+      <c r="AK21" s="3" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="25" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G22" s="19" t="n">
         <v>619000</v>
       </c>
       <c r="L22" s="25" t="s">
-        <v>211</v>
-      </c>
-      <c r="AI22" s="25" t="s">
         <v>212</v>
       </c>
-      <c r="AJ22" s="32" t="s">
-        <v>140</v>
+      <c r="AJ22" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK22" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="25" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G23" s="19" t="n">
         <v>524900</v>
       </c>
       <c r="L23" s="25" t="s">
-        <v>215</v>
-      </c>
-      <c r="AI23" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ23" s="32" t="s">
-        <v>140</v>
+        <v>216</v>
+      </c>
+      <c r="AJ23" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK23" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="25" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G24" s="19" t="n">
         <v>499000</v>
       </c>
       <c r="L24" s="25" t="s">
-        <v>217</v>
-      </c>
-      <c r="AI24" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ24" s="32" t="s">
-        <v>140</v>
+        <v>218</v>
+      </c>
+      <c r="AJ24" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK24" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="25" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G25" s="19" t="n">
         <v>450000</v>
       </c>
       <c r="L25" s="25" t="s">
-        <v>219</v>
-      </c>
-      <c r="AI25" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ25" s="32" t="s">
-        <v>140</v>
+        <v>220</v>
+      </c>
+      <c r="AJ25" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK25" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="25" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G26" s="19" t="n">
         <v>625000</v>
       </c>
       <c r="L26" s="25" t="s">
-        <v>221</v>
-      </c>
-      <c r="AI26" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ26" s="32" t="s">
-        <v>140</v>
+        <v>222</v>
+      </c>
+      <c r="AJ26" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK26" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="25" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G27" s="19" t="n">
         <v>419999</v>
       </c>
       <c r="L27" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="AI27" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ27" s="32" t="s">
-        <v>140</v>
+        <v>225</v>
+      </c>
+      <c r="AJ27" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK27" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="25" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C28" s="25" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G28" s="19" t="n">
         <v>374900</v>
       </c>
       <c r="L28" s="25" t="s">
-        <v>227</v>
-      </c>
-      <c r="AI28" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ28" s="32" t="s">
-        <v>140</v>
+        <v>228</v>
+      </c>
+      <c r="AJ28" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK28" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -6016,7 +6036,7 @@
       <formula1>Assumptions!$B$22:$B$25</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="P6:P17" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="Q6:Q17" type="list">
       <formula1>"STR,Seasonal"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6026,25 +6046,25 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="AJ6" r:id="rId2" display="Zillow"/>
-    <hyperlink ref="AJ7" r:id="rId3" display="Zillow"/>
-    <hyperlink ref="AJ8" r:id="rId4" display="Zillow"/>
-    <hyperlink ref="AJ9" r:id="rId5" display="Zillow"/>
-    <hyperlink ref="AJ10" r:id="rId6" display="Zillow"/>
-    <hyperlink ref="AJ11" r:id="rId7" display="Zillow"/>
-    <hyperlink ref="AJ12" r:id="rId8" display="Zillow"/>
-    <hyperlink ref="AJ13" r:id="rId9" display="Zillow"/>
-    <hyperlink ref="AJ14" r:id="rId10" display="Zillow"/>
-    <hyperlink ref="AJ15" r:id="rId11" display="Zillow"/>
-    <hyperlink ref="AJ16" r:id="rId12" display="Zillow"/>
-    <hyperlink ref="AJ17" r:id="rId13" display="Zillow"/>
-    <hyperlink ref="AJ22" r:id="rId14" display="Zillow"/>
-    <hyperlink ref="AJ23" r:id="rId15" display="Zillow"/>
-    <hyperlink ref="AJ24" r:id="rId16" display="Zillow"/>
-    <hyperlink ref="AJ25" r:id="rId17" display="Zillow"/>
-    <hyperlink ref="AJ26" r:id="rId18" display="Zillow"/>
-    <hyperlink ref="AJ27" r:id="rId19" display="Zillow"/>
-    <hyperlink ref="AJ28" r:id="rId20" display="Zillow"/>
+    <hyperlink ref="AK6" r:id="rId2" display="Zillow"/>
+    <hyperlink ref="AK7" r:id="rId3" display="Zillow"/>
+    <hyperlink ref="AK8" r:id="rId4" display="Zillow"/>
+    <hyperlink ref="AK9" r:id="rId5" display="Zillow"/>
+    <hyperlink ref="AK10" r:id="rId6" display="Zillow"/>
+    <hyperlink ref="AK11" r:id="rId7" display="Zillow"/>
+    <hyperlink ref="AK12" r:id="rId8" display="Zillow"/>
+    <hyperlink ref="AK13" r:id="rId9" display="Zillow"/>
+    <hyperlink ref="AK14" r:id="rId10" display="Zillow"/>
+    <hyperlink ref="AK15" r:id="rId11" display="Zillow"/>
+    <hyperlink ref="AK16" r:id="rId12" display="Zillow"/>
+    <hyperlink ref="AK17" r:id="rId13" display="Zillow"/>
+    <hyperlink ref="AK22" r:id="rId14" display="Zillow"/>
+    <hyperlink ref="AK23" r:id="rId15" display="Zillow"/>
+    <hyperlink ref="AK24" r:id="rId16" display="Zillow"/>
+    <hyperlink ref="AK25" r:id="rId17" display="Zillow"/>
+    <hyperlink ref="AK26" r:id="rId18" display="Zillow"/>
+    <hyperlink ref="AK27" r:id="rId19" display="Zillow"/>
+    <hyperlink ref="AK28" r:id="rId20" display="Zillow"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6062,7 +6082,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AJ30"/>
+  <dimension ref="A1:AK30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -6078,34 +6098,36 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="19" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="31" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="20" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="32" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6162,7 +6184,7 @@
       <c r="P5" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="Q5" s="23" t="s">
+      <c r="Q5" s="3" t="s">
         <v>118</v>
       </c>
       <c r="R5" s="23" t="s">
@@ -6178,19 +6200,19 @@
         <v>122</v>
       </c>
       <c r="V5" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="W5" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="W5" s="23" t="s">
+      <c r="X5" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="X5" s="23" t="s">
+      <c r="Y5" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="Y5" s="23" t="s">
+      <c r="Z5" s="23" t="s">
         <v>10</v>
-      </c>
-      <c r="Z5" s="23" t="s">
-        <v>123</v>
       </c>
       <c r="AA5" s="23" t="s">
         <v>124</v>
@@ -6199,18 +6221,18 @@
         <v>125</v>
       </c>
       <c r="AC5" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="AD5" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="AD5" s="23" t="s">
+      <c r="AE5" s="23" t="s">
         <v>12</v>
-      </c>
-      <c r="AE5" s="23" t="s">
-        <v>126</v>
       </c>
       <c r="AF5" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="AG5" s="3" t="s">
+      <c r="AG5" s="23" t="s">
         <v>128</v>
       </c>
       <c r="AH5" s="3" t="s">
@@ -6221,6 +6243,9 @@
       </c>
       <c r="AJ5" s="3" t="s">
         <v>131</v>
+      </c>
+      <c r="AK5" s="3" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6228,19 +6253,19 @@
         <v>1</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D6" s="26" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G6" s="19" t="n">
         <v>499000</v>
@@ -6259,93 +6284,94 @@
         <v>71000</v>
       </c>
       <c r="L6" s="25" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M6" s="26" t="s">
         <v>70</v>
       </c>
       <c r="N6" s="26" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O6" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="P6" s="26" t="s">
+      <c r="P6" s="19"/>
+      <c r="Q6" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="Q6" s="21" t="n">
+      <c r="R6" s="21" t="n">
         <f aca="false">H6*(1-J6)</f>
         <v>363750</v>
       </c>
-      <c r="R6" s="28" t="n">
+      <c r="S6" s="28" t="n">
         <f aca="false">IF((1-J6)&gt;0.75,Assumptions!$C$11,IF((1-J6)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S6" s="21" t="n">
-        <f aca="false">PMT(R6/12,Assumptions!$C$14,-Q6)</f>
+      <c r="T6" s="21" t="n">
+        <f aca="false">PMT(S6/12,Assumptions!$C$14,-R6)</f>
         <v>2481.4162187044</v>
       </c>
-      <c r="T6" s="21" t="n">
+      <c r="U6" s="21" t="n">
         <f aca="false">H6*INDEX(Assumptions!$C$28:$C$33,MATCH(D6,Assumptions!$B$28:$B$33,0))/12</f>
         <v>646.666666666667</v>
       </c>
-      <c r="U6" s="21" t="n">
-        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D6,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M6,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="V6" s="21" t="n">
+        <f aca="false">IF(ISNUMBER(P6),P6,INDEX(Assumptions!$D$28:$D$33,MATCH(D6,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M6,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>750</v>
       </c>
-      <c r="V6" s="21" t="n">
-        <f aca="false">S6+T6+U6+O6</f>
+      <c r="W6" s="21" t="n">
+        <f aca="false">T6+U6+V6+O6</f>
         <v>3878.08288537106</v>
       </c>
-      <c r="W6" s="29" t="n">
-        <f aca="false">IFERROR(K6/12/V6,0)</f>
+      <c r="X6" s="29" t="n">
+        <f aca="false">IFERROR(K6/12/W6,0)</f>
         <v>1.52566792447515</v>
       </c>
-      <c r="X6" s="30" t="n">
-        <f aca="false">IFERROR(K6*Assumptions!$C$18/12/V6,0)</f>
+      <c r="Y6" s="30" t="n">
+        <f aca="false">IFERROR(K6*Assumptions!$C$18/12/W6,0)</f>
         <v>1.22053433958012</v>
       </c>
-      <c r="Y6" s="31" t="n">
+      <c r="Z6" s="31" t="n">
         <f aca="false">H6*J6+H6*(Assumptions!$C$16-I6)</f>
         <v>140650</v>
       </c>
-      <c r="Z6" s="21" t="n">
-        <f aca="false">V6*Assumptions!$C$17</f>
+      <c r="AA6" s="21" t="n">
+        <f aca="false">W6*Assumptions!$C$17</f>
         <v>23268.4973122264</v>
       </c>
-      <c r="AA6" s="21" t="n">
-        <f aca="false">K6*INDEX(Assumptions!$H$36:$H$37,MATCH(P6,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N6="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
+      <c r="AB6" s="21" t="n">
+        <f aca="false">K6*INDEX(Assumptions!$H$36:$H$37,MATCH(Q6,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N6="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>32430</v>
       </c>
-      <c r="AB6" s="21" t="n">
-        <f aca="false">K6*INDEX(Assumptions!$C$36:$C$37,MATCH(P6,Assumptions!$B$36:$B$37,0))</f>
+      <c r="AC6" s="21" t="n">
+        <f aca="false">K6*INDEX(Assumptions!$C$36:$C$37,MATCH(Q6,Assumptions!$B$36:$B$37,0))</f>
         <v>14200</v>
       </c>
-      <c r="AC6" s="21" t="n">
-        <f aca="false">K6-AA6-V6*12</f>
+      <c r="AD6" s="21" t="n">
+        <f aca="false">K6-AB6-W6*12</f>
         <v>-7966.99462445278</v>
       </c>
-      <c r="AD6" s="21" t="n">
-        <f aca="false">AC6-AB6</f>
+      <c r="AE6" s="21" t="n">
+        <f aca="false">AD6-AC6</f>
         <v>-22166.9946244528</v>
       </c>
-      <c r="AE6" s="22" t="n">
+      <c r="AF6" s="22" t="n">
         <f aca="false">IFERROR(K6/H6,0)</f>
         <v>0.14639175257732</v>
       </c>
-      <c r="AF6" s="22" t="n">
-        <f aca="false">IFERROR((K6-AA6-AB6)/H6,0)</f>
+      <c r="AG6" s="22" t="n">
+        <f aca="false">IFERROR((K6-AB6-AC6)/H6,0)</f>
         <v>0.0502474226804124</v>
       </c>
-      <c r="AG6" s="25"/>
-      <c r="AH6" s="13" t="n">
+      <c r="AH6" s="25"/>
+      <c r="AI6" s="13" t="n">
         <v>29</v>
       </c>
-      <c r="AI6" s="25" t="s">
-        <v>234</v>
-      </c>
-      <c r="AJ6" s="32" t="s">
-        <v>140</v>
+      <c r="AJ6" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="AK6" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6353,19 +6379,19 @@
         <v>2</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D7" s="35" t="s">
         <v>18</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F7" s="34" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G7" s="36" t="n">
         <v>500000</v>
@@ -6384,93 +6410,94 @@
         <v>85000</v>
       </c>
       <c r="L7" s="34" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M7" s="35" t="s">
         <v>70</v>
       </c>
       <c r="N7" s="35" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O7" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="P7" s="35" t="s">
+      <c r="P7" s="36"/>
+      <c r="Q7" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="Q7" s="39" t="n">
+      <c r="R7" s="39" t="n">
         <f aca="false">H7*(1-J7)</f>
         <v>363750</v>
       </c>
-      <c r="R7" s="40" t="n">
+      <c r="S7" s="40" t="n">
         <f aca="false">IF((1-J7)&gt;0.75,Assumptions!$C$11,IF((1-J7)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S7" s="39" t="n">
-        <f aca="false">PMT(R7/12,Assumptions!$C$14,-Q7)</f>
+      <c r="T7" s="39" t="n">
+        <f aca="false">PMT(S7/12,Assumptions!$C$14,-R7)</f>
         <v>2481.4162187044</v>
       </c>
-      <c r="T7" s="39" t="n">
+      <c r="U7" s="39" t="n">
         <f aca="false">H7*INDEX(Assumptions!$C$28:$C$33,MATCH(D7,Assumptions!$B$28:$B$33,0))/12</f>
         <v>646.666666666667</v>
       </c>
-      <c r="U7" s="39" t="n">
-        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D7,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M7,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="V7" s="39" t="n">
+        <f aca="false">IF(ISNUMBER(P7),P7,INDEX(Assumptions!$D$28:$D$33,MATCH(D7,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M7,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>750</v>
       </c>
-      <c r="V7" s="39" t="n">
-        <f aca="false">S7+T7+U7+O7</f>
+      <c r="W7" s="39" t="n">
+        <f aca="false">T7+U7+V7+O7</f>
         <v>3878.08288537106</v>
       </c>
-      <c r="W7" s="41" t="n">
-        <f aca="false">IFERROR(K7/12/V7,0)</f>
+      <c r="X7" s="41" t="n">
+        <f aca="false">IFERROR(K7/12/W7,0)</f>
         <v>1.8265038532449</v>
       </c>
-      <c r="X7" s="41" t="n">
-        <f aca="false">IFERROR(K7*Assumptions!$C$18/12/V7,0)</f>
+      <c r="Y7" s="41" t="n">
+        <f aca="false">IFERROR(K7*Assumptions!$C$18/12/W7,0)</f>
         <v>1.46120308259592</v>
       </c>
-      <c r="Y7" s="39" t="n">
+      <c r="Z7" s="39" t="n">
         <f aca="false">H7*J7+H7*(Assumptions!$C$16-I7)</f>
         <v>140650</v>
       </c>
-      <c r="Z7" s="39" t="n">
-        <f aca="false">V7*Assumptions!$C$17</f>
+      <c r="AA7" s="39" t="n">
+        <f aca="false">W7*Assumptions!$C$17</f>
         <v>23268.4973122264</v>
       </c>
-      <c r="AA7" s="39" t="n">
-        <f aca="false">K7*INDEX(Assumptions!$H$36:$H$37,MATCH(P7,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N7="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
+      <c r="AB7" s="39" t="n">
+        <f aca="false">K7*INDEX(Assumptions!$H$36:$H$37,MATCH(Q7,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N7="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>37050</v>
       </c>
-      <c r="AB7" s="39" t="n">
-        <f aca="false">K7*INDEX(Assumptions!$C$36:$C$37,MATCH(P7,Assumptions!$B$36:$B$37,0))</f>
+      <c r="AC7" s="39" t="n">
+        <f aca="false">K7*INDEX(Assumptions!$C$36:$C$37,MATCH(Q7,Assumptions!$B$36:$B$37,0))</f>
         <v>17000</v>
       </c>
-      <c r="AC7" s="39" t="n">
-        <f aca="false">K7-AA7-V7*12</f>
+      <c r="AD7" s="39" t="n">
+        <f aca="false">K7-AB7-W7*12</f>
         <v>1413.00537554723</v>
       </c>
-      <c r="AD7" s="39" t="n">
-        <f aca="false">AC7-AB7</f>
+      <c r="AE7" s="39" t="n">
+        <f aca="false">AD7-AC7</f>
         <v>-15586.9946244528</v>
       </c>
-      <c r="AE7" s="42" t="n">
+      <c r="AF7" s="42" t="n">
         <f aca="false">IFERROR(K7/H7,0)</f>
         <v>0.175257731958763</v>
       </c>
-      <c r="AF7" s="42" t="n">
-        <f aca="false">IFERROR((K7-AA7-AB7)/H7,0)</f>
+      <c r="AG7" s="42" t="n">
+        <f aca="false">IFERROR((K7-AB7-AC7)/H7,0)</f>
         <v>0.0638144329896907</v>
       </c>
-      <c r="AG7" s="34"/>
-      <c r="AH7" s="33" t="n">
+      <c r="AH7" s="34"/>
+      <c r="AI7" s="33" t="n">
         <v>18</v>
       </c>
-      <c r="AI7" s="34" t="s">
-        <v>239</v>
-      </c>
-      <c r="AJ7" s="43" t="s">
-        <v>140</v>
+      <c r="AJ7" s="34" t="s">
+        <v>240</v>
+      </c>
+      <c r="AK7" s="43" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6478,19 +6505,19 @@
         <v>3</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D8" s="26" t="s">
         <v>18</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G8" s="19" t="n">
         <v>359000</v>
@@ -6509,93 +6536,94 @@
         <v>51000</v>
       </c>
       <c r="L8" s="25" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M8" s="26" t="s">
         <v>70</v>
       </c>
       <c r="N8" s="26" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O8" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="P8" s="26" t="s">
+      <c r="P8" s="19"/>
+      <c r="Q8" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="Q8" s="21" t="n">
+      <c r="R8" s="21" t="n">
         <f aca="false">H8*(1-J8)</f>
         <v>255000</v>
       </c>
-      <c r="R8" s="28" t="n">
+      <c r="S8" s="28" t="n">
         <f aca="false">IF((1-J8)&gt;0.75,Assumptions!$C$11,IF((1-J8)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S8" s="21" t="n">
-        <f aca="false">PMT(R8/12,Assumptions!$C$14,-Q8)</f>
+      <c r="T8" s="21" t="n">
+        <f aca="false">PMT(S8/12,Assumptions!$C$14,-R8)</f>
         <v>1739.54951414329</v>
       </c>
-      <c r="T8" s="21" t="n">
+      <c r="U8" s="21" t="n">
         <f aca="false">H8*INDEX(Assumptions!$C$28:$C$33,MATCH(D8,Assumptions!$B$28:$B$33,0))/12</f>
         <v>453.333333333333</v>
       </c>
-      <c r="U8" s="21" t="n">
-        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D8,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M8,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="V8" s="21" t="n">
+        <f aca="false">IF(ISNUMBER(P8),P8,INDEX(Assumptions!$D$28:$D$33,MATCH(D8,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M8,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>750</v>
       </c>
-      <c r="V8" s="21" t="n">
-        <f aca="false">S8+T8+U8+O8</f>
+      <c r="W8" s="21" t="n">
+        <f aca="false">T8+U8+V8+O8</f>
         <v>2942.88284747662</v>
       </c>
-      <c r="W8" s="29" t="n">
-        <f aca="false">IFERROR(K8/12/V8,0)</f>
+      <c r="X8" s="29" t="n">
+        <f aca="false">IFERROR(K8/12/W8,0)</f>
         <v>1.4441621431326</v>
       </c>
-      <c r="X8" s="29" t="n">
-        <f aca="false">IFERROR(K8*Assumptions!$C$18/12/V8,0)</f>
+      <c r="Y8" s="29" t="n">
+        <f aca="false">IFERROR(K8*Assumptions!$C$18/12/W8,0)</f>
         <v>1.15532971450608</v>
       </c>
-      <c r="Y8" s="21" t="n">
+      <c r="Z8" s="21" t="n">
         <f aca="false">H8*J8+H8*(Assumptions!$C$16-I8)</f>
         <v>98600</v>
       </c>
-      <c r="Z8" s="21" t="n">
-        <f aca="false">V8*Assumptions!$C$17</f>
+      <c r="AA8" s="21" t="n">
+        <f aca="false">W8*Assumptions!$C$17</f>
         <v>17657.2970848597</v>
       </c>
-      <c r="AA8" s="21" t="n">
-        <f aca="false">K8*INDEX(Assumptions!$H$36:$H$37,MATCH(P8,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N8="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
+      <c r="AB8" s="21" t="n">
+        <f aca="false">K8*INDEX(Assumptions!$H$36:$H$37,MATCH(Q8,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N8="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>24030</v>
       </c>
-      <c r="AB8" s="21" t="n">
-        <f aca="false">K8*INDEX(Assumptions!$C$36:$C$37,MATCH(P8,Assumptions!$B$36:$B$37,0))</f>
+      <c r="AC8" s="21" t="n">
+        <f aca="false">K8*INDEX(Assumptions!$C$36:$C$37,MATCH(Q8,Assumptions!$B$36:$B$37,0))</f>
         <v>10200</v>
       </c>
-      <c r="AC8" s="21" t="n">
-        <f aca="false">K8-AA8-V8*12</f>
+      <c r="AD8" s="21" t="n">
+        <f aca="false">K8-AB8-W8*12</f>
         <v>-8344.59416971947</v>
       </c>
-      <c r="AD8" s="21" t="n">
-        <f aca="false">AC8-AB8</f>
+      <c r="AE8" s="21" t="n">
+        <f aca="false">AD8-AC8</f>
         <v>-18544.5941697195</v>
       </c>
-      <c r="AE8" s="22" t="n">
+      <c r="AF8" s="22" t="n">
         <f aca="false">IFERROR(K8/H8,0)</f>
         <v>0.15</v>
       </c>
-      <c r="AF8" s="22" t="n">
-        <f aca="false">IFERROR((K8-AA8-AB8)/H8,0)</f>
+      <c r="AG8" s="22" t="n">
+        <f aca="false">IFERROR((K8-AB8-AC8)/H8,0)</f>
         <v>0.0493235294117647</v>
       </c>
-      <c r="AG8" s="25"/>
-      <c r="AH8" s="13" t="n">
+      <c r="AH8" s="25"/>
+      <c r="AI8" s="13" t="n">
         <v>257</v>
       </c>
-      <c r="AI8" s="25" t="s">
-        <v>244</v>
-      </c>
-      <c r="AJ8" s="32" t="s">
-        <v>140</v>
+      <c r="AJ8" s="25" t="s">
+        <v>245</v>
+      </c>
+      <c r="AK8" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6603,19 +6631,19 @@
         <v>4</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D9" s="35" t="s">
         <v>18</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G9" s="36" t="n">
         <v>659900</v>
@@ -6634,93 +6662,94 @@
         <v>75000</v>
       </c>
       <c r="L9" s="34" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M9" s="35" t="s">
         <v>66</v>
       </c>
       <c r="N9" s="35" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O9" s="36" t="n">
         <v>961</v>
       </c>
-      <c r="P9" s="35" t="s">
+      <c r="P9" s="36"/>
+      <c r="Q9" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="Q9" s="39" t="n">
+      <c r="R9" s="39" t="n">
         <f aca="false">H9*(1-J9)</f>
         <v>480000</v>
       </c>
-      <c r="R9" s="40" t="n">
+      <c r="S9" s="40" t="n">
         <f aca="false">IF((1-J9)&gt;0.75,Assumptions!$C$11,IF((1-J9)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S9" s="39" t="n">
-        <f aca="false">PMT(R9/12,Assumptions!$C$14,-Q9)</f>
+      <c r="T9" s="39" t="n">
+        <f aca="false">PMT(S9/12,Assumptions!$C$14,-R9)</f>
         <v>3274.44614426972</v>
       </c>
-      <c r="T9" s="39" t="n">
+      <c r="U9" s="39" t="n">
         <f aca="false">H9*INDEX(Assumptions!$C$28:$C$33,MATCH(D9,Assumptions!$B$28:$B$33,0))/12</f>
         <v>853.333333333333</v>
       </c>
-      <c r="U9" s="39" t="n">
-        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D9,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M9,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="V9" s="39" t="n">
+        <f aca="false">IF(ISNUMBER(P9),P9,INDEX(Assumptions!$D$28:$D$33,MATCH(D9,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M9,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>958.333333333333</v>
       </c>
-      <c r="V9" s="39" t="n">
-        <f aca="false">S9+T9+U9+O9</f>
+      <c r="W9" s="39" t="n">
+        <f aca="false">T9+U9+V9+O9</f>
         <v>6047.11281093639</v>
       </c>
-      <c r="W9" s="41" t="n">
-        <f aca="false">IFERROR(K9/12/V9,0)</f>
+      <c r="X9" s="41" t="n">
+        <f aca="false">IFERROR(K9/12/W9,0)</f>
         <v>1.03355108386546</v>
       </c>
-      <c r="X9" s="41" t="n">
-        <f aca="false">IFERROR(K9*Assumptions!$C$18/12/V9,0)</f>
+      <c r="Y9" s="41" t="n">
+        <f aca="false">IFERROR(K9*Assumptions!$C$18/12/W9,0)</f>
         <v>0.826840867092367</v>
       </c>
-      <c r="Y9" s="39" t="n">
+      <c r="Z9" s="39" t="n">
         <f aca="false">H9*J9+H9*(Assumptions!$C$16-I9)</f>
         <v>185600</v>
       </c>
-      <c r="Z9" s="39" t="n">
-        <f aca="false">V9*Assumptions!$C$17</f>
+      <c r="AA9" s="39" t="n">
+        <f aca="false">W9*Assumptions!$C$17</f>
         <v>36282.6768656183</v>
       </c>
-      <c r="AA9" s="39" t="n">
-        <f aca="false">K9*INDEX(Assumptions!$H$36:$H$37,MATCH(P9,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N9="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
+      <c r="AB9" s="39" t="n">
+        <f aca="false">K9*INDEX(Assumptions!$H$36:$H$37,MATCH(Q9,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N9="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>31950</v>
       </c>
-      <c r="AB9" s="39" t="n">
-        <f aca="false">K9*INDEX(Assumptions!$C$36:$C$37,MATCH(P9,Assumptions!$B$36:$B$37,0))</f>
+      <c r="AC9" s="39" t="n">
+        <f aca="false">K9*INDEX(Assumptions!$C$36:$C$37,MATCH(Q9,Assumptions!$B$36:$B$37,0))</f>
         <v>15000</v>
       </c>
-      <c r="AC9" s="39" t="n">
-        <f aca="false">K9-AA9-V9*12</f>
+      <c r="AD9" s="39" t="n">
+        <f aca="false">K9-AB9-W9*12</f>
         <v>-29515.3537312367</v>
       </c>
-      <c r="AD9" s="39" t="n">
-        <f aca="false">AC9-AB9</f>
+      <c r="AE9" s="39" t="n">
+        <f aca="false">AD9-AC9</f>
         <v>-44515.3537312367</v>
       </c>
-      <c r="AE9" s="42" t="n">
+      <c r="AF9" s="42" t="n">
         <f aca="false">IFERROR(K9/H9,0)</f>
         <v>0.1171875</v>
       </c>
-      <c r="AF9" s="42" t="n">
-        <f aca="false">IFERROR((K9-AA9-AB9)/H9,0)</f>
+      <c r="AG9" s="42" t="n">
+        <f aca="false">IFERROR((K9-AB9-AC9)/H9,0)</f>
         <v>0.043828125</v>
       </c>
-      <c r="AG9" s="34"/>
-      <c r="AH9" s="33" t="n">
+      <c r="AH9" s="34"/>
+      <c r="AI9" s="33" t="n">
         <v>36</v>
       </c>
-      <c r="AI9" s="34" t="s">
-        <v>249</v>
-      </c>
-      <c r="AJ9" s="43" t="s">
-        <v>140</v>
+      <c r="AJ9" s="34" t="s">
+        <v>250</v>
+      </c>
+      <c r="AK9" s="43" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6728,19 +6757,19 @@
         <v>5</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D10" s="26" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G10" s="19" t="n">
         <v>575000</v>
@@ -6759,93 +6788,94 @@
         <v>59000</v>
       </c>
       <c r="L10" s="25" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M10" s="26" t="s">
         <v>66</v>
       </c>
       <c r="N10" s="26" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O10" s="19" t="n">
         <v>630</v>
       </c>
-      <c r="P10" s="26" t="s">
+      <c r="P10" s="19"/>
+      <c r="Q10" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="Q10" s="21" t="n">
+      <c r="R10" s="21" t="n">
         <f aca="false">H10*(1-J10)</f>
         <v>420000</v>
       </c>
-      <c r="R10" s="28" t="n">
+      <c r="S10" s="28" t="n">
         <f aca="false">IF((1-J10)&gt;0.75,Assumptions!$C$11,IF((1-J10)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S10" s="21" t="n">
-        <f aca="false">PMT(R10/12,Assumptions!$C$14,-Q10)</f>
+      <c r="T10" s="21" t="n">
+        <f aca="false">PMT(S10/12,Assumptions!$C$14,-R10)</f>
         <v>2865.14037623601</v>
       </c>
-      <c r="T10" s="21" t="n">
+      <c r="U10" s="21" t="n">
         <f aca="false">H10*INDEX(Assumptions!$C$28:$C$33,MATCH(D10,Assumptions!$B$28:$B$33,0))/12</f>
         <v>746.666666666667</v>
       </c>
-      <c r="U10" s="21" t="n">
-        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D10,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M10,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="V10" s="21" t="n">
+        <f aca="false">IF(ISNUMBER(P10),P10,INDEX(Assumptions!$D$28:$D$33,MATCH(D10,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M10,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>958.333333333333</v>
       </c>
-      <c r="V10" s="21" t="n">
-        <f aca="false">S10+T10+U10+O10</f>
+      <c r="W10" s="21" t="n">
+        <f aca="false">T10+U10+V10+O10</f>
         <v>5200.14037623601</v>
       </c>
-      <c r="W10" s="29" t="n">
-        <f aca="false">IFERROR(K10/12/V10,0)</f>
+      <c r="X10" s="29" t="n">
+        <f aca="false">IFERROR(K10/12/W10,0)</f>
         <v>0.945487296676686</v>
       </c>
-      <c r="X10" s="29" t="n">
-        <f aca="false">IFERROR(K10*Assumptions!$C$18/12/V10,0)</f>
+      <c r="Y10" s="29" t="n">
+        <f aca="false">IFERROR(K10*Assumptions!$C$18/12/W10,0)</f>
         <v>0.756389837341349</v>
       </c>
-      <c r="Y10" s="21" t="n">
+      <c r="Z10" s="21" t="n">
         <f aca="false">H10*J10+H10*(Assumptions!$C$16-I10)</f>
         <v>162400</v>
       </c>
-      <c r="Z10" s="21" t="n">
-        <f aca="false">V10*Assumptions!$C$17</f>
+      <c r="AA10" s="21" t="n">
+        <f aca="false">W10*Assumptions!$C$17</f>
         <v>31200.842257416</v>
       </c>
-      <c r="AA10" s="21" t="n">
-        <f aca="false">K10*INDEX(Assumptions!$H$36:$H$37,MATCH(P10,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N10="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
+      <c r="AB10" s="21" t="n">
+        <f aca="false">K10*INDEX(Assumptions!$H$36:$H$37,MATCH(Q10,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N10="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>26670</v>
       </c>
-      <c r="AB10" s="21" t="n">
-        <f aca="false">K10*INDEX(Assumptions!$C$36:$C$37,MATCH(P10,Assumptions!$B$36:$B$37,0))</f>
+      <c r="AC10" s="21" t="n">
+        <f aca="false">K10*INDEX(Assumptions!$C$36:$C$37,MATCH(Q10,Assumptions!$B$36:$B$37,0))</f>
         <v>11800</v>
       </c>
-      <c r="AC10" s="21" t="n">
-        <f aca="false">K10-AA10-V10*12</f>
+      <c r="AD10" s="21" t="n">
+        <f aca="false">K10-AB10-W10*12</f>
         <v>-30071.6845148321</v>
       </c>
-      <c r="AD10" s="21" t="n">
-        <f aca="false">AC10-AB10</f>
+      <c r="AE10" s="21" t="n">
+        <f aca="false">AD10-AC10</f>
         <v>-41871.6845148321</v>
       </c>
-      <c r="AE10" s="22" t="n">
+      <c r="AF10" s="22" t="n">
         <f aca="false">IFERROR(K10/H10,0)</f>
         <v>0.105357142857143</v>
       </c>
-      <c r="AF10" s="22" t="n">
-        <f aca="false">IFERROR((K10-AA10-AB10)/H10,0)</f>
+      <c r="AG10" s="22" t="n">
+        <f aca="false">IFERROR((K10-AB10-AC10)/H10,0)</f>
         <v>0.0366607142857143</v>
       </c>
-      <c r="AG10" s="25"/>
-      <c r="AH10" s="13" t="n">
+      <c r="AH10" s="25"/>
+      <c r="AI10" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="AI10" s="25" t="s">
-        <v>253</v>
-      </c>
-      <c r="AJ10" s="32" t="s">
-        <v>140</v>
+      <c r="AJ10" s="25" t="s">
+        <v>254</v>
+      </c>
+      <c r="AK10" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6853,19 +6883,19 @@
         <v>6</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D11" s="35" t="s">
         <v>18</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G11" s="36" t="n">
         <v>614999</v>
@@ -6884,93 +6914,94 @@
         <v>47890</v>
       </c>
       <c r="L11" s="34" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M11" s="35" t="s">
         <v>68</v>
       </c>
       <c r="N11" s="35" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O11" s="36" t="n">
         <v>835</v>
       </c>
-      <c r="P11" s="35" t="s">
+      <c r="P11" s="36"/>
+      <c r="Q11" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="Q11" s="39" t="n">
+      <c r="R11" s="39" t="n">
         <f aca="false">H11*(1-J11)</f>
         <v>442500</v>
       </c>
-      <c r="R11" s="40" t="n">
+      <c r="S11" s="40" t="n">
         <f aca="false">IF((1-J11)&gt;0.75,Assumptions!$C$11,IF((1-J11)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S11" s="39" t="n">
-        <f aca="false">PMT(R11/12,Assumptions!$C$14,-Q11)</f>
+      <c r="T11" s="39" t="n">
+        <f aca="false">PMT(S11/12,Assumptions!$C$14,-R11)</f>
         <v>3018.63003924865</v>
       </c>
-      <c r="T11" s="39" t="n">
+      <c r="U11" s="39" t="n">
         <f aca="false">H11*INDEX(Assumptions!$C$28:$C$33,MATCH(D11,Assumptions!$B$28:$B$33,0))/12</f>
         <v>786.666666666667</v>
       </c>
-      <c r="U11" s="39" t="n">
-        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D11,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M11,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="V11" s="39" t="n">
+        <f aca="false">IF(ISNUMBER(P11),P11,INDEX(Assumptions!$D$28:$D$33,MATCH(D11,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M11,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>1333.33333333333</v>
       </c>
-      <c r="V11" s="39" t="n">
-        <f aca="false">S11+T11+U11+O11</f>
+      <c r="W11" s="39" t="n">
+        <f aca="false">T11+U11+V11+O11</f>
         <v>5973.63003924865</v>
       </c>
-      <c r="W11" s="41" t="n">
-        <f aca="false">IFERROR(K11/12/V11,0)</f>
+      <c r="X11" s="41" t="n">
+        <f aca="false">IFERROR(K11/12/W11,0)</f>
         <v>0.668075074471015</v>
       </c>
-      <c r="X11" s="41" t="n">
-        <f aca="false">IFERROR(K11*Assumptions!$C$18/12/V11,0)</f>
+      <c r="Y11" s="41" t="n">
+        <f aca="false">IFERROR(K11*Assumptions!$C$18/12/W11,0)</f>
         <v>0.534460059576812</v>
       </c>
-      <c r="Y11" s="39" t="n">
+      <c r="Z11" s="39" t="n">
         <f aca="false">H11*J11+H11*(Assumptions!$C$16-I11)</f>
         <v>171100</v>
       </c>
-      <c r="Z11" s="39" t="n">
-        <f aca="false">V11*Assumptions!$C$17</f>
+      <c r="AA11" s="39" t="n">
+        <f aca="false">W11*Assumptions!$C$17</f>
         <v>35841.7802354919</v>
       </c>
-      <c r="AA11" s="39" t="n">
-        <f aca="false">K11*INDEX(Assumptions!$H$36:$H$37,MATCH(P11,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N11="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
+      <c r="AB11" s="39" t="n">
+        <f aca="false">K11*INDEX(Assumptions!$H$36:$H$37,MATCH(Q11,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N11="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>14862.4</v>
       </c>
-      <c r="AB11" s="39" t="n">
-        <f aca="false">K11*INDEX(Assumptions!$C$36:$C$37,MATCH(P11,Assumptions!$B$36:$B$37,0))</f>
+      <c r="AC11" s="39" t="n">
+        <f aca="false">K11*INDEX(Assumptions!$C$36:$C$37,MATCH(Q11,Assumptions!$B$36:$B$37,0))</f>
         <v>5746.8</v>
       </c>
-      <c r="AC11" s="39" t="n">
-        <f aca="false">K11-AA11-V11*12</f>
+      <c r="AD11" s="39" t="n">
+        <f aca="false">K11-AB11-W11*12</f>
         <v>-38655.9604709838</v>
       </c>
-      <c r="AD11" s="39" t="n">
-        <f aca="false">AC11-AB11</f>
+      <c r="AE11" s="39" t="n">
+        <f aca="false">AD11-AC11</f>
         <v>-44402.7604709838</v>
       </c>
-      <c r="AE11" s="42" t="n">
+      <c r="AF11" s="42" t="n">
         <f aca="false">IFERROR(K11/H11,0)</f>
         <v>0.0811694915254237</v>
       </c>
-      <c r="AF11" s="42" t="n">
-        <f aca="false">IFERROR((K11-AA11-AB11)/H11,0)</f>
+      <c r="AG11" s="42" t="n">
+        <f aca="false">IFERROR((K11-AB11-AC11)/H11,0)</f>
         <v>0.0462386440677966</v>
       </c>
-      <c r="AG11" s="34"/>
-      <c r="AH11" s="33" t="n">
+      <c r="AH11" s="34"/>
+      <c r="AI11" s="33" t="n">
         <v>152</v>
       </c>
-      <c r="AI11" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="AJ11" s="43" t="s">
-        <v>140</v>
+      <c r="AJ11" s="34" t="s">
+        <v>259</v>
+      </c>
+      <c r="AK11" s="43" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6978,19 +7009,19 @@
         <v>7</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D12" s="26" t="s">
         <v>18</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G12" s="19" t="n">
         <v>699000</v>
@@ -7009,98 +7040,99 @@
         <v>50000</v>
       </c>
       <c r="L12" s="25" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M12" s="26" t="s">
         <v>66</v>
       </c>
       <c r="N12" s="26" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O12" s="19" t="n">
         <v>1325</v>
       </c>
-      <c r="P12" s="26" t="s">
+      <c r="P12" s="19"/>
+      <c r="Q12" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="Q12" s="21" t="n">
+      <c r="R12" s="21" t="n">
         <f aca="false">H12*(1-J12)</f>
         <v>524250</v>
       </c>
-      <c r="R12" s="28" t="n">
+      <c r="S12" s="28" t="n">
         <f aca="false">IF((1-J12)&gt;0.75,Assumptions!$C$11,IF((1-J12)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S12" s="21" t="n">
-        <f aca="false">PMT(R12/12,Assumptions!$C$14,-Q12)</f>
+      <c r="T12" s="21" t="n">
+        <f aca="false">PMT(S12/12,Assumptions!$C$14,-R12)</f>
         <v>3576.30914819459</v>
       </c>
-      <c r="T12" s="21" t="n">
+      <c r="U12" s="21" t="n">
         <f aca="false">H12*INDEX(Assumptions!$C$28:$C$33,MATCH(D12,Assumptions!$B$28:$B$33,0))/12</f>
         <v>932</v>
       </c>
-      <c r="U12" s="21" t="n">
-        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D12,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M12,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="V12" s="21" t="n">
+        <f aca="false">IF(ISNUMBER(P12),P12,INDEX(Assumptions!$D$28:$D$33,MATCH(D12,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M12,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>958.333333333333</v>
       </c>
-      <c r="V12" s="21" t="n">
-        <f aca="false">S12+T12+U12+O12</f>
+      <c r="W12" s="21" t="n">
+        <f aca="false">T12+U12+V12+O12</f>
         <v>6791.64248152792</v>
       </c>
-      <c r="W12" s="29" t="n">
-        <f aca="false">IFERROR(K12/12/V12,0)</f>
+      <c r="X12" s="29" t="n">
+        <f aca="false">IFERROR(K12/12/W12,0)</f>
         <v>0.613499117186936</v>
       </c>
-      <c r="X12" s="29" t="n">
-        <f aca="false">IFERROR(K12*Assumptions!$C$18/12/V12,0)</f>
+      <c r="Y12" s="29" t="n">
+        <f aca="false">IFERROR(K12*Assumptions!$C$18/12/W12,0)</f>
         <v>0.490799293749548</v>
       </c>
-      <c r="Y12" s="21" t="n">
+      <c r="Z12" s="21" t="n">
         <f aca="false">H12*J12+H12*(Assumptions!$C$16-I12)</f>
         <v>202710</v>
       </c>
-      <c r="Z12" s="21" t="n">
-        <f aca="false">V12*Assumptions!$C$17</f>
+      <c r="AA12" s="21" t="n">
+        <f aca="false">W12*Assumptions!$C$17</f>
         <v>40749.8548891675</v>
       </c>
-      <c r="AA12" s="21" t="n">
-        <f aca="false">K12*INDEX(Assumptions!$H$36:$H$37,MATCH(P12,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N12="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
+      <c r="AB12" s="21" t="n">
+        <f aca="false">K12*INDEX(Assumptions!$H$36:$H$37,MATCH(Q12,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N12="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>23700</v>
       </c>
-      <c r="AB12" s="21" t="n">
-        <f aca="false">K12*INDEX(Assumptions!$C$36:$C$37,MATCH(P12,Assumptions!$B$36:$B$37,0))</f>
+      <c r="AC12" s="21" t="n">
+        <f aca="false">K12*INDEX(Assumptions!$C$36:$C$37,MATCH(Q12,Assumptions!$B$36:$B$37,0))</f>
         <v>10000</v>
       </c>
-      <c r="AC12" s="21" t="n">
-        <f aca="false">K12-AA12-V12*12</f>
+      <c r="AD12" s="21" t="n">
+        <f aca="false">K12-AB12-W12*12</f>
         <v>-55199.709778335</v>
       </c>
-      <c r="AD12" s="21" t="n">
-        <f aca="false">AC12-AB12</f>
+      <c r="AE12" s="21" t="n">
+        <f aca="false">AD12-AC12</f>
         <v>-65199.709778335</v>
       </c>
-      <c r="AE12" s="22" t="n">
+      <c r="AF12" s="22" t="n">
         <f aca="false">IFERROR(K12/H12,0)</f>
         <v>0.0715307582260372</v>
       </c>
-      <c r="AF12" s="22" t="n">
-        <f aca="false">IFERROR((K12-AA12-AB12)/H12,0)</f>
+      <c r="AG12" s="22" t="n">
+        <f aca="false">IFERROR((K12-AB12-AC12)/H12,0)</f>
         <v>0.0233190271816881</v>
       </c>
-      <c r="AG12" s="25"/>
-      <c r="AH12" s="13" t="n">
+      <c r="AH12" s="25"/>
+      <c r="AI12" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="AI12" s="25" t="s">
-        <v>263</v>
-      </c>
-      <c r="AJ12" s="32" t="s">
-        <v>140</v>
+      <c r="AJ12" s="25" t="s">
+        <v>264</v>
+      </c>
+      <c r="AK12" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7111,296 +7143,296 @@
         <v>4</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="AI16" s="3" t="s">
         <v>208</v>
       </c>
       <c r="AJ16" s="3" t="s">
         <v>209</v>
       </c>
+      <c r="AK16" s="3" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="25" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G17" s="19" t="n">
         <v>699000</v>
       </c>
       <c r="L17" s="25" t="s">
-        <v>267</v>
-      </c>
-      <c r="AI17" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ17" s="32" t="s">
-        <v>140</v>
+        <v>268</v>
+      </c>
+      <c r="AJ17" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK17" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="25" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C18" s="25" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G18" s="19" t="n">
         <v>629000</v>
       </c>
       <c r="L18" s="25" t="s">
-        <v>270</v>
-      </c>
-      <c r="AI18" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ18" s="32" t="s">
-        <v>140</v>
+        <v>271</v>
+      </c>
+      <c r="AJ18" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK18" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="25" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G19" s="19" t="n">
         <v>575000</v>
       </c>
       <c r="L19" s="25" t="s">
-        <v>273</v>
-      </c>
-      <c r="AI19" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ19" s="32" t="s">
-        <v>140</v>
+        <v>274</v>
+      </c>
+      <c r="AJ19" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK19" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="25" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G20" s="19" t="n">
         <v>599000</v>
       </c>
       <c r="L20" s="25" t="s">
-        <v>275</v>
-      </c>
-      <c r="AI20" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ20" s="32" t="s">
-        <v>140</v>
+        <v>276</v>
+      </c>
+      <c r="AJ20" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK20" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="25" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G21" s="19" t="n">
         <v>550000</v>
       </c>
       <c r="L21" s="25" t="s">
-        <v>278</v>
-      </c>
-      <c r="AI21" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ21" s="32" t="s">
-        <v>140</v>
+        <v>279</v>
+      </c>
+      <c r="AJ21" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK21" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="25" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G22" s="19" t="n">
         <v>425000</v>
       </c>
       <c r="L22" s="25" t="s">
-        <v>281</v>
-      </c>
-      <c r="AI22" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ22" s="32" t="s">
-        <v>140</v>
+        <v>282</v>
+      </c>
+      <c r="AJ22" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK22" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="25" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G23" s="19" t="n">
         <v>550000</v>
       </c>
       <c r="L23" s="25" t="s">
-        <v>284</v>
-      </c>
-      <c r="AI23" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ23" s="32" t="s">
-        <v>140</v>
+        <v>285</v>
+      </c>
+      <c r="AJ23" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK23" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="25" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G24" s="19" t="n">
         <v>524900</v>
       </c>
       <c r="L24" s="25" t="s">
-        <v>287</v>
-      </c>
-      <c r="AI24" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ24" s="32" t="s">
-        <v>140</v>
+        <v>288</v>
+      </c>
+      <c r="AJ24" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK24" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="25" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G25" s="19" t="n">
         <v>490000</v>
       </c>
       <c r="L25" s="25" t="s">
-        <v>290</v>
-      </c>
-      <c r="AI25" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ25" s="32" t="s">
-        <v>140</v>
+        <v>291</v>
+      </c>
+      <c r="AJ25" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK25" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="25" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G26" s="19" t="n">
         <v>585000</v>
       </c>
       <c r="L26" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="AI26" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ26" s="32" t="s">
-        <v>140</v>
+        <v>293</v>
+      </c>
+      <c r="AJ26" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK26" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="25" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G27" s="19" t="n">
         <v>520000</v>
       </c>
       <c r="L27" s="25" t="s">
-        <v>294</v>
-      </c>
-      <c r="AI27" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ27" s="32" t="s">
-        <v>140</v>
+        <v>295</v>
+      </c>
+      <c r="AJ27" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK27" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="25" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C28" s="25" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G28" s="19" t="n">
         <v>499900</v>
       </c>
       <c r="L28" s="25" t="s">
-        <v>297</v>
-      </c>
-      <c r="AI28" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ28" s="32" t="s">
-        <v>140</v>
+        <v>298</v>
+      </c>
+      <c r="AJ28" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK28" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="25" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G29" s="19" t="n">
         <v>594900</v>
       </c>
       <c r="L29" s="25" t="s">
-        <v>300</v>
-      </c>
-      <c r="AI29" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ29" s="32" t="s">
-        <v>140</v>
+        <v>301</v>
+      </c>
+      <c r="AJ29" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK29" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="25" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C30" s="25" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G30" s="19" t="n">
         <v>349900</v>
       </c>
       <c r="L30" s="25" t="s">
-        <v>303</v>
-      </c>
-      <c r="AI30" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ30" s="32" t="s">
-        <v>140</v>
+        <v>304</v>
+      </c>
+      <c r="AJ30" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK30" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -7409,7 +7441,7 @@
       <formula1>Assumptions!$B$22:$B$25</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="P6:P12" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="Q6:Q12" type="list">
       <formula1>"STR,Seasonal"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7419,27 +7451,27 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="AJ6" r:id="rId2" display="Zillow"/>
-    <hyperlink ref="AJ7" r:id="rId3" display="Zillow"/>
-    <hyperlink ref="AJ8" r:id="rId4" display="Zillow"/>
-    <hyperlink ref="AJ9" r:id="rId5" display="Zillow"/>
-    <hyperlink ref="AJ10" r:id="rId6" display="Zillow"/>
-    <hyperlink ref="AJ11" r:id="rId7" display="Zillow"/>
-    <hyperlink ref="AJ12" r:id="rId8" display="Zillow"/>
-    <hyperlink ref="AJ17" r:id="rId9" display="Zillow"/>
-    <hyperlink ref="AJ18" r:id="rId10" display="Zillow"/>
-    <hyperlink ref="AJ19" r:id="rId11" display="Zillow"/>
-    <hyperlink ref="AJ20" r:id="rId12" display="Zillow"/>
-    <hyperlink ref="AJ21" r:id="rId13" display="Zillow"/>
-    <hyperlink ref="AJ22" r:id="rId14" display="Zillow"/>
-    <hyperlink ref="AJ23" r:id="rId15" display="Zillow"/>
-    <hyperlink ref="AJ24" r:id="rId16" display="Zillow"/>
-    <hyperlink ref="AJ25" r:id="rId17" display="Zillow"/>
-    <hyperlink ref="AJ26" r:id="rId18" display="Zillow"/>
-    <hyperlink ref="AJ27" r:id="rId19" display="Zillow"/>
-    <hyperlink ref="AJ28" r:id="rId20" display="Zillow"/>
-    <hyperlink ref="AJ29" r:id="rId21" display="Zillow"/>
-    <hyperlink ref="AJ30" r:id="rId22" display="Zillow"/>
+    <hyperlink ref="AK6" r:id="rId2" display="Zillow"/>
+    <hyperlink ref="AK7" r:id="rId3" display="Zillow"/>
+    <hyperlink ref="AK8" r:id="rId4" display="Zillow"/>
+    <hyperlink ref="AK9" r:id="rId5" display="Zillow"/>
+    <hyperlink ref="AK10" r:id="rId6" display="Zillow"/>
+    <hyperlink ref="AK11" r:id="rId7" display="Zillow"/>
+    <hyperlink ref="AK12" r:id="rId8" display="Zillow"/>
+    <hyperlink ref="AK17" r:id="rId9" display="Zillow"/>
+    <hyperlink ref="AK18" r:id="rId10" display="Zillow"/>
+    <hyperlink ref="AK19" r:id="rId11" display="Zillow"/>
+    <hyperlink ref="AK20" r:id="rId12" display="Zillow"/>
+    <hyperlink ref="AK21" r:id="rId13" display="Zillow"/>
+    <hyperlink ref="AK22" r:id="rId14" display="Zillow"/>
+    <hyperlink ref="AK23" r:id="rId15" display="Zillow"/>
+    <hyperlink ref="AK24" r:id="rId16" display="Zillow"/>
+    <hyperlink ref="AK25" r:id="rId17" display="Zillow"/>
+    <hyperlink ref="AK26" r:id="rId18" display="Zillow"/>
+    <hyperlink ref="AK27" r:id="rId19" display="Zillow"/>
+    <hyperlink ref="AK28" r:id="rId20" display="Zillow"/>
+    <hyperlink ref="AK29" r:id="rId21" display="Zillow"/>
+    <hyperlink ref="AK30" r:id="rId22" display="Zillow"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7457,7 +7489,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AJ21"/>
+  <dimension ref="A1:AK21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -7473,34 +7505,36 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="19" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="31" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="20" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="32" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7557,7 +7591,7 @@
       <c r="P5" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="Q5" s="23" t="s">
+      <c r="Q5" s="3" t="s">
         <v>118</v>
       </c>
       <c r="R5" s="23" t="s">
@@ -7573,19 +7607,19 @@
         <v>122</v>
       </c>
       <c r="V5" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="W5" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="W5" s="23" t="s">
+      <c r="X5" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="X5" s="23" t="s">
+      <c r="Y5" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="Y5" s="23" t="s">
+      <c r="Z5" s="23" t="s">
         <v>10</v>
-      </c>
-      <c r="Z5" s="23" t="s">
-        <v>123</v>
       </c>
       <c r="AA5" s="23" t="s">
         <v>124</v>
@@ -7594,18 +7628,18 @@
         <v>125</v>
       </c>
       <c r="AC5" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="AD5" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="AD5" s="23" t="s">
+      <c r="AE5" s="23" t="s">
         <v>12</v>
-      </c>
-      <c r="AE5" s="23" t="s">
-        <v>126</v>
       </c>
       <c r="AF5" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="AG5" s="3" t="s">
+      <c r="AG5" s="23" t="s">
         <v>128</v>
       </c>
       <c r="AH5" s="3" t="s">
@@ -7616,6 +7650,9 @@
       </c>
       <c r="AJ5" s="3" t="s">
         <v>131</v>
+      </c>
+      <c r="AK5" s="3" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7623,19 +7660,19 @@
         <v>1</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D6" s="26" t="s">
         <v>80</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G6" s="19" t="n">
         <v>475000</v>
@@ -7654,93 +7691,94 @@
         <v>60000</v>
       </c>
       <c r="L6" s="25" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M6" s="26" t="s">
         <v>70</v>
       </c>
       <c r="N6" s="26" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O6" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="P6" s="26" t="s">
+      <c r="P6" s="19"/>
+      <c r="Q6" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="Q6" s="21" t="n">
+      <c r="R6" s="21" t="n">
         <f aca="false">H6*(1-J6)</f>
         <v>345000</v>
       </c>
-      <c r="R6" s="28" t="n">
+      <c r="S6" s="28" t="n">
         <f aca="false">IF((1-J6)&gt;0.75,Assumptions!$C$11,IF((1-J6)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S6" s="21" t="n">
-        <f aca="false">PMT(R6/12,Assumptions!$C$14,-Q6)</f>
+      <c r="T6" s="21" t="n">
+        <f aca="false">PMT(S6/12,Assumptions!$C$14,-R6)</f>
         <v>2353.50816619386</v>
       </c>
-      <c r="T6" s="21" t="n">
+      <c r="U6" s="21" t="n">
         <f aca="false">H6*INDEX(Assumptions!$C$28:$C$33,MATCH(D6,Assumptions!$B$28:$B$33,0))/12</f>
         <v>651.666666666667</v>
       </c>
-      <c r="U6" s="21" t="n">
-        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D6,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M6,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="V6" s="21" t="n">
+        <f aca="false">IF(ISNUMBER(P6),P6,INDEX(Assumptions!$D$28:$D$33,MATCH(D6,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M6,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>750</v>
       </c>
-      <c r="V6" s="21" t="n">
-        <f aca="false">S6+T6+U6+O6</f>
+      <c r="W6" s="21" t="n">
+        <f aca="false">T6+U6+V6+O6</f>
         <v>3755.17483286053</v>
       </c>
-      <c r="W6" s="29" t="n">
-        <f aca="false">IFERROR(K6/12/V6,0)</f>
+      <c r="X6" s="29" t="n">
+        <f aca="false">IFERROR(K6/12/W6,0)</f>
         <v>1.33149592829776</v>
       </c>
-      <c r="X6" s="29" t="n">
-        <f aca="false">IFERROR(K6*Assumptions!$C$18/12/V6,0)</f>
+      <c r="Y6" s="29" t="n">
+        <f aca="false">IFERROR(K6*Assumptions!$C$18/12/W6,0)</f>
         <v>1.0651967426382</v>
       </c>
-      <c r="Y6" s="21" t="n">
+      <c r="Z6" s="21" t="n">
         <f aca="false">H6*J6+H6*(Assumptions!$C$16-I6)</f>
         <v>133400</v>
       </c>
-      <c r="Z6" s="21" t="n">
-        <f aca="false">V6*Assumptions!$C$17</f>
+      <c r="AA6" s="21" t="n">
+        <f aca="false">W6*Assumptions!$C$17</f>
         <v>22531.0489971632</v>
       </c>
-      <c r="AA6" s="21" t="n">
-        <f aca="false">K6*INDEX(Assumptions!$H$36:$H$37,MATCH(P6,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N6="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
+      <c r="AB6" s="21" t="n">
+        <f aca="false">K6*INDEX(Assumptions!$H$36:$H$37,MATCH(Q6,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N6="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>28800</v>
       </c>
-      <c r="AB6" s="21" t="n">
-        <f aca="false">K6*INDEX(Assumptions!$C$36:$C$37,MATCH(P6,Assumptions!$B$36:$B$37,0))</f>
+      <c r="AC6" s="21" t="n">
+        <f aca="false">K6*INDEX(Assumptions!$C$36:$C$37,MATCH(Q6,Assumptions!$B$36:$B$37,0))</f>
         <v>12000</v>
       </c>
-      <c r="AC6" s="21" t="n">
-        <f aca="false">K6-AA6-V6*12</f>
+      <c r="AD6" s="21" t="n">
+        <f aca="false">K6-AB6-W6*12</f>
         <v>-13862.0979943264</v>
       </c>
-      <c r="AD6" s="21" t="n">
-        <f aca="false">AC6-AB6</f>
+      <c r="AE6" s="21" t="n">
+        <f aca="false">AD6-AC6</f>
         <v>-25862.0979943264</v>
       </c>
-      <c r="AE6" s="22" t="n">
+      <c r="AF6" s="22" t="n">
         <f aca="false">IFERROR(K6/H6,0)</f>
         <v>0.130434782608696</v>
       </c>
-      <c r="AF6" s="22" t="n">
-        <f aca="false">IFERROR((K6-AA6-AB6)/H6,0)</f>
+      <c r="AG6" s="22" t="n">
+        <f aca="false">IFERROR((K6-AB6-AC6)/H6,0)</f>
         <v>0.0417391304347826</v>
       </c>
-      <c r="AG6" s="25"/>
-      <c r="AH6" s="13" t="n">
+      <c r="AH6" s="25"/>
+      <c r="AI6" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="AI6" s="25" t="s">
-        <v>310</v>
-      </c>
-      <c r="AJ6" s="32" t="s">
-        <v>140</v>
+      <c r="AJ6" s="25" t="s">
+        <v>311</v>
+      </c>
+      <c r="AK6" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7748,19 +7786,19 @@
         <v>2</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D7" s="35" t="s">
         <v>80</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F7" s="34" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G7" s="36" t="n">
         <v>589900</v>
@@ -7779,93 +7817,94 @@
         <v>60000</v>
       </c>
       <c r="L7" s="34" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M7" s="35" t="s">
         <v>66</v>
       </c>
       <c r="N7" s="35" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O7" s="36" t="n">
         <v>583</v>
       </c>
-      <c r="P7" s="35" t="s">
+      <c r="P7" s="36"/>
+      <c r="Q7" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="Q7" s="39" t="n">
+      <c r="R7" s="39" t="n">
         <f aca="false">H7*(1-J7)</f>
         <v>442425</v>
       </c>
-      <c r="R7" s="40" t="n">
+      <c r="S7" s="40" t="n">
         <f aca="false">IF((1-J7)&gt;0.75,Assumptions!$C$11,IF((1-J7)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S7" s="39" t="n">
-        <f aca="false">PMT(R7/12,Assumptions!$C$14,-Q7)</f>
+      <c r="T7" s="39" t="n">
+        <f aca="false">PMT(S7/12,Assumptions!$C$14,-R7)</f>
         <v>3018.11840703861</v>
       </c>
-      <c r="T7" s="39" t="n">
+      <c r="U7" s="39" t="n">
         <f aca="false">H7*INDEX(Assumptions!$C$28:$C$33,MATCH(D7,Assumptions!$B$28:$B$33,0))/12</f>
         <v>835.691666666667</v>
       </c>
-      <c r="U7" s="39" t="n">
-        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D7,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M7,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="V7" s="39" t="n">
+        <f aca="false">IF(ISNUMBER(P7),P7,INDEX(Assumptions!$D$28:$D$33,MATCH(D7,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M7,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>958.333333333333</v>
       </c>
-      <c r="V7" s="39" t="n">
-        <f aca="false">S7+T7+U7+O7</f>
+      <c r="W7" s="39" t="n">
+        <f aca="false">T7+U7+V7+O7</f>
         <v>5395.14340703861</v>
       </c>
-      <c r="W7" s="41" t="n">
-        <f aca="false">IFERROR(K7/12/V7,0)</f>
+      <c r="X7" s="41" t="n">
+        <f aca="false">IFERROR(K7/12/W7,0)</f>
         <v>0.926759424684969</v>
       </c>
-      <c r="X7" s="41" t="n">
-        <f aca="false">IFERROR(K7*Assumptions!$C$18/12/V7,0)</f>
+      <c r="Y7" s="41" t="n">
+        <f aca="false">IFERROR(K7*Assumptions!$C$18/12/W7,0)</f>
         <v>0.741407539747975</v>
       </c>
-      <c r="Y7" s="39" t="n">
+      <c r="Z7" s="39" t="n">
         <f aca="false">H7*J7+H7*(Assumptions!$C$16-I7)</f>
         <v>171071</v>
       </c>
-      <c r="Z7" s="39" t="n">
-        <f aca="false">V7*Assumptions!$C$17</f>
+      <c r="AA7" s="39" t="n">
+        <f aca="false">W7*Assumptions!$C$17</f>
         <v>32370.8604422316</v>
       </c>
-      <c r="AA7" s="39" t="n">
-        <f aca="false">K7*INDEX(Assumptions!$H$36:$H$37,MATCH(P7,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N7="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
+      <c r="AB7" s="39" t="n">
+        <f aca="false">K7*INDEX(Assumptions!$H$36:$H$37,MATCH(Q7,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N7="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>27000</v>
       </c>
-      <c r="AB7" s="39" t="n">
-        <f aca="false">K7*INDEX(Assumptions!$C$36:$C$37,MATCH(P7,Assumptions!$B$36:$B$37,0))</f>
+      <c r="AC7" s="39" t="n">
+        <f aca="false">K7*INDEX(Assumptions!$C$36:$C$37,MATCH(Q7,Assumptions!$B$36:$B$37,0))</f>
         <v>12000</v>
       </c>
-      <c r="AC7" s="39" t="n">
-        <f aca="false">K7-AA7-V7*12</f>
+      <c r="AD7" s="39" t="n">
+        <f aca="false">K7-AB7-W7*12</f>
         <v>-31741.7208844633</v>
       </c>
-      <c r="AD7" s="39" t="n">
-        <f aca="false">AC7-AB7</f>
+      <c r="AE7" s="39" t="n">
+        <f aca="false">AD7-AC7</f>
         <v>-43741.7208844633</v>
       </c>
-      <c r="AE7" s="42" t="n">
+      <c r="AF7" s="42" t="n">
         <f aca="false">IFERROR(K7/H7,0)</f>
         <v>0.101712154602475</v>
       </c>
-      <c r="AF7" s="42" t="n">
-        <f aca="false">IFERROR((K7-AA7-AB7)/H7,0)</f>
+      <c r="AG7" s="42" t="n">
+        <f aca="false">IFERROR((K7-AB7-AC7)/H7,0)</f>
         <v>0.0355992541108663</v>
       </c>
-      <c r="AG7" s="34"/>
-      <c r="AH7" s="33" t="n">
+      <c r="AH7" s="34"/>
+      <c r="AI7" s="33" t="n">
         <v>23</v>
       </c>
-      <c r="AI7" s="34" t="s">
-        <v>315</v>
-      </c>
-      <c r="AJ7" s="43" t="s">
-        <v>140</v>
+      <c r="AJ7" s="34" t="s">
+        <v>316</v>
+      </c>
+      <c r="AK7" s="43" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7873,19 +7912,19 @@
         <v>3</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D8" s="26" t="s">
         <v>82</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G8" s="19" t="n">
         <v>530000</v>
@@ -7904,98 +7943,99 @@
         <v>29250</v>
       </c>
       <c r="L8" s="25" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M8" s="26" t="s">
         <v>70</v>
       </c>
       <c r="N8" s="26" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O8" s="19" t="n">
         <v>520</v>
       </c>
-      <c r="P8" s="26" t="s">
+      <c r="P8" s="19"/>
+      <c r="Q8" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="Q8" s="21" t="n">
+      <c r="R8" s="21" t="n">
         <f aca="false">H8*(1-J8)</f>
         <v>397500</v>
       </c>
-      <c r="R8" s="28" t="n">
+      <c r="S8" s="28" t="n">
         <f aca="false">IF((1-J8)&gt;0.75,Assumptions!$C$11,IF((1-J8)&gt;0.7,Assumptions!$C$12,Assumptions!$C$13))</f>
         <v>0.0725</v>
       </c>
-      <c r="S8" s="21" t="n">
-        <f aca="false">PMT(R8/12,Assumptions!$C$14,-Q8)</f>
+      <c r="T8" s="21" t="n">
+        <f aca="false">PMT(S8/12,Assumptions!$C$14,-R8)</f>
         <v>2711.65071322336</v>
       </c>
-      <c r="T8" s="21" t="n">
+      <c r="U8" s="21" t="n">
         <f aca="false">H8*INDEX(Assumptions!$C$28:$C$33,MATCH(D8,Assumptions!$B$28:$B$33,0))/12</f>
         <v>728.75</v>
       </c>
-      <c r="U8" s="21" t="n">
-        <f aca="false">(INDEX(Assumptions!$D$28:$D$33,MATCH(D8,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M8,Assumptions!$B$22:$B$25,0)))/12</f>
+      <c r="V8" s="21" t="n">
+        <f aca="false">IF(ISNUMBER(P8),P8,INDEX(Assumptions!$D$28:$D$33,MATCH(D8,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M8,Assumptions!$B$22:$B$25,0)))/12</f>
         <v>750</v>
       </c>
-      <c r="V8" s="21" t="n">
-        <f aca="false">S8+T8+U8+O8</f>
+      <c r="W8" s="21" t="n">
+        <f aca="false">T8+U8+V8+O8</f>
         <v>4710.40071322336</v>
       </c>
-      <c r="W8" s="29" t="n">
-        <f aca="false">IFERROR(K8/12/V8,0)</f>
+      <c r="X8" s="29" t="n">
+        <f aca="false">IFERROR(K8/12/W8,0)</f>
         <v>0.51747189854937</v>
       </c>
-      <c r="X8" s="29" t="n">
-        <f aca="false">IFERROR(K8*Assumptions!$C$18/12/V8,0)</f>
+      <c r="Y8" s="29" t="n">
+        <f aca="false">IFERROR(K8*Assumptions!$C$18/12/W8,0)</f>
         <v>0.413977518839496</v>
       </c>
-      <c r="Y8" s="21" t="n">
+      <c r="Z8" s="21" t="n">
         <f aca="false">H8*J8+H8*(Assumptions!$C$16-I8)</f>
         <v>153700</v>
       </c>
-      <c r="Z8" s="21" t="n">
-        <f aca="false">V8*Assumptions!$C$17</f>
+      <c r="AA8" s="21" t="n">
+        <f aca="false">W8*Assumptions!$C$17</f>
         <v>28262.4042793402</v>
       </c>
-      <c r="AA8" s="21" t="n">
-        <f aca="false">K8*INDEX(Assumptions!$H$36:$H$37,MATCH(P8,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N8="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
+      <c r="AB8" s="21" t="n">
+        <f aca="false">K8*INDEX(Assumptions!$H$36:$H$37,MATCH(Q8,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(N8="Y",Assumptions!$C$41,Assumptions!$C$42)</f>
         <v>11880</v>
       </c>
-      <c r="AB8" s="21" t="n">
-        <f aca="false">K8*INDEX(Assumptions!$C$36:$C$37,MATCH(P8,Assumptions!$B$36:$B$37,0))</f>
+      <c r="AC8" s="21" t="n">
+        <f aca="false">K8*INDEX(Assumptions!$C$36:$C$37,MATCH(Q8,Assumptions!$B$36:$B$37,0))</f>
         <v>3510</v>
       </c>
-      <c r="AC8" s="21" t="n">
-        <f aca="false">K8-AA8-V8*12</f>
+      <c r="AD8" s="21" t="n">
+        <f aca="false">K8-AB8-W8*12</f>
         <v>-39154.8085586803</v>
       </c>
-      <c r="AD8" s="21" t="n">
-        <f aca="false">AC8-AB8</f>
+      <c r="AE8" s="21" t="n">
+        <f aca="false">AD8-AC8</f>
         <v>-42664.8085586803</v>
       </c>
-      <c r="AE8" s="22" t="n">
+      <c r="AF8" s="22" t="n">
         <f aca="false">IFERROR(K8/H8,0)</f>
         <v>0.055188679245283</v>
       </c>
-      <c r="AF8" s="22" t="n">
-        <f aca="false">IFERROR((K8-AA8-AB8)/H8,0)</f>
+      <c r="AG8" s="22" t="n">
+        <f aca="false">IFERROR((K8-AB8-AC8)/H8,0)</f>
         <v>0.0261509433962264</v>
       </c>
-      <c r="AG8" s="25"/>
-      <c r="AH8" s="13" t="n">
+      <c r="AH8" s="25"/>
+      <c r="AI8" s="13" t="n">
         <v>126</v>
       </c>
-      <c r="AI8" s="25" t="s">
-        <v>320</v>
-      </c>
-      <c r="AJ8" s="32" t="s">
-        <v>140</v>
+      <c r="AJ8" s="25" t="s">
+        <v>321</v>
+      </c>
+      <c r="AK8" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8006,196 +8046,196 @@
         <v>4</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="AI12" s="3" t="s">
         <v>208</v>
       </c>
       <c r="AJ12" s="3" t="s">
         <v>209</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="25" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G13" s="19" t="n">
         <v>599000</v>
       </c>
       <c r="L13" s="25" t="s">
-        <v>324</v>
-      </c>
-      <c r="AI13" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ13" s="32" t="s">
-        <v>140</v>
+        <v>325</v>
+      </c>
+      <c r="AJ13" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK13" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="25" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G14" s="19" t="n">
         <v>542500</v>
       </c>
       <c r="L14" s="25" t="s">
-        <v>327</v>
-      </c>
-      <c r="AI14" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ14" s="32" t="s">
-        <v>140</v>
+        <v>328</v>
+      </c>
+      <c r="AJ14" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK14" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="25" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G15" s="19" t="n">
         <v>599900</v>
       </c>
       <c r="L15" s="25" t="s">
-        <v>329</v>
-      </c>
-      <c r="AI15" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ15" s="32" t="s">
-        <v>140</v>
+        <v>330</v>
+      </c>
+      <c r="AJ15" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK15" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="25" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G16" s="19" t="n">
         <v>659900</v>
       </c>
       <c r="L16" s="25" t="s">
-        <v>331</v>
-      </c>
-      <c r="AI16" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ16" s="32" t="s">
-        <v>140</v>
+        <v>332</v>
+      </c>
+      <c r="AJ16" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK16" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="25" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G17" s="19" t="n">
         <v>390000</v>
       </c>
       <c r="L17" s="25" t="s">
-        <v>333</v>
-      </c>
-      <c r="AI17" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ17" s="32" t="s">
-        <v>140</v>
+        <v>334</v>
+      </c>
+      <c r="AJ17" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK17" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="25" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C18" s="25" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G18" s="19" t="n">
         <v>599000</v>
       </c>
       <c r="L18" s="25" t="s">
-        <v>336</v>
-      </c>
-      <c r="AI18" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ18" s="32" t="s">
-        <v>140</v>
+        <v>337</v>
+      </c>
+      <c r="AJ18" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK18" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="25" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G19" s="19" t="n">
         <v>659000</v>
       </c>
       <c r="L19" s="25" t="s">
-        <v>339</v>
-      </c>
-      <c r="AI19" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ19" s="32" t="s">
-        <v>140</v>
+        <v>340</v>
+      </c>
+      <c r="AJ19" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK19" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="25" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G20" s="19" t="n">
         <v>449900</v>
       </c>
       <c r="L20" s="25" t="s">
-        <v>342</v>
-      </c>
-      <c r="AI20" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ20" s="32" t="s">
-        <v>140</v>
+        <v>343</v>
+      </c>
+      <c r="AJ20" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK20" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="25" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G21" s="19" t="n">
         <v>665000</v>
       </c>
       <c r="L21" s="25" t="s">
-        <v>345</v>
-      </c>
-      <c r="AI21" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ21" s="32" t="s">
-        <v>140</v>
+        <v>346</v>
+      </c>
+      <c r="AJ21" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK21" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -8204,7 +8244,7 @@
       <formula1>Assumptions!$B$22:$B$25</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="P6:P8" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="Q6:Q8" type="list">
       <formula1>"STR,Seasonal"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -8214,18 +8254,18 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="AJ6" r:id="rId1" display="Zillow"/>
-    <hyperlink ref="AJ7" r:id="rId2" display="Zillow"/>
-    <hyperlink ref="AJ8" r:id="rId3" display="Zillow"/>
-    <hyperlink ref="AJ13" r:id="rId4" display="Zillow"/>
-    <hyperlink ref="AJ14" r:id="rId5" display="Zillow"/>
-    <hyperlink ref="AJ15" r:id="rId6" display="Zillow"/>
-    <hyperlink ref="AJ16" r:id="rId7" display="Zillow"/>
-    <hyperlink ref="AJ17" r:id="rId8" display="Zillow"/>
-    <hyperlink ref="AJ18" r:id="rId9" display="Zillow"/>
-    <hyperlink ref="AJ19" r:id="rId10" display="Zillow"/>
-    <hyperlink ref="AJ20" r:id="rId11" display="Zillow"/>
-    <hyperlink ref="AJ21" r:id="rId12" display="Zillow"/>
+    <hyperlink ref="AK6" r:id="rId1" display="Zillow"/>
+    <hyperlink ref="AK7" r:id="rId2" display="Zillow"/>
+    <hyperlink ref="AK8" r:id="rId3" display="Zillow"/>
+    <hyperlink ref="AK13" r:id="rId4" display="Zillow"/>
+    <hyperlink ref="AK14" r:id="rId5" display="Zillow"/>
+    <hyperlink ref="AK15" r:id="rId6" display="Zillow"/>
+    <hyperlink ref="AK16" r:id="rId7" display="Zillow"/>
+    <hyperlink ref="AK17" r:id="rId8" display="Zillow"/>
+    <hyperlink ref="AK18" r:id="rId9" display="Zillow"/>
+    <hyperlink ref="AK19" r:id="rId10" display="Zillow"/>
+    <hyperlink ref="AK20" r:id="rId11" display="Zillow"/>
+    <hyperlink ref="AK21" r:id="rId12" display="Zillow"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -8262,20 +8302,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>5</v>
@@ -8284,16 +8324,16 @@
         <v>110</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>7</v>
@@ -8302,10 +8342,10 @@
         <v>8</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>11</v>
@@ -8314,10 +8354,10 @@
         <v>12</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8353,7 +8393,7 @@
         <v>3132.48099831645</v>
       </c>
       <c r="I5" s="21" t="n">
-        <f aca="false">H5+C5*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$6,Assumptions!$B$28:$B$33,0))/12+(INDEX(Assumptions!$D$28:$D$33,MATCH('Manatee-Sarasota'!$D$6,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$6,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$6</f>
+        <f aca="false">H5+C5*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$6,Assumptions!$B$28:$B$33,0))/12+IF(ISNUMBER('Manatee-Sarasota'!$P$6),'Manatee-Sarasota'!$P$6,INDEX(Assumptions!$D$28:$D$33,MATCH('Manatee-Sarasota'!$D$6,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$6,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$6</f>
         <v>4582.48099831645</v>
       </c>
       <c r="J5" s="29" t="n">
@@ -8369,11 +8409,11 @@
         <v>117600</v>
       </c>
       <c r="M5" s="21" t="n">
-        <f aca="false">E5-(E5*INDEX(Assumptions!$H$36:$H$37,MATCH('Manatee-Sarasota'!$P$6,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF('Manatee-Sarasota'!$N$6="Y",Assumptions!$C$41,Assumptions!$C$42))-I5*12</f>
+        <f aca="false">E5-(E5*INDEX(Assumptions!$H$36:$H$37,MATCH('Manatee-Sarasota'!$Q$6,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF('Manatee-Sarasota'!$N$6="Y",Assumptions!$C$41,Assumptions!$C$42))-I5*12</f>
         <v>-7039.77197979741</v>
       </c>
       <c r="N5" s="21" t="n">
-        <f aca="false">M5-E5*INDEX(Assumptions!$C$36:$C$37,MATCH('Manatee-Sarasota'!$P$6,Assumptions!$B$36:$B$37,0))</f>
+        <f aca="false">M5-E5*INDEX(Assumptions!$C$36:$C$37,MATCH('Manatee-Sarasota'!$Q$6,Assumptions!$B$36:$B$37,0))</f>
         <v>-24039.7719797974</v>
       </c>
       <c r="O5" s="22" t="n">
@@ -8381,7 +8421,7 @@
         <v>-0.0598620066309303</v>
       </c>
       <c r="P5" s="46" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8417,7 +8457,7 @@
         <v>2865.14037623601</v>
       </c>
       <c r="I6" s="21" t="n">
-        <f aca="false">H6+C6*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$6,Assumptions!$B$28:$B$33,0))/12+(INDEX(Assumptions!$D$28:$D$33,MATCH('Manatee-Sarasota'!$D$6,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$6,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$6</f>
+        <f aca="false">H6+C6*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$6,Assumptions!$B$28:$B$33,0))/12+IF(ISNUMBER('Manatee-Sarasota'!$P$6),'Manatee-Sarasota'!$P$6,INDEX(Assumptions!$D$28:$D$33,MATCH('Manatee-Sarasota'!$D$6,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$6,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$6</f>
         <v>4315.14037623601</v>
       </c>
       <c r="J6" s="29" t="n">
@@ -8433,11 +8473,11 @@
         <v>145600</v>
       </c>
       <c r="M6" s="21" t="n">
-        <f aca="false">E6-(E6*INDEX(Assumptions!$H$36:$H$37,MATCH('Manatee-Sarasota'!$P$6,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF('Manatee-Sarasota'!$N$6="Y",Assumptions!$C$41,Assumptions!$C$42))-I6*12</f>
+        <f aca="false">E6-(E6*INDEX(Assumptions!$H$36:$H$37,MATCH('Manatee-Sarasota'!$Q$6,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF('Manatee-Sarasota'!$N$6="Y",Assumptions!$C$41,Assumptions!$C$42))-I6*12</f>
         <v>-3831.68451483207</v>
       </c>
       <c r="N6" s="21" t="n">
-        <f aca="false">M6-E6*INDEX(Assumptions!$C$36:$C$37,MATCH('Manatee-Sarasota'!$P$6,Assumptions!$B$36:$B$37,0))</f>
+        <f aca="false">M6-E6*INDEX(Assumptions!$C$36:$C$37,MATCH('Manatee-Sarasota'!$Q$6,Assumptions!$B$36:$B$37,0))</f>
         <v>-20831.6845148321</v>
       </c>
       <c r="O6" s="22" t="n">
@@ -8482,7 +8522,7 @@
         <v>2640.97661134044</v>
       </c>
       <c r="I7" s="21" t="n">
-        <f aca="false">H7+C7*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$6,Assumptions!$B$28:$B$33,0))/12+(INDEX(Assumptions!$D$28:$D$33,MATCH('Manatee-Sarasota'!$D$6,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$6,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$6</f>
+        <f aca="false">H7+C7*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$6,Assumptions!$B$28:$B$33,0))/12+IF(ISNUMBER('Manatee-Sarasota'!$P$6),'Manatee-Sarasota'!$P$6,INDEX(Assumptions!$D$28:$D$33,MATCH('Manatee-Sarasota'!$D$6,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$6,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$6</f>
         <v>4090.97661134044</v>
       </c>
       <c r="J7" s="29" t="n">
@@ -8498,11 +8538,11 @@
         <v>173600</v>
       </c>
       <c r="M7" s="21" t="n">
-        <f aca="false">E7-(E7*INDEX(Assumptions!$H$36:$H$37,MATCH('Manatee-Sarasota'!$P$6,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF('Manatee-Sarasota'!$N$6="Y",Assumptions!$C$41,Assumptions!$C$42))-I7*12</f>
+        <f aca="false">E7-(E7*INDEX(Assumptions!$H$36:$H$37,MATCH('Manatee-Sarasota'!$Q$6,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF('Manatee-Sarasota'!$N$6="Y",Assumptions!$C$41,Assumptions!$C$42))-I7*12</f>
         <v>-1141.71933608533</v>
       </c>
       <c r="N7" s="21" t="n">
-        <f aca="false">M7-E7*INDEX(Assumptions!$C$36:$C$37,MATCH('Manatee-Sarasota'!$P$6,Assumptions!$B$36:$B$37,0))</f>
+        <f aca="false">M7-E7*INDEX(Assumptions!$C$36:$C$37,MATCH('Manatee-Sarasota'!$Q$6,Assumptions!$B$36:$B$37,0))</f>
         <v>-18141.7193360853</v>
       </c>
       <c r="O7" s="22" t="n">
@@ -8547,7 +8587,7 @@
         <v>2573.10939147423</v>
       </c>
       <c r="I9" s="21" t="n">
-        <f aca="false">H9+C9*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$7,Assumptions!$B$28:$B$33,0))/12+(INDEX(Assumptions!$D$28:$D$33,MATCH('Manatee-Sarasota'!$D$7,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$7,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$7</f>
+        <f aca="false">H9+C9*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$7,Assumptions!$B$28:$B$33,0))/12+IF(ISNUMBER('Manatee-Sarasota'!$P$7),'Manatee-Sarasota'!$P$7,INDEX(Assumptions!$D$28:$D$33,MATCH('Manatee-Sarasota'!$D$7,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$7,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$7</f>
         <v>3898.10939147423</v>
       </c>
       <c r="J9" s="29" t="n">
@@ -8563,11 +8603,11 @@
         <v>110400</v>
       </c>
       <c r="M9" s="21" t="n">
-        <f aca="false">E9-(E9*INDEX(Assumptions!$H$36:$H$37,MATCH('Manatee-Sarasota'!$P$7,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF('Manatee-Sarasota'!$N$7="Y",Assumptions!$C$41,Assumptions!$C$42))-I9*12</f>
+        <f aca="false">E9-(E9*INDEX(Assumptions!$H$36:$H$37,MATCH('Manatee-Sarasota'!$Q$7,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF('Manatee-Sarasota'!$N$7="Y",Assumptions!$C$41,Assumptions!$C$42))-I9*12</f>
         <v>-5067.31269769074</v>
       </c>
       <c r="N9" s="21" t="n">
-        <f aca="false">M9-E9*INDEX(Assumptions!$C$36:$C$37,MATCH('Manatee-Sarasota'!$P$7,Assumptions!$B$36:$B$37,0))</f>
+        <f aca="false">M9-E9*INDEX(Assumptions!$C$36:$C$37,MATCH('Manatee-Sarasota'!$Q$7,Assumptions!$B$36:$B$37,0))</f>
         <v>-19667.3126976907</v>
       </c>
       <c r="O9" s="22" t="n">
@@ -8575,7 +8615,7 @@
         <v>-0.0458995715370538</v>
       </c>
       <c r="P9" s="46" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8611,7 +8651,7 @@
         <v>2353.50816619386</v>
       </c>
       <c r="I10" s="21" t="n">
-        <f aca="false">H10+C10*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$7,Assumptions!$B$28:$B$33,0))/12+(INDEX(Assumptions!$D$28:$D$33,MATCH('Manatee-Sarasota'!$D$7,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$7,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$7</f>
+        <f aca="false">H10+C10*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$7,Assumptions!$B$28:$B$33,0))/12+IF(ISNUMBER('Manatee-Sarasota'!$P$7),'Manatee-Sarasota'!$P$7,INDEX(Assumptions!$D$28:$D$33,MATCH('Manatee-Sarasota'!$D$7,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$7,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$7</f>
         <v>3678.50816619386</v>
       </c>
       <c r="J10" s="29" t="n">
@@ -8627,11 +8667,11 @@
         <v>133400</v>
       </c>
       <c r="M10" s="21" t="n">
-        <f aca="false">E10-(E10*INDEX(Assumptions!$H$36:$H$37,MATCH('Manatee-Sarasota'!$P$7,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF('Manatee-Sarasota'!$N$7="Y",Assumptions!$C$41,Assumptions!$C$42))-I10*12</f>
+        <f aca="false">E10-(E10*INDEX(Assumptions!$H$36:$H$37,MATCH('Manatee-Sarasota'!$Q$7,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF('Manatee-Sarasota'!$N$7="Y",Assumptions!$C$41,Assumptions!$C$42))-I10*12</f>
         <v>-2432.09799432634</v>
       </c>
       <c r="N10" s="21" t="n">
-        <f aca="false">M10-E10*INDEX(Assumptions!$C$36:$C$37,MATCH('Manatee-Sarasota'!$P$7,Assumptions!$B$36:$B$37,0))</f>
+        <f aca="false">M10-E10*INDEX(Assumptions!$C$36:$C$37,MATCH('Manatee-Sarasota'!$Q$7,Assumptions!$B$36:$B$37,0))</f>
         <v>-17032.0979943263</v>
       </c>
       <c r="O10" s="22" t="n">
@@ -8676,7 +8716,7 @@
         <v>2169.37364502965</v>
       </c>
       <c r="I11" s="21" t="n">
-        <f aca="false">H11+C11*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$7,Assumptions!$B$28:$B$33,0))/12+(INDEX(Assumptions!$D$28:$D$33,MATCH('Manatee-Sarasota'!$D$7,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$7,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$7</f>
+        <f aca="false">H11+C11*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$7,Assumptions!$B$28:$B$33,0))/12+IF(ISNUMBER('Manatee-Sarasota'!$P$7),'Manatee-Sarasota'!$P$7,INDEX(Assumptions!$D$28:$D$33,MATCH('Manatee-Sarasota'!$D$7,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$7,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$7</f>
         <v>3494.37364502965</v>
       </c>
       <c r="J11" s="29" t="n">
@@ -8692,11 +8732,11 @@
         <v>156400</v>
       </c>
       <c r="M11" s="21" t="n">
-        <f aca="false">E11-(E11*INDEX(Assumptions!$H$36:$H$37,MATCH('Manatee-Sarasota'!$P$7,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF('Manatee-Sarasota'!$N$7="Y",Assumptions!$C$41,Assumptions!$C$42))-I11*12</f>
+        <f aca="false">E11-(E11*INDEX(Assumptions!$H$36:$H$37,MATCH('Manatee-Sarasota'!$Q$7,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF('Manatee-Sarasota'!$N$7="Y",Assumptions!$C$41,Assumptions!$C$42))-I11*12</f>
         <v>-222.483740355812</v>
       </c>
       <c r="N11" s="21" t="n">
-        <f aca="false">M11-E11*INDEX(Assumptions!$C$36:$C$37,MATCH('Manatee-Sarasota'!$P$7,Assumptions!$B$36:$B$37,0))</f>
+        <f aca="false">M11-E11*INDEX(Assumptions!$C$36:$C$37,MATCH('Manatee-Sarasota'!$Q$7,Assumptions!$B$36:$B$37,0))</f>
         <v>-14822.4837403558</v>
       </c>
       <c r="O11" s="22" t="n">
@@ -8741,7 +8781,7 @@
         <v>3356.22964105334</v>
       </c>
       <c r="I13" s="21" t="n">
-        <f aca="false">H13+C13*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$8,Assumptions!$B$28:$B$33,0))/12+(INDEX(Assumptions!$D$28:$D$33,MATCH('Manatee-Sarasota'!$D$8,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$8,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$8</f>
+        <f aca="false">H13+C13*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$8,Assumptions!$B$28:$B$33,0))/12+IF(ISNUMBER('Manatee-Sarasota'!$P$8),'Manatee-Sarasota'!$P$8,INDEX(Assumptions!$D$28:$D$33,MATCH('Manatee-Sarasota'!$D$8,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$8,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$8</f>
         <v>4856.22964105334</v>
       </c>
       <c r="J13" s="29" t="n">
@@ -8757,11 +8797,11 @@
         <v>126000</v>
       </c>
       <c r="M13" s="21" t="n">
-        <f aca="false">E13-(E13*INDEX(Assumptions!$H$36:$H$37,MATCH('Manatee-Sarasota'!$P$8,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF('Manatee-Sarasota'!$N$8="Y",Assumptions!$C$41,Assumptions!$C$42))-I13*12</f>
+        <f aca="false">E13-(E13*INDEX(Assumptions!$H$36:$H$37,MATCH('Manatee-Sarasota'!$Q$8,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF('Manatee-Sarasota'!$N$8="Y",Assumptions!$C$41,Assumptions!$C$42))-I13*12</f>
         <v>-7644.75569264008</v>
       </c>
       <c r="N13" s="21" t="n">
-        <f aca="false">M13-E13*INDEX(Assumptions!$C$36:$C$37,MATCH('Manatee-Sarasota'!$P$8,Assumptions!$B$36:$B$37,0))</f>
+        <f aca="false">M13-E13*INDEX(Assumptions!$C$36:$C$37,MATCH('Manatee-Sarasota'!$Q$8,Assumptions!$B$36:$B$37,0))</f>
         <v>-25444.7556926401</v>
       </c>
       <c r="O13" s="22" t="n">
@@ -8769,7 +8809,7 @@
         <v>-0.0606726642273022</v>
       </c>
       <c r="P13" s="46" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8805,7 +8845,7 @@
         <v>3069.79326025286</v>
       </c>
       <c r="I14" s="21" t="n">
-        <f aca="false">H14+C14*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$8,Assumptions!$B$28:$B$33,0))/12+(INDEX(Assumptions!$D$28:$D$33,MATCH('Manatee-Sarasota'!$D$8,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$8,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$8</f>
+        <f aca="false">H14+C14*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$8,Assumptions!$B$28:$B$33,0))/12+IF(ISNUMBER('Manatee-Sarasota'!$P$8),'Manatee-Sarasota'!$P$8,INDEX(Assumptions!$D$28:$D$33,MATCH('Manatee-Sarasota'!$D$8,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$8,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$8</f>
         <v>4569.79326025286</v>
       </c>
       <c r="J14" s="29" t="n">
@@ -8821,11 +8861,11 @@
         <v>156000</v>
       </c>
       <c r="M14" s="21" t="n">
-        <f aca="false">E14-(E14*INDEX(Assumptions!$H$36:$H$37,MATCH('Manatee-Sarasota'!$P$8,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF('Manatee-Sarasota'!$N$8="Y",Assumptions!$C$41,Assumptions!$C$42))-I14*12</f>
+        <f aca="false">E14-(E14*INDEX(Assumptions!$H$36:$H$37,MATCH('Manatee-Sarasota'!$Q$8,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF('Manatee-Sarasota'!$N$8="Y",Assumptions!$C$41,Assumptions!$C$42))-I14*12</f>
         <v>-4207.51912303436</v>
       </c>
       <c r="N14" s="21" t="n">
-        <f aca="false">M14-E14*INDEX(Assumptions!$C$36:$C$37,MATCH('Manatee-Sarasota'!$P$8,Assumptions!$B$36:$B$37,0))</f>
+        <f aca="false">M14-E14*INDEX(Assumptions!$C$36:$C$37,MATCH('Manatee-Sarasota'!$Q$8,Assumptions!$B$36:$B$37,0))</f>
         <v>-22007.5191230344</v>
       </c>
       <c r="O14" s="22" t="n">
@@ -8870,7 +8910,7 @@
         <v>2829.61779786476</v>
       </c>
       <c r="I15" s="21" t="n">
-        <f aca="false">H15+C15*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$8,Assumptions!$B$28:$B$33,0))/12+(INDEX(Assumptions!$D$28:$D$33,MATCH('Manatee-Sarasota'!$D$8,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$8,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$8</f>
+        <f aca="false">H15+C15*INDEX(Assumptions!$C$28:$C$33,MATCH('Manatee-Sarasota'!$D$8,Assumptions!$B$28:$B$33,0))/12+IF(ISNUMBER('Manatee-Sarasota'!$P$8),'Manatee-Sarasota'!$P$8,INDEX(Assumptions!$D$28:$D$33,MATCH('Manatee-Sarasota'!$D$8,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH('Manatee-Sarasota'!$M$8,Assumptions!$B$22:$B$25,0)))/12+'Manatee-Sarasota'!$O$8</f>
         <v>4329.61779786476</v>
       </c>
       <c r="J15" s="29" t="n">
@@ -8886,11 +8926,11 @@
         <v>186000</v>
       </c>
       <c r="M15" s="21" t="n">
-        <f aca="false">E15-(E15*INDEX(Assumptions!$H$36:$H$37,MATCH('Manatee-Sarasota'!$P$8,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF('Manatee-Sarasota'!$N$8="Y",Assumptions!$C$41,Assumptions!$C$42))-I15*12</f>
+        <f aca="false">E15-(E15*INDEX(Assumptions!$H$36:$H$37,MATCH('Manatee-Sarasota'!$Q$8,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF('Manatee-Sarasota'!$N$8="Y",Assumptions!$C$41,Assumptions!$C$42))-I15*12</f>
         <v>-1325.41357437715</v>
       </c>
       <c r="N15" s="21" t="n">
-        <f aca="false">M15-E15*INDEX(Assumptions!$C$36:$C$37,MATCH('Manatee-Sarasota'!$P$8,Assumptions!$B$36:$B$37,0))</f>
+        <f aca="false">M15-E15*INDEX(Assumptions!$C$36:$C$37,MATCH('Manatee-Sarasota'!$Q$8,Assumptions!$B$36:$B$37,0))</f>
         <v>-19125.4135743771</v>
       </c>
       <c r="O15" s="22" t="n">
@@ -8935,7 +8975,7 @@
         <v>2712.95229318478</v>
       </c>
       <c r="I17" s="21" t="n">
-        <f aca="false">H17+C17*INDEX(Assumptions!$C$28:$C$33,MATCH(Pinellas!$D$6,Assumptions!$B$28:$B$33,0))/12+(INDEX(Assumptions!$D$28:$D$33,MATCH(Pinellas!$D$6,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(Pinellas!$M$6,Assumptions!$B$22:$B$25,0)))/12+Pinellas!$O$6</f>
+        <f aca="false">H17+C17*INDEX(Assumptions!$C$28:$C$33,MATCH(Pinellas!$D$6,Assumptions!$B$28:$B$33,0))/12+IF(ISNUMBER(Pinellas!$P$6),Pinellas!$P$6,INDEX(Assumptions!$D$28:$D$33,MATCH(Pinellas!$D$6,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(Pinellas!$M$6,Assumptions!$B$22:$B$25,0)))/12+Pinellas!$O$6</f>
         <v>4109.61895985145</v>
       </c>
       <c r="J17" s="29" t="n">
@@ -8951,11 +8991,11 @@
         <v>116400</v>
       </c>
       <c r="M17" s="21" t="n">
-        <f aca="false">E17-(E17*INDEX(Assumptions!$H$36:$H$37,MATCH(Pinellas!$P$6,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(Pinellas!$N$6="Y",Assumptions!$C$41,Assumptions!$C$42))-I17*12</f>
+        <f aca="false">E17-(E17*INDEX(Assumptions!$H$36:$H$37,MATCH(Pinellas!$Q$6,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(Pinellas!$N$6="Y",Assumptions!$C$41,Assumptions!$C$42))-I17*12</f>
         <v>-10745.4275182174</v>
       </c>
       <c r="N17" s="21" t="n">
-        <f aca="false">M17-E17*INDEX(Assumptions!$C$36:$C$37,MATCH(Pinellas!$P$6,Assumptions!$B$36:$B$37,0))</f>
+        <f aca="false">M17-E17*INDEX(Assumptions!$C$36:$C$37,MATCH(Pinellas!$Q$6,Assumptions!$B$36:$B$37,0))</f>
         <v>-24945.4275182174</v>
       </c>
       <c r="O17" s="22" t="n">
@@ -8963,7 +9003,7 @@
         <v>-0.0923146694004932</v>
       </c>
       <c r="P17" s="46" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8999,7 +9039,7 @@
         <v>2481.4162187044</v>
       </c>
       <c r="I18" s="21" t="n">
-        <f aca="false">H18+C18*INDEX(Assumptions!$C$28:$C$33,MATCH(Pinellas!$D$6,Assumptions!$B$28:$B$33,0))/12+(INDEX(Assumptions!$D$28:$D$33,MATCH(Pinellas!$D$6,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(Pinellas!$M$6,Assumptions!$B$22:$B$25,0)))/12+Pinellas!$O$6</f>
+        <f aca="false">H18+C18*INDEX(Assumptions!$C$28:$C$33,MATCH(Pinellas!$D$6,Assumptions!$B$28:$B$33,0))/12+IF(ISNUMBER(Pinellas!$P$6),Pinellas!$P$6,INDEX(Assumptions!$D$28:$D$33,MATCH(Pinellas!$D$6,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(Pinellas!$M$6,Assumptions!$B$22:$B$25,0)))/12+Pinellas!$O$6</f>
         <v>3878.08288537106</v>
       </c>
       <c r="J18" s="29" t="n">
@@ -9015,11 +9055,11 @@
         <v>140650</v>
       </c>
       <c r="M18" s="21" t="n">
-        <f aca="false">E18-(E18*INDEX(Assumptions!$H$36:$H$37,MATCH(Pinellas!$P$6,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(Pinellas!$N$6="Y",Assumptions!$C$41,Assumptions!$C$42))-I18*12</f>
+        <f aca="false">E18-(E18*INDEX(Assumptions!$H$36:$H$37,MATCH(Pinellas!$Q$6,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(Pinellas!$N$6="Y",Assumptions!$C$41,Assumptions!$C$42))-I18*12</f>
         <v>-7966.99462445278</v>
       </c>
       <c r="N18" s="21" t="n">
-        <f aca="false">M18-E18*INDEX(Assumptions!$C$36:$C$37,MATCH(Pinellas!$P$6,Assumptions!$B$36:$B$37,0))</f>
+        <f aca="false">M18-E18*INDEX(Assumptions!$C$36:$C$37,MATCH(Pinellas!$Q$6,Assumptions!$B$36:$B$37,0))</f>
         <v>-22166.9946244528</v>
       </c>
       <c r="O18" s="22" t="n">
@@ -9064,7 +9104,7 @@
         <v>2287.27438660735</v>
       </c>
       <c r="I19" s="21" t="n">
-        <f aca="false">H19+C19*INDEX(Assumptions!$C$28:$C$33,MATCH(Pinellas!$D$6,Assumptions!$B$28:$B$33,0))/12+(INDEX(Assumptions!$D$28:$D$33,MATCH(Pinellas!$D$6,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(Pinellas!$M$6,Assumptions!$B$22:$B$25,0)))/12+Pinellas!$O$6</f>
+        <f aca="false">H19+C19*INDEX(Assumptions!$C$28:$C$33,MATCH(Pinellas!$D$6,Assumptions!$B$28:$B$33,0))/12+IF(ISNUMBER(Pinellas!$P$6),Pinellas!$P$6,INDEX(Assumptions!$D$28:$D$33,MATCH(Pinellas!$D$6,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(Pinellas!$M$6,Assumptions!$B$22:$B$25,0)))/12+Pinellas!$O$6</f>
         <v>3683.94105327402</v>
       </c>
       <c r="J19" s="29" t="n">
@@ -9080,11 +9120,11 @@
         <v>164900</v>
       </c>
       <c r="M19" s="21" t="n">
-        <f aca="false">E19-(E19*INDEX(Assumptions!$H$36:$H$37,MATCH(Pinellas!$P$6,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(Pinellas!$N$6="Y",Assumptions!$C$41,Assumptions!$C$42))-I19*12</f>
+        <f aca="false">E19-(E19*INDEX(Assumptions!$H$36:$H$37,MATCH(Pinellas!$Q$6,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(Pinellas!$N$6="Y",Assumptions!$C$41,Assumptions!$C$42))-I19*12</f>
         <v>-5637.29263928819</v>
       </c>
       <c r="N19" s="21" t="n">
-        <f aca="false">M19-E19*INDEX(Assumptions!$C$36:$C$37,MATCH(Pinellas!$P$6,Assumptions!$B$36:$B$37,0))</f>
+        <f aca="false">M19-E19*INDEX(Assumptions!$C$36:$C$37,MATCH(Pinellas!$Q$6,Assumptions!$B$36:$B$37,0))</f>
         <v>-19837.2926392882</v>
       </c>
       <c r="O19" s="22" t="n">
@@ -9129,7 +9169,7 @@
         <v>2712.95229318478</v>
       </c>
       <c r="I21" s="21" t="n">
-        <f aca="false">H21+C21*INDEX(Assumptions!$C$28:$C$33,MATCH(Pinellas!$D$7,Assumptions!$B$28:$B$33,0))/12+(INDEX(Assumptions!$D$28:$D$33,MATCH(Pinellas!$D$7,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(Pinellas!$M$7,Assumptions!$B$22:$B$25,0)))/12+Pinellas!$O$7</f>
+        <f aca="false">H21+C21*INDEX(Assumptions!$C$28:$C$33,MATCH(Pinellas!$D$7,Assumptions!$B$28:$B$33,0))/12+IF(ISNUMBER(Pinellas!$P$7),Pinellas!$P$7,INDEX(Assumptions!$D$28:$D$33,MATCH(Pinellas!$D$7,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(Pinellas!$M$7,Assumptions!$B$22:$B$25,0)))/12+Pinellas!$O$7</f>
         <v>4109.61895985145</v>
       </c>
       <c r="J21" s="29" t="n">
@@ -9145,11 +9185,11 @@
         <v>116400</v>
       </c>
       <c r="M21" s="21" t="n">
-        <f aca="false">E21-(E21*INDEX(Assumptions!$H$36:$H$37,MATCH(Pinellas!$P$7,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(Pinellas!$N$7="Y",Assumptions!$C$41,Assumptions!$C$42))-I21*12</f>
+        <f aca="false">E21-(E21*INDEX(Assumptions!$H$36:$H$37,MATCH(Pinellas!$Q$7,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(Pinellas!$N$7="Y",Assumptions!$C$41,Assumptions!$C$42))-I21*12</f>
         <v>-1365.4275182174</v>
       </c>
       <c r="N21" s="21" t="n">
-        <f aca="false">M21-E21*INDEX(Assumptions!$C$36:$C$37,MATCH(Pinellas!$P$7,Assumptions!$B$36:$B$37,0))</f>
+        <f aca="false">M21-E21*INDEX(Assumptions!$C$36:$C$37,MATCH(Pinellas!$Q$7,Assumptions!$B$36:$B$37,0))</f>
         <v>-18365.4275182174</v>
       </c>
       <c r="O21" s="22" t="n">
@@ -9157,7 +9197,7 @@
         <v>-0.0117304769606306</v>
       </c>
       <c r="P21" s="46" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9193,7 +9233,7 @@
         <v>2481.4162187044</v>
       </c>
       <c r="I22" s="21" t="n">
-        <f aca="false">H22+C22*INDEX(Assumptions!$C$28:$C$33,MATCH(Pinellas!$D$7,Assumptions!$B$28:$B$33,0))/12+(INDEX(Assumptions!$D$28:$D$33,MATCH(Pinellas!$D$7,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(Pinellas!$M$7,Assumptions!$B$22:$B$25,0)))/12+Pinellas!$O$7</f>
+        <f aca="false">H22+C22*INDEX(Assumptions!$C$28:$C$33,MATCH(Pinellas!$D$7,Assumptions!$B$28:$B$33,0))/12+IF(ISNUMBER(Pinellas!$P$7),Pinellas!$P$7,INDEX(Assumptions!$D$28:$D$33,MATCH(Pinellas!$D$7,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(Pinellas!$M$7,Assumptions!$B$22:$B$25,0)))/12+Pinellas!$O$7</f>
         <v>3878.08288537106</v>
       </c>
       <c r="J22" s="29" t="n">
@@ -9209,11 +9249,11 @@
         <v>140650</v>
       </c>
       <c r="M22" s="21" t="n">
-        <f aca="false">E22-(E22*INDEX(Assumptions!$H$36:$H$37,MATCH(Pinellas!$P$7,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(Pinellas!$N$7="Y",Assumptions!$C$41,Assumptions!$C$42))-I22*12</f>
+        <f aca="false">E22-(E22*INDEX(Assumptions!$H$36:$H$37,MATCH(Pinellas!$Q$7,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(Pinellas!$N$7="Y",Assumptions!$C$41,Assumptions!$C$42))-I22*12</f>
         <v>1413.00537554723</v>
       </c>
       <c r="N22" s="21" t="n">
-        <f aca="false">M22-E22*INDEX(Assumptions!$C$36:$C$37,MATCH(Pinellas!$P$7,Assumptions!$B$36:$B$37,0))</f>
+        <f aca="false">M22-E22*INDEX(Assumptions!$C$36:$C$37,MATCH(Pinellas!$Q$7,Assumptions!$B$36:$B$37,0))</f>
         <v>-15586.9946244528</v>
       </c>
       <c r="O22" s="22" t="n">
@@ -9258,7 +9298,7 @@
         <v>2287.27438660735</v>
       </c>
       <c r="I23" s="21" t="n">
-        <f aca="false">H23+C23*INDEX(Assumptions!$C$28:$C$33,MATCH(Pinellas!$D$7,Assumptions!$B$28:$B$33,0))/12+(INDEX(Assumptions!$D$28:$D$33,MATCH(Pinellas!$D$7,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(Pinellas!$M$7,Assumptions!$B$22:$B$25,0)))/12+Pinellas!$O$7</f>
+        <f aca="false">H23+C23*INDEX(Assumptions!$C$28:$C$33,MATCH(Pinellas!$D$7,Assumptions!$B$28:$B$33,0))/12+IF(ISNUMBER(Pinellas!$P$7),Pinellas!$P$7,INDEX(Assumptions!$D$28:$D$33,MATCH(Pinellas!$D$7,Assumptions!$B$28:$B$33,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(Pinellas!$M$7,Assumptions!$B$22:$B$25,0)))/12+Pinellas!$O$7</f>
         <v>3683.94105327402</v>
       </c>
       <c r="J23" s="29" t="n">
@@ -9274,11 +9314,11 @@
         <v>164900</v>
       </c>
       <c r="M23" s="21" t="n">
-        <f aca="false">E23-(E23*INDEX(Assumptions!$H$36:$H$37,MATCH(Pinellas!$P$7,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(Pinellas!$N$7="Y",Assumptions!$C$41,Assumptions!$C$42))-I23*12</f>
+        <f aca="false">E23-(E23*INDEX(Assumptions!$H$36:$H$37,MATCH(Pinellas!$Q$7,Assumptions!$B$36:$B$37,0))+Assumptions!$C$40+IF(Pinellas!$N$7="Y",Assumptions!$C$41,Assumptions!$C$42))-I23*12</f>
         <v>3742.70736071181</v>
       </c>
       <c r="N23" s="21" t="n">
-        <f aca="false">M23-E23*INDEX(Assumptions!$C$36:$C$37,MATCH(Pinellas!$P$7,Assumptions!$B$36:$B$37,0))</f>
+        <f aca="false">M23-E23*INDEX(Assumptions!$C$36:$C$37,MATCH(Pinellas!$Q$7,Assumptions!$B$36:$B$37,0))</f>
         <v>-13257.2926392882</v>
       </c>
       <c r="O23" s="22" t="n">
@@ -9323,12 +9363,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9336,28 +9376,28 @@
         <v>105</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>13</v>
@@ -9368,31 +9408,31 @@
         <v>1</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9400,95 +9440,95 @@
         <v>2</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D6" s="47" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E6" s="47" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F6" s="47" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G6" s="47" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H6" s="47" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="I6" s="47" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J6" s="47" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="47" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D8" s="47" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E8" s="47" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F8" s="47" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G8" s="47" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H8" s="47" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I8" s="47" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J8" s="47" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9496,63 +9536,63 @@
         <v>3</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="47" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B10" s="47" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D10" s="47" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E10" s="47" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F10" s="47" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G10" s="47" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H10" s="47" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="I10" s="47" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="J10" s="47" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9560,31 +9600,31 @@
         <v>4</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9592,31 +9632,31 @@
         <v>5</v>
       </c>
       <c r="B12" s="47" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D12" s="47" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E12" s="47" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F12" s="47" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G12" s="47" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H12" s="47" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="I12" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J12" s="47" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9624,31 +9664,31 @@
         <v>6</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9656,31 +9696,31 @@
         <v>7</v>
       </c>
       <c r="B14" s="47" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D14" s="47" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E14" s="47" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F14" s="47" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G14" s="47" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H14" s="47" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I14" s="47" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J14" s="47" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9688,31 +9728,31 @@
         <v>8</v>
       </c>
       <c r="B15" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="J15" s="9" t="s">
         <v>452</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>453</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>455</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>456</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>457</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>458</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>459</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9720,31 +9760,31 @@
         <v>9</v>
       </c>
       <c r="B16" s="47" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D16" s="47" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E16" s="47" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F16" s="47" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="G16" s="47" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H16" s="47" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I16" s="47" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J16" s="47" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9752,31 +9792,31 @@
         <v>10</v>
       </c>
       <c r="B17" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="J17" s="9" t="s">
         <v>468</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>469</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>438</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>470</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>471</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>472</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>473</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9784,31 +9824,31 @@
         <v>11</v>
       </c>
       <c r="B18" s="47" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C18" s="47" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D18" s="47" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E18" s="47" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F18" s="47" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="G18" s="47" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H18" s="47" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I18" s="47" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="J18" s="47" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9816,31 +9856,31 @@
         <v>12</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9848,63 +9888,63 @@
         <v>13</v>
       </c>
       <c r="B20" s="47" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C20" s="47" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D20" s="47" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E20" s="47" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F20" s="47" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="G20" s="47" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H20" s="47" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I20" s="47" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="J20" s="47" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>
@@ -9937,12 +9977,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9950,22 +9990,22 @@
         <v>106</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9973,22 +10013,22 @@
         <v>75</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9996,22 +10036,22 @@
         <v>75</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D6" s="47" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E6" s="47" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F6" s="47" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G6" s="47" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10019,22 +10059,22 @@
         <v>75</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10042,22 +10082,22 @@
         <v>75</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D8" s="47" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E8" s="47" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F8" s="47" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="G8" s="47" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10065,22 +10105,22 @@
         <v>75</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10088,22 +10128,22 @@
         <v>77</v>
       </c>
       <c r="B10" s="47" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D10" s="47" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E10" s="47" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F10" s="47" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="G10" s="47" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10111,45 +10151,45 @@
         <v>77</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="47" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B12" s="47" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D12" s="47" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E12" s="47" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F12" s="47" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="G12" s="47" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10157,22 +10197,22 @@
         <v>77</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10180,45 +10220,45 @@
         <v>77</v>
       </c>
       <c r="B14" s="47" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D14" s="47" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E14" s="47" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F14" s="47" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="G14" s="47" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10226,22 +10266,22 @@
         <v>18</v>
       </c>
       <c r="B16" s="47" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D16" s="47" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E16" s="47" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="F16" s="47" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G16" s="47" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10249,22 +10289,22 @@
         <v>18</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10272,22 +10312,22 @@
         <v>18</v>
       </c>
       <c r="B18" s="47" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C18" s="47" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D18" s="47" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E18" s="47" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F18" s="47" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G18" s="47" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10295,22 +10335,22 @@
         <v>18</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10318,22 +10358,22 @@
         <v>18</v>
       </c>
       <c r="B20" s="47" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C20" s="47" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D20" s="47" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E20" s="47" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F20" s="47" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="G20" s="47" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10341,22 +10381,22 @@
         <v>18</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10364,22 +10404,22 @@
         <v>18</v>
       </c>
       <c r="B22" s="47" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C22" s="47" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D22" s="47" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E22" s="47" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F22" s="47" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="G22" s="47" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10387,22 +10427,22 @@
         <v>18</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10410,22 +10450,22 @@
         <v>18</v>
       </c>
       <c r="B24" s="47" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C24" s="47" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D24" s="47" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E24" s="47" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F24" s="47" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="G24" s="47" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10433,22 +10473,22 @@
         <v>18</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10456,22 +10496,22 @@
         <v>18</v>
       </c>
       <c r="B26" s="47" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C26" s="47" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D26" s="47" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E26" s="47" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="F26" s="47" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="G26" s="47" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10479,22 +10519,22 @@
         <v>80</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10502,22 +10542,22 @@
         <v>80</v>
       </c>
       <c r="B28" s="47" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C28" s="47" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D28" s="47" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E28" s="47" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F28" s="47" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G28" s="47" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10525,22 +10565,22 @@
         <v>80</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10548,22 +10588,22 @@
         <v>80</v>
       </c>
       <c r="B30" s="47" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C30" s="47" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D30" s="47" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E30" s="47" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F30" s="47" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="G30" s="47" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10571,22 +10611,22 @@
         <v>82</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10594,22 +10634,22 @@
         <v>84</v>
       </c>
       <c r="B32" s="47" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C32" s="47" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D32" s="47" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E32" s="47" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F32" s="47" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G32" s="47" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10617,45 +10657,45 @@
         <v>84</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="47" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B34" s="47" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C34" s="47" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D34" s="47" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E34" s="47" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F34" s="47" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="G34" s="47" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
   </sheetData>
@@ -10684,23 +10724,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10708,10 +10748,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10719,10 +10759,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10730,10 +10770,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10741,10 +10781,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10752,10 +10792,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10763,10 +10803,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="47" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10774,10 +10814,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10785,10 +10825,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="47" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10796,10 +10836,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10807,10 +10847,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="47" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
   </sheetData>

--- a/str-deal-search/STR_DSCR_Analysis.xlsx
+++ b/str-deal-search/STR_DSCR_Analysis.xlsx
@@ -193,7 +193,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1469" uniqueCount="887">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1492" uniqueCount="902">
   <si>
     <t xml:space="preserve">STR DSCR Search: Summary of Top Picks</t>
   </si>
@@ -468,7 +468,7 @@
     <t xml:space="preserve">Monroe</t>
   </si>
   <si>
-    <t xml:space="preserve">Keys: low millage (~1.0-1.2% of price est.). Base ins. = Keys house wind+HO+STR liability; flood by zone on top. Condos use per-row override.</t>
+    <t xml:space="preserve">Keys: ~7.9-9.0 mills (2026) -&gt; 0.70-0.90% of price + $800-1,200/yr non-ad valorem (solid waste, wastewater). Base ins. = wind + non-wind STR policy for an elevated CBS house; flood by zone on top (~$12.5k AE total). Ground-level pre-FIRM: override ~$20k+. Condos: per-row HO-6 override.</t>
   </si>
   <si>
     <t xml:space="preserve">OPERATING PROFILE</t>
@@ -1899,6 +1899,24 @@
     <t xml:space="preserve">Verdict for this buyer</t>
   </si>
   <si>
+    <t xml:space="preserve">KEYS-WIDE 2026 (context)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mixed; verify per parcel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median SFH ~$1.02M, condo ~$610k (Aug 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~6,500 STR listings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanced-to-buyer-leaning: prices flat (+/-5%), DOM 100-150, ~6.6 months supply (single source); condos favor buyers. Bed tax FY25 $60.8M (-1%); RevPAR ~+10% YTD 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insurance ($12k+ house) + HOA ($800-2,000 condo) are the DSCR killers</t>
+  </si>
+  <si>
     <t xml:space="preserve">Marathon (city)</t>
   </si>
   <si>
@@ -2848,6 +2866,33 @@
   </si>
   <si>
     <t xml:space="preserve">Visit Florida Keys partner newsletter (Sep 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keys insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OIR county averages (Monroe $7,863 w/ wind, Mar 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Citizens STR eligibility (ATB 006-14)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keys tax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FL DOR millage comparison 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keys market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KeysListings market report (Aug 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keys storms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monroe County Irma recovery (1,179 destroyed / 2,977 major)</t>
   </si>
   <si>
     <t xml:space="preserve">Tourism</t>
@@ -3911,15 +3956,15 @@
       </c>
       <c r="F12" s="6" t="n">
         <f aca="false">'Monroe (Keys)'!$W$7</f>
-        <v>5510.28464609673</v>
+        <v>5390.49297943007</v>
       </c>
       <c r="G12" s="7" t="n">
         <f aca="false">'Monroe (Keys)'!$X$7</f>
-        <v>1.51232356739254</v>
+        <v>1.54593158086525</v>
       </c>
       <c r="H12" s="7" t="n">
         <f aca="false">'Monroe (Keys)'!$Y$7</f>
-        <v>1.20985885391403</v>
+        <v>1.2367452646922</v>
       </c>
       <c r="I12" s="6" t="n">
         <f aca="false">'Monroe (Keys)'!$Z$7</f>
@@ -3927,11 +3972,11 @@
       </c>
       <c r="J12" s="6" t="n">
         <f aca="false">'Monroe (Keys)'!$AD$7</f>
-        <v>-6323.41575316078</v>
+        <v>-4885.91575316079</v>
       </c>
       <c r="K12" s="6" t="n">
         <f aca="false">'Monroe (Keys)'!$AE$7</f>
-        <v>-26323.4157531608</v>
+        <v>-24885.9157531608</v>
       </c>
       <c r="L12" s="9" t="s">
         <v>25</v>
@@ -3959,15 +4004,15 @@
       </c>
       <c r="F13" s="6" t="n">
         <f aca="false">'Monroe (Keys)'!$W$6</f>
-        <v>6076.73812965363</v>
+        <v>5940.07146298696</v>
       </c>
       <c r="G13" s="7" t="n">
         <f aca="false">'Monroe (Keys)'!$X$6</f>
-        <v>1.35736198554988</v>
+        <v>1.38859159939899</v>
       </c>
       <c r="H13" s="7" t="n">
         <f aca="false">'Monroe (Keys)'!$Y$6</f>
-        <v>1.08588958843991</v>
+        <v>1.11087327951919</v>
       </c>
       <c r="I13" s="6" t="n">
         <f aca="false">'Monroe (Keys)'!$Z$6</f>
@@ -3975,11 +4020,11 @@
       </c>
       <c r="J13" s="6" t="n">
         <f aca="false">'Monroe (Keys)'!$AD$6</f>
-        <v>-13804.2575558435</v>
+        <v>-12164.2575558435</v>
       </c>
       <c r="K13" s="6" t="n">
         <f aca="false">'Monroe (Keys)'!$AE$6</f>
-        <v>-33600.2575558435</v>
+        <v>-31960.2575558435</v>
       </c>
       <c r="L13" s="9" t="s">
         <v>26</v>
@@ -4141,12 +4186,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4154,22 +4199,22 @@
         <v>112</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4177,22 +4222,22 @@
         <v>79</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4200,22 +4245,22 @@
         <v>79</v>
       </c>
       <c r="B6" s="48" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="C6" s="48" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="E6" s="48" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="F6" s="48" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="G6" s="48" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4223,22 +4268,22 @@
         <v>79</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4246,22 +4291,22 @@
         <v>79</v>
       </c>
       <c r="B8" s="48" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="C8" s="48" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="D8" s="48" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="E8" s="48" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="F8" s="48" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="G8" s="48" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4269,22 +4314,22 @@
         <v>79</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4292,22 +4337,22 @@
         <v>81</v>
       </c>
       <c r="B10" s="48" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="C10" s="48" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="D10" s="48" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="E10" s="48" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="F10" s="48" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="G10" s="48" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4315,45 +4360,45 @@
         <v>81</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>415</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="48" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="B12" s="48" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="C12" s="48" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="D12" s="48" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="E12" s="48" t="s">
         <v>415</v>
       </c>
       <c r="F12" s="48" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="G12" s="48" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4361,22 +4406,22 @@
         <v>81</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>415</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4384,36 +4429,36 @@
         <v>81</v>
       </c>
       <c r="B14" s="48" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="C14" s="48" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="D14" s="48" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="E14" s="48" t="s">
         <v>415</v>
       </c>
       <c r="F14" s="48" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="G14" s="48" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>415</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>415</v>
@@ -4422,7 +4467,7 @@
         <v>415</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4430,22 +4475,22 @@
         <v>18</v>
       </c>
       <c r="B16" s="48" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="D16" s="48" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="E16" s="48" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="F16" s="48" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="G16" s="48" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4453,22 +4498,22 @@
         <v>18</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4476,22 +4521,22 @@
         <v>18</v>
       </c>
       <c r="B18" s="48" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="D18" s="48" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="E18" s="48" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="F18" s="48" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="G18" s="48" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4499,22 +4544,22 @@
         <v>18</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4522,10 +4567,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="48" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="C20" s="48" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="D20" s="48" t="s">
         <v>415</v>
@@ -4534,10 +4579,10 @@
         <v>415</v>
       </c>
       <c r="F20" s="48" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="G20" s="48" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4545,22 +4590,22 @@
         <v>18</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>415</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4568,22 +4613,22 @@
         <v>18</v>
       </c>
       <c r="B22" s="48" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="D22" s="48" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="E22" s="48" t="s">
         <v>415</v>
       </c>
       <c r="F22" s="48" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="G22" s="48" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4591,22 +4636,22 @@
         <v>18</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4614,22 +4659,22 @@
         <v>18</v>
       </c>
       <c r="B24" s="48" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="C24" s="48" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="D24" s="48" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="E24" s="48" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="F24" s="48" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="G24" s="48" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4637,10 +4682,10 @@
         <v>18</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>415</v>
@@ -4649,10 +4694,10 @@
         <v>415</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4660,22 +4705,22 @@
         <v>18</v>
       </c>
       <c r="B26" s="48" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="C26" s="48" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="D26" s="48" t="s">
         <v>415</v>
       </c>
       <c r="E26" s="48" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="F26" s="48" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="G26" s="48" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4683,22 +4728,22 @@
         <v>84</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>750</v>
+        <v>756</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4706,22 +4751,22 @@
         <v>84</v>
       </c>
       <c r="B28" s="48" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="C28" s="48" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="D28" s="48" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
       <c r="E28" s="48" t="s">
         <v>415</v>
       </c>
       <c r="F28" s="48" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="G28" s="48" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4729,22 +4774,22 @@
         <v>84</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>415</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>758</v>
+        <v>764</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4752,10 +4797,10 @@
         <v>84</v>
       </c>
       <c r="B30" s="48" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="C30" s="48" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="D30" s="48" t="s">
         <v>415</v>
@@ -4764,10 +4809,10 @@
         <v>415</v>
       </c>
       <c r="F30" s="48" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="G30" s="48" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4775,22 +4820,22 @@
         <v>86</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>766</v>
+        <v>772</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4798,22 +4843,22 @@
         <v>88</v>
       </c>
       <c r="B32" s="48" t="s">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="C32" s="48" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="D32" s="48" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
       <c r="E32" s="48" t="s">
-        <v>769</v>
+        <v>775</v>
       </c>
       <c r="F32" s="48" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="G32" s="48" t="s">
-        <v>770</v>
+        <v>776</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4821,10 +4866,10 @@
         <v>88</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>772</v>
+        <v>778</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>415</v>
@@ -4833,21 +4878,21 @@
         <v>415</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="48" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
       <c r="B34" s="48" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="C34" s="48" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="D34" s="48" t="s">
         <v>415</v>
@@ -4859,7 +4904,7 @@
         <v>526</v>
       </c>
       <c r="G34" s="48" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4867,22 +4912,22 @@
         <v>90</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>778</v>
+        <v>784</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>780</v>
+        <v>786</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>781</v>
+        <v>787</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>782</v>
+        <v>788</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4890,22 +4935,22 @@
         <v>90</v>
       </c>
       <c r="B36" s="48" t="s">
-        <v>784</v>
+        <v>790</v>
       </c>
       <c r="C36" s="48" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="D36" s="48" t="s">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="E36" s="48" t="s">
-        <v>787</v>
+        <v>793</v>
       </c>
       <c r="F36" s="48" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="G36" s="48" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4913,22 +4958,22 @@
         <v>90</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>792</v>
+        <v>798</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>793</v>
+        <v>799</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>795</v>
+        <v>801</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4936,22 +4981,22 @@
         <v>90</v>
       </c>
       <c r="B38" s="48" t="s">
-        <v>796</v>
+        <v>802</v>
       </c>
       <c r="C38" s="48" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="D38" s="48" t="s">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="E38" s="48" t="s">
-        <v>799</v>
+        <v>805</v>
       </c>
       <c r="F38" s="48" t="s">
-        <v>800</v>
+        <v>806</v>
       </c>
       <c r="G38" s="48" t="s">
-        <v>801</v>
+        <v>807</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4959,22 +5004,22 @@
         <v>90</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>804</v>
+        <v>810</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>805</v>
+        <v>811</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>800</v>
+        <v>806</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4982,10 +5027,10 @@
         <v>90</v>
       </c>
       <c r="B40" s="48" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="C40" s="48" t="s">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="D40" s="48" t="s">
         <v>415</v>
@@ -4994,10 +5039,10 @@
         <v>415</v>
       </c>
       <c r="F40" s="48" t="s">
-        <v>809</v>
+        <v>815</v>
       </c>
       <c r="G40" s="48" t="s">
-        <v>810</v>
+        <v>816</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5005,13 +5050,13 @@
         <v>90</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>415</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>415</v>
@@ -5020,7 +5065,7 @@
         <v>415</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>812</v>
+        <v>818</v>
       </c>
     </row>
   </sheetData>
@@ -5049,23 +5094,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>813</v>
+        <v>819</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>814</v>
+        <v>820</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5073,10 +5118,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5084,10 +5129,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="48" t="s">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="C6" s="48" t="s">
-        <v>821</v>
+        <v>827</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5095,10 +5140,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5106,10 +5151,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="48" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="C8" s="48" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5117,10 +5162,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>827</v>
+        <v>833</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5128,10 +5173,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="48" t="s">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="C10" s="48" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5139,10 +5184,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>830</v>
+        <v>836</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>831</v>
+        <v>837</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5150,10 +5195,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="48" t="s">
-        <v>832</v>
+        <v>838</v>
       </c>
       <c r="C12" s="48" t="s">
-        <v>833</v>
+        <v>839</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5161,10 +5206,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>835</v>
+        <v>841</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5172,10 +5217,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="48" t="s">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="C14" s="48" t="s">
-        <v>837</v>
+        <v>843</v>
       </c>
     </row>
   </sheetData>
@@ -5194,7 +5239,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
@@ -5204,23 +5249,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>839</v>
+        <v>845</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>842</v>
+        <v>848</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5228,7 +5273,7 @@
         <v>565</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="C5" s="33" t="s">
         <v>216</v>
@@ -5239,7 +5284,7 @@
         <v>565</v>
       </c>
       <c r="B6" s="48" t="s">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="C6" s="33" t="s">
         <v>216</v>
@@ -5247,10 +5292,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>846</v>
+        <v>852</v>
       </c>
       <c r="C7" s="33" t="s">
         <v>216</v>
@@ -5258,10 +5303,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="48" t="s">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="B8" s="48" t="s">
-        <v>848</v>
+        <v>854</v>
       </c>
       <c r="C8" s="33" t="s">
         <v>216</v>
@@ -5269,10 +5314,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="C9" s="33" t="s">
         <v>216</v>
@@ -5280,10 +5325,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="48" t="s">
-        <v>850</v>
+        <v>856</v>
       </c>
       <c r="B10" s="48" t="s">
-        <v>851</v>
+        <v>857</v>
       </c>
       <c r="C10" s="33" t="s">
         <v>216</v>
@@ -5291,10 +5336,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>850</v>
+        <v>856</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="C11" s="33" t="s">
         <v>216</v>
@@ -5302,10 +5347,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="48" t="s">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="B12" s="48" t="s">
-        <v>854</v>
+        <v>860</v>
       </c>
       <c r="C12" s="33" t="s">
         <v>216</v>
@@ -5313,10 +5358,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>855</v>
+        <v>861</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="C13" s="33" t="s">
         <v>216</v>
@@ -5324,10 +5369,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="48" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="B14" s="48" t="s">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="C14" s="33" t="s">
         <v>216</v>
@@ -5335,10 +5380,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="C15" s="33" t="s">
         <v>216</v>
@@ -5346,10 +5391,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="48" t="s">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="B16" s="48" t="s">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="C16" s="33" t="s">
         <v>216</v>
@@ -5357,10 +5402,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="C17" s="33" t="s">
         <v>216</v>
@@ -5368,10 +5413,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="48" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="B18" s="48" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="C18" s="33" t="s">
         <v>216</v>
@@ -5379,10 +5424,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>866</v>
+        <v>872</v>
       </c>
       <c r="C19" s="33" t="s">
         <v>216</v>
@@ -5390,10 +5435,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="48" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="B20" s="48" t="s">
-        <v>867</v>
+        <v>873</v>
       </c>
       <c r="C20" s="33" t="s">
         <v>216</v>
@@ -5401,10 +5446,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>869</v>
+        <v>875</v>
       </c>
       <c r="C21" s="33" t="s">
         <v>216</v>
@@ -5412,10 +5457,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="48" t="s">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="B22" s="48" t="s">
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="C22" s="33" t="s">
         <v>216</v>
@@ -5423,10 +5468,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>873</v>
+        <v>879</v>
       </c>
       <c r="C23" s="33" t="s">
         <v>216</v>
@@ -5434,10 +5479,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="48" t="s">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="B24" s="48" t="s">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="C24" s="33" t="s">
         <v>216</v>
@@ -5445,10 +5490,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="C25" s="33" t="s">
         <v>216</v>
@@ -5456,10 +5501,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="48" t="s">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="B26" s="48" t="s">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="C26" s="33" t="s">
         <v>216</v>
@@ -5467,10 +5512,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="C27" s="33" t="s">
         <v>216</v>
@@ -5478,10 +5523,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="48" t="s">
-        <v>878</v>
+        <v>884</v>
       </c>
       <c r="B28" s="48" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="C28" s="33" t="s">
         <v>216</v>
@@ -5489,10 +5534,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="C29" s="33" t="s">
         <v>216</v>
@@ -5500,10 +5545,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="48" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="B30" s="48" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="C30" s="33" t="s">
         <v>216</v>
@@ -5511,10 +5556,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>884</v>
+        <v>890</v>
       </c>
       <c r="C31" s="33" t="s">
         <v>216</v>
@@ -5522,12 +5567,67 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="48" t="s">
-        <v>885</v>
+        <v>891</v>
       </c>
       <c r="B32" s="48" t="s">
-        <v>886</v>
+        <v>892</v>
       </c>
       <c r="C32" s="33" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="9" t="s">
+        <v>891</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>893</v>
+      </c>
+      <c r="C33" s="33" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="48" t="s">
+        <v>894</v>
+      </c>
+      <c r="B34" s="48" t="s">
+        <v>895</v>
+      </c>
+      <c r="C34" s="33" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="9" t="s">
+        <v>896</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>897</v>
+      </c>
+      <c r="C35" s="33" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="48" t="s">
+        <v>898</v>
+      </c>
+      <c r="B36" s="48" t="s">
+        <v>899</v>
+      </c>
+      <c r="C36" s="33" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="9" t="s">
+        <v>900</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>901</v>
+      </c>
+      <c r="C37" s="33" t="s">
         <v>216</v>
       </c>
     </row>
@@ -5561,6 +5661,11 @@
     <hyperlink ref="C30" r:id="rId26" display="Link"/>
     <hyperlink ref="C31" r:id="rId27" display="Link"/>
     <hyperlink ref="C32" r:id="rId28" display="Link"/>
+    <hyperlink ref="C33" r:id="rId29" display="Link"/>
+    <hyperlink ref="C34" r:id="rId30" display="Link"/>
+    <hyperlink ref="C35" r:id="rId31" display="Link"/>
+    <hyperlink ref="C36" r:id="rId32" display="Link"/>
+    <hyperlink ref="C37" r:id="rId33" display="Link"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -5920,15 +6025,15 @@
         <v>89</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="4" t="s">
         <v>90</v>
       </c>
       <c r="C34" s="20" t="n">
-        <v>0.011</v>
+        <v>0.0095</v>
       </c>
       <c r="D34" s="22" t="n">
-        <v>14000</v>
+        <v>8000</v>
       </c>
       <c r="I34" s="14" t="s">
         <v>91</v>
@@ -10399,7 +10504,7 @@
         <v>1200</v>
       </c>
       <c r="P6" s="19" t="n">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="Q6" s="27" t="s">
         <v>99</v>
@@ -10418,23 +10523,23 @@
       </c>
       <c r="U6" s="21" t="n">
         <f aca="false">H6*INDEX(Assumptions!$C$28:$C$34,MATCH(D6,Assumptions!$B$28:$B$34,0))/12</f>
-        <v>696.666666666667</v>
+        <v>601.666666666667</v>
       </c>
       <c r="V6" s="21" t="n">
         <f aca="false">IF(ISNUMBER(P6),P6,INDEX(Assumptions!$D$28:$D$34,MATCH(D6,Assumptions!$B$28:$B$34,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M6,Assumptions!$B$22:$B$25,0)))/12</f>
-        <v>291.666666666667</v>
+        <v>250</v>
       </c>
       <c r="W6" s="21" t="n">
         <f aca="false">T6+U6+V6+O6</f>
-        <v>6076.73812965363</v>
+        <v>5940.07146298696</v>
       </c>
       <c r="X6" s="30" t="n">
         <f aca="false">IFERROR(K6/12/W6,0)</f>
-        <v>1.35736198554988</v>
+        <v>1.38859159939899</v>
       </c>
       <c r="Y6" s="31" t="n">
         <f aca="false">IFERROR(K6*Assumptions!$C$18/12/W6,0)</f>
-        <v>1.08588958843991</v>
+        <v>1.11087327951919</v>
       </c>
       <c r="Z6" s="32" t="n">
         <f aca="false">H6*J6+H6*(Assumptions!$C$16-I6)</f>
@@ -10442,7 +10547,7 @@
       </c>
       <c r="AA6" s="21" t="n">
         <f aca="false">W6*Assumptions!$C$17</f>
-        <v>36460.4287779218</v>
+        <v>35640.4287779218</v>
       </c>
       <c r="AB6" s="21" t="n">
         <f aca="false">K6*INDEX(Assumptions!$H$37:$H$38,MATCH(Q6,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N6="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
@@ -10454,11 +10559,11 @@
       </c>
       <c r="AD6" s="21" t="n">
         <f aca="false">K6-AB6-W6*12</f>
-        <v>-13804.2575558435</v>
+        <v>-12164.2575558435</v>
       </c>
       <c r="AE6" s="21" t="n">
         <f aca="false">AD6-AC6</f>
-        <v>-33600.2575558435</v>
+        <v>-31960.2575558435</v>
       </c>
       <c r="AF6" s="23" t="n">
         <f aca="false">IFERROR(K6/H6,0)</f>
@@ -10525,7 +10630,7 @@
         <v>1448</v>
       </c>
       <c r="P7" s="37" t="n">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="Q7" s="36" t="s">
         <v>99</v>
@@ -10544,23 +10649,23 @@
       </c>
       <c r="U7" s="40" t="n">
         <f aca="false">H7*INDEX(Assumptions!$C$28:$C$34,MATCH(D7,Assumptions!$B$28:$B$34,0))/12</f>
-        <v>572.916666666667</v>
+        <v>494.791666666667</v>
       </c>
       <c r="V7" s="40" t="n">
         <f aca="false">IF(ISNUMBER(P7),P7,INDEX(Assumptions!$D$28:$D$34,MATCH(D7,Assumptions!$B$28:$B$34,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M7,Assumptions!$B$22:$B$25,0)))/12</f>
-        <v>291.666666666667</v>
+        <v>250</v>
       </c>
       <c r="W7" s="40" t="n">
         <f aca="false">T7+U7+V7+O7</f>
-        <v>5510.28464609673</v>
+        <v>5390.49297943007</v>
       </c>
       <c r="X7" s="42" t="n">
         <f aca="false">IFERROR(K7/12/W7,0)</f>
-        <v>1.51232356739254</v>
+        <v>1.54593158086525</v>
       </c>
       <c r="Y7" s="42" t="n">
         <f aca="false">IFERROR(K7*Assumptions!$C$18/12/W7,0)</f>
-        <v>1.20985885391403</v>
+        <v>1.2367452646922</v>
       </c>
       <c r="Z7" s="40" t="n">
         <f aca="false">H7*J7+H7*(Assumptions!$C$16-I7)</f>
@@ -10568,7 +10673,7 @@
       </c>
       <c r="AA7" s="40" t="n">
         <f aca="false">W7*Assumptions!$C$17</f>
-        <v>33061.7078765804</v>
+        <v>32342.9578765804</v>
       </c>
       <c r="AB7" s="40" t="n">
         <f aca="false">K7*INDEX(Assumptions!$H$37:$H$38,MATCH(Q7,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N7="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
@@ -10580,11 +10685,11 @@
       </c>
       <c r="AD7" s="40" t="n">
         <f aca="false">K7-AB7-W7*12</f>
-        <v>-6323.41575316078</v>
+        <v>-4885.91575316079</v>
       </c>
       <c r="AE7" s="40" t="n">
         <f aca="false">AD7-AC7</f>
-        <v>-26323.4157531608</v>
+        <v>-24885.9157531608</v>
       </c>
       <c r="AF7" s="43" t="n">
         <f aca="false">IFERROR(K7/H7,0)</f>
@@ -10653,7 +10758,7 @@
         <v>1448</v>
       </c>
       <c r="P8" s="19" t="n">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="Q8" s="27" t="s">
         <v>99</v>
@@ -10672,23 +10777,23 @@
       </c>
       <c r="U8" s="21" t="n">
         <f aca="false">H8*INDEX(Assumptions!$C$28:$C$34,MATCH(D8,Assumptions!$B$28:$B$34,0))/12</f>
-        <v>614.166666666667</v>
+        <v>530.416666666667</v>
       </c>
       <c r="V8" s="21" t="n">
         <f aca="false">IF(ISNUMBER(P8),P8,INDEX(Assumptions!$D$28:$D$34,MATCH(D8,Assumptions!$B$28:$B$34,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M8,Assumptions!$B$22:$B$25,0)))/12</f>
-        <v>291.666666666667</v>
+        <v>250</v>
       </c>
       <c r="W8" s="21" t="n">
         <f aca="false">T8+U8+V8+O8</f>
-        <v>5781.7691406157</v>
+        <v>5656.35247394903</v>
       </c>
       <c r="X8" s="30" t="n">
         <f aca="false">IFERROR(K8/12/W8,0)</f>
-        <v>0.835788011559856</v>
+        <v>0.854319697294182</v>
       </c>
       <c r="Y8" s="30" t="n">
         <f aca="false">IFERROR(K8*Assumptions!$C$18/12/W8,0)</f>
-        <v>0.668630409247885</v>
+        <v>0.683455757835346</v>
       </c>
       <c r="Z8" s="21" t="n">
         <f aca="false">H8*J8+H8*(Assumptions!$C$16-I8)</f>
@@ -10696,7 +10801,7 @@
       </c>
       <c r="AA8" s="21" t="n">
         <f aca="false">W8*Assumptions!$C$17</f>
-        <v>34690.6148436942</v>
+        <v>33938.1148436942</v>
       </c>
       <c r="AB8" s="21" t="n">
         <f aca="false">K8*INDEX(Assumptions!$H$37:$H$38,MATCH(Q8,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N8="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
@@ -10708,11 +10813,11 @@
       </c>
       <c r="AD8" s="21" t="n">
         <f aca="false">K8-AB8-W8*12</f>
-        <v>-37729.2696873884</v>
+        <v>-36224.2696873884</v>
       </c>
       <c r="AE8" s="21" t="n">
         <f aca="false">AD8-AC8</f>
-        <v>-49326.8696873884</v>
+        <v>-47821.8696873884</v>
       </c>
       <c r="AF8" s="23" t="n">
         <f aca="false">IFERROR(K8/H8,0)</f>
@@ -10779,7 +10884,7 @@
         <v>1448</v>
       </c>
       <c r="P9" s="37" t="n">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="Q9" s="36" t="s">
         <v>99</v>
@@ -10798,23 +10903,23 @@
       </c>
       <c r="U9" s="40" t="n">
         <f aca="false">H9*INDEX(Assumptions!$C$28:$C$34,MATCH(D9,Assumptions!$B$28:$B$34,0))/12</f>
-        <v>595.833333333333</v>
+        <v>514.583333333333</v>
       </c>
       <c r="V9" s="40" t="n">
         <f aca="false">IF(ISNUMBER(P9),P9,INDEX(Assumptions!$D$28:$D$34,MATCH(D9,Assumptions!$B$28:$B$34,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M9,Assumptions!$B$22:$B$25,0)))/12</f>
-        <v>291.666666666667</v>
+        <v>250</v>
       </c>
       <c r="W9" s="40" t="n">
         <f aca="false">T9+U9+V9+O9</f>
-        <v>5661.10936527394</v>
+        <v>5538.19269860727</v>
       </c>
       <c r="X9" s="42" t="n">
         <f aca="false">IFERROR(K9/12/W9,0)</f>
-        <v>0.721295610076197</v>
+        <v>0.737304307659826</v>
       </c>
       <c r="Y9" s="42" t="n">
         <f aca="false">IFERROR(K9*Assumptions!$C$18/12/W9,0)</f>
-        <v>0.577036488060957</v>
+        <v>0.58984344612786</v>
       </c>
       <c r="Z9" s="40" t="n">
         <f aca="false">H9*J9+H9*(Assumptions!$C$16-I9)</f>
@@ -10822,7 +10927,7 @@
       </c>
       <c r="AA9" s="40" t="n">
         <f aca="false">W9*Assumptions!$C$17</f>
-        <v>33966.6561916436</v>
+        <v>33229.1561916436</v>
       </c>
       <c r="AB9" s="40" t="n">
         <f aca="false">K9*INDEX(Assumptions!$H$37:$H$38,MATCH(Q9,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N9="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
@@ -10834,11 +10939,11 @@
       </c>
       <c r="AD9" s="40" t="n">
         <f aca="false">K9-AB9-W9*12</f>
-        <v>-42303.3123832872</v>
+        <v>-40828.3123832872</v>
       </c>
       <c r="AE9" s="40" t="n">
         <f aca="false">AD9-AC9</f>
-        <v>-52103.3123832872</v>
+        <v>-50628.3123832872</v>
       </c>
       <c r="AF9" s="43" t="n">
         <f aca="false">IFERROR(K9/H9,0)</f>
@@ -10905,7 +11010,7 @@
         <v>1404</v>
       </c>
       <c r="P10" s="19" t="n">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="Q10" s="27" t="s">
         <v>99</v>
@@ -10924,23 +11029,23 @@
       </c>
       <c r="U10" s="21" t="n">
         <f aca="false">H10*INDEX(Assumptions!$C$28:$C$34,MATCH(D10,Assumptions!$B$28:$B$34,0))/12</f>
-        <v>733.333333333333</v>
+        <v>633.333333333333</v>
       </c>
       <c r="V10" s="21" t="n">
         <f aca="false">IF(ISNUMBER(P10),P10,INDEX(Assumptions!$D$28:$D$34,MATCH(D10,Assumptions!$B$28:$B$34,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M10,Assumptions!$B$22:$B$25,0)))/12</f>
-        <v>291.666666666667</v>
+        <v>250</v>
       </c>
       <c r="W10" s="21" t="n">
         <f aca="false">T10+U10+V10+O10</f>
-        <v>6522.05768033715</v>
+        <v>6380.39101367049</v>
       </c>
       <c r="X10" s="30" t="n">
         <f aca="false">IFERROR(K10/12/W10,0)</f>
-        <v>1.27771536864153</v>
+        <v>1.30608505269952</v>
       </c>
       <c r="Y10" s="30" t="n">
         <f aca="false">IFERROR(K10*Assumptions!$C$18/12/W10,0)</f>
-        <v>1.02217229491323</v>
+        <v>1.04486804215961</v>
       </c>
       <c r="Z10" s="21" t="n">
         <f aca="false">H10*J10+H10*(Assumptions!$C$16-I10)</f>
@@ -10948,7 +11053,7 @@
       </c>
       <c r="AA10" s="21" t="n">
         <f aca="false">W10*Assumptions!$C$17</f>
-        <v>39132.3460820229</v>
+        <v>38282.3460820229</v>
       </c>
       <c r="AB10" s="21" t="n">
         <f aca="false">K10*INDEX(Assumptions!$H$37:$H$38,MATCH(Q10,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N10="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
@@ -10960,11 +11065,11 @@
       </c>
       <c r="AD10" s="21" t="n">
         <f aca="false">K10-AB10-W10*12</f>
-        <v>-18464.6921640458</v>
+        <v>-16764.6921640458</v>
       </c>
       <c r="AE10" s="21" t="n">
         <f aca="false">AD10-AC10</f>
-        <v>-38464.6921640458</v>
+        <v>-36764.6921640458</v>
       </c>
       <c r="AF10" s="23" t="n">
         <f aca="false">IFERROR(K10/H10,0)</f>
@@ -11033,7 +11138,7 @@
         <v>1448</v>
       </c>
       <c r="P11" s="37" t="n">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="Q11" s="36" t="s">
         <v>99</v>
@@ -11052,23 +11157,23 @@
       </c>
       <c r="U11" s="40" t="n">
         <f aca="false">H11*INDEX(Assumptions!$C$28:$C$34,MATCH(D11,Assumptions!$B$28:$B$34,0))/12</f>
-        <v>490.416666666667</v>
+        <v>423.541666666667</v>
       </c>
       <c r="V11" s="40" t="n">
         <f aca="false">IF(ISNUMBER(P11),P11,INDEX(Assumptions!$D$28:$D$34,MATCH(D11,Assumptions!$B$28:$B$34,0))+INDEX(Assumptions!$C$22:$C$25,MATCH(M11,Assumptions!$B$22:$B$25,0)))/12</f>
-        <v>291.666666666667</v>
+        <v>250</v>
       </c>
       <c r="W11" s="40" t="n">
         <f aca="false">T11+U11+V11+O11</f>
-        <v>4967.3156570588</v>
+        <v>4858.77399039214</v>
       </c>
       <c r="X11" s="42" t="n">
         <f aca="false">IFERROR(K11/12/W11,0)</f>
-        <v>0.63750059092111</v>
+        <v>0.651741915332657</v>
       </c>
       <c r="Y11" s="42" t="n">
         <f aca="false">IFERROR(K11*Assumptions!$C$18/12/W11,0)</f>
-        <v>0.510000472736888</v>
+        <v>0.521393532266126</v>
       </c>
       <c r="Z11" s="40" t="n">
         <f aca="false">H11*J11+H11*(Assumptions!$C$16-I11)</f>
@@ -11076,7 +11181,7 @@
       </c>
       <c r="AA11" s="40" t="n">
         <f aca="false">W11*Assumptions!$C$17</f>
-        <v>29803.8939423528</v>
+        <v>29152.6439423528</v>
       </c>
       <c r="AB11" s="40" t="n">
         <f aca="false">K11*INDEX(Assumptions!$H$37:$H$38,MATCH(Q11,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N11="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
@@ -11088,11 +11193,11 @@
       </c>
       <c r="AD11" s="40" t="n">
         <f aca="false">K11-AB11-W11*12</f>
-        <v>-41347.7878847056</v>
+        <v>-40045.2878847056</v>
       </c>
       <c r="AE11" s="40" t="n">
         <f aca="false">AD11-AC11</f>
-        <v>-48947.7878847056</v>
+        <v>-47645.2878847056</v>
       </c>
       <c r="AF11" s="43" t="n">
         <f aca="false">IFERROR(K11/H11,0)</f>
@@ -12427,15 +12532,15 @@
       </c>
       <c r="I25" s="21" t="n">
         <f aca="false">H25+C25*INDEX(Assumptions!$C$28:$C$34,MATCH('Monroe (Keys)'!$D$6,Assumptions!$B$28:$B$34,0))/12+IF(ISNUMBER('Monroe (Keys)'!$P$6),'Monroe (Keys)'!$P$6,INDEX(Assumptions!$D$28:$D$34,MATCH('Monroe (Keys)'!$D$6,Assumptions!$B$28:$B$34,0))+INDEX(Assumptions!$C$22:$C$25,MATCH('Monroe (Keys)'!$M$6,Assumptions!$B$22:$B$25,0)))/12+'Monroe (Keys)'!$O$6</f>
-        <v>6439.55754533423</v>
+        <v>6302.89087866756</v>
       </c>
       <c r="J25" s="30" t="n">
         <f aca="false">IFERROR(E25/12/I25,0)</f>
-        <v>1.28088510355958</v>
+        <v>1.30865875550062</v>
       </c>
       <c r="K25" s="30" t="n">
         <f aca="false">IFERROR(E25*Assumptions!$C$18/12/I25,0)</f>
-        <v>1.02470808284767</v>
+        <v>1.0469270044005</v>
       </c>
       <c r="L25" s="21" t="n">
         <f aca="false">C25*B25+C25*(Assumptions!$C$16-D25)</f>
@@ -12443,15 +12548,15 @@
       </c>
       <c r="M25" s="21" t="n">
         <f aca="false">E25-(E25*INDEX(Assumptions!$H$37:$H$38,MATCH('Monroe (Keys)'!$Q$6,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF('Monroe (Keys)'!$N$6="Y",Assumptions!$C$42,Assumptions!$C$43))-I25*12</f>
-        <v>-18158.0905440108</v>
+        <v>-16518.0905440108</v>
       </c>
       <c r="N25" s="21" t="n">
         <f aca="false">M25-E25*INDEX(Assumptions!$C$37:$C$38,MATCH('Monroe (Keys)'!$Q$6,Assumptions!$B$37:$B$38,0))</f>
-        <v>-37954.0905440108</v>
+        <v>-36314.0905440108</v>
       </c>
       <c r="O25" s="23" t="n">
         <f aca="false">IFERROR(M25/L25,0)</f>
-        <v>-0.099550935000059</v>
+        <v>-0.0905597069298836</v>
       </c>
       <c r="P25" s="47" t="s">
         <v>415</v>
@@ -12491,15 +12596,15 @@
       </c>
       <c r="I26" s="21" t="n">
         <f aca="false">H26+C26*INDEX(Assumptions!$C$28:$C$34,MATCH('Monroe (Keys)'!$D$6,Assumptions!$B$28:$B$34,0))/12+IF(ISNUMBER('Monroe (Keys)'!$P$6),'Monroe (Keys)'!$P$6,INDEX(Assumptions!$D$28:$D$34,MATCH('Monroe (Keys)'!$D$6,Assumptions!$B$28:$B$34,0))+INDEX(Assumptions!$C$22:$C$25,MATCH('Monroe (Keys)'!$M$6,Assumptions!$B$22:$B$25,0)))/12+'Monroe (Keys)'!$O$6</f>
-        <v>6076.73812965363</v>
+        <v>5940.07146298696</v>
       </c>
       <c r="J26" s="30" t="n">
         <f aca="false">IFERROR(E26/12/I26,0)</f>
-        <v>1.35736198554988</v>
+        <v>1.38859159939899</v>
       </c>
       <c r="K26" s="30" t="n">
         <f aca="false">IFERROR(E26*Assumptions!$C$18/12/I26,0)</f>
-        <v>1.08588958843991</v>
+        <v>1.11087327951919</v>
       </c>
       <c r="L26" s="21" t="n">
         <f aca="false">C26*B26+C26*(Assumptions!$C$16-D26)</f>
@@ -12507,15 +12612,15 @@
       </c>
       <c r="M26" s="21" t="n">
         <f aca="false">E26-(E26*INDEX(Assumptions!$H$37:$H$38,MATCH('Monroe (Keys)'!$Q$6,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF('Monroe (Keys)'!$N$6="Y",Assumptions!$C$42,Assumptions!$C$43))-I26*12</f>
-        <v>-13804.2575558435</v>
+        <v>-12164.2575558435</v>
       </c>
       <c r="N26" s="21" t="n">
         <f aca="false">M26-E26*INDEX(Assumptions!$C$37:$C$38,MATCH('Monroe (Keys)'!$Q$6,Assumptions!$B$37:$B$38,0))</f>
-        <v>-33600.2575558435</v>
+        <v>-31960.2575558435</v>
       </c>
       <c r="O26" s="23" t="n">
         <f aca="false">IFERROR(M26/L26,0)</f>
-        <v>-0.0626327475310505</v>
+        <v>-0.0551917311971121</v>
       </c>
       <c r="P26" s="23" t="n">
         <f aca="false">IFERROR((M26-M25)/(L26-L25),0)</f>
@@ -12556,15 +12661,15 @@
       </c>
       <c r="I27" s="21" t="n">
         <f aca="false">H27+C27*INDEX(Assumptions!$C$28:$C$34,MATCH('Monroe (Keys)'!$D$6,Assumptions!$B$28:$B$34,0))/12+IF(ISNUMBER('Monroe (Keys)'!$P$6),'Monroe (Keys)'!$P$6,INDEX(Assumptions!$D$28:$D$34,MATCH('Monroe (Keys)'!$D$6,Assumptions!$B$28:$B$34,0))+INDEX(Assumptions!$C$22:$C$25,MATCH('Monroe (Keys)'!$M$6,Assumptions!$B$22:$B$25,0)))/12+'Monroe (Keys)'!$O$6</f>
-        <v>5772.51587729537</v>
+        <v>5635.8492106287</v>
       </c>
       <c r="J27" s="30" t="n">
         <f aca="false">IFERROR(E27/12/I27,0)</f>
-        <v>1.42889747012666</v>
+        <v>1.46354755513645</v>
       </c>
       <c r="K27" s="30" t="n">
         <f aca="false">IFERROR(E27*Assumptions!$C$18/12/I27,0)</f>
-        <v>1.14311797610133</v>
+        <v>1.17083804410916</v>
       </c>
       <c r="L27" s="21" t="n">
         <f aca="false">C27*B27+C27*(Assumptions!$C$16-D27)</f>
@@ -12572,19 +12677,19 @@
       </c>
       <c r="M27" s="21" t="n">
         <f aca="false">E27-(E27*INDEX(Assumptions!$H$37:$H$38,MATCH('Monroe (Keys)'!$Q$6,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF('Monroe (Keys)'!$N$6="Y",Assumptions!$C$42,Assumptions!$C$43))-I27*12</f>
-        <v>-10153.5905275444</v>
+        <v>-8513.59052754439</v>
       </c>
       <c r="N27" s="21" t="n">
         <f aca="false">M27-E27*INDEX(Assumptions!$C$37:$C$38,MATCH('Monroe (Keys)'!$Q$6,Assumptions!$B$37:$B$38,0))</f>
-        <v>-29949.5905275444</v>
+        <v>-28309.5905275444</v>
       </c>
       <c r="O27" s="23" t="n">
         <f aca="false">IFERROR(M27/L27,0)</f>
-        <v>-0.0392940809889489</v>
+        <v>-0.0329473317629427</v>
       </c>
       <c r="P27" s="23" t="n">
         <f aca="false">IFERROR((M27-M26)/(L27-L26),0)</f>
-        <v>0.0960701849552405</v>
+        <v>0.0960701849552401</v>
       </c>
     </row>
   </sheetData>
@@ -13220,7 +13325,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -13268,7 +13373,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
         <v>568</v>
       </c>
@@ -13279,201 +13384,227 @@
         <v>570</v>
       </c>
       <c r="D5" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>571</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="G5" s="9" t="s">
         <v>572</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="H5" s="9" t="s">
         <v>573</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>574</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="48" t="s">
+        <v>574</v>
+      </c>
+      <c r="B6" s="48" t="s">
+        <v>575</v>
+      </c>
+      <c r="C6" s="48" t="s">
         <v>576</v>
       </c>
-      <c r="B6" s="48" t="s">
+      <c r="D6" s="48" t="s">
         <v>577</v>
       </c>
-      <c r="C6" s="48" t="s">
+      <c r="E6" s="48" t="s">
         <v>578</v>
       </c>
-      <c r="D6" s="48" t="s">
+      <c r="F6" s="48" t="s">
         <v>579</v>
       </c>
-      <c r="E6" s="48" t="s">
+      <c r="G6" s="48" t="s">
         <v>580</v>
       </c>
-      <c r="F6" s="48" t="s">
+      <c r="H6" s="48" t="s">
         <v>581</v>
-      </c>
-      <c r="G6" s="48" t="s">
-        <v>582</v>
-      </c>
-      <c r="H6" s="48" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
+        <v>582</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>583</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>584</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="D7" s="9" t="s">
         <v>585</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="E7" s="9" t="s">
         <v>586</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="F7" s="9" t="s">
         <v>587</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="G7" s="9" t="s">
         <v>588</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="H7" s="9" t="s">
         <v>589</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>590</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="48" t="s">
+        <v>590</v>
+      </c>
+      <c r="B8" s="48" t="s">
+        <v>591</v>
+      </c>
+      <c r="C8" s="48" t="s">
         <v>592</v>
       </c>
-      <c r="B8" s="48" t="s">
+      <c r="D8" s="48" t="s">
         <v>593</v>
       </c>
-      <c r="C8" s="48" t="s">
+      <c r="E8" s="48" t="s">
         <v>594</v>
       </c>
-      <c r="D8" s="48" t="s">
+      <c r="F8" s="48" t="s">
         <v>595</v>
       </c>
-      <c r="E8" s="48" t="s">
+      <c r="G8" s="48" t="s">
         <v>596</v>
       </c>
-      <c r="F8" s="48" t="s">
+      <c r="H8" s="48" t="s">
         <v>597</v>
       </c>
-      <c r="G8" s="48" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
         <v>598</v>
       </c>
-      <c r="H8" s="48" t="s">
+      <c r="B9" s="9" t="s">
         <v>599</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
+      <c r="C9" s="9" t="s">
         <v>600</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="D9" s="9" t="s">
         <v>601</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="E9" s="9" t="s">
         <v>602</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="F9" s="9" t="s">
         <v>603</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="G9" s="9" t="s">
         <v>604</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="H9" s="9" t="s">
         <v>605</v>
       </c>
-      <c r="G9" s="9" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="48" t="s">
         <v>606</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="B10" s="48" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="48" t="s">
+      <c r="C10" s="48" t="s">
         <v>608</v>
       </c>
-      <c r="B10" s="48" t="s">
+      <c r="D10" s="48" t="s">
         <v>609</v>
       </c>
-      <c r="C10" s="48" t="s">
+      <c r="E10" s="48" t="s">
         <v>610</v>
       </c>
-      <c r="D10" s="48" t="s">
+      <c r="F10" s="48" t="s">
         <v>611</v>
       </c>
-      <c r="E10" s="48" t="s">
+      <c r="G10" s="48" t="s">
         <v>612</v>
       </c>
-      <c r="F10" s="48" t="s">
+      <c r="H10" s="48" t="s">
         <v>613</v>
       </c>
-      <c r="G10" s="48" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="s">
         <v>614</v>
       </c>
-      <c r="H10" s="48" t="s">
+      <c r="B11" s="9" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
+      <c r="C11" s="9" t="s">
         <v>616</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="D11" s="9" t="s">
         <v>617</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="E11" s="9" t="s">
         <v>618</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="F11" s="9" t="s">
         <v>619</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="G11" s="9" t="s">
         <v>620</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="H11" s="9" t="s">
         <v>621</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>622</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="48" t="s">
+        <v>622</v>
+      </c>
+      <c r="B12" s="48" t="s">
+        <v>623</v>
+      </c>
+      <c r="C12" s="48" t="s">
         <v>624</v>
       </c>
-      <c r="B12" s="48" t="s">
+      <c r="D12" s="48" t="s">
         <v>625</v>
       </c>
-      <c r="C12" s="48" t="s">
+      <c r="E12" s="48" t="s">
         <v>626</v>
       </c>
-      <c r="D12" s="48" t="s">
+      <c r="F12" s="48" t="s">
         <v>627</v>
       </c>
-      <c r="E12" s="48" t="s">
+      <c r="G12" s="48" t="s">
         <v>628</v>
       </c>
-      <c r="F12" s="48" t="s">
+      <c r="H12" s="48" t="s">
         <v>629</v>
       </c>
-      <c r="G12" s="48" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="s">
         <v>630</v>
       </c>
-      <c r="H12" s="48" t="s">
+      <c r="B13" s="9" t="s">
         <v>631</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>632</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>633</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>637</v>
       </c>
     </row>
   </sheetData>

--- a/str-deal-search/STR_DSCR_Analysis.xlsx
+++ b/str-deal-search/STR_DSCR_Analysis.xlsx
@@ -502,7 +502,7 @@
     <t xml:space="preserve">STR</t>
   </si>
   <si>
-    <t xml:space="preserve">Nightly/weekly. Full-service PM 18-30% locally; Airbnb host-only fee 15.5% (blended 10%); cleaning ~10% of gross (offset if guest-paid fees are inside the seller's gross).</t>
+    <t xml:space="preserve">Nightly/weekly. Full-service PM 18-30% locally; Airbnb host-only fee 15.5% (blended 10%); cleaning = 0: passed through to guests as a cleaning fee. Use gross EXCLUDING guest-paid cleaning fees.</t>
   </si>
   <si>
     <t xml:space="preserve">Seasonal</t>
@@ -5298,11 +5298,11 @@
       </c>
       <c r="J5" s="6" t="n">
         <f aca="false">'Manatee-Sarasota'!$AD$6</f>
-        <v>-3831.68451483207</v>
+        <v>4668.31548516793</v>
       </c>
       <c r="K5" s="6" t="n">
         <f aca="false">'Manatee-Sarasota'!$AE$6</f>
-        <v>-20831.6845148321</v>
+        <v>-12331.6845148321</v>
       </c>
       <c r="L5" s="8" t="s">
         <v>15</v>
@@ -5346,11 +5346,11 @@
       </c>
       <c r="J6" s="6" t="n">
         <f aca="false">'Manatee-Sarasota'!$AD$7</f>
-        <v>-2432.09799432634</v>
+        <v>4867.90200567366</v>
       </c>
       <c r="K6" s="6" t="n">
         <f aca="false">'Manatee-Sarasota'!$AE$7</f>
-        <v>-17032.0979943263</v>
+        <v>-9732.09799432635</v>
       </c>
       <c r="L6" s="9" t="s">
         <v>16</v>
@@ -5394,11 +5394,11 @@
       </c>
       <c r="J7" s="6" t="n">
         <f aca="false">'Manatee-Sarasota'!$AD$8</f>
-        <v>-4207.51912303436</v>
+        <v>4692.48087696564</v>
       </c>
       <c r="K7" s="6" t="n">
         <f aca="false">'Manatee-Sarasota'!$AE$8</f>
-        <v>-22007.5191230344</v>
+        <v>-13107.5191230344</v>
       </c>
       <c r="L7" s="9" t="s">
         <v>17</v>
@@ -5442,11 +5442,11 @@
       </c>
       <c r="J8" s="6" t="n">
         <f aca="false">Pinellas!$AD$6</f>
-        <v>-7966.99462445278</v>
+        <v>-866.994624452775</v>
       </c>
       <c r="K8" s="6" t="n">
         <f aca="false">Pinellas!$AE$6</f>
-        <v>-22166.9946244528</v>
+        <v>-15066.9946244528</v>
       </c>
       <c r="L8" s="9" t="s">
         <v>19</v>
@@ -5490,11 +5490,11 @@
       </c>
       <c r="J9" s="6" t="n">
         <f aca="false">Pinellas!$AD$7</f>
-        <v>1413.00537554723</v>
+        <v>9913.00537554723</v>
       </c>
       <c r="K9" s="6" t="n">
         <f aca="false">Pinellas!$AE$7</f>
-        <v>-15586.9946244528</v>
+        <v>-7086.99462445278</v>
       </c>
       <c r="L9" s="9" t="s">
         <v>20</v>
@@ -5538,11 +5538,11 @@
       </c>
       <c r="J10" s="6" t="n">
         <f aca="false">Pinellas!$AD$8</f>
-        <v>-8344.59416971947</v>
+        <v>-3244.59416971947</v>
       </c>
       <c r="K10" s="6" t="n">
         <f aca="false">Pinellas!$AE$8</f>
-        <v>-18544.5941697195</v>
+        <v>-13444.5941697195</v>
       </c>
       <c r="L10" s="9" t="s">
         <v>21</v>
@@ -5586,11 +5586,11 @@
       </c>
       <c r="J11" s="6" t="n">
         <f aca="false">'Other SWFL Listings'!$AD$6</f>
-        <v>-13862.0979943264</v>
+        <v>-7862.09799432635</v>
       </c>
       <c r="K11" s="6" t="n">
         <f aca="false">'Other SWFL Listings'!$AE$6</f>
-        <v>-25862.0979943264</v>
+        <v>-19862.0979943264</v>
       </c>
       <c r="L11" s="9" t="s">
         <v>23</v>
@@ -5634,11 +5634,11 @@
       </c>
       <c r="J12" s="6" t="n">
         <f aca="false">'Monroe (Keys)'!$AD$7</f>
-        <v>-4885.91575316079</v>
+        <v>5114.08424683921</v>
       </c>
       <c r="K12" s="6" t="n">
         <f aca="false">'Monroe (Keys)'!$AE$7</f>
-        <v>-24885.9157531608</v>
+        <v>-14885.9157531608</v>
       </c>
       <c r="L12" s="9" t="s">
         <v>25</v>
@@ -5682,11 +5682,11 @@
       </c>
       <c r="J13" s="6" t="n">
         <f aca="false">'Monroe (Keys)'!$AD$6</f>
-        <v>-12164.2575558435</v>
+        <v>-2266.25755584351</v>
       </c>
       <c r="K13" s="6" t="n">
         <f aca="false">'Monroe (Keys)'!$AE$6</f>
-        <v>-31960.2575558435</v>
+        <v>-22062.2575558435</v>
       </c>
       <c r="L13" s="9" t="s">
         <v>26</v>
@@ -8054,7 +8054,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="4" t="s">
         <v>100</v>
       </c>
@@ -8065,7 +8065,7 @@
         <v>0.1</v>
       </c>
       <c r="E37" s="18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F37" s="18" t="n">
         <v>0.08</v>
@@ -8075,7 +8075,7 @@
       </c>
       <c r="H37" s="23" t="n">
         <f aca="false">SUM(D37:G37)</f>
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
       <c r="I37" s="14" t="s">
         <v>101</v>
@@ -8092,7 +8092,7 @@
         <v>0.02</v>
       </c>
       <c r="E38" s="18" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="F38" s="18" t="n">
         <v>0.06</v>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="H38" s="23" t="n">
         <f aca="false">SUM(D38:G38)</f>
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="I38" s="14" t="s">
         <v>103</v>
@@ -8423,7 +8423,7 @@
       </c>
       <c r="AB6" s="21" t="n">
         <f aca="false">K6*INDEX(Assumptions!$H$37:$H$38,MATCH(Q6,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N6="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
-        <v>37050</v>
+        <v>28550</v>
       </c>
       <c r="AC6" s="21" t="n">
         <f aca="false">K6*INDEX(Assumptions!$C$37:$C$38,MATCH(Q6,Assumptions!$B$37:$B$38,0))</f>
@@ -8431,11 +8431,11 @@
       </c>
       <c r="AD6" s="21" t="n">
         <f aca="false">K6-AB6-W6*12</f>
-        <v>-3831.68451483207</v>
+        <v>4668.31548516793</v>
       </c>
       <c r="AE6" s="21" t="n">
         <f aca="false">AD6-AC6</f>
-        <v>-20831.6845148321</v>
+        <v>-12331.6845148321</v>
       </c>
       <c r="AF6" s="23" t="n">
         <f aca="false">IFERROR(K6/H6,0)</f>
@@ -8443,7 +8443,7 @@
       </c>
       <c r="AG6" s="23" t="n">
         <f aca="false">IFERROR((K6-AB6-AC6)/H6,0)</f>
-        <v>0.0552678571428571</v>
+        <v>0.0704464285714286</v>
       </c>
       <c r="AH6" s="26" t="s">
         <v>146</v>
@@ -8551,7 +8551,7 @@
       </c>
       <c r="AB7" s="40" t="n">
         <f aca="false">K7*INDEX(Assumptions!$H$37:$H$38,MATCH(Q7,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N7="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
-        <v>31290</v>
+        <v>23990</v>
       </c>
       <c r="AC7" s="40" t="n">
         <f aca="false">K7*INDEX(Assumptions!$C$37:$C$38,MATCH(Q7,Assumptions!$B$37:$B$38,0))</f>
@@ -8559,11 +8559,11 @@
       </c>
       <c r="AD7" s="40" t="n">
         <f aca="false">K7-AB7-W7*12</f>
-        <v>-2432.09799432634</v>
+        <v>4867.90200567366</v>
       </c>
       <c r="AE7" s="40" t="n">
         <f aca="false">AD7-AC7</f>
-        <v>-17032.0979943263</v>
+        <v>-9732.09799432635</v>
       </c>
       <c r="AF7" s="43" t="n">
         <f aca="false">IFERROR(K7/H7,0)</f>
@@ -8571,7 +8571,7 @@
       </c>
       <c r="AG7" s="43" t="n">
         <f aca="false">IFERROR((K7-AB7-AC7)/H7,0)</f>
-        <v>0.0589347826086957</v>
+        <v>0.074804347826087</v>
       </c>
       <c r="AH7" s="35" t="s">
         <v>155</v>
@@ -8679,7 +8679,7 @@
       </c>
       <c r="AB8" s="21" t="n">
         <f aca="false">K8*INDEX(Assumptions!$H$37:$H$38,MATCH(Q8,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N8="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
-        <v>38370</v>
+        <v>29470</v>
       </c>
       <c r="AC8" s="21" t="n">
         <f aca="false">K8*INDEX(Assumptions!$C$37:$C$38,MATCH(Q8,Assumptions!$B$37:$B$38,0))</f>
@@ -8687,11 +8687,11 @@
       </c>
       <c r="AD8" s="21" t="n">
         <f aca="false">K8-AB8-W8*12</f>
-        <v>-4207.51912303436</v>
+        <v>4692.48087696564</v>
       </c>
       <c r="AE8" s="21" t="n">
         <f aca="false">AD8-AC8</f>
-        <v>-22007.5191230344</v>
+        <v>-13107.5191230344</v>
       </c>
       <c r="AF8" s="23" t="n">
         <f aca="false">IFERROR(K8/H8,0)</f>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="AG8" s="23" t="n">
         <f aca="false">IFERROR((K8-AB8-AC8)/H8,0)</f>
-        <v>0.0547166666666667</v>
+        <v>0.06955</v>
       </c>
       <c r="AH8" s="26" t="s">
         <v>161</v>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="AB9" s="40" t="n">
         <f aca="false">K9*INDEX(Assumptions!$H$37:$H$38,MATCH(Q9,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N9="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
-        <v>27000</v>
+        <v>21000</v>
       </c>
       <c r="AC9" s="40" t="n">
         <f aca="false">K9*INDEX(Assumptions!$C$37:$C$38,MATCH(Q9,Assumptions!$B$37:$B$38,0))</f>
@@ -8815,11 +8815,11 @@
       </c>
       <c r="AD9" s="40" t="n">
         <f aca="false">K9-AB9-W9*12</f>
-        <v>-9077.61866830105</v>
+        <v>-3077.61866830105</v>
       </c>
       <c r="AE9" s="40" t="n">
         <f aca="false">AD9-AC9</f>
-        <v>-21077.6186683011</v>
+        <v>-15077.6186683011</v>
       </c>
       <c r="AF9" s="43" t="n">
         <f aca="false">IFERROR(K9/H9,0)</f>
@@ -8827,7 +8827,7 @@
       </c>
       <c r="AG9" s="43" t="n">
         <f aca="false">IFERROR((K9-AB9-AC9)/H9,0)</f>
-        <v>0.0461538461538462</v>
+        <v>0.0593406593406593</v>
       </c>
       <c r="AH9" s="35" t="s">
         <v>167</v>
@@ -8935,7 +8935,7 @@
       </c>
       <c r="AB10" s="21" t="n">
         <f aca="false">K10*INDEX(Assumptions!$H$37:$H$38,MATCH(Q10,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N10="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
-        <v>26820</v>
+        <v>21420</v>
       </c>
       <c r="AC10" s="21" t="n">
         <f aca="false">K10*INDEX(Assumptions!$C$37:$C$38,MATCH(Q10,Assumptions!$B$37:$B$38,0))</f>
@@ -8943,11 +8943,11 @@
       </c>
       <c r="AD10" s="21" t="n">
         <f aca="false">K10-AB10-W10*12</f>
-        <v>-17107.959576537</v>
+        <v>-11707.959576537</v>
       </c>
       <c r="AE10" s="21" t="n">
         <f aca="false">AD10-AC10</f>
-        <v>-27907.959576537</v>
+        <v>-22507.959576537</v>
       </c>
       <c r="AF10" s="23" t="n">
         <f aca="false">IFERROR(K10/H10,0)</f>
@@ -8955,7 +8955,7 @@
       </c>
       <c r="AG10" s="23" t="n">
         <f aca="false">IFERROR((K10-AB10-AC10)/H10,0)</f>
-        <v>0.0344842831248066</v>
+        <v>0.0458527281110066</v>
       </c>
       <c r="AH10" s="26" t="s">
         <v>172</v>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="AB11" s="40" t="n">
         <f aca="false">K11*INDEX(Assumptions!$H$37:$H$38,MATCH(Q11,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N11="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
-        <v>28800</v>
+        <v>22800</v>
       </c>
       <c r="AC11" s="40" t="n">
         <f aca="false">K11*INDEX(Assumptions!$C$37:$C$38,MATCH(Q11,Assumptions!$B$37:$B$38,0))</f>
@@ -9071,11 +9071,11 @@
       </c>
       <c r="AD11" s="40" t="n">
         <f aca="false">K11-AB11-W11*12</f>
-        <v>-17143.8705806045</v>
+        <v>-11143.8705806045</v>
       </c>
       <c r="AE11" s="40" t="n">
         <f aca="false">AD11-AC11</f>
-        <v>-29143.8705806045</v>
+        <v>-23143.8705806045</v>
       </c>
       <c r="AF11" s="43" t="n">
         <f aca="false">IFERROR(K11/H11,0)</f>
@@ -9083,7 +9083,7 @@
       </c>
       <c r="AG11" s="43" t="n">
         <f aca="false">IFERROR((K11-AB11-AC11)/H11,0)</f>
-        <v>0.0372815533980583</v>
+        <v>0.0489320388349515</v>
       </c>
       <c r="AH11" s="35" t="s">
         <v>177</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="AB12" s="21" t="n">
         <f aca="false">K12*INDEX(Assumptions!$H$37:$H$38,MATCH(Q12,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N12="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
-        <v>23751.81</v>
+        <v>18736.11</v>
       </c>
       <c r="AC12" s="21" t="n">
         <f aca="false">K12*INDEX(Assumptions!$C$37:$C$38,MATCH(Q12,Assumptions!$B$37:$B$38,0))</f>
@@ -9199,11 +9199,11 @@
       </c>
       <c r="AD12" s="21" t="n">
         <f aca="false">K12-AB12-W12*12</f>
-        <v>-19417.2219285539</v>
+        <v>-14401.5219285539</v>
       </c>
       <c r="AE12" s="21" t="n">
         <f aca="false">AD12-AC12</f>
-        <v>-29448.6219285539</v>
+        <v>-24432.9219285539</v>
       </c>
       <c r="AF12" s="23" t="n">
         <f aca="false">IFERROR(K12/H12,0)</f>
@@ -9211,7 +9211,7 @@
       </c>
       <c r="AG12" s="23" t="n">
         <f aca="false">IFERROR((K12-AB12-AC12)/H12,0)</f>
-        <v>0.0324233465346535</v>
+        <v>0.0423554257425743</v>
       </c>
       <c r="AH12" s="26" t="s">
         <v>182</v>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="AB13" s="40" t="n">
         <f aca="false">K13*INDEX(Assumptions!$H$37:$H$38,MATCH(Q13,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N13="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
-        <v>24840</v>
+        <v>20040</v>
       </c>
       <c r="AC13" s="40" t="n">
         <f aca="false">K13*INDEX(Assumptions!$C$37:$C$38,MATCH(Q13,Assumptions!$B$37:$B$38,0))</f>
@@ -9327,11 +9327,11 @@
       </c>
       <c r="AD13" s="40" t="n">
         <f aca="false">K13-AB13-W13*12</f>
-        <v>-26425.8085586803</v>
+        <v>-21625.8085586803</v>
       </c>
       <c r="AE13" s="40" t="n">
         <f aca="false">AD13-AC13</f>
-        <v>-36025.8085586803</v>
+        <v>-31225.8085586803</v>
       </c>
       <c r="AF13" s="43" t="n">
         <f aca="false">IFERROR(K13/H13,0)</f>
@@ -9339,7 +9339,7 @@
       </c>
       <c r="AG13" s="43" t="n">
         <f aca="false">IFERROR((K13-AB13-AC13)/H13,0)</f>
-        <v>0.0255849056603774</v>
+        <v>0.0346415094339623</v>
       </c>
       <c r="AH13" s="35" t="s">
         <v>187</v>
@@ -9447,7 +9447,7 @@
       </c>
       <c r="AB14" s="21" t="n">
         <f aca="false">K14*INDEX(Assumptions!$H$37:$H$38,MATCH(Q14,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N14="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
-        <v>20400</v>
+        <v>16400</v>
       </c>
       <c r="AC14" s="21" t="n">
         <f aca="false">K14*INDEX(Assumptions!$C$37:$C$38,MATCH(Q14,Assumptions!$B$37:$B$38,0))</f>
@@ -9455,11 +9455,11 @@
       </c>
       <c r="AD14" s="21" t="n">
         <f aca="false">K14-AB14-W14*12</f>
-        <v>-15902.5114738206</v>
+        <v>-11902.5114738206</v>
       </c>
       <c r="AE14" s="21" t="n">
         <f aca="false">AD14-AC14</f>
-        <v>-23902.5114738206</v>
+        <v>-19902.5114738206</v>
       </c>
       <c r="AF14" s="23" t="n">
         <f aca="false">IFERROR(K14/H14,0)</f>
@@ -9467,7 +9467,7 @@
       </c>
       <c r="AG14" s="23" t="n">
         <f aca="false">IFERROR((K14-AB14-AC14)/H14,0)</f>
-        <v>0.0322222222222222</v>
+        <v>0.0433333333333333</v>
       </c>
       <c r="AH14" s="26" t="s">
         <v>192</v>
@@ -9575,7 +9575,7 @@
       </c>
       <c r="AB15" s="40" t="n">
         <f aca="false">K15*INDEX(Assumptions!$H$37:$H$38,MATCH(Q15,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N15="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
-        <v>23520</v>
+        <v>20460</v>
       </c>
       <c r="AC15" s="40" t="n">
         <f aca="false">K15*INDEX(Assumptions!$C$37:$C$38,MATCH(Q15,Assumptions!$B$37:$B$38,0))</f>
@@ -9583,11 +9583,11 @@
       </c>
       <c r="AD15" s="40" t="n">
         <f aca="false">K15-AB15-W15*12</f>
-        <v>20423.2082906875</v>
+        <v>23483.2082906875</v>
       </c>
       <c r="AE15" s="40" t="n">
         <f aca="false">AD15-AC15</f>
-        <v>8183.20829068749</v>
+        <v>11243.2082906875</v>
       </c>
       <c r="AF15" s="43" t="n">
         <f aca="false">IFERROR(K15/H15,0)</f>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="AG15" s="43" t="n">
         <f aca="false">IFERROR((K15-AB15-AC15)/H15,0)</f>
-        <v>0.101129770992366</v>
+        <v>0.105801526717557</v>
       </c>
       <c r="AH15" s="35" t="s">
         <v>199</v>
@@ -9703,7 +9703,7 @@
       </c>
       <c r="AB16" s="21" t="n">
         <f aca="false">K16*INDEX(Assumptions!$H$37:$H$38,MATCH(Q16,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N16="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
-        <v>21720</v>
+        <v>17320</v>
       </c>
       <c r="AC16" s="21" t="n">
         <f aca="false">K16*INDEX(Assumptions!$C$37:$C$38,MATCH(Q16,Assumptions!$B$37:$B$38,0))</f>
@@ -9711,11 +9711,11 @@
       </c>
       <c r="AD16" s="21" t="n">
         <f aca="false">K16-AB16-W16*12</f>
-        <v>-13758.446392211</v>
+        <v>-9358.44639221097</v>
       </c>
       <c r="AE16" s="21" t="n">
         <f aca="false">AD16-AC16</f>
-        <v>-22558.446392211</v>
+        <v>-18158.446392211</v>
       </c>
       <c r="AF16" s="23" t="n">
         <f aca="false">IFERROR(K16/H16,0)</f>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="AG16" s="23" t="n">
         <f aca="false">IFERROR((K16-AB16-AC16)/H16,0)</f>
-        <v>0.0483154121863799</v>
+        <v>0.0640860215053763</v>
       </c>
       <c r="AH16" s="26"/>
       <c r="AI16" s="13" t="n">
@@ -9829,7 +9829,7 @@
       </c>
       <c r="AB17" s="40" t="n">
         <f aca="false">K17*INDEX(Assumptions!$H$37:$H$38,MATCH(Q17,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N17="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
-        <v>23700</v>
+        <v>18700</v>
       </c>
       <c r="AC17" s="40" t="n">
         <f aca="false">K17*INDEX(Assumptions!$C$37:$C$38,MATCH(Q17,Assumptions!$B$37:$B$38,0))</f>
@@ -9837,11 +9837,11 @@
       </c>
       <c r="AD17" s="40" t="n">
         <f aca="false">K17-AB17-W17*12</f>
-        <v>-44398.4578660316</v>
+        <v>-39398.4578660316</v>
       </c>
       <c r="AE17" s="40" t="n">
         <f aca="false">AD17-AC17</f>
-        <v>-54398.4578660316</v>
+        <v>-49398.4578660316</v>
       </c>
       <c r="AF17" s="43" t="n">
         <f aca="false">IFERROR(K17/H17,0)</f>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="AG17" s="43" t="n">
         <f aca="false">IFERROR((K17-AB17-AC17)/H17,0)</f>
-        <v>0.025508607198748</v>
+        <v>0.0333333333333333</v>
       </c>
       <c r="AH17" s="35"/>
       <c r="AI17" s="34" t="n">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="AB6" s="21" t="n">
         <f aca="false">K6*INDEX(Assumptions!$H$37:$H$38,MATCH(Q6,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N6="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
-        <v>32430</v>
+        <v>25330</v>
       </c>
       <c r="AC6" s="21" t="n">
         <f aca="false">K6*INDEX(Assumptions!$C$37:$C$38,MATCH(Q6,Assumptions!$B$37:$B$38,0))</f>
@@ -10346,11 +10346,11 @@
       </c>
       <c r="AD6" s="21" t="n">
         <f aca="false">K6-AB6-W6*12</f>
-        <v>-7966.99462445278</v>
+        <v>-866.994624452775</v>
       </c>
       <c r="AE6" s="21" t="n">
         <f aca="false">AD6-AC6</f>
-        <v>-22166.9946244528</v>
+        <v>-15066.9946244528</v>
       </c>
       <c r="AF6" s="23" t="n">
         <f aca="false">IFERROR(K6/H6,0)</f>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="AG6" s="23" t="n">
         <f aca="false">IFERROR((K6-AB6-AC6)/H6,0)</f>
-        <v>0.0502474226804124</v>
+        <v>0.0648865979381443</v>
       </c>
       <c r="AH6" s="26"/>
       <c r="AI6" s="13" t="n">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="AB7" s="40" t="n">
         <f aca="false">K7*INDEX(Assumptions!$H$37:$H$38,MATCH(Q7,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N7="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
-        <v>37050</v>
+        <v>28550</v>
       </c>
       <c r="AC7" s="40" t="n">
         <f aca="false">K7*INDEX(Assumptions!$C$37:$C$38,MATCH(Q7,Assumptions!$B$37:$B$38,0))</f>
@@ -10472,11 +10472,11 @@
       </c>
       <c r="AD7" s="40" t="n">
         <f aca="false">K7-AB7-W7*12</f>
-        <v>1413.00537554723</v>
+        <v>9913.00537554723</v>
       </c>
       <c r="AE7" s="40" t="n">
         <f aca="false">AD7-AC7</f>
-        <v>-15586.9946244528</v>
+        <v>-7086.99462445278</v>
       </c>
       <c r="AF7" s="43" t="n">
         <f aca="false">IFERROR(K7/H7,0)</f>
@@ -10484,7 +10484,7 @@
       </c>
       <c r="AG7" s="43" t="n">
         <f aca="false">IFERROR((K7-AB7-AC7)/H7,0)</f>
-        <v>0.0638144329896907</v>
+        <v>0.081340206185567</v>
       </c>
       <c r="AH7" s="35"/>
       <c r="AI7" s="34" t="n">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="AB8" s="21" t="n">
         <f aca="false">K8*INDEX(Assumptions!$H$37:$H$38,MATCH(Q8,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N8="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
-        <v>24030</v>
+        <v>18930</v>
       </c>
       <c r="AC8" s="21" t="n">
         <f aca="false">K8*INDEX(Assumptions!$C$37:$C$38,MATCH(Q8,Assumptions!$B$37:$B$38,0))</f>
@@ -10598,11 +10598,11 @@
       </c>
       <c r="AD8" s="21" t="n">
         <f aca="false">K8-AB8-W8*12</f>
-        <v>-8344.59416971947</v>
+        <v>-3244.59416971947</v>
       </c>
       <c r="AE8" s="21" t="n">
         <f aca="false">AD8-AC8</f>
-        <v>-18544.5941697195</v>
+        <v>-13444.5941697195</v>
       </c>
       <c r="AF8" s="23" t="n">
         <f aca="false">IFERROR(K8/H8,0)</f>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="AG8" s="23" t="n">
         <f aca="false">IFERROR((K8-AB8-AC8)/H8,0)</f>
-        <v>0.0493235294117647</v>
+        <v>0.0643235294117647</v>
       </c>
       <c r="AH8" s="26"/>
       <c r="AI8" s="13" t="n">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="AB9" s="40" t="n">
         <f aca="false">K9*INDEX(Assumptions!$H$37:$H$38,MATCH(Q9,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N9="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
-        <v>31950</v>
+        <v>24450</v>
       </c>
       <c r="AC9" s="40" t="n">
         <f aca="false">K9*INDEX(Assumptions!$C$37:$C$38,MATCH(Q9,Assumptions!$B$37:$B$38,0))</f>
@@ -10724,11 +10724,11 @@
       </c>
       <c r="AD9" s="40" t="n">
         <f aca="false">K9-AB9-W9*12</f>
-        <v>-29515.3537312367</v>
+        <v>-22015.3537312367</v>
       </c>
       <c r="AE9" s="40" t="n">
         <f aca="false">AD9-AC9</f>
-        <v>-44515.3537312367</v>
+        <v>-37015.3537312367</v>
       </c>
       <c r="AF9" s="43" t="n">
         <f aca="false">IFERROR(K9/H9,0)</f>
@@ -10736,7 +10736,7 @@
       </c>
       <c r="AG9" s="43" t="n">
         <f aca="false">IFERROR((K9-AB9-AC9)/H9,0)</f>
-        <v>0.043828125</v>
+        <v>0.055546875</v>
       </c>
       <c r="AH9" s="35"/>
       <c r="AI9" s="34" t="n">
@@ -10842,7 +10842,7 @@
       </c>
       <c r="AB10" s="21" t="n">
         <f aca="false">K10*INDEX(Assumptions!$H$37:$H$38,MATCH(Q10,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N10="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
-        <v>26670</v>
+        <v>20770</v>
       </c>
       <c r="AC10" s="21" t="n">
         <f aca="false">K10*INDEX(Assumptions!$C$37:$C$38,MATCH(Q10,Assumptions!$B$37:$B$38,0))</f>
@@ -10850,11 +10850,11 @@
       </c>
       <c r="AD10" s="21" t="n">
         <f aca="false">K10-AB10-W10*12</f>
-        <v>-30071.6845148321</v>
+        <v>-24171.6845148321</v>
       </c>
       <c r="AE10" s="21" t="n">
         <f aca="false">AD10-AC10</f>
-        <v>-41871.6845148321</v>
+        <v>-35971.6845148321</v>
       </c>
       <c r="AF10" s="23" t="n">
         <f aca="false">IFERROR(K10/H10,0)</f>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="AG10" s="23" t="n">
         <f aca="false">IFERROR((K10-AB10-AC10)/H10,0)</f>
-        <v>0.0366607142857143</v>
+        <v>0.0471964285714286</v>
       </c>
       <c r="AH10" s="26"/>
       <c r="AI10" s="13" t="n">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="AB11" s="40" t="n">
         <f aca="false">K11*INDEX(Assumptions!$H$37:$H$38,MATCH(Q11,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N11="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
-        <v>14862.4</v>
+        <v>13425.7</v>
       </c>
       <c r="AC11" s="40" t="n">
         <f aca="false">K11*INDEX(Assumptions!$C$37:$C$38,MATCH(Q11,Assumptions!$B$37:$B$38,0))</f>
@@ -10976,11 +10976,11 @@
       </c>
       <c r="AD11" s="40" t="n">
         <f aca="false">K11-AB11-W11*12</f>
-        <v>-38655.9604709838</v>
+        <v>-37219.2604709838</v>
       </c>
       <c r="AE11" s="40" t="n">
         <f aca="false">AD11-AC11</f>
-        <v>-44402.7604709838</v>
+        <v>-42966.0604709838</v>
       </c>
       <c r="AF11" s="43" t="n">
         <f aca="false">IFERROR(K11/H11,0)</f>
@@ -10988,7 +10988,7 @@
       </c>
       <c r="AG11" s="43" t="n">
         <f aca="false">IFERROR((K11-AB11-AC11)/H11,0)</f>
-        <v>0.0462386440677966</v>
+        <v>0.0486737288135593</v>
       </c>
       <c r="AH11" s="35"/>
       <c r="AI11" s="34" t="n">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AB12" s="21" t="n">
         <f aca="false">K12*INDEX(Assumptions!$H$37:$H$38,MATCH(Q12,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N12="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
-        <v>23700</v>
+        <v>18700</v>
       </c>
       <c r="AC12" s="21" t="n">
         <f aca="false">K12*INDEX(Assumptions!$C$37:$C$38,MATCH(Q12,Assumptions!$B$37:$B$38,0))</f>
@@ -11102,11 +11102,11 @@
       </c>
       <c r="AD12" s="21" t="n">
         <f aca="false">K12-AB12-W12*12</f>
-        <v>-55199.709778335</v>
+        <v>-50199.709778335</v>
       </c>
       <c r="AE12" s="21" t="n">
         <f aca="false">AD12-AC12</f>
-        <v>-65199.709778335</v>
+        <v>-60199.709778335</v>
       </c>
       <c r="AF12" s="23" t="n">
         <f aca="false">IFERROR(K12/H12,0)</f>
@@ -11114,7 +11114,7 @@
       </c>
       <c r="AG12" s="23" t="n">
         <f aca="false">IFERROR((K12-AB12-AC12)/H12,0)</f>
-        <v>0.0233190271816881</v>
+        <v>0.0304721030042918</v>
       </c>
       <c r="AH12" s="26"/>
       <c r="AI12" s="13" t="n">
@@ -11745,7 +11745,7 @@
       </c>
       <c r="AB6" s="21" t="n">
         <f aca="false">K6*INDEX(Assumptions!$H$37:$H$38,MATCH(Q6,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N6="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
-        <v>28800</v>
+        <v>22800</v>
       </c>
       <c r="AC6" s="21" t="n">
         <f aca="false">K6*INDEX(Assumptions!$C$37:$C$38,MATCH(Q6,Assumptions!$B$37:$B$38,0))</f>
@@ -11753,11 +11753,11 @@
       </c>
       <c r="AD6" s="21" t="n">
         <f aca="false">K6-AB6-W6*12</f>
-        <v>-13862.0979943264</v>
+        <v>-7862.09799432635</v>
       </c>
       <c r="AE6" s="21" t="n">
         <f aca="false">AD6-AC6</f>
-        <v>-25862.0979943264</v>
+        <v>-19862.0979943264</v>
       </c>
       <c r="AF6" s="23" t="n">
         <f aca="false">IFERROR(K6/H6,0)</f>
@@ -11765,7 +11765,7 @@
       </c>
       <c r="AG6" s="23" t="n">
         <f aca="false">IFERROR((K6-AB6-AC6)/H6,0)</f>
-        <v>0.0417391304347826</v>
+        <v>0.0547826086956522</v>
       </c>
       <c r="AH6" s="26"/>
       <c r="AI6" s="13" t="n">
@@ -11871,7 +11871,7 @@
       </c>
       <c r="AB7" s="40" t="n">
         <f aca="false">K7*INDEX(Assumptions!$H$37:$H$38,MATCH(Q7,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N7="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
-        <v>27000</v>
+        <v>21000</v>
       </c>
       <c r="AC7" s="40" t="n">
         <f aca="false">K7*INDEX(Assumptions!$C$37:$C$38,MATCH(Q7,Assumptions!$B$37:$B$38,0))</f>
@@ -11879,11 +11879,11 @@
       </c>
       <c r="AD7" s="40" t="n">
         <f aca="false">K7-AB7-W7*12</f>
-        <v>-31741.7208844633</v>
+        <v>-25741.7208844633</v>
       </c>
       <c r="AE7" s="40" t="n">
         <f aca="false">AD7-AC7</f>
-        <v>-43741.7208844633</v>
+        <v>-37741.7208844633</v>
       </c>
       <c r="AF7" s="43" t="n">
         <f aca="false">IFERROR(K7/H7,0)</f>
@@ -11891,7 +11891,7 @@
       </c>
       <c r="AG7" s="43" t="n">
         <f aca="false">IFERROR((K7-AB7-AC7)/H7,0)</f>
-        <v>0.0355992541108663</v>
+        <v>0.0457704695711138</v>
       </c>
       <c r="AH7" s="35"/>
       <c r="AI7" s="34" t="n">
@@ -11997,7 +11997,7 @@
       </c>
       <c r="AB8" s="21" t="n">
         <f aca="false">K8*INDEX(Assumptions!$H$37:$H$38,MATCH(Q8,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N8="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
-        <v>11880</v>
+        <v>11002.5</v>
       </c>
       <c r="AC8" s="21" t="n">
         <f aca="false">K8*INDEX(Assumptions!$C$37:$C$38,MATCH(Q8,Assumptions!$B$37:$B$38,0))</f>
@@ -12005,11 +12005,11 @@
       </c>
       <c r="AD8" s="21" t="n">
         <f aca="false">K8-AB8-W8*12</f>
-        <v>-39154.8085586803</v>
+        <v>-38277.3085586803</v>
       </c>
       <c r="AE8" s="21" t="n">
         <f aca="false">AD8-AC8</f>
-        <v>-42664.8085586803</v>
+        <v>-41787.3085586803</v>
       </c>
       <c r="AF8" s="23" t="n">
         <f aca="false">IFERROR(K8/H8,0)</f>
@@ -12017,7 +12017,7 @@
       </c>
       <c r="AG8" s="23" t="n">
         <f aca="false">IFERROR((K8-AB8-AC8)/H8,0)</f>
-        <v>0.0261509433962264</v>
+        <v>0.0278066037735849</v>
       </c>
       <c r="AH8" s="26"/>
       <c r="AI8" s="13" t="n">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="AB6" s="21" t="n">
         <f aca="false">K6*INDEX(Assumptions!$H$37:$H$38,MATCH(Q6,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N6="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
-        <v>39863.4</v>
+        <v>29965.4</v>
       </c>
       <c r="AC6" s="21" t="n">
         <f aca="false">K6*INDEX(Assumptions!$C$37:$C$38,MATCH(Q6,Assumptions!$B$37:$B$38,0))</f>
@@ -12569,11 +12569,11 @@
       </c>
       <c r="AD6" s="21" t="n">
         <f aca="false">K6-AB6-W6*12</f>
-        <v>-12164.2575558435</v>
+        <v>-2266.25755584351</v>
       </c>
       <c r="AE6" s="21" t="n">
         <f aca="false">AD6-AC6</f>
-        <v>-31960.2575558435</v>
+        <v>-22062.2575558435</v>
       </c>
       <c r="AF6" s="23" t="n">
         <f aca="false">IFERROR(K6/H6,0)</f>
@@ -12581,7 +12581,7 @@
       </c>
       <c r="AG6" s="23" t="n">
         <f aca="false">IFERROR((K6-AB6-AC6)/H6,0)</f>
-        <v>0.0517376315789474</v>
+        <v>0.0647613157894737</v>
       </c>
       <c r="AH6" s="26"/>
       <c r="AI6" s="13"/>
@@ -12687,7 +12687,7 @@
       </c>
       <c r="AB7" s="40" t="n">
         <f aca="false">K7*INDEX(Assumptions!$H$37:$H$38,MATCH(Q7,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N7="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
-        <v>40200</v>
+        <v>30200</v>
       </c>
       <c r="AC7" s="40" t="n">
         <f aca="false">K7*INDEX(Assumptions!$C$37:$C$38,MATCH(Q7,Assumptions!$B$37:$B$38,0))</f>
@@ -12695,11 +12695,11 @@
       </c>
       <c r="AD7" s="40" t="n">
         <f aca="false">K7-AB7-W7*12</f>
-        <v>-4885.91575316079</v>
+        <v>5114.08424683921</v>
       </c>
       <c r="AE7" s="40" t="n">
         <f aca="false">AD7-AC7</f>
-        <v>-24885.9157531608</v>
+        <v>-14885.9157531608</v>
       </c>
       <c r="AF7" s="43" t="n">
         <f aca="false">IFERROR(K7/H7,0)</f>
@@ -12707,7 +12707,7 @@
       </c>
       <c r="AG7" s="43" t="n">
         <f aca="false">IFERROR((K7-AB7-AC7)/H7,0)</f>
-        <v>0.06368</v>
+        <v>0.07968</v>
       </c>
       <c r="AH7" s="35" t="s">
         <v>369</v>
@@ -12815,7 +12815,7 @@
       </c>
       <c r="AB8" s="21" t="n">
         <f aca="false">K8*INDEX(Assumptions!$H$37:$H$38,MATCH(Q8,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N8="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
-        <v>26336.04</v>
+        <v>20537.24</v>
       </c>
       <c r="AC8" s="21" t="n">
         <f aca="false">K8*INDEX(Assumptions!$C$37:$C$38,MATCH(Q8,Assumptions!$B$37:$B$38,0))</f>
@@ -12823,11 +12823,11 @@
       </c>
       <c r="AD8" s="21" t="n">
         <f aca="false">K8-AB8-W8*12</f>
-        <v>-36224.2696873884</v>
+        <v>-30425.4696873884</v>
       </c>
       <c r="AE8" s="21" t="n">
         <f aca="false">AD8-AC8</f>
-        <v>-47821.8696873884</v>
+        <v>-42023.0696873884</v>
       </c>
       <c r="AF8" s="23" t="n">
         <f aca="false">IFERROR(K8/H8,0)</f>
@@ -12835,7 +12835,7 @@
       </c>
       <c r="AG8" s="23" t="n">
         <f aca="false">IFERROR((K8-AB8-AC8)/H8,0)</f>
-        <v>0.0299318805970149</v>
+        <v>0.0385868059701493</v>
       </c>
       <c r="AH8" s="26"/>
       <c r="AI8" s="13"/>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="AB9" s="40" t="n">
         <f aca="false">K9*INDEX(Assumptions!$H$37:$H$38,MATCH(Q9,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N9="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
-        <v>23370</v>
+        <v>18470</v>
       </c>
       <c r="AC9" s="40" t="n">
         <f aca="false">K9*INDEX(Assumptions!$C$37:$C$38,MATCH(Q9,Assumptions!$B$37:$B$38,0))</f>
@@ -12949,11 +12949,11 @@
       </c>
       <c r="AD9" s="40" t="n">
         <f aca="false">K9-AB9-W9*12</f>
-        <v>-40828.3123832872</v>
+        <v>-35928.3123832872</v>
       </c>
       <c r="AE9" s="40" t="n">
         <f aca="false">AD9-AC9</f>
-        <v>-50628.3123832872</v>
+        <v>-45728.3123832872</v>
       </c>
       <c r="AF9" s="43" t="n">
         <f aca="false">IFERROR(K9/H9,0)</f>
@@ -12961,7 +12961,7 @@
       </c>
       <c r="AG9" s="43" t="n">
         <f aca="false">IFERROR((K9-AB9-AC9)/H9,0)</f>
-        <v>0.0243538461538462</v>
+        <v>0.0318923076923077</v>
       </c>
       <c r="AH9" s="35"/>
       <c r="AI9" s="34"/>
@@ -13067,7 +13067,7 @@
       </c>
       <c r="AB10" s="21" t="n">
         <f aca="false">K10*INDEX(Assumptions!$H$37:$H$38,MATCH(Q10,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N10="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
-        <v>40200</v>
+        <v>30200</v>
       </c>
       <c r="AC10" s="21" t="n">
         <f aca="false">K10*INDEX(Assumptions!$C$37:$C$38,MATCH(Q10,Assumptions!$B$37:$B$38,0))</f>
@@ -13075,11 +13075,11 @@
       </c>
       <c r="AD10" s="21" t="n">
         <f aca="false">K10-AB10-W10*12</f>
-        <v>-16764.6921640458</v>
+        <v>-6764.69216404582</v>
       </c>
       <c r="AE10" s="21" t="n">
         <f aca="false">AD10-AC10</f>
-        <v>-36764.6921640458</v>
+        <v>-26764.6921640458</v>
       </c>
       <c r="AF10" s="23" t="n">
         <f aca="false">IFERROR(K10/H10,0)</f>
@@ -13087,7 +13087,7 @@
       </c>
       <c r="AG10" s="23" t="n">
         <f aca="false">IFERROR((K10-AB10-AC10)/H10,0)</f>
-        <v>0.04975</v>
+        <v>0.06225</v>
       </c>
       <c r="AH10" s="26" t="s">
         <v>383</v>
@@ -13195,7 +13195,7 @@
       </c>
       <c r="AB11" s="40" t="n">
         <f aca="false">K11*INDEX(Assumptions!$H$37:$H$38,MATCH(Q11,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(N11="Y",Assumptions!$C$42,Assumptions!$C$43)</f>
-        <v>19740</v>
+        <v>15940</v>
       </c>
       <c r="AC11" s="40" t="n">
         <f aca="false">K11*INDEX(Assumptions!$C$37:$C$38,MATCH(Q11,Assumptions!$B$37:$B$38,0))</f>
@@ -13203,11 +13203,11 @@
       </c>
       <c r="AD11" s="40" t="n">
         <f aca="false">K11-AB11-W11*12</f>
-        <v>-40045.2878847056</v>
+        <v>-36245.2878847056</v>
       </c>
       <c r="AE11" s="40" t="n">
         <f aca="false">AD11-AC11</f>
-        <v>-47645.2878847056</v>
+        <v>-43845.2878847056</v>
       </c>
       <c r="AF11" s="43" t="n">
         <f aca="false">IFERROR(K11/H11,0)</f>
@@ -13215,7 +13215,7 @@
       </c>
       <c r="AG11" s="43" t="n">
         <f aca="false">IFERROR((K11-AB11-AC11)/H11,0)</f>
-        <v>0.0199252336448598</v>
+        <v>0.0270280373831776</v>
       </c>
       <c r="AH11" s="35"/>
       <c r="AI11" s="34" t="n">
@@ -13588,15 +13588,15 @@
       </c>
       <c r="M5" s="21" t="n">
         <f aca="false">E5-(E5*INDEX(Assumptions!$H$37:$H$38,MATCH('Manatee-Sarasota'!$Q$6,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF('Manatee-Sarasota'!$N$6="Y",Assumptions!$C$42,Assumptions!$C$43))-I5*12</f>
-        <v>-7039.77197979741</v>
+        <v>1460.22802020259</v>
       </c>
       <c r="N5" s="21" t="n">
         <f aca="false">M5-E5*INDEX(Assumptions!$C$37:$C$38,MATCH('Manatee-Sarasota'!$Q$6,Assumptions!$B$37:$B$38,0))</f>
-        <v>-24039.7719797974</v>
+        <v>-15539.7719797974</v>
       </c>
       <c r="O5" s="23" t="n">
         <f aca="false">IFERROR(M5/L5,0)</f>
-        <v>-0.0598620066309303</v>
+        <v>0.0124169049336955</v>
       </c>
       <c r="P5" s="47" t="s">
         <v>420</v>
@@ -13652,15 +13652,15 @@
       </c>
       <c r="M6" s="21" t="n">
         <f aca="false">E6-(E6*INDEX(Assumptions!$H$37:$H$38,MATCH('Manatee-Sarasota'!$Q$6,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF('Manatee-Sarasota'!$N$6="Y",Assumptions!$C$42,Assumptions!$C$43))-I6*12</f>
-        <v>-3831.68451483207</v>
+        <v>4668.31548516793</v>
       </c>
       <c r="N6" s="21" t="n">
         <f aca="false">M6-E6*INDEX(Assumptions!$C$37:$C$38,MATCH('Manatee-Sarasota'!$Q$6,Assumptions!$B$37:$B$38,0))</f>
-        <v>-20831.6845148321</v>
+        <v>-12331.6845148321</v>
       </c>
       <c r="O6" s="23" t="n">
         <f aca="false">IFERROR(M6/L6,0)</f>
-        <v>-0.0263165145249455</v>
+        <v>0.0320626063541753</v>
       </c>
       <c r="P6" s="23" t="n">
         <f aca="false">IFERROR((M6-M5)/(L6-L5),0)</f>
@@ -13717,15 +13717,15 @@
       </c>
       <c r="M7" s="21" t="n">
         <f aca="false">E7-(E7*INDEX(Assumptions!$H$37:$H$38,MATCH('Manatee-Sarasota'!$Q$6,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF('Manatee-Sarasota'!$N$6="Y",Assumptions!$C$42,Assumptions!$C$43))-I7*12</f>
-        <v>-1141.71933608533</v>
+        <v>7358.28066391467</v>
       </c>
       <c r="N7" s="21" t="n">
         <f aca="false">M7-E7*INDEX(Assumptions!$C$37:$C$38,MATCH('Manatee-Sarasota'!$Q$6,Assumptions!$B$37:$B$38,0))</f>
-        <v>-18141.7193360853</v>
+        <v>-9641.71933608533</v>
       </c>
       <c r="O7" s="23" t="n">
         <f aca="false">IFERROR(M7/L7,0)</f>
-        <v>-0.00657672428620584</v>
+        <v>0.0423864093543472</v>
       </c>
       <c r="P7" s="23" t="n">
         <f aca="false">IFERROR((M7-M6)/(L7-L6),0)</f>
@@ -13782,15 +13782,15 @@
       </c>
       <c r="M9" s="21" t="n">
         <f aca="false">E9-(E9*INDEX(Assumptions!$H$37:$H$38,MATCH('Manatee-Sarasota'!$Q$7,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF('Manatee-Sarasota'!$N$7="Y",Assumptions!$C$42,Assumptions!$C$43))-I9*12</f>
-        <v>-5067.31269769074</v>
+        <v>2232.68730230926</v>
       </c>
       <c r="N9" s="21" t="n">
         <f aca="false">M9-E9*INDEX(Assumptions!$C$37:$C$38,MATCH('Manatee-Sarasota'!$Q$7,Assumptions!$B$37:$B$38,0))</f>
-        <v>-19667.3126976907</v>
+        <v>-12367.3126976907</v>
       </c>
       <c r="O9" s="23" t="n">
         <f aca="false">IFERROR(M9/L9,0)</f>
-        <v>-0.0458995715370538</v>
+        <v>0.0202236168687433</v>
       </c>
       <c r="P9" s="47" t="s">
         <v>420</v>
@@ -13846,15 +13846,15 @@
       </c>
       <c r="M10" s="21" t="n">
         <f aca="false">E10-(E10*INDEX(Assumptions!$H$37:$H$38,MATCH('Manatee-Sarasota'!$Q$7,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF('Manatee-Sarasota'!$N$7="Y",Assumptions!$C$42,Assumptions!$C$43))-I10*12</f>
-        <v>-2432.09799432634</v>
+        <v>4867.90200567366</v>
       </c>
       <c r="N10" s="21" t="n">
         <f aca="false">M10-E10*INDEX(Assumptions!$C$37:$C$38,MATCH('Manatee-Sarasota'!$Q$7,Assumptions!$B$37:$B$38,0))</f>
-        <v>-17032.0979943263</v>
+        <v>-9732.09799432635</v>
       </c>
       <c r="O10" s="23" t="n">
         <f aca="false">IFERROR(M10/L10,0)</f>
-        <v>-0.0182316191478737</v>
+        <v>0.036491019532786</v>
       </c>
       <c r="P10" s="23" t="n">
         <f aca="false">IFERROR((M10-M9)/(L10-L9),0)</f>
@@ -13911,15 +13911,15 @@
       </c>
       <c r="M11" s="21" t="n">
         <f aca="false">E11-(E11*INDEX(Assumptions!$H$37:$H$38,MATCH('Manatee-Sarasota'!$Q$7,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF('Manatee-Sarasota'!$N$7="Y",Assumptions!$C$42,Assumptions!$C$43))-I11*12</f>
-        <v>-222.483740355812</v>
+        <v>7077.51625964419</v>
       </c>
       <c r="N11" s="21" t="n">
         <f aca="false">M11-E11*INDEX(Assumptions!$C$37:$C$38,MATCH('Manatee-Sarasota'!$Q$7,Assumptions!$B$37:$B$38,0))</f>
-        <v>-14822.4837403558</v>
+        <v>-7522.48374035581</v>
       </c>
       <c r="O11" s="23" t="n">
         <f aca="false">IFERROR(M11/L11,0)</f>
-        <v>-0.00142253030918038</v>
+        <v>0.0452526615066764</v>
       </c>
       <c r="P11" s="23" t="n">
         <f aca="false">IFERROR((M11-M10)/(L11-L10),0)</f>
@@ -13976,15 +13976,15 @@
       </c>
       <c r="M13" s="21" t="n">
         <f aca="false">E13-(E13*INDEX(Assumptions!$H$37:$H$38,MATCH('Manatee-Sarasota'!$Q$8,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF('Manatee-Sarasota'!$N$8="Y",Assumptions!$C$42,Assumptions!$C$43))-I13*12</f>
-        <v>-7644.75569264008</v>
+        <v>1255.24430735992</v>
       </c>
       <c r="N13" s="21" t="n">
         <f aca="false">M13-E13*INDEX(Assumptions!$C$37:$C$38,MATCH('Manatee-Sarasota'!$Q$8,Assumptions!$B$37:$B$38,0))</f>
-        <v>-25444.7556926401</v>
+        <v>-16544.7556926401</v>
       </c>
       <c r="O13" s="23" t="n">
         <f aca="false">IFERROR(M13/L13,0)</f>
-        <v>-0.0606726642273022</v>
+        <v>0.00996225640761842</v>
       </c>
       <c r="P13" s="47" t="s">
         <v>420</v>
@@ -14040,15 +14040,15 @@
       </c>
       <c r="M14" s="21" t="n">
         <f aca="false">E14-(E14*INDEX(Assumptions!$H$37:$H$38,MATCH('Manatee-Sarasota'!$Q$8,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF('Manatee-Sarasota'!$N$8="Y",Assumptions!$C$42,Assumptions!$C$43))-I14*12</f>
-        <v>-4207.51912303436</v>
+        <v>4692.48087696564</v>
       </c>
       <c r="N14" s="21" t="n">
         <f aca="false">M14-E14*INDEX(Assumptions!$C$37:$C$38,MATCH('Manatee-Sarasota'!$Q$8,Assumptions!$B$37:$B$38,0))</f>
-        <v>-22007.5191230344</v>
+        <v>-13107.5191230344</v>
       </c>
       <c r="O14" s="23" t="n">
         <f aca="false">IFERROR(M14/L14,0)</f>
-        <v>-0.0269712764297075</v>
+        <v>0.0300800056215746</v>
       </c>
       <c r="P14" s="23" t="n">
         <f aca="false">IFERROR((M14-M13)/(L14-L13),0)</f>
@@ -14105,15 +14105,15 @@
       </c>
       <c r="M15" s="21" t="n">
         <f aca="false">E15-(E15*INDEX(Assumptions!$H$37:$H$38,MATCH('Manatee-Sarasota'!$Q$8,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF('Manatee-Sarasota'!$N$8="Y",Assumptions!$C$42,Assumptions!$C$43))-I15*12</f>
-        <v>-1325.41357437715</v>
+        <v>7574.58642562285</v>
       </c>
       <c r="N15" s="21" t="n">
         <f aca="false">M15-E15*INDEX(Assumptions!$C$37:$C$38,MATCH('Manatee-Sarasota'!$Q$8,Assumptions!$B$37:$B$38,0))</f>
-        <v>-19125.4135743771</v>
+        <v>-10225.4135743771</v>
       </c>
       <c r="O15" s="23" t="n">
         <f aca="false">IFERROR(M15/L15,0)</f>
-        <v>-0.0071258794321352</v>
+        <v>0.0407235829334562</v>
       </c>
       <c r="P15" s="23" t="n">
         <f aca="false">IFERROR((M15-M14)/(L15-L14),0)</f>
@@ -14170,15 +14170,15 @@
       </c>
       <c r="M17" s="21" t="n">
         <f aca="false">E17-(E17*INDEX(Assumptions!$H$37:$H$38,MATCH(Pinellas!$Q$6,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(Pinellas!$N$6="Y",Assumptions!$C$42,Assumptions!$C$43))-I17*12</f>
-        <v>-10745.4275182174</v>
+        <v>-3645.4275182174</v>
       </c>
       <c r="N17" s="21" t="n">
         <f aca="false">M17-E17*INDEX(Assumptions!$C$37:$C$38,MATCH(Pinellas!$Q$6,Assumptions!$B$37:$B$38,0))</f>
-        <v>-24945.4275182174</v>
+        <v>-17845.4275182174</v>
       </c>
       <c r="O17" s="23" t="n">
         <f aca="false">IFERROR(M17/L17,0)</f>
-        <v>-0.0923146694004932</v>
+        <v>-0.03131810582661</v>
       </c>
       <c r="P17" s="47" t="s">
         <v>420</v>
@@ -14234,15 +14234,15 @@
       </c>
       <c r="M18" s="21" t="n">
         <f aca="false">E18-(E18*INDEX(Assumptions!$H$37:$H$38,MATCH(Pinellas!$Q$6,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(Pinellas!$N$6="Y",Assumptions!$C$42,Assumptions!$C$43))-I18*12</f>
-        <v>-7966.99462445278</v>
+        <v>-866.994624452775</v>
       </c>
       <c r="N18" s="21" t="n">
         <f aca="false">M18-E18*INDEX(Assumptions!$C$37:$C$38,MATCH(Pinellas!$Q$6,Assumptions!$B$37:$B$38,0))</f>
-        <v>-22166.9946244528</v>
+        <v>-15066.9946244528</v>
       </c>
       <c r="O18" s="23" t="n">
         <f aca="false">IFERROR(M18/L18,0)</f>
-        <v>-0.0566441139314097</v>
+        <v>-0.00616419924957536</v>
       </c>
       <c r="P18" s="23" t="n">
         <f aca="false">IFERROR((M18-M17)/(L18-L17),0)</f>
@@ -14299,15 +14299,15 @@
       </c>
       <c r="M19" s="21" t="n">
         <f aca="false">E19-(E19*INDEX(Assumptions!$H$37:$H$38,MATCH(Pinellas!$Q$6,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(Pinellas!$N$6="Y",Assumptions!$C$42,Assumptions!$C$43))-I19*12</f>
-        <v>-5637.29263928819</v>
+        <v>1462.70736071181</v>
       </c>
       <c r="N19" s="21" t="n">
         <f aca="false">M19-E19*INDEX(Assumptions!$C$37:$C$38,MATCH(Pinellas!$Q$6,Assumptions!$B$37:$B$38,0))</f>
-        <v>-19837.2926392882</v>
+        <v>-12737.2926392882</v>
       </c>
       <c r="O19" s="23" t="n">
         <f aca="false">IFERROR(M19/L19,0)</f>
-        <v>-0.03418612880102</v>
+        <v>0.00887026901583874</v>
       </c>
       <c r="P19" s="23" t="n">
         <f aca="false">IFERROR((M19-M18)/(L19-L18),0)</f>
@@ -14364,15 +14364,15 @@
       </c>
       <c r="M21" s="21" t="n">
         <f aca="false">E21-(E21*INDEX(Assumptions!$H$37:$H$38,MATCH(Pinellas!$Q$7,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(Pinellas!$N$7="Y",Assumptions!$C$42,Assumptions!$C$43))-I21*12</f>
-        <v>-1365.4275182174</v>
+        <v>7134.5724817826</v>
       </c>
       <c r="N21" s="21" t="n">
         <f aca="false">M21-E21*INDEX(Assumptions!$C$37:$C$38,MATCH(Pinellas!$Q$7,Assumptions!$B$37:$B$38,0))</f>
-        <v>-18365.4275182174</v>
+        <v>-9865.4275182174</v>
       </c>
       <c r="O21" s="23" t="n">
         <f aca="false">IFERROR(M21/L21,0)</f>
-        <v>-0.0117304769606306</v>
+        <v>0.0612935780221873</v>
       </c>
       <c r="P21" s="47" t="s">
         <v>420</v>
@@ -14428,15 +14428,15 @@
       </c>
       <c r="M22" s="21" t="n">
         <f aca="false">E22-(E22*INDEX(Assumptions!$H$37:$H$38,MATCH(Pinellas!$Q$7,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(Pinellas!$N$7="Y",Assumptions!$C$42,Assumptions!$C$43))-I22*12</f>
-        <v>1413.00537554723</v>
+        <v>9913.00537554723</v>
       </c>
       <c r="N22" s="21" t="n">
         <f aca="false">M22-E22*INDEX(Assumptions!$C$37:$C$38,MATCH(Pinellas!$Q$7,Assumptions!$B$37:$B$38,0))</f>
-        <v>-15586.9946244528</v>
+        <v>-7086.99462445278</v>
       </c>
       <c r="O22" s="23" t="n">
         <f aca="false">IFERROR(M22/L22,0)</f>
-        <v>0.0100462522257179</v>
+        <v>0.0704799529011534</v>
       </c>
       <c r="P22" s="23" t="n">
         <f aca="false">IFERROR((M22-M21)/(L22-L21),0)</f>
@@ -14493,15 +14493,15 @@
       </c>
       <c r="M23" s="21" t="n">
         <f aca="false">E23-(E23*INDEX(Assumptions!$H$37:$H$38,MATCH(Pinellas!$Q$7,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF(Pinellas!$N$7="Y",Assumptions!$C$42,Assumptions!$C$43))-I23*12</f>
-        <v>3742.70736071181</v>
+        <v>12242.7073607118</v>
       </c>
       <c r="N23" s="21" t="n">
         <f aca="false">M23-E23*INDEX(Assumptions!$C$37:$C$38,MATCH(Pinellas!$Q$7,Assumptions!$B$37:$B$38,0))</f>
-        <v>-13257.2926392882</v>
+        <v>-4757.29263928819</v>
       </c>
       <c r="O23" s="23" t="n">
         <f aca="false">IFERROR(M23/L23,0)</f>
-        <v>0.0226968305682948</v>
+        <v>0.0742432223208721</v>
       </c>
       <c r="P23" s="23" t="n">
         <f aca="false">IFERROR((M23-M22)/(L23-L22),0)</f>
@@ -14558,15 +14558,15 @@
       </c>
       <c r="M25" s="21" t="n">
         <f aca="false">E25-(E25*INDEX(Assumptions!$H$37:$H$38,MATCH('Monroe (Keys)'!$Q$6,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF('Monroe (Keys)'!$N$6="Y",Assumptions!$C$42,Assumptions!$C$43))-I25*12</f>
-        <v>-16518.0905440108</v>
+        <v>-6620.09054401076</v>
       </c>
       <c r="N25" s="21" t="n">
         <f aca="false">M25-E25*INDEX(Assumptions!$C$37:$C$38,MATCH('Monroe (Keys)'!$Q$6,Assumptions!$B$37:$B$38,0))</f>
-        <v>-36314.0905440108</v>
+        <v>-26416.0905440108</v>
       </c>
       <c r="O25" s="23" t="n">
         <f aca="false">IFERROR(M25/L25,0)</f>
-        <v>-0.0905597069298836</v>
+        <v>-0.0362943560526906</v>
       </c>
       <c r="P25" s="47" t="s">
         <v>420</v>
@@ -14622,15 +14622,15 @@
       </c>
       <c r="M26" s="21" t="n">
         <f aca="false">E26-(E26*INDEX(Assumptions!$H$37:$H$38,MATCH('Monroe (Keys)'!$Q$6,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF('Monroe (Keys)'!$N$6="Y",Assumptions!$C$42,Assumptions!$C$43))-I26*12</f>
-        <v>-12164.2575558435</v>
+        <v>-2266.25755584351</v>
       </c>
       <c r="N26" s="21" t="n">
         <f aca="false">M26-E26*INDEX(Assumptions!$C$37:$C$38,MATCH('Monroe (Keys)'!$Q$6,Assumptions!$B$37:$B$38,0))</f>
-        <v>-31960.2575558435</v>
+        <v>-22062.2575558435</v>
       </c>
       <c r="O26" s="23" t="n">
         <f aca="false">IFERROR(M26/L26,0)</f>
-        <v>-0.0551917311971121</v>
+        <v>-0.0102824752987455</v>
       </c>
       <c r="P26" s="23" t="n">
         <f aca="false">IFERROR((M26-M25)/(L26-L25),0)</f>
@@ -14687,15 +14687,15 @@
       </c>
       <c r="M27" s="21" t="n">
         <f aca="false">E27-(E27*INDEX(Assumptions!$H$37:$H$38,MATCH('Monroe (Keys)'!$Q$6,Assumptions!$B$37:$B$38,0))+Assumptions!$C$41+IF('Monroe (Keys)'!$N$6="Y",Assumptions!$C$42,Assumptions!$C$43))-I27*12</f>
-        <v>-8513.59052754439</v>
+        <v>1384.40947245562</v>
       </c>
       <c r="N27" s="21" t="n">
         <f aca="false">M27-E27*INDEX(Assumptions!$C$37:$C$38,MATCH('Monroe (Keys)'!$Q$6,Assumptions!$B$37:$B$38,0))</f>
-        <v>-28309.5905275444</v>
+        <v>-18411.5905275444</v>
       </c>
       <c r="O27" s="23" t="n">
         <f aca="false">IFERROR(M27/L27,0)</f>
-        <v>-0.0329473317629427</v>
+        <v>0.00535762179742887</v>
       </c>
       <c r="P27" s="23" t="n">
         <f aca="false">IFERROR((M27-M26)/(L27-L26),0)</f>

--- a/str-deal-search/STR_DSCR_Analysis.xlsx
+++ b/str-deal-search/STR_DSCR_Analysis.xlsx
@@ -289,7 +289,7 @@
     <t xml:space="preserve">- Rates are placeholders (7.50 / 7.25 / 7.125% by LTV tier): overwrite on the Assumptions tab and every tab reflows.</t>
   </si>
   <si>
-    <t xml:space="preserve">- Cash flow is conservative (10% platform + 10% cleaning on top of seller gross). A co-host at 10-15% is what makes these work; full-service PM does not cash flow at today's rates.</t>
+    <t xml:space="preserve">- Cleaning is not a cost (passed through to guests as a cleaning fee): use gross EXCLUDING guest-paid cleaning fees. Platform fees 10%. #1 nets ~+$4.7k/yr self-managed; a 10-15% co-host is about breakeven; full-service PM does not cash flow at today's rates.</t>
   </si>
   <si>
     <t xml:space="preserve">- Pinellas: nightly SFH STRs are legal mainly in unincorporated county (Certificate of Use), Largo, Indian Rocks Beach, Redington Beach. St. Pete, St. Pete Beach, Clearwater residential, Gulfport, Dunedin = 30-day+.</t>
